--- a/deliverables/AC-Brands-RACI.xlsx
+++ b/deliverables/AC-Brands-RACI.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Gaps" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$Q$80</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$Q$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$G$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q105"/>
+  <dimension ref="A1:Q106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -854,8 +854,16 @@
           <t>Packaging development with fillers and component vendors</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -866,31 +874,35 @@
       <c r="H5" s="7" t="inlineStr"/>
       <c r="I5" s="7" t="inlineStr"/>
       <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr"/>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="N5" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr"/>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:16,23</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:16,23; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>PD Lead owns packaging dev calls; Jan executes packaging and artwork under Erin. Both are contractors.</t>
+          <t>PD Lead owns packaging dev calls; Jan executes packaging and artwork under Erin. Both are contractors. Erin is the lead technical authority on packaging and artwork and answers for the outcome; Jan executes under her. Perrine consults where formula contact or compatibility is in play. Both Erin and Jan are contractors.</t>
         </is>
       </c>
     </row>
@@ -2462,10 +2474,14 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr"/>
       <c r="E35" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
@@ -2484,7 +2500,11 @@
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" s="7" t="inlineStr"/>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L35" s="7" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="7" t="inlineStr">
@@ -2499,12 +2519,12 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:97; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:29</t>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:97; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:29; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>Operator approves the path; Reg Lead approves the Pedrero stage. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off. A and R both AB.</t>
+          <t>Operator approves the path; Reg Lead approves the Pedrero stage. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off. A and R both AB. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off, so both are consulted rather than bypassed.</t>
         </is>
       </c>
     </row>
@@ -2519,21 +2539,33 @@
           <t>Label artwork archive, IL cross-check and label-law checks (Pantone, Canada, Quebec, 19-state toxics)</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr"/>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr"/>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G36" s="7" t="inlineStr"/>
       <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr"/>
@@ -2550,12 +2582,12 @@
       <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:85; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:93</t>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:85; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:93; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>Operator approves each pass outcome; Reg Lead approves any archive entry. Creative produces the artwork under review.</t>
+          <t>Operator approves each pass outcome; Reg Lead approves any archive entry. Creative produces the artwork under review. Erin answers for the artwork being right as lead technical authority. Alvin runs the IL cross-check and the label-law passes and holds the Reg Lead gate on archive entries, so the regulatory approval and the artwork authority are separate people.</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2649,11 @@
           <t>Retailer attestation responses (Sephora, Ulta, Whole Foods, Credo)</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr"/>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
           <t>I</t>
@@ -2656,12 +2692,12 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:105; .claude/skills/regulatory-manager/SKILL.md:122</t>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:105; .claude/skills/regulatory-manager/SKILL.md:122; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>Reg Lead approves the retailer submission after Pedrero approval. Voice of Customer consults where customer-perceived attributes matter. A and R both AB.</t>
+          <t>Reg Lead approves the retailer submission after Pedrero approval. Voice of Customer consults where customer-perceived attributes matter. A and R both AB. Ayesha consulted - retailer clean-standard positioning is a brand claim.</t>
         </is>
       </c>
     </row>
@@ -2931,8 +2967,16 @@
           <t>Quarterly competitive teardowns across the five comp brands</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr"/>
-      <c r="D44" s="7" t="inlineStr"/>
+      <c r="C44" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
           <t>I</t>
@@ -2962,12 +3006,12 @@
       <c r="O44" s="6" t="inlineStr"/>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:19,23-30</t>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:19,23-30; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>Soraya owns teardown production and comp brand profile maintenance. A and R both SS.</t>
+          <t>Soraya owns teardown production and comp brand profile maintenance. A and R both SS. Danielle consulted rather than only receiving the finished teardown.</t>
         </is>
       </c>
     </row>
@@ -3033,8 +3077,16 @@
           <t>Monthly competitive trend digest and cross-stream signal routing</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr"/>
-      <c r="D46" s="7" t="inlineStr"/>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
           <t>I</t>
@@ -3064,12 +3116,12 @@
       <c r="O46" s="6" t="inlineStr"/>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:3,9-15</t>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:3,9-15; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>Stream DRI owns digest production and the 'what it means for SJS' analytical layer. Named as the stream's heartbeat - first thing protected under capacity pressure. A and R both NI.</t>
+          <t>Stream DRI owns digest production and the 'what it means for SJS' analytical layer. Named as the stream's heartbeat - first thing protected under capacity pressure. A and R both NI. Danielle consulted on the digest's read.</t>
         </is>
       </c>
     </row>
@@ -3084,8 +3136,16 @@
           <t>Social listening and comp brand monitoring (TikTok, IG, Pinterest, retailer new arrivals)</t>
         </is>
       </c>
-      <c r="C47" s="7" t="inlineStr"/>
-      <c r="D47" s="7" t="inlineStr"/>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E47" s="7" t="inlineStr"/>
       <c r="F47" s="7" t="inlineStr"/>
       <c r="G47" s="7" t="inlineStr"/>
@@ -3107,12 +3167,12 @@
       <c r="O47" s="6" t="inlineStr"/>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:34,40-44</t>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:34,40-44; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>Kate owns social listening tool maintenance, query hygiene and the weekly retailer new-arrivals scan. A and R both KL.</t>
+          <t>Kate owns social listening tool maintenance, query hygiene and the weekly retailer new-arrivals scan. A and R both KL. Danielle consulted on what the social signal implies for brand.</t>
         </is>
       </c>
     </row>
@@ -3129,10 +3189,14 @@
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="E48" s="7" t="inlineStr"/>
       <c r="F48" s="7" t="inlineStr"/>
       <c r="G48" s="7" t="inlineStr"/>
@@ -3142,15 +3206,19 @@
           <t>C</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr"/>
-      <c r="K48" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L48" s="8" t="inlineStr">
+      <c r="J48" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K48" s="8" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="M48" s="7" t="inlineStr"/>
@@ -3158,12 +3226,12 @@
       <c r="O48" s="6" t="inlineStr"/>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sweet-july-skin-brand/SKILL.md:1; references/architecture/system_map.md:157</t>
+          <t>.claude/skills/sweet-july-skin-brand/SKILL.md:1; references/architecture/system_map.md:157; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>Every output-producing skill defers here for canonical brand spec; no skill carries its own copy.</t>
+          <t>Every output-producing skill defers here for canonical brand spec; no skill carries its own copy. President answers for brand custody; Creative Director maintains it. Ayesha consulted - the brand carries her name. Every output-producing skill defers here for canonical spec.</t>
         </is>
       </c>
     </row>
@@ -3292,9 +3360,21 @@
           <t>Creative direction on packaging, artwork and brand visuals</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr"/>
-      <c r="D51" s="7" t="inlineStr"/>
-      <c r="E51" s="7" t="inlineStr"/>
+      <c r="C51" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="F51" s="7" t="inlineStr"/>
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
@@ -3319,12 +3399,12 @@
       <c r="O51" s="6" t="inlineStr"/>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:22</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:22; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>Creative Director owns packaging, artwork and brand visuals. A and R both EH.</t>
+          <t>Creative Director owns packaging, artwork and brand visuals. A and R both EH. Creative Director owns the direction as lead technical authority, and is a contractor. Danielle and Ayesha both consulted. A and R the same person - no second pair of eyes, and no internal backup either.</t>
         </is>
       </c>
     </row>
@@ -3339,8 +3419,16 @@
           <t>Packaging and artwork execution</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr"/>
-      <c r="D52" s="7" t="inlineStr"/>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
           <t>I</t>
@@ -3356,7 +3444,11 @@
           <t>A</t>
         </is>
       </c>
-      <c r="L52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M52" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -3370,12 +3462,12 @@
       <c r="O52" s="6" t="inlineStr"/>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:23; .claude/skills/sjs-comp-intel/references/team-ownership.md:79</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:23; .claude/skills/sjs-comp-intel/references/team-ownership.md:79; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>Jan is the creative contractor under Erin. Title differs between sources - Packaging Engineer in one, creative contractor in the other.</t>
+          <t>Jan is the creative contractor under Erin. Title differs between sources - Packaging Engineer in one, creative contractor in the other. Erin holds technical authority; Jan executes. Both contractors.</t>
         </is>
       </c>
     </row>
@@ -3391,8 +3483,16 @@
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr"/>
-      <c r="D53" s="7" t="inlineStr"/>
-      <c r="E53" s="7" t="inlineStr"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr"/>
@@ -3417,12 +3517,12 @@
       <c r="O53" s="6" t="inlineStr"/>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-status-reporter/SKILL.md:352; .claude/skills/asana-pd-manager/references/role-map.md:24</t>
+          <t>.claude/skills/sjs-status-reporter/SKILL.md:352; .claude/skills/asana-pd-manager/references/role-map.md:24; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>Creative Requests Asana project owner is Ivy, Editorial/Design team. Ivy supports Erin and Jan. A and R both IT.</t>
+          <t>Creative Requests Asana project owner is Ivy, Editorial/Design team. Ivy supports Erin and Jan. A and R both IT. Danielle consulted on intake priority.</t>
         </is>
       </c>
     </row>
@@ -4519,8 +4619,16 @@
           <t>Operational special projects: labels, PR seeding, sampling</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr"/>
-      <c r="D76" s="7" t="inlineStr"/>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -4562,12 +4670,12 @@
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
       <c r="Q76" s="6" t="inlineStr">
         <is>
-          <t>Named in the Ops Specialist JD, and in the email as making sure product is where it needs to be for launches, promos, PR seeding and sampling.</t>
+          <t>Named in the Ops Specialist JD, and in the email as making sure product is where it needs to be for launches, promos, PR seeding and sampling. Danielle consulted - PR seeding and sampling are brand-facing.</t>
         </is>
       </c>
     </row>
@@ -4767,163 +4875,189 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="10" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Brand</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Campaign direction and seasonal brand moments</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G81" s="7" t="inlineStr"/>
+      <c r="H81" s="7" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K81" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L81" s="7" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+      <c r="N81" s="7" t="inlineStr"/>
+      <c r="O81" s="6" t="inlineStr"/>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (role correction); .claude/skills/sjs-margin-walk-away/SKILL.md:93</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>Added 2026-07-31. Campaign direction was absent from the matrix, which is why the President and the Founder had almost no Marketing presence. Danielle answers for it - Soraya reports to her and the margin sources already have her approving every repricing and channel call. Ayesha consulted on brand moments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="11" t="n"/>
-      <c r="B83" s="12" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="11" t="n"/>
+      <c r="B84" s="12" t="inlineStr">
         <is>
           <t>A = answers for the outcome (exactly one per row)</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="13" t="n"/>
-      <c r="B84" s="12" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="13" t="n"/>
+      <c r="B85" s="12" t="inlineStr">
         <is>
           <t>R = does the work (exactly one per row)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="11" t="n"/>
-      <c r="B85" s="12" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="11" t="n"/>
+      <c r="B86" s="12" t="inlineStr">
         <is>
           <t>A/R = the same person holds both, so the row has no second pair of eyes</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>C = consulted before the decision</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>I = informed after it</t>
+          <t>C = consulted before the decision</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="12" t="inlineStr">
         <is>
+          <t>I = informed after it</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="12" t="inlineStr">
+        <is>
           <t>-&gt; = the open seat that absorbs R on hire. Open seats never hold A or R.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
         <is>
           <t>Positions</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="14" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B91" s="14" t="inlineStr">
+      <c r="B92" s="14" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="C91" s="14" t="inlineStr">
+      <c r="C92" s="14" t="inlineStr">
         <is>
           <t>Holder</t>
         </is>
       </c>
-      <c r="D91" s="14" t="inlineStr">
+      <c r="D92" s="14" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E91" s="14" t="inlineStr">
+      <c r="E92" s="14" t="inlineStr">
         <is>
           <t>A count</t>
         </is>
       </c>
-      <c r="F91" s="14" t="inlineStr">
+      <c r="F92" s="14" t="inlineStr">
         <is>
           <t>R count</t>
         </is>
       </c>
-      <c r="G91" s="14" t="inlineStr">
+      <c r="G92" s="14" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H91" s="14" t="inlineStr">
+      <c r="H92" s="14" t="inlineStr">
         <is>
           <t>Hands off</t>
         </is>
       </c>
-      <c r="I91" s="14" t="inlineStr">
+      <c r="I92" s="14" t="inlineStr">
         <is>
           <t>Absorbs</t>
         </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="12" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="B92" s="12" t="inlineStr">
-        <is>
-          <t>Owner / Founder</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="inlineStr">
-        <is>
-          <t>Ayesha Curry</t>
-        </is>
-      </c>
-      <c r="D92" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E92" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Owner / Founder</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Danielle Iturbe</t>
+          <t>Ayesha Curry</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -4932,7 +5066,7 @@
         </is>
       </c>
       <c r="E93" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" s="15" t="n">
         <v>0</v>
@@ -4950,17 +5084,17 @@
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>VP of Operations</t>
+          <t>President</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>Alvin Belt</t>
+          <t>Danielle Iturbe</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -4969,16 +5103,16 @@
         </is>
       </c>
       <c r="E94" s="15" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F94" s="15" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G94" s="15" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I94" s="15" t="n">
         <v>0</v>
@@ -4987,17 +5121,17 @@
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
+          <t>VP of Operations</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Nicole Iturbe</t>
+          <t>Alvin Belt</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -5006,16 +5140,16 @@
         </is>
       </c>
       <c r="E95" s="15" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="F95" s="15" t="n">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="G95" s="15" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="H95" s="15" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I95" s="15" t="n">
         <v>0</v>
@@ -5024,49 +5158,49 @@
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>OPS</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>Operations Specialist</t>
+          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>Open seat</t>
-        </is>
-      </c>
-      <c r="D96" s="16" t="inlineStr">
-        <is>
-          <t>recruiting</t>
+          <t>Nicole Iturbe</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
         </is>
       </c>
       <c r="E96" s="15" t="n">
+        <v>21</v>
+      </c>
+      <c r="F96" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="G96" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I96" s="15" t="n">
         <v>0</v>
-      </c>
-      <c r="F96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="15" t="n">
-        <v>16</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>PDS</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Product Development Specialist</t>
+          <t>Operations Specialist</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -5076,7 +5210,7 @@
       </c>
       <c r="D97" s="16" t="inlineStr">
         <is>
-          <t>phased</t>
+          <t>recruiting</t>
         </is>
       </c>
       <c r="E97" s="15" t="n">
@@ -5098,54 +5232,54 @@
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>PDS</t>
         </is>
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Product Development Specialist</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>Soraya Salgadoe</t>
-        </is>
-      </c>
-      <c r="D98" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
+          <t>Open seat</t>
+        </is>
+      </c>
+      <c r="D98" s="16" t="inlineStr">
+        <is>
+          <t>phased</t>
         </is>
       </c>
       <c r="E98" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F98" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G98" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Social Media Coordinator</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Kate Le</t>
+          <t>Soraya Salgadoe</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -5157,7 +5291,7 @@
         <v>1</v>
       </c>
       <c r="F99" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G99" s="15" t="n">
         <v>1</v>
@@ -5172,17 +5306,17 @@
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>Creative Director</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>Erin Hover</t>
+          <t>Kate Le</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -5191,10 +5325,10 @@
         </is>
       </c>
       <c r="E100" s="15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G100" s="15" t="n">
         <v>1</v>
@@ -5209,26 +5343,26 @@
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EH</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Creative / Design Coordinator</t>
+          <t>Creative Director</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Ivy Tan</t>
+          <t>Erin Hover</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="E101" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F101" s="15" t="n">
         <v>2</v>
@@ -5246,32 +5380,32 @@
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>Packaging Engineer</t>
+          <t>Creative / Design Coordinator</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Jan Haeck</t>
+          <t>Ivy Tan</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>contractor</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E102" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>0</v>
@@ -5283,17 +5417,17 @@
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>PD / R&amp;D contractor, Milinyc</t>
+          <t>Packaging Engineer</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Perrine Calvet</t>
+          <t>Jan Haeck</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -5302,13 +5436,13 @@
         </is>
       </c>
       <c r="E103" s="15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F103" s="15" t="n">
         <v>2</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H103" s="15" t="n">
         <v>0</v>
@@ -5317,20 +5451,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="14" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>PD / R&amp;D contractor, Milinyc</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Perrine Calvet</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>contractor</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F104" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="inlineStr">
         <is>
           <t>Source of truth</t>
         </is>
       </c>
-      <c r="B105" s="17" t="inlineStr">
+      <c r="B106" s="17" t="inlineStr">
         <is>
           <t>Rows citing a path are relative to the SJ-OS repo. Rows citing the 30 July leadership review, the 27 July email to Danielle, or a job description come from those documents directly. Rows marked INFERRED in Notes have no owner named in any source; A defaults to Alvin Belt because the work falls there in practice.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q80"/>
+  <autoFilter ref="A2:Q81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5341,7 +5512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -5367,7 +5538,7 @@
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
-          <t>Counts are live formulas over the RACI sheet, so they move if a row changes. Read against the matrix. Reflects the 30 July 2026 leadership review.</t>
+          <t>Counts are live formulas over the RACI sheet, so they move if a row changes. Read against the matrix. Reflects the 30 July 2026 leadership review and the 31 July role corrections.</t>
         </is>
       </c>
     </row>
@@ -5423,15 +5594,15 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>COUNTIF(RACI!C3:C80,"A")+COUNTIF(RACI!C3:C80,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C81,"A")+COUNTIF(RACI!C3:C81,"A/R")</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>COUNTIF(RACI!C3:C80,"R")+COUNTIF(RACI!C3:C80,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C81,"R")+COUNTIF(RACI!C3:C81,"A/R")</f>
         <v/>
       </c>
       <c r="D6" s="15">
-        <f>COUNTIF(RACI!C3:C80,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C81,"A/R")</f>
         <v/>
       </c>
       <c r="E6" s="15" t="n">
@@ -5456,15 +5627,15 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>COUNTIF(RACI!D3:D80,"A")+COUNTIF(RACI!D3:D80,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D81,"A")+COUNTIF(RACI!D3:D81,"A/R")</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>COUNTIF(RACI!D3:D80,"R")+COUNTIF(RACI!D3:D80,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D81,"R")+COUNTIF(RACI!D3:D81,"A/R")</f>
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>COUNTIF(RACI!D3:D80,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D81,"A/R")</f>
         <v/>
       </c>
       <c r="E7" s="15" t="n">
@@ -5489,15 +5660,15 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>COUNTIF(RACI!E3:E80,"A")+COUNTIF(RACI!E3:E80,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E81,"A")+COUNTIF(RACI!E3:E81,"A/R")</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>COUNTIF(RACI!E3:E80,"R")+COUNTIF(RACI!E3:E80,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E81,"R")+COUNTIF(RACI!E3:E81,"A/R")</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>COUNTIF(RACI!E3:E80,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E81,"A/R")</f>
         <v/>
       </c>
       <c r="E8" s="15" t="n">
@@ -5522,15 +5693,15 @@
         </is>
       </c>
       <c r="B9" s="15">
-        <f>COUNTIF(RACI!F3:F80,"A")+COUNTIF(RACI!F3:F80,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F81,"A")+COUNTIF(RACI!F3:F81,"A/R")</f>
         <v/>
       </c>
       <c r="C9" s="15">
-        <f>COUNTIF(RACI!F3:F80,"R")+COUNTIF(RACI!F3:F80,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F81,"R")+COUNTIF(RACI!F3:F81,"A/R")</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>COUNTIF(RACI!F3:F80,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F81,"A/R")</f>
         <v/>
       </c>
       <c r="E9" s="15" t="n">
@@ -5555,15 +5726,15 @@
         </is>
       </c>
       <c r="B10" s="15">
-        <f>COUNTIF(RACI!G3:G80,"A")+COUNTIF(RACI!G3:G80,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G81,"A")+COUNTIF(RACI!G3:G81,"A/R")</f>
         <v/>
       </c>
       <c r="C10" s="15">
-        <f>COUNTIF(RACI!G3:G80,"R")+COUNTIF(RACI!G3:G80,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G81,"R")+COUNTIF(RACI!G3:G81,"A/R")</f>
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>COUNTIF(RACI!G3:G80,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G81,"A/R")</f>
         <v/>
       </c>
       <c r="E10" s="15" t="n">
@@ -5588,15 +5759,15 @@
         </is>
       </c>
       <c r="B11" s="15">
-        <f>COUNTIF(RACI!H3:H80,"A")+COUNTIF(RACI!H3:H80,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H81,"A")+COUNTIF(RACI!H3:H81,"A/R")</f>
         <v/>
       </c>
       <c r="C11" s="15">
-        <f>COUNTIF(RACI!H3:H80,"R")+COUNTIF(RACI!H3:H80,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H81,"R")+COUNTIF(RACI!H3:H81,"A/R")</f>
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>COUNTIF(RACI!H3:H80,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H81,"A/R")</f>
         <v/>
       </c>
       <c r="E11" s="15" t="n">
@@ -5621,15 +5792,15 @@
         </is>
       </c>
       <c r="B12" s="15">
-        <f>COUNTIF(RACI!I3:I80,"A")+COUNTIF(RACI!I3:I80,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I81,"A")+COUNTIF(RACI!I3:I81,"A/R")</f>
         <v/>
       </c>
       <c r="C12" s="15">
-        <f>COUNTIF(RACI!I3:I80,"R")+COUNTIF(RACI!I3:I80,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I81,"R")+COUNTIF(RACI!I3:I81,"A/R")</f>
         <v/>
       </c>
       <c r="D12" s="15">
-        <f>COUNTIF(RACI!I3:I80,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I81,"A/R")</f>
         <v/>
       </c>
       <c r="E12" s="15" t="n">
@@ -5654,15 +5825,15 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>COUNTIF(RACI!J3:J80,"A")+COUNTIF(RACI!J3:J80,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J81,"A")+COUNTIF(RACI!J3:J81,"A/R")</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>COUNTIF(RACI!J3:J80,"R")+COUNTIF(RACI!J3:J80,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J81,"R")+COUNTIF(RACI!J3:J81,"A/R")</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>COUNTIF(RACI!J3:J80,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J81,"A/R")</f>
         <v/>
       </c>
       <c r="E13" s="15" t="n">
@@ -5687,15 +5858,15 @@
         </is>
       </c>
       <c r="B14" s="15">
-        <f>COUNTIF(RACI!K3:K80,"A")+COUNTIF(RACI!K3:K80,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K81,"A")+COUNTIF(RACI!K3:K81,"A/R")</f>
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>COUNTIF(RACI!K3:K80,"R")+COUNTIF(RACI!K3:K80,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K81,"R")+COUNTIF(RACI!K3:K81,"A/R")</f>
         <v/>
       </c>
       <c r="D14" s="15">
-        <f>COUNTIF(RACI!K3:K80,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K81,"A/R")</f>
         <v/>
       </c>
       <c r="E14" s="15" t="n">
@@ -5720,15 +5891,15 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF(RACI!L3:L80,"A")+COUNTIF(RACI!L3:L80,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L81,"A")+COUNTIF(RACI!L3:L81,"A/R")</f>
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>COUNTIF(RACI!L3:L80,"R")+COUNTIF(RACI!L3:L80,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L81,"R")+COUNTIF(RACI!L3:L81,"A/R")</f>
         <v/>
       </c>
       <c r="D15" s="15">
-        <f>COUNTIF(RACI!L3:L80,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L81,"A/R")</f>
         <v/>
       </c>
       <c r="E15" s="15" t="n">
@@ -5753,15 +5924,15 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF(RACI!M3:M80,"A")+COUNTIF(RACI!M3:M80,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M81,"A")+COUNTIF(RACI!M3:M81,"A/R")</f>
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>COUNTIF(RACI!M3:M80,"R")+COUNTIF(RACI!M3:M80,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M81,"R")+COUNTIF(RACI!M3:M81,"A/R")</f>
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>COUNTIF(RACI!M3:M80,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M81,"A/R")</f>
         <v/>
       </c>
       <c r="E16" s="15" t="n">
@@ -5786,15 +5957,15 @@
         </is>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF(RACI!N3:N80,"A")+COUNTIF(RACI!N3:N80,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N81,"A")+COUNTIF(RACI!N3:N81,"A/R")</f>
         <v/>
       </c>
       <c r="C17" s="15">
-        <f>COUNTIF(RACI!N3:N80,"R")+COUNTIF(RACI!N3:N80,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N81,"R")+COUNTIF(RACI!N3:N81,"A/R")</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>COUNTIF(RACI!N3:N80,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N81,"A/R")</f>
         <v/>
       </c>
       <c r="E17" s="15" t="n">
@@ -5819,7 +5990,7 @@
         </is>
       </c>
       <c r="B18" s="21">
-        <f>COUNTA(RACI!B3:B80)</f>
+        <f>COUNTA(RACI!B3:B81)</f>
         <v/>
       </c>
     </row>
@@ -5866,10 +6037,10 @@
     <row r="27">
       <c r="A27" t="inlineStr"/>
     </row>
-    <row r="28" ht="104" customHeight="1">
+    <row r="28" ht="117" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>She keeps A on the 8 rows where the judgment is genuinely technical - formula stage-gate, compatibility and stability and RIPT and PET, packaging development, in-market stability testing, reformulation, PD-linked receipt, and the two margin rows that turn on formulation cost. She moves to consulted on everything process-shaped: NCR and CAPA lifecycle, batch hold and release, vendor quality flags, lab finding classification, SOP ratification. Danielle's framing in the review was that there were things the team had assumed Perrine would manage or organize that she is not, and that leadership can pull the plug even when she has submitted an approval. Splitting technical judgment from process ownership is what that means in practice.</t>
+          <t>She keeps A on the 7 rows where the judgment is genuinely formulation - formula stage-gate, compatibility and stability and RIPT and PET, in-market stability testing, reformulation, PD-linked receipt, and the two margin rows that turn on formulation cost. Packaging development moved to Erin Hover as the lead technical authority on packaging and artwork. She moves to consulted on everything process-shaped: NCR and CAPA lifecycle, batch hold and release, vendor quality flags, lab finding classification, SOP ratification. Danielle's framing in the review was that there were things the team had assumed Perrine would manage or organize that she is not, and that leadership can pull the plug even when she has submitted an approval. Splitting technical judgment from process ownership is what that means in practice.</t>
         </is>
       </c>
     </row>
@@ -5879,17 +6050,17 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="23" t="inlineStr">
         <is>
-          <t>Alvin owns the framework, and still does most of the work</t>
+          <t>Three contractors hold accountability, and two of them hold it alone</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
     </row>
-    <row r="32" ht="65" customHeight="1">
+    <row r="32" ht="104" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>Accountable for 40 of 78 activities and doing the work on 55. The framework rows are deliberate - quality management system, SOP framework, this RACI, the skill suite, the 23 scheduled Routines. The problem is not the A column. It is that 31 rows have him as both A and R, and that he does the work on 11 of the 12 Operations rows and 5 of the 8 Product Development rows. He holds the gates and does the work behind them.</t>
+          <t>Erin Hover is the lead technical authority on packaging and artwork and is accountable for 4 rows - creative direction, packaging development, artwork execution, and the label artwork archive. She is also a contractor, and on creative direction she is both A and R with no internal counterpart. Jan Haeck, who executes under her, is a contractor too, so the whole packaging and artwork chain runs through people outside the company. Perrine Calvet is the third, accountable for 7 formulation rows. Between them that is 11 of 79 activities where nobody on staff can check the work or continue it. Neither specialist job description covers creative or formulation authority, so the two hires do not close this.</t>
         </is>
       </c>
     </row>
@@ -5899,17 +6070,17 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="23" t="inlineStr">
         <is>
-          <t>What the two seats actually move</t>
+          <t>Where the President and the Founder sit</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
     </row>
-    <row r="36" ht="65" customHeight="1">
+    <row r="36" ht="104" customHeight="1">
       <c r="A36" s="17" t="inlineStr">
         <is>
-          <t>32 rows transition on hire: 16 to the Operations Specialist and 16 to the Product Development Specialist. 29 of those come off Alvin, 3 off Nicole. His R book drops from 55 to 26. Rows with no second pair of eyes drop from 42 to 25 across the whole matrix. Both seats report to Nicole, which is the point Danielle made in the review - moving day-to-day management off the VP seat is the succession outcome the system is being built for.</t>
+          <t>Danielle Iturbe is accountable for 4 rows - direction-changing PD decisions, the margin walk-away call, brand guideline custody, and campaign direction - and is consulted on 13 more. She now appears on all 9 Marketing rows and all 3 Creative rows, which she did not before. Campaign direction was missing from the matrix entirely; adding it is what gave the President somewhere to sit in Marketing rather than only receiving finished work. Ayesha Curry keeps sole accountability for brand-line moves and is consulted on 6 rows where the brand carries her name - brand guideline custody, creative direction, campaign direction, claim substantiation, retailer attestations, and packaging. Informed on the rest.</t>
         </is>
       </c>
     </row>
@@ -5919,17 +6090,17 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="23" t="inlineStr">
         <is>
-          <t>Ops first is the right order, and the matrix says why</t>
+          <t>Alvin owns the framework, and still does most of the work</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
     </row>
-    <row r="40" ht="91" customHeight="1">
+    <row r="40" ht="65" customHeight="1">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>Alvin does the work on 11 of 12 Operations rows. The Operations Specialist job description covers almost exactly that list: daily order operations and the third-party logistics relationship, channel operations across the direct store and Ulta Beauty Marketplace and Amazon, inventory reconciliation and FEFO and out-of-stock signals, receiving, purchase-to-pay, freight and customs and broker relationships, routing-guide and advance-ship-notice compliance, sales and operations planning support, production scheduling, and the label and seeding and sampling projects. That is a defined function sitting on one person today.</t>
+          <t>Accountable for 39 of 79 activities and doing the work on 56. The framework rows are deliberate - quality management system, SOP framework, this RACI, the skill suite, the 23 scheduled Routines. The problem is not the A column. It is that 31 rows have him as both A and R, and that he does the work on 11 of the 12 Operations rows and 5 of the 8 Product Development rows. He holds the gates and does the work behind them.</t>
         </is>
       </c>
     </row>
@@ -5939,17 +6110,17 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="23" t="inlineStr">
         <is>
-          <t>The PD seat is the one that closes the quality loop</t>
+          <t>What the two seats actually move</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
     </row>
-    <row r="44" ht="104" customHeight="1">
+    <row r="44" ht="65" customHeight="1">
       <c r="A44" s="17" t="inlineStr">
         <is>
-          <t>Its job description names running the quality system outright - corrective and preventive actions, non-conformances, complaint intake and trend monitoring, lab results, supplier quality flags, batch lifecycle including stability and hold-release, and the quality dashboard - plus pre-launch ingredient and label review, claim substantiation, retailer compliance responses and the registration tracker, and document control across specifications and dielines and artwork versions and bills of materials. Until it is filled, Nicole gates quality and Alvin executes it. That works, and it is the reason the gate is worth having now rather than after the hire, but it is two people covering a role that was written as one.</t>
+          <t>32 rows transition on hire: 16 to the Operations Specialist and 16 to the Product Development Specialist. 29 of those come off Alvin, 3 off Nicole. His R book drops from 55 to 26. Rows with no second pair of eyes drop from 42 to 25 across the whole matrix. Both seats report to Nicole, which is the point Danielle made in the review - moving day-to-day management off the VP seat is the succession outcome the system is being built for.</t>
         </is>
       </c>
     </row>
@@ -5959,17 +6130,17 @@
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="23" t="inlineStr">
         <is>
-          <t>What is still unowned</t>
+          <t>Ops first is the right order, and the matrix says why</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
     </row>
-    <row r="48" ht="65" customHeight="1">
+    <row r="48" ht="91" customHeight="1">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Three rows have no documented owner anywhere and default to Alvin as an inference rather than a sourced claim: accounts payable and bookkeeping and payroll, employee onboarding and offboarding and access deprovisioning, and Shopify revenue ownership. Finance appears in the operating documentation only as an email-sender category and a briefing heading. The function closest to the top line is the least specified.</t>
+          <t>Alvin does the work on 11 of 12 Operations rows. The Operations Specialist job description covers almost exactly that list: daily order operations and the third-party logistics relationship, channel operations across the direct store and Ulta Beauty Marketplace and Amazon, inventory reconciliation and FEFO and out-of-stock signals, receiving, purchase-to-pay, freight and customs and broker relationships, routing-guide and advance-ship-notice compliance, sales and operations planning support, production scheduling, and the label and seeding and sampling projects. That is a defined function sitting on one person today.</t>
         </is>
       </c>
     </row>
@@ -5979,22 +6150,62 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="23" t="inlineStr">
         <is>
-          <t>Single points of failure that remain after both hires</t>
+          <t>The PD seat is the one that closes the quality loop</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
     </row>
-    <row r="52" ht="91" customHeight="1">
+    <row r="52" ht="104" customHeight="1">
       <c r="A52" s="17" t="inlineStr">
         <is>
-          <t>Perrine is an external contractor holding A on 8 rows with no internal counterpart, and one of those - compatibility and stability and RIPT and PET - has her as both A and R. Nobody inside AC Brands can check that work or continue it. Alvin is the other: the Operator gate has no alternate anywhere in the suite, and all 23 scheduled Routines stop at a human approval only he can clear. Succession is documented exactly once in the entire system, for competitive intelligence. Nothing comparable exists for the quality gate, the technical advisor, or the framework owner. That gap costs hours to close, not headcount, and it is the one I would fix first.</t>
+          <t>Its job description names running the quality system outright - corrective and preventive actions, non-conformances, complaint intake and trend monitoring, lab results, supplier quality flags, batch lifecycle including stability and hold-release, and the quality dashboard - plus pre-launch ingredient and label review, claim substantiation, retailer compliance responses and the registration tracker, and document control across specifications and dielines and artwork versions and bills of materials. Until it is filled, Nicole gates quality and Alvin executes it. That works, and it is the reason the gate is worth having now rather than after the hire, but it is two people covering a role that was written as one.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="23" t="inlineStr">
+        <is>
+          <t>What is still unowned</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+    </row>
+    <row r="56" ht="65" customHeight="1">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Three rows have no documented owner anywhere and default to Alvin as an inference rather than a sourced claim: accounts payable and bookkeeping and payroll, employee onboarding and offboarding and access deprovisioning, and Shopify revenue ownership. Finance appears in the operating documentation only as an email-sender category and a briefing heading. The function closest to the top line is the least specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>Single points of failure that remain after both hires</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+    </row>
+    <row r="60" ht="91" customHeight="1">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>Perrine is an external contractor holding A on 8 rows with no internal counterpart, and one of those - compatibility and stability and RIPT and PET - has her as both A and R. Nobody inside AC Brands can check that work or continue it. Alvin is the other: the Operator gate has no alternate anywhere in the suite, and all 23 scheduled Routines stop at a human approval only he can clear. Succession is documented exactly once in the entire system, for competitive intelligence. Nothing comparable exists for the quality gate, the technical advisor, or the framework owner. That gap costs hours to close, not headcount, and it is the one I would fix first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6007,7 +6218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6274,22 +6485,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Perrine holds A on 8 technical rows as a contractor, with no named backup.</t>
+          <t>Erin Hover is a contractor and the lead technical authority on packaging and artwork, accountable for 4 rows with no internal backup. On creative direction she is both A and R.</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Reduced from 11 by moving process gates to Nicole, which is real progress. What remains is genuinely technical and genuinely single-threaded.</t>
+          <t>Jan Haeck executes under her and is also a contractor, so the entire packaging and artwork chain sits outside the company. Neither approved job description covers creative authority.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Name a backup technical reviewer</t>
+          <t>Name an internal creative counterpart, or scope it into a future role</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
@@ -6297,7 +6508,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 25:18-25:50; quality-manager/references/role-map.md:14</t>
+          <t>Alvin, 2026-07-31 (role correction); asana-pd-manager/references/role-map.md:22-23</t>
         </is>
       </c>
     </row>
@@ -6309,22 +6520,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Compliance</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Operator and Reg Lead are the same person, so two gates designed to be independent fire against one approver.</t>
+          <t>Perrine holds A on 7 formulation rows as a contractor, with no named backup.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>On ingredient-list packets, retailer attestations and FDA filings the second approval adds an audit entry but no second judgment. The 15-day reporting clock has no alternate.</t>
+          <t>Reduced from 11 by moving process gates to Nicole and packaging to Erin, which is real progress. What remains is genuinely formulation and genuinely single-threaded.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Split Reg Lead, or route the second gate to Pedrero</t>
+          <t>Name a backup technical reviewer</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
@@ -6332,7 +6543,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>regulatory-manager/references/role-map.md:14; adverse-event-and-recall-reporter/SKILL.md:108</t>
+          <t>Leadership Business Review 2026-07-30 25:18-25:50; quality-manager/references/role-map.md:14</t>
         </is>
       </c>
     </row>
@@ -6344,22 +6555,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>All 23 scheduled Routines stop at a human approval only Alvin can clear.</t>
+          <t>Operator and Reg Lead are the same person, so two gates designed to be independent fire against one approver.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Automation that fires unattended still needs him to commit. A week away queues the work rather than pausing it, and the Routines keep firing.</t>
+          <t>On ingredient-list packets, retailer attestations and FDA filings the second approval adds an audit entry but no second judgment. The 15-day reporting clock has no alternate.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Delegate publish gates to the new specialists</t>
+          <t>Split Reg Lead, or route the second gate to Pedrero</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
@@ -6367,7 +6578,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>scheduled-prompts/weekly-pd-update.md:91</t>
+          <t>regulatory-manager/references/role-map.md:14; adverse-event-and-recall-reporter/SKILL.md:108</t>
         </is>
       </c>
     </row>
@@ -6379,65 +6590,65 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>All functions</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Succession is documented once in the whole system - Soraya as interim CI lead if Nicole is out.</t>
+          <t>All 23 scheduled Routines stop at a human approval only Alvin can clear.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Nothing comparable exists for the quality gate, the technical advisor, the Reg Lead or Creative. The repo's stated purpose is succession.</t>
+          <t>Automation that fires unattended still needs him to commit. A week away queues the work rather than pausing it, and the Routines keep firing.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Alvin to write per-role backups into each role-map</t>
+          <t>Delegate publish gates to the new specialists</t>
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>sjs-comp-intel/references/team-ownership.md:95; decisions/log.md:41</t>
+          <t>scheduled-prompts/weekly-pd-update.md:91</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>Open item</t>
+          <t>Single point of failure</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>All functions</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Quality management system and monthly trend review not yet stood up. Target end of Q3.</t>
+          <t>Succession is documented once in the whole system - Soraya as interim CI lead if Nicole is out.</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>The gate is assigned but the reporting cadence behind it is not built. Without trend data a recurring issue like the pump defect cannot drive a packaging decision.</t>
+          <t>Nothing comparable exists for the quality gate, the technical advisor, the Reg Lead or Creative. The repo's stated purpose is succession.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Alvin owns framework, Nicole runs it</t>
+          <t>Alvin to write per-role backups into each role-map</t>
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 26:02-26:17</t>
+          <t>sjs-comp-intel/references/team-ownership.md:95; decisions/log.md:41</t>
         </is>
       </c>
     </row>
@@ -6449,30 +6660,30 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Operations &amp; Supply Chain</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>22 tasks from the retired coordinator seat sit unassigned in an archived holding project; 4 overdue.</t>
+          <t>Quality management system and monthly trend review not yet stood up. Target end of Q3.</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>An unassigned task drops out of every per-person sweep and goes stale silently. Concrete cost of running the interim split for a quarter.</t>
+          <t>The gate is assigned but the reporting cadence behind it is not built. Without trend data a recurring issue like the pump defect cannot drive a packaging decision.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Alvin to reassign under the interim split</t>
+          <t>Alvin owns framework, Nicole runs it</t>
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>decisions/log.md:60</t>
+          <t>Leadership Business Review 2026-07-30 26:02-26:17</t>
         </is>
       </c>
     </row>
@@ -6484,30 +6695,30 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Operations &amp; Supply Chain</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>SOP cleanup and operational prep before onboarding is not done.</t>
+          <t>22 tasks from the retired coordinator seat sit unassigned in an archived holding project; 4 overdue.</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Danielle's stated condition on the hire: clean up the system first so the role can function. Onboarding into the current state recreates the too-broad seat.</t>
+          <t>An unassigned task drops out of every per-person sweep and goes stale silently. Concrete cost of running the interim split for a quarter.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Alvin and Nicole, before the Ops seat starts</t>
+          <t>Alvin to reassign under the interim split</t>
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
+          <t>decisions/log.md:60</t>
         </is>
       </c>
     </row>
@@ -6519,30 +6730,30 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Wiki write-back has not fired since 2026-05-26. 123 of 133 pages are untouched seed content.</t>
+          <t>SOP cleanup and operational prep before onboarding is not done.</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>The bridges' runtime lexicon reads stale seed data, degrading vendor, contact and product recognition on every sweep.</t>
+          <t>Danielle's stated condition on the hire: clean up the system first so the role can function. Onboarding into the current state recreates the too-broad seat.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Alvin; part of the skills-architecture backlog</t>
+          <t>Alvin and Nicole, before the Ops seat starts</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>decisions/wiki-layer-audit-2026-07-29.md:52; decisions/log.md:75</t>
+          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
         </is>
       </c>
     </row>
@@ -6554,82 +6765,117 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Nine SOPs and forms are 29 days overdue on annual review.</t>
+          <t>Wiki write-back has not fired since 2026-05-26. 123 of 133 pages are untouched seed content.</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Review dates were null so the annual sweep had nothing to fire on. Dates are restored; the reviews are not done, and each needs sign-off.</t>
+          <t>The bridges' runtime lexicon reads stale seed data, degrading vendor, contact and product recognition on every sweep.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Nicole approves as the quality gate; Alvin stages</t>
+          <t>Alvin; part of the skills-architecture backlog</t>
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>decisions/log.md:69</t>
+          <t>decisions/wiki-layer-audit-2026-07-29.md:52; decisions/log.md:75</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
         <is>
+          <t>Open item</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Nine SOPs and forms are 29 days overdue on annual review.</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Review dates were null so the annual sweep had nothing to fire on. Dates are restored; the reviews are not done, and each needs sign-off.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Nicole approves as the quality gate; Alvin stages</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>decisions/log.md:69</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
+        <is>
           <t>Uncovered brand</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>All functions</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>Sweet July, the lifestyle brand, has no coverage. The suite is Sweet July Skin plus company-wide work.</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>Merch, licensing and non-skincare retail are run somewhere, but nothing documents who owns them. They cannot be put on a RACI from these sources.</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>Danielle to confirm scope for the next version</t>
         </is>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="F18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>references/architecture/system_map.md:3; context/about-business.md:3</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Hours per month</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Rough estimates. Open-seat rows are full-time-equivalent load, not incremental. Zero means the gap is a structural exposure rather than unbilled hours.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/deliverables/AC-Brands-RACI.xlsx
+++ b/deliverables/AC-Brands-RACI.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Gaps" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$Q$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$G$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$T$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$G$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q106"/>
+  <dimension ref="A1:T116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -578,9 +578,12 @@
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="6" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="58" customWidth="1" min="16" max="16"/>
-    <col width="82" customWidth="1" min="17" max="17"/>
+    <col width="6" customWidth="1" min="15" max="15"/>
+    <col width="6" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="58" customWidth="1" min="19" max="19"/>
+    <col width="82" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -654,17 +657,32 @@
           <t>PC</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>IF</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Transitions to</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -733,9 +751,24 @@
           <t>Perrine Calvet</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>Pedrero Regulatory</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>Ironclad Finance</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>Calm HR</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -780,17 +813,20 @@
           <t>A</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr"/>
+      <c r="P3" s="7" t="inlineStr"/>
+      <c r="Q3" s="7" t="inlineStr"/>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="S3" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/asana-pd-manager/SKILL.md:60</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="T3" s="6" t="inlineStr">
         <is>
           <t>PD Lead holds technical sign-off on formula stage moves. Operator confirms every move (Rule 1 preview); reversals get a stronger intent check.</t>
         </is>
@@ -831,13 +867,16 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="O4" s="6" t="inlineStr"/>
-      <c r="P4" s="6" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr"/>
+      <c r="P4" s="7" t="inlineStr"/>
+      <c r="Q4" s="7" t="inlineStr"/>
+      <c r="R4" s="6" t="inlineStr"/>
+      <c r="S4" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:16</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="T4" s="6" t="inlineStr">
         <is>
           <t>PD Lead owns the technical call outright. A and R the same person, and PC is an external contractor.</t>
         </is>
@@ -894,13 +933,16 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr"/>
-      <c r="P5" s="6" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr"/>
+      <c r="P5" s="7" t="inlineStr"/>
+      <c r="Q5" s="7" t="inlineStr"/>
+      <c r="R5" s="6" t="inlineStr"/>
+      <c r="S5" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:16,23; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="T5" s="6" t="inlineStr">
         <is>
           <t>PD Lead owns packaging dev calls; Jan executes packaging and artwork under Erin. Both are contractors. Erin is the lead technical authority on packaging and artwork and answers for the outcome; Jan executes under her. Perrine consults where formula contact or compatibility is in play. Both Erin and Jan are contractors.</t>
         </is>
@@ -949,13 +991,16 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O6" s="6" t="inlineStr"/>
-      <c r="P6" s="6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr"/>
+      <c r="P6" s="7" t="inlineStr"/>
+      <c r="Q6" s="7" t="inlineStr"/>
+      <c r="R6" s="6" t="inlineStr"/>
+      <c r="S6" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:17,18</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="T6" s="6" t="inlineStr">
         <is>
           <t>President approves. PD Consult is final-line approver alongside the President.</t>
         </is>
@@ -1000,13 +1045,16 @@
       <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
       <c r="N7" s="7" t="inlineStr"/>
-      <c r="O7" s="6" t="inlineStr"/>
-      <c r="P7" s="6" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr"/>
+      <c r="Q7" s="7" t="inlineStr"/>
+      <c r="R7" s="6" t="inlineStr"/>
+      <c r="S7" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:19</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="T7" s="6" t="inlineStr">
         <is>
           <t>Founder gate. Ayesha receives weekly PD signal through the Friday briefing.</t>
         </is>
@@ -1055,17 +1103,20 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O8" s="6" t="inlineStr">
+      <c r="O8" s="7" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr"/>
+      <c r="Q8" s="7" t="inlineStr"/>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
+      <c r="S8" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/fireflies-asana-bridge/SKILL.md:287; .claude/skills/outlook-plm-bridge/SKILL.md:191; .claude/skills/sjs-status-reporter/SKILL.md:331,385</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="T8" s="6" t="inlineStr">
         <is>
           <t>Alvin is the named approver on Flow D formula-approval decisions and classifies every meeting item. Covers the three PD hub dashboards. A and R both AB.</t>
         </is>
@@ -1110,13 +1161,16 @@
           <t>A</t>
         </is>
       </c>
-      <c r="O9" s="6" t="inlineStr"/>
-      <c r="P9" s="6" t="inlineStr">
+      <c r="O9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr"/>
+      <c r="R9" s="6" t="inlineStr"/>
+      <c r="S9" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/capa-coordinator/SKILL.md:85</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="T9" s="6" t="inlineStr">
         <is>
           <t>PD Lead is cross-flagged for any PD-side reformulation. Reformulation handoff rides the root-cause approval - no separate gate.</t>
         </is>
@@ -1125,59 +1179,66 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Operations &amp; Supply Chain</t>
+          <t>Product Development</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Vendor master data, onboarding (NDA + W9 gate), sourcing and performance scorecards</t>
+          <t>Document control: specifications, dielines, artwork versions, BOMs, landed-cost integrity</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr"/>
       <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I10" s="7" t="inlineStr"/>
       <c r="J10" s="7" t="inlineStr"/>
-      <c r="K10" s="7" t="inlineStr"/>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L10" s="7" t="inlineStr"/>
-      <c r="M10" s="7" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O10" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:42,46,75,154,158</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>PLM vendor record created only after Operations approves at 2D. First-contact routing varies by vendor_type (SKILL.md:50-56) but the approval gate does not. A and R both AB.</t>
+      <c r="O10" s="7" t="inlineStr"/>
+      <c r="P10" s="7" t="inlineStr"/>
+      <c r="Q10" s="7" t="inlineStr"/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>SharePoint: Sweet July Skin - Product Development Specialist - Job Description.docx</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>Documentation quality is Nicole's gate. The PD Specialist JD names document control as a core responsibility, so this row transitions on hire.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1250,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Purchase order lifecycle: placement, acknowledgement variance, close and discrepancy</t>
+          <t>Vendor master data, onboarding (NDA + W9 gate), sourcing and performance scorecards</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr"/>
@@ -1199,14 +1260,22 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="F11" s="7" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J11" s="7" t="inlineStr"/>
       <c r="K11" s="7" t="inlineStr"/>
       <c r="L11" s="7" t="inlineStr"/>
@@ -1216,19 +1285,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O11" s="6" t="inlineStr">
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr"/>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:108,116,140,248</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>Six sub-flows from draft to close, plus Job 10 discrepancy investigation. Every gate is Operations. A and R both AB.</t>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/purchasing-manager/SKILL.md:42,46,75,154,158</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>PLM vendor record created only after Operations approves at 2D. First-contact routing varies by vendor_type (SKILL.md:50-56) but the approval gate does not. A and R both AB.</t>
         </is>
       </c>
     </row>
@@ -1240,42 +1312,49 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Goods receipt on PD-linked purchase orders</t>
+          <t>Purchase order lifecycle: placement, acknowledgement variance, close and discrepancy</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr"/>
       <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="7" t="inlineStr"/>
       <c r="J12" s="7" t="inlineStr"/>
       <c r="K12" s="7" t="inlineStr"/>
       <c r="L12" s="7" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O12" s="6" t="inlineStr"/>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:130</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>PD owns the close on PD-linked receipts; Purchasing carries the receipt signal only. The one Ops row where accountability sits off the VP seat.</t>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr"/>
+      <c r="Q12" s="7" t="inlineStr"/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/purchasing-manager/SKILL.md:108,116,140,248</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>Six sub-flows from draft to close, plus Job 10 discrepancy investigation. Every gate is Operations. A and R both AB.</t>
         </is>
       </c>
     </row>
@@ -1287,14 +1366,14 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Three-way reconciliation across PLM, Shopify and Logiwa</t>
+          <t>Goods receipt on PD-linked purchase orders</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr"/>
       <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1302,31 +1381,30 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr"/>
       <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
-      <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/inventory-manager/SKILL.md:68</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>Operations decides the correction direction, usually trusting Logiwa as physical reality. A and R both AB.</t>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr"/>
+      <c r="R13" s="6" t="inlineStr"/>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/purchasing-manager/SKILL.md:130</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>PD owns the close on PD-linked receipts; Purchasing carries the receipt signal only. The one Ops row where accountability sits off the VP seat.</t>
         </is>
       </c>
     </row>
@@ -1338,15 +1416,11 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Vendor invoice classification and cost capture (five HITL gates)</t>
+          <t>Three-way reconciliation across PLM, Shopify and Logiwa</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr"/>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="D14" s="7" t="inlineStr"/>
       <c r="E14" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
@@ -1363,29 +1437,28 @@
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I14" s="7" t="inlineStr"/>
       <c r="J14" s="7" t="inlineStr"/>
       <c r="K14" s="7" t="inlineStr"/>
       <c r="L14" s="7" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
       <c r="N14" s="7" t="inlineStr"/>
-      <c r="O14" s="6" t="inlineStr">
+      <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr"/>
+      <c r="Q14" s="7" t="inlineStr"/>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:234,235,238</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>Operator confirms cost_category, regulatory_driver, linked SKU and multi-home routing before any PLM write, and approves the dispute branch. A and R both AB.</t>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/inventory-manager/SKILL.md:68</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>Operations decides the correction direction, usually trusting Logiwa as physical reality. A and R both AB.</t>
         </is>
       </c>
     </row>
@@ -1397,11 +1470,15 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Inventory position keeping, batch creation on receipt and the location ledger</t>
+          <t>Vendor invoice classification and cost capture (five HITL gates)</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr"/>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
@@ -1409,7 +1486,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -1418,29 +1495,36 @@
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J15" s="7" t="inlineStr"/>
       <c r="K15" s="7" t="inlineStr"/>
       <c r="L15" s="7" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O15" s="6" t="inlineStr">
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="inlineStr"/>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/inventory-manager/SKILL.md:18,52,60</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>Ex-Ops-Coordinator scope. Alvin took inventory under the 2026-07-17 interim split. A and R both AB.</t>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/purchasing-manager/SKILL.md:234,235,238; Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>Operator confirms cost_category, regulatory_driver, linked SKU and multi-home routing before any PLM write, and approves the dispute branch. A and R both AB. Ironclad consulted - classified invoices land in their ledger.</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1536,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Adjustments, write-offs and return dispositions</t>
+          <t>Inventory position keeping, batch creation on receipt and the location ledger</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr"/>
@@ -1462,7 +1546,11 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -1479,19 +1567,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O16" s="6" t="inlineStr">
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="7" t="inlineStr"/>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/inventory-manager/SKILL.md:94</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>Operations approves. Near-expiry write-offs wait on the quality call first. A and R both AB.</t>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/inventory-manager/SKILL.md:18,52,60</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>Ex-Ops-Coordinator scope. Alvin took inventory under the 2026-07-17 interim split. A and R both AB.</t>
         </is>
       </c>
     </row>
@@ -1503,25 +1594,17 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>S&amp;OP: forecast, inventory targets and buy recommendations</t>
+          <t>Adjustments, write-offs and return dispositions</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="D17" s="7" t="inlineStr"/>
       <c r="E17" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -1533,20 +1616,27 @@
       <c r="K17" s="7" t="inlineStr"/>
       <c r="L17" s="7" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="6" t="inlineStr">
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr"/>
+      <c r="P17" s="7" t="inlineStr"/>
+      <c r="Q17" s="7" t="inlineStr"/>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/supply-demand-planner/SKILL.md:30-52; .claude/skills/supply-demand-planner/references/plm-schema-additions.md:139</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>Operations approves; plm-assistant executes the SQL. Four intertwined jobs on one person. A and R both AB.</t>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/inventory-manager/SKILL.md:94</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>Operations approves. Near-expiry write-offs wait on the quality call first. A and R both AB.</t>
         </is>
       </c>
     </row>
@@ -1558,17 +1648,25 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Inbound freight, customs, duty and carrier claims</t>
+          <t>S&amp;OP: forecast, inventory targets and buy recommendations</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -1580,24 +1678,23 @@
       <c r="K18" s="7" t="inlineStr"/>
       <c r="L18" s="7" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="inlineStr">
+      <c r="N18" s="7" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr"/>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/logistics-manager/SKILL.md:59,186; .claude/skills/logistics-manager/forms/international-dtc-shipment.md:11</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>Nothing created or updated until Operations signs off. Ex-Ops-Coordinator logistics scope, now Alvin. HCT and Impress origin Asia so customs is routine. A and R both AB.</t>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/supply-demand-planner/SKILL.md:30-52; .claude/skills/supply-demand-planner/references/plm-schema-additions.md:139</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>Operations approves; plm-assistant executes the SQL. Four intertwined jobs on one person. A and R both AB.</t>
         </is>
       </c>
     </row>
@@ -1609,21 +1706,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Daily DTC order operations and the Logiwa report parse</t>
+          <t>Inbound freight, customs, duty and carrier claims</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr"/>
       <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
+      <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -1635,20 +1728,27 @@
       <c r="K19" s="7" t="inlineStr"/>
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
-      <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="6" t="inlineStr">
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr"/>
+      <c r="P19" s="7" t="inlineStr"/>
+      <c r="Q19" s="7" t="inlineStr"/>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:123; .claude/skills/oc3pl-order-manager/SKILL.md:109,191</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>Ex-Ops-Coordinator scope. Nicole covers order management and OC3PL under the 2026-07-17 interim split. A and R both NI.</t>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/logistics-manager/SKILL.md:59,186; .claude/skills/logistics-manager/forms/international-dtc-shipment.md:11</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>Nothing created or updated until Operations signs off. Ex-Ops-Coordinator logistics scope, now Alvin. HCT and Impress origin Asia so customs is routine. A and R both AB.</t>
         </is>
       </c>
     </row>
@@ -1660,19 +1760,19 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Pre-ship out-of-stock holds from the shortage sheet</t>
+          <t>Daily DTC order operations and the Logiwa report parse</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr"/>
       <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A/R</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -1687,19 +1787,22 @@
       <c r="L20" s="7" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
       <c r="N20" s="7" t="inlineStr"/>
-      <c r="O20" s="6" t="inlineStr">
+      <c r="O20" s="7" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr"/>
+      <c r="Q20" s="7" t="inlineStr"/>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/oc3pl-order-manager/SKILL.md:201; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>Order-side holds sit with Nicole; SKU-level shortage routing belongs to inventory-manager, so Alvin does the work.</t>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:123; .claude/skills/oc3pl-order-manager/SKILL.md:109,191</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>Ex-Ops-Coordinator scope. Nicole covers order management and OC3PL under the 2026-07-17 interim split. A and R both NI.</t>
         </is>
       </c>
     </row>
@@ -1711,15 +1814,11 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Retailer ASN / EDI 856 and routing-guide compliance (Ulta DC, Amazon Vendor)</t>
+          <t>Pre-ship out-of-stock holds from the shortage sheet</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="inlineStr"/>
       <c r="E21" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -1742,35 +1841,42 @@
       <c r="L21" s="7" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
       <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="6" t="inlineStr">
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr"/>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/logistics-manager/SKILL.md:80; .claude/skills/purchasing-manager/SKILL.md:55</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>Operations or Order Ops reviews. UBM launch June 2026 is the deadline driver on this lane.</t>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/oc3pl-order-manager/SKILL.md:201; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>Order-side holds sit with Nicole; SKU-level shortage routing belongs to inventory-manager, so Alvin does the work.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Operations &amp; Supply Chain</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Customer complaint intake, classification and first response</t>
+          <t>Retailer ASN / EDI 856 and routing-guide compliance (Ulta DC, Amazon Vendor)</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr"/>
-      <c r="D22" s="7" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -1781,67 +1887,66 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="G22" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
+      <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr"/>
       <c r="K22" s="7" t="inlineStr"/>
       <c r="L22" s="7" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>Product Development Specialist</t>
-        </is>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/complaint-and-event-handler/SKILL.md:20,53</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>HITL on every write. Operator approves classification plus first response. A and R both AB. Gate moved to Nicole as the final quality check per Leadership Business Review 2026-07-30 25:18-26:01.</t>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr"/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/logistics-manager/SKILL.md:80; .claude/skills/purchasing-manager/SKILL.md:55</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>Operations or Order Ops reviews. UBM launch June 2026 is the deadline driver on this lane.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Operations &amp; Supply Chain</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>Complaint trend analysis by SKU and batch</t>
+          <t>Production scheduling with manufacturing partners</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr"/>
       <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr"/>
       <c r="K23" s="7" t="inlineStr"/>
@@ -1852,19 +1957,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>Product Development Specialist</t>
-        </is>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/quality-manager/references/role-map.md:15</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>Voice of Customer holds gates on complaint classification and complaint-driven escalations. Nicole already held this gate; monthly trend review formalizes it per Leadership Business Review 2026-07-30 26:02-26:17.</t>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr"/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Leadership Business Review 2026-07-30 35:18</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>Named in the Ops Specialist JD under Planning &amp; Special Projects. Today Alvin coordinates KDC scheduling directly. A and R both AB until the seat is filled.</t>
         </is>
       </c>
     </row>
@@ -1876,15 +1984,11 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>NCR and CAPA lifecycle, intake through close (SKN-OPS-001)</t>
+          <t>Customer complaint intake, classification and first response</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="D24" s="7" t="inlineStr"/>
       <c r="E24" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -1911,19 +2015,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O24" s="6" t="inlineStr">
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="7" t="inlineStr"/>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/capa-coordinator/SKILL.md:54,136; .claude/skills/capa-coordinator/references/ncr-procedure.md:135; .claude/skills/capa-coordinator/references/skn-ops-001.md:64,102</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>Operator approves intake and both action plans; QA Lead approves conversion, root cause, verification, effectiveness and close. Six SOP phases, one external contractor on every technical gate. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults on technical root cause.</t>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/complaint-and-event-handler/SKILL.md:20,53</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>HITL on every write. Operator approves classification plus first response. A and R both AB. Gate moved to Nicole as the final quality check per Leadership Business Review 2026-07-30 25:18-26:01.</t>
         </is>
       </c>
     </row>
@@ -1935,7 +2042,7 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>Lab finding intake and OOS / OOT classification (SKN-OPS-006)</t>
+          <t>Complaint trend analysis by SKU and batch</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr"/>
@@ -1966,19 +2073,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O25" s="6" t="inlineStr">
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr"/>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/quality-lab-coordinator/SKILL.md:48,56</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>Operator approves intake and the single-versus-systemic classification. A and R both AB. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:35-25:50. Perrine consults on the technical call.</t>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/quality-manager/references/role-map.md:15</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>Voice of Customer holds gates on complaint classification and complaint-driven escalations. Nicole already held this gate; monthly trend review formalizes it per Leadership Business Review 2026-07-30 26:02-26:17.</t>
         </is>
       </c>
     </row>
@@ -1990,11 +2100,15 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Vendor quality flag and scorecard signal back to Purchasing</t>
+          <t>NCR and CAPA lifecycle, intake through close (SKN-OPS-001)</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr"/>
-      <c r="D26" s="7" t="inlineStr"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -2021,19 +2135,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O26" s="6" t="inlineStr">
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr"/>
+      <c r="Q26" s="7" t="inlineStr"/>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/quality-lab-coordinator/SKILL.md:76; .claude/skills/quality-lab-coordinator/references/vendor-scorecard-signal.md:103</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>QA Lead approves any vendor flag and the scorecard band. Operator can stage but not commit. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults.</t>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/capa-coordinator/SKILL.md:54,136; .claude/skills/capa-coordinator/references/ncr-procedure.md:135; .claude/skills/capa-coordinator/references/skn-ops-001.md:64,102</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>Operator approves intake and both action plans; QA Lead approves conversion, root cause, verification, effectiveness and close. Six SOP phases, one external contractor on every technical gate. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults on technical root cause.</t>
         </is>
       </c>
     </row>
@@ -2045,15 +2162,11 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Batch hold and release (SKN-OPS-007)</t>
+          <t>Lab finding intake and OOS / OOT classification (SKN-OPS-006)</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="D27" s="7" t="inlineStr"/>
       <c r="E27" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -2080,19 +2193,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O27" s="6" t="inlineStr">
+      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr"/>
+      <c r="Q27" s="7" t="inlineStr"/>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/batch-lifecycle-tracker/references/batch-lifecycle-procedure.md:208; .claude/skills/batch-lifecycle-tracker/SKILL.md:86</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>QA Lead approves every hold and every release. No exceptions at v5.4. Releases need a CAPA close or clean retest plus QA Lead judgment. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:35-26:01. Perrine consults on the technical basis.</t>
+      <c r="S27" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/quality-lab-coordinator/SKILL.md:48,56</t>
+        </is>
+      </c>
+      <c r="T27" s="6" t="inlineStr">
+        <is>
+          <t>Operator approves intake and the single-versus-systemic classification. A and R both AB. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:35-25:50. Perrine consults on the technical call.</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2220,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>In-market stability testing decisions (PET, accelerated, real-time)</t>
+          <t>Vendor quality flag and scorecard signal back to Purchasing</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr"/>
@@ -2114,9 +2230,9 @@
           <t>R</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr"/>
@@ -2130,24 +2246,27 @@
       <c r="K28" s="7" t="inlineStr"/>
       <c r="L28" s="7" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
-      <c r="N28" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O28" s="6" t="inlineStr">
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr"/>
+      <c r="Q28" s="7" t="inlineStr"/>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>Technical testing call stays with Perrine as the R&amp;D and quality technical advisor. Operator approves schedule edits. Per Leadership Business Review 2026-07-30 25:18-25:35 the process gate moved to Nicole but the technical judgment did not.</t>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/quality-lab-coordinator/SKILL.md:76; .claude/skills/quality-lab-coordinator/references/vendor-scorecard-signal.md:103</t>
+        </is>
+      </c>
+      <c r="T28" s="6" t="inlineStr">
+        <is>
+          <t>QA Lead approves any vendor flag and the scorecard band. Operator can stage but not commit. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults.</t>
         </is>
       </c>
     </row>
@@ -2159,11 +2278,15 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Near-expiry batch disposition at the 30-day threshold</t>
+          <t>Batch hold and release (SKN-OPS-007)</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr"/>
-      <c r="D29" s="7" t="inlineStr"/>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -2190,19 +2313,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O29" s="6" t="inlineStr">
+      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr"/>
+      <c r="Q29" s="7" t="inlineStr"/>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>Disposition is a quality gate, so it moves to Nicole. Posts back to inventory before any write-off.</t>
+      <c r="S29" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/batch-lifecycle-tracker/references/batch-lifecycle-procedure.md:208; .claude/skills/batch-lifecycle-tracker/SKILL.md:86</t>
+        </is>
+      </c>
+      <c r="T29" s="6" t="inlineStr">
+        <is>
+          <t>QA Lead approves every hold and every release. No exceptions at v5.4. Releases need a CAPA close or clean retest plus QA Lead judgment. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:35-26:01. Perrine consults on the technical basis.</t>
         </is>
       </c>
     </row>
@@ -2214,22 +2340,14 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Serious adverse event triage and recall kickoff (SKN-OPS-002, SKN-OPS-003)</t>
-        </is>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+          <t>In-market stability testing decisions (PET, accelerated, real-time)</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr"/>
+      <c r="D30" s="7" t="inlineStr"/>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2238,26 +2356,37 @@
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr"/>
-      <c r="H30" s="7" t="inlineStr"/>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="I30" s="7" t="inlineStr"/>
       <c r="J30" s="7" t="inlineStr"/>
       <c r="K30" s="7" t="inlineStr"/>
       <c r="L30" s="7" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="inlineStr"/>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/complaint-and-event-handler/SKILL.md:85,89,95</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>The strictest gate in the suite: explicit approval at every step, §4.A through §4.F each a separate gate. Operator decides severity, team and whether external reporting is needed. A and R both AB. Stays with Alvin as Reg Lead — legal and agency exposure. Nicole consults.</t>
+      <c r="N30" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr"/>
+      <c r="Q30" s="7" t="inlineStr"/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
+        </is>
+      </c>
+      <c r="T30" s="6" t="inlineStr">
+        <is>
+          <t>Technical testing call stays with Perrine as the R&amp;D and quality technical advisor. Operator approves schedule edits. Per Leadership Business Review 2026-07-30 25:18-25:35 the process gate moved to Nicole but the technical judgment did not.</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2398,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>SOP ratification, annual review and cross-cutting quality tasks</t>
+          <t>Near-expiry batch disposition at the 30-day threshold</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr"/>
@@ -2285,7 +2414,11 @@
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
       <c r="K31" s="7" t="inlineStr"/>
@@ -2296,15 +2429,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O31" s="6" t="inlineStr"/>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/quality-manager/SKILL.md:66,135; .claude/skills/quality-manager/references/sop-catalog.md:120; .claude/skills/quality-manager/references/qos-thresholds.md:52</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>QA Lead approves every ratification, review outcome, cross-cutting task and QoS threshold task. SOP §7 names a QA Manager for this; that seat is vacant and Perrine is filling it. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:18-25:50.</t>
+      <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr"/>
+      <c r="Q31" s="7" t="inlineStr"/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
+        </is>
+      </c>
+      <c r="T31" s="6" t="inlineStr">
+        <is>
+          <t>Disposition is a quality gate, so it moves to Nicole. Posts back to inventory before any write-off.</t>
         </is>
       </c>
     </row>
@@ -2316,27 +2456,31 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Quality dashboard publish to the landing hub</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr"/>
-      <c r="D32" s="7" t="inlineStr"/>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>Serious adverse event triage and recall kickoff (SKN-OPS-002, SKN-OPS-003)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="H32" s="7" t="inlineStr"/>
       <c r="I32" s="7" t="inlineStr"/>
       <c r="J32" s="7" t="inlineStr"/>
       <c r="K32" s="7" t="inlineStr"/>
@@ -2347,51 +2491,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>Product Development Specialist</t>
-        </is>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/quality-status-reporter/SKILL.md:78</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>Operator approves the commit before push. Never commit without confirmation. A and R both AB. Nicole gates the content; Alvin retains the publish mechanics. Per Leadership Business Review 2026-07-30 26:02-26:17.</t>
+      <c r="O32" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P32" s="7" t="inlineStr"/>
+      <c r="Q32" s="7" t="inlineStr"/>
+      <c r="R32" s="6" t="inlineStr"/>
+      <c r="S32" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/complaint-and-event-handler/SKILL.md:85,89,95; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T32" s="6" t="inlineStr">
+        <is>
+          <t>The strictest gate in the suite: explicit approval at every step, §4.A through §4.F each a separate gate. Operator decides severity, team and whether external reporting is needed. A and R both AB. Stays with Alvin as Reg Lead — legal and agency exposure. Nicole consults. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Compliance</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Pre-launch ingredient list review gate (SKN-OPS-008)</t>
+          <t>SOP ratification, annual review and cross-cutting quality tasks</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr"/>
       <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr"/>
       <c r="J33" s="7" t="inlineStr"/>
       <c r="K33" s="7" t="inlineStr"/>
@@ -2402,43 +2545,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>Product Development Specialist</t>
-        </is>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:50; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:62</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>Operator approves intake. Reg Lead is the same person at v6.6, so the gate fires twice against one person. Pedrero holds the binding external call. A and R both AB.</t>
+      <c r="O33" s="7" t="inlineStr"/>
+      <c r="P33" s="7" t="inlineStr"/>
+      <c r="Q33" s="7" t="inlineStr"/>
+      <c r="R33" s="6" t="inlineStr"/>
+      <c r="S33" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/quality-manager/SKILL.md:66,135; .claude/skills/quality-manager/references/sop-catalog.md:120; .claude/skills/quality-manager/references/qos-thresholds.md:52</t>
+        </is>
+      </c>
+      <c r="T33" s="6" t="inlineStr">
+        <is>
+          <t>QA Lead approves every ratification, review outcome, cross-cutting task and QoS threshold task. SOP §7 names a QA Manager for this; that seat is vacant and Perrine is filling it. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:18-25:50.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Compliance</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Pedrero engagement and send approval</t>
+          <t>Quality dashboard publish to the landing hub</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr"/>
       <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="G34" s="7" t="inlineStr"/>
-      <c r="H34" s="7" t="inlineStr"/>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="I34" s="7" t="inlineStr"/>
       <c r="J34" s="7" t="inlineStr"/>
       <c r="K34" s="7" t="inlineStr"/>
@@ -2449,32 +2599,39 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O34" s="6" t="inlineStr"/>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:60; .claude/skills/regulatory-manager/SKILL.md:140</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>Reg Lead approves every Pedrero send; Operator hits send manually. Both roles are Alvin. A and R both AB.</t>
+      <c r="O34" s="7" t="inlineStr"/>
+      <c r="P34" s="7" t="inlineStr"/>
+      <c r="Q34" s="7" t="inlineStr"/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="S34" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/quality-status-reporter/SKILL.md:78</t>
+        </is>
+      </c>
+      <c r="T34" s="6" t="inlineStr">
+        <is>
+          <t>Operator approves the commit before push. Never commit without confirmation. A and R both AB. Nicole gates the content; Alvin retains the publish mechanics. Per Leadership Business Review 2026-07-30 26:02-26:17.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Compliance</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>Claim substantiation and new-claim defensibility</t>
+          <t>Final quality check on product and documentation across every function</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
@@ -2482,18 +2639,18 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr"/>
       <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -2512,82 +2669,72 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O35" s="6" t="inlineStr">
-        <is>
-          <t>Product Development Specialist</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:97; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:29; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>Operator approves the path; Reg Lead approves the Pedrero stage. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off. A and R both AB. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off, so both are consulted rather than bypassed.</t>
+      <c r="O35" s="7" t="inlineStr"/>
+      <c r="P35" s="7" t="inlineStr"/>
+      <c r="Q35" s="7" t="inlineStr"/>
+      <c r="R35" s="6" t="inlineStr"/>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>Leadership Business Review 2026-07-30 25:35-26:01</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
+          <t>The new cross-function gate. Verbatim: "anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check... Even with each function having or being the primary owner, we'll still have that quality gate." A and R both NI.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Compliance</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Label artwork archive, IL cross-check and label-law checks (Pantone, Canada, Quebec, 19-state toxics)</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>Quality management system framework and monthly quality-trend review</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
         <is>
           <t>R</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr"/>
       <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="7" t="inlineStr"/>
       <c r="J36" s="7" t="inlineStr"/>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="K36" s="7" t="inlineStr"/>
       <c r="L36" s="7" t="inlineStr"/>
-      <c r="M36" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="M36" s="7" t="inlineStr"/>
       <c r="N36" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O36" s="6" t="inlineStr"/>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:85; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:93; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>Operator approves each pass outcome; Reg Lead approves any archive entry. Creative produces the artwork under review. Erin answers for the artwork being right as lead technical authority. Alvin runs the IL cross-check and the label-law passes and holds the Reg Lead gate on archive entries, so the regulatory approval and the artwork authority are separate people.</t>
+      <c r="O36" s="7" t="inlineStr"/>
+      <c r="P36" s="7" t="inlineStr"/>
+      <c r="Q36" s="7" t="inlineStr"/>
+      <c r="R36" s="6" t="inlineStr"/>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>Leadership Business Review 2026-07-30 25:18-26:17</t>
+        </is>
+      </c>
+      <c r="T36" s="6" t="inlineStr">
+        <is>
+          <t>Alvin owns the overall framework; Nicole runs it. Monthly trend review so recurring issues (the pump issue was the worked example) can drive packaging or formula decisions. Target: implemented by end of Q3.</t>
         </is>
       </c>
     </row>
@@ -2599,42 +2746,57 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>Reformulation claim bridge when a SKU reformulates without QIL parity</t>
+          <t>Pre-launch ingredient list review gate (SKN-OPS-008)</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr"/>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A/R</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="7" t="inlineStr"/>
       <c r="K37" s="7" t="inlineStr"/>
       <c r="L37" s="7" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
-      <c r="N37" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="inlineStr"/>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:281</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>Reg Lead approves the QIL recovery ask to the prior manufacturer; PD Lead does the formulation work.</t>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O37" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P37" s="7" t="inlineStr"/>
+      <c r="Q37" s="7" t="inlineStr"/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="S37" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:50; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:62; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T37" s="6" t="inlineStr">
+        <is>
+          <t>Operator approves intake. Reg Lead is the same person at v6.6, so the gate fires twice against one person. Pedrero holds the binding external call. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
@@ -2646,35 +2808,19 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Retailer attestation responses (Sephora, Ulta, Whole Foods, Credo)</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>Pedrero engagement and send approval</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr"/>
+      <c r="D38" s="7" t="inlineStr"/>
       <c r="E38" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="F38" s="7" t="inlineStr"/>
       <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="H38" s="7" t="inlineStr"/>
       <c r="I38" s="7" t="inlineStr"/>
       <c r="J38" s="7" t="inlineStr"/>
       <c r="K38" s="7" t="inlineStr"/>
@@ -2685,19 +2831,22 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O38" s="6" t="inlineStr">
-        <is>
-          <t>Product Development Specialist</t>
-        </is>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:105; .claude/skills/regulatory-manager/SKILL.md:122; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>Reg Lead approves the retailer submission after Pedrero approval. Voice of Customer consults where customer-perceived attributes matter. A and R both AB. Ayesha consulted - retailer clean-standard positioning is a brand claim.</t>
+      <c r="O38" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P38" s="7" t="inlineStr"/>
+      <c r="Q38" s="7" t="inlineStr"/>
+      <c r="R38" s="6" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:60; .claude/skills/regulatory-manager/SKILL.md:140; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T38" s="6" t="inlineStr">
+        <is>
+          <t>Reg Lead approves every Pedrero send; Operator hits send manually. Both roles are Alvin. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
@@ -2709,11 +2858,19 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>MoCRA registrations, state filings and Leaping Bunny renewal</t>
-        </is>
-      </c>
-      <c r="C39" s="7" t="inlineStr"/>
-      <c r="D39" s="7" t="inlineStr"/>
+          <t>Claim substantiation and new-claim defensibility</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
@@ -2728,31 +2885,42 @@
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr"/>
-      <c r="K39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L39" s="7" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
       <c r="N39" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="O39" s="6" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O39" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P39" s="7" t="inlineStr"/>
+      <c r="Q39" s="7" t="inlineStr"/>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/regulatory-manager/SKILL.md:114,367</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>Operator approves the filing draft; Reg Lead approves every registration record write. Both roles are Alvin. A and R both AB.</t>
+      <c r="S39" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:97; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:29; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T39" s="6" t="inlineStr">
+        <is>
+          <t>Operator approves the path; Reg Lead approves the Pedrero stage. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off. A and R both AB. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off, so both are consulted rather than bypassed. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
@@ -2764,22 +2932,22 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>SAE and recall agency filings, including the 15-day MoCRA clock (SKN-OPS-009)</t>
+          <t>Label artwork archive, IL cross-check and label-law checks (Pantone, Canada, Quebec, 19-state toxics)</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2791,23 +2959,38 @@
       <c r="H40" s="7" t="inlineStr"/>
       <c r="I40" s="7" t="inlineStr"/>
       <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="L40" s="7" t="inlineStr"/>
-      <c r="M40" s="7" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O40" s="6" t="inlineStr"/>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/adverse-event-and-recall-reporter/SKILL.md:65,108</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>Two distinct gates per filing - Pedrero send approval and agency submission approval - both held by Alvin. Statutory clock with no named backup. A and R both AB.</t>
+      <c r="O40" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P40" s="7" t="inlineStr"/>
+      <c r="Q40" s="7" t="inlineStr"/>
+      <c r="R40" s="6" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:85; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:93; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T40" s="6" t="inlineStr">
+        <is>
+          <t>Operator approves each pass outcome; Reg Lead approves any archive entry. Creative produces the artwork under review. Erin answers for the artwork being right as lead technical authority. Alvin runs the IL cross-check and the label-law passes and holds the Reg Lead gate on archive entries, so the regulatory approval and the artwork authority are separate people. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
@@ -2819,19 +3002,19 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Regulatory fan-out routing and the regulatory dashboard publish</t>
+          <t>Reformulation claim bridge when a SKU reformulates without QIL parity</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr"/>
       <c r="D41" s="7" t="inlineStr"/>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr"/>
@@ -2841,130 +3024,171 @@
       <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O41" s="6" t="inlineStr"/>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/regulatory-manager/SKILL.md:60; .claude/skills/regulatory-status-reporter/SKILL.md:90</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>Two gates per fan-out (Operator for the routing call, Reg Lead for task creation), both Alvin. Operator approves the dashboard commit before push. A and R both AB.</t>
+      <c r="N41" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="O41" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P41" s="7" t="inlineStr"/>
+      <c r="Q41" s="7" t="inlineStr"/>
+      <c r="R41" s="6" t="inlineStr"/>
+      <c r="S41" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:281; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T41" s="6" t="inlineStr">
+        <is>
+          <t>Reg Lead approves the QIL recovery ask to the prior manufacturer; PD Lead does the formulation work. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Retail &amp; Wholesale</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Retailer and reseller first contact</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr"/>
+          <t>Retailer attestation responses (Sephora, Ulta, Whole Foods, Credo)</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G42" s="7" t="inlineStr"/>
-      <c r="H42" s="7" t="inlineStr"/>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="I42" s="7" t="inlineStr"/>
       <c r="J42" s="7" t="inlineStr"/>
       <c r="K42" s="7" t="inlineStr"/>
       <c r="L42" s="7" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-      <c r="O42" s="6" t="inlineStr"/>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:55</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>First-contact owner for retailer, promotional_goods and accessories vendor types is the Sr. Director Consumer Strategy &amp; Ops. A and R both NI.</t>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O42" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P42" s="7" t="inlineStr"/>
+      <c r="Q42" s="7" t="inlineStr"/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:105; .claude/skills/regulatory-manager/SKILL.md:122; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T42" s="6" t="inlineStr">
+        <is>
+          <t>Reg Lead approves the retailer submission after Pedrero approval. Voice of Customer consults where customer-perceived attributes matter. A and R both AB. Ayesha consulted - retailer clean-standard positioning is a brand claim. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Retail &amp; Wholesale</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Retail channel launch programs: UBM cohort positioning, price ladder, Amazon Vendor</t>
+          <t>MoCRA registrations, state filings and Leaping Bunny renewal</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr"/>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr"/>
       <c r="K43" s="7" t="inlineStr"/>
       <c r="L43" s="7" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
-      <c r="N43" s="7" t="inlineStr"/>
-      <c r="O43" s="6" t="inlineStr"/>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:55; .claude/skills/sjs-retail-intel/SKILL.md:52; .claude/skills/logistics-manager/SKILL.md:80</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>UBM launch June 2026. Nicole holds the channel relationship; Alvin runs the positioning and outbound work.</t>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="O43" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P43" s="7" t="inlineStr"/>
+      <c r="Q43" s="7" t="inlineStr"/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/regulatory-manager/SKILL.md:114,367; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T43" s="6" t="inlineStr">
+        <is>
+          <t>Operator approves the filing draft; Reg Lead approves every registration record write. Both roles are Alvin. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Quarterly competitive teardowns across the five comp brands</t>
+          <t>SAE and recall agency filings, including the 15-day MoCRA clock (SKN-OPS-009)</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -2974,12 +3198,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
-        <is>
           <t>I</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2989,216 +3213,220 @@
       </c>
       <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="J44" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I44" s="7" t="inlineStr"/>
+      <c r="J44" s="7" t="inlineStr"/>
       <c r="K44" s="7" t="inlineStr"/>
       <c r="L44" s="7" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
-      <c r="N44" s="7" t="inlineStr"/>
-      <c r="O44" s="6" t="inlineStr"/>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:19,23-30; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>Soraya owns teardown production and comp brand profile maintenance. A and R both SS. Danielle consulted rather than only receiving the finished teardown.</t>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O44" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P44" s="7" t="inlineStr"/>
+      <c r="Q44" s="7" t="inlineStr"/>
+      <c r="R44" s="6" t="inlineStr"/>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/adverse-event-and-recall-reporter/SKILL.md:65,108; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T44" s="6" t="inlineStr">
+        <is>
+          <t>Two distinct gates per filing - Pedrero send approval and agency submission approval - both held by Alvin. Statutory clock with no named backup. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>Quarterly teardown sign-off before circulation</t>
+          <t>Regulatory fan-out routing and the regulatory dashboard publish</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr"/>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr"/>
+      <c r="E45" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I45" s="7" t="inlineStr"/>
       <c r="J45" s="7" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr"/>
       <c r="L45" s="7" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
-      <c r="N45" s="7" t="inlineStr"/>
-      <c r="O45" s="6" t="inlineStr"/>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:65; .claude/skills/sjs-comp-intel/SKILL.md:50</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>Alvin signs off before it circulates to Danielle and the SJS brand team.</t>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P45" s="7" t="inlineStr"/>
+      <c r="Q45" s="7" t="inlineStr"/>
+      <c r="R45" s="6" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/regulatory-manager/SKILL.md:60; .claude/skills/regulatory-status-reporter/SKILL.md:90; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+        </is>
+      </c>
+      <c r="T45" s="6" t="inlineStr">
+        <is>
+          <t>Two gates per fan-out (Operator for the routing call, Reg Lead for task creation), both Alvin. Operator approves the dashboard commit before push. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>Monthly competitive trend digest and cross-stream signal routing</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
+          <t>Pedrero engagement letter, scope and renewal</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J46" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I46" s="7" t="inlineStr"/>
+      <c r="J46" s="7" t="inlineStr"/>
       <c r="K46" s="7" t="inlineStr"/>
       <c r="L46" s="7" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
       <c r="N46" s="7" t="inlineStr"/>
-      <c r="O46" s="6" t="inlineStr"/>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:3,9-15; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>Stream DRI owns digest production and the 'what it means for SJS' analytical layer. Named as the stream's heartbeat - first thing protected under capacity pressure. A and R both NI. Danielle consulted on the digest's read.</t>
+      <c r="O46" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="P46" s="7" t="inlineStr"/>
+      <c r="Q46" s="7" t="inlineStr"/>
+      <c r="R46" s="6" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/regulatory-manager/references/pedrero-contacts.md:50; Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T46" s="6" t="inlineStr">
+        <is>
+          <t>The engagement letter governs scope, retainer, response windows and dispute resolution. Annual renewal. A and R both AB - the only person managing the regulatory partner relationship.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Retail &amp; Wholesale</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Social listening and comp brand monitoring (TikTok, IG, Pinterest, retailer new arrivals)</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
+          <t>Retailer and reseller first contact</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr"/>
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr"/>
-      <c r="F47" s="7" t="inlineStr"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
       <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
+      <c r="I47" s="7" t="inlineStr"/>
+      <c r="J47" s="7" t="inlineStr"/>
       <c r="K47" s="7" t="inlineStr"/>
       <c r="L47" s="7" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
       <c r="N47" s="7" t="inlineStr"/>
-      <c r="O47" s="6" t="inlineStr"/>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:34,40-44; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>Kate owns social listening tool maintenance, query hygiene and the weekly retailer new-arrivals scan. A and R both KL. Danielle consulted on what the social signal implies for brand.</t>
+      <c r="O47" s="7" t="inlineStr"/>
+      <c r="P47" s="7" t="inlineStr"/>
+      <c r="Q47" s="7" t="inlineStr"/>
+      <c r="R47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/purchasing-manager/SKILL.md:55</t>
+        </is>
+      </c>
+      <c r="T47" s="6" t="inlineStr">
+        <is>
+          <t>First-contact owner for retailer, promotional_goods and accessories vendor types is the Sr. Director Consumer Strategy &amp; Ops. A and R both NI.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Retail &amp; Wholesale</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Brand guideline custody (fonts, colors, logos, voice)</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
+          <t>Retail channel launch programs: UBM cohort positioning, price ladder, Amazon Vendor</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr"/>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr"/>
-      <c r="F48" s="7" t="inlineStr"/>
       <c r="G48" s="7" t="inlineStr"/>
       <c r="H48" s="7" t="inlineStr"/>
       <c r="I48" s="7" t="inlineStr">
@@ -3206,32 +3434,23 @@
           <t>C</t>
         </is>
       </c>
-      <c r="J48" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K48" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L48" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J48" s="7" t="inlineStr"/>
+      <c r="K48" s="7" t="inlineStr"/>
+      <c r="L48" s="7" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
       <c r="N48" s="7" t="inlineStr"/>
-      <c r="O48" s="6" t="inlineStr"/>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sweet-july-skin-brand/SKILL.md:1; references/architecture/system_map.md:157; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>Every output-producing skill defers here for canonical brand spec; no skill carries its own copy. President answers for brand custody; Creative Director maintains it. Ayesha consulted - the brand carries her name. Every output-producing skill defers here for canonical spec.</t>
+      <c r="O48" s="7" t="inlineStr"/>
+      <c r="P48" s="7" t="inlineStr"/>
+      <c r="Q48" s="7" t="inlineStr"/>
+      <c r="R48" s="6" t="inlineStr"/>
+      <c r="S48" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/purchasing-manager/SKILL.md:55; .claude/skills/sjs-retail-intel/SKILL.md:52; .claude/skills/logistics-manager/SKILL.md:80</t>
+        </is>
+      </c>
+      <c r="T48" s="6" t="inlineStr">
+        <is>
+          <t>UBM launch June 2026. Nicole holds the channel relationship; Alvin runs the positioning and outbound work.</t>
         </is>
       </c>
     </row>
@@ -3243,54 +3462,57 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Annual team holiday communications (11 sends across 3 templates)</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr"/>
+          <t>Quarterly competitive teardowns across the five comp brands</t>
+        </is>
+      </c>
+      <c r="C49" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr"/>
-      <c r="L49" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
       <c r="N49" s="7" t="inlineStr"/>
-      <c r="O49" s="6" t="inlineStr"/>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/ac-brands-holiday-comms/SKILL.md:26,165</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>Sends from alvin@ac-brands.com with the team on BCC. Includes the Outlook calendar sync and annual maintenance. A and R both AB.</t>
+      <c r="O49" s="7" t="inlineStr"/>
+      <c r="P49" s="7" t="inlineStr"/>
+      <c r="Q49" s="7" t="inlineStr"/>
+      <c r="R49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:19,23-30; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="T49" s="6" t="inlineStr">
+        <is>
+          <t>Soraya owns teardown production and comp brand profile maintenance. A and R both SS. Danielle consulted rather than only receiving the finished teardown.</t>
         </is>
       </c>
     </row>
@@ -3302,22 +3524,18 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Weekly founder briefing, Slides 5 and 6</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
+          <t>Quarterly teardown sign-off before circulation</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr"/>
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
       <c r="E50" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -3327,42 +3545,45 @@
       </c>
       <c r="G50" s="7" t="inlineStr"/>
       <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
+      <c r="I50" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="J50" s="7" t="inlineStr"/>
       <c r="K50" s="7" t="inlineStr"/>
       <c r="L50" s="7" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O50" s="6" t="inlineStr"/>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:49,72</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>Alvin owns both Slide 5 (Business Operations) and Slide 6 PD-Ops content; Nicole co-authors Slide 6 with her core PD content. A and R both AB.</t>
+      <c r="N50" s="7" t="inlineStr"/>
+      <c r="O50" s="7" t="inlineStr"/>
+      <c r="P50" s="7" t="inlineStr"/>
+      <c r="Q50" s="7" t="inlineStr"/>
+      <c r="R50" s="6" t="inlineStr"/>
+      <c r="S50" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:65; .claude/skills/sjs-comp-intel/SKILL.md:50</t>
+        </is>
+      </c>
+      <c r="T50" s="6" t="inlineStr">
+        <is>
+          <t>Alvin signs off before it circulates to Danielle and the SJS brand team.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Creative direction on packaging, artwork and brand visuals</t>
+          <t>Monthly competitive trend digest and cross-stream signal routing</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
@@ -3375,7 +3596,11 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr"/>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="7" t="inlineStr">
@@ -3383,40 +3608,39 @@
           <t>C</t>
         </is>
       </c>
-      <c r="J51" s="7" t="inlineStr"/>
-      <c r="K51" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="L51" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J51" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K51" s="7" t="inlineStr"/>
+      <c r="L51" s="7" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
       <c r="N51" s="7" t="inlineStr"/>
-      <c r="O51" s="6" t="inlineStr"/>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:22; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>Creative Director owns packaging, artwork and brand visuals. A and R both EH. Creative Director owns the direction as lead technical authority, and is a contractor. Danielle and Ayesha both consulted. A and R the same person - no second pair of eyes, and no internal backup either.</t>
+      <c r="O51" s="7" t="inlineStr"/>
+      <c r="P51" s="7" t="inlineStr"/>
+      <c r="Q51" s="7" t="inlineStr"/>
+      <c r="R51" s="6" t="inlineStr"/>
+      <c r="S51" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:3,9-15; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="T51" s="6" t="inlineStr">
+        <is>
+          <t>Stream DRI owns digest production and the 'what it means for SJS' analytical layer. Named as the stream's heartbeat - first thing protected under capacity pressure. A and R both NI. Danielle consulted on the digest's read.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Packaging and artwork execution</t>
+          <t>Social listening and comp brand monitoring (TikTok, IG, Pinterest, retailer new arrivals)</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -3426,73 +3650,64 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr"/>
       <c r="G52" s="7" t="inlineStr"/>
       <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr"/>
-      <c r="K52" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L52" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M52" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N52" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:23; .claude/skills/sjs-comp-intel/references/team-ownership.md:79; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>Jan is the creative contractor under Erin. Title differs between sources - Packaging Engineer in one, creative contractor in the other. Erin holds technical authority; Jan executes. Both contractors.</t>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr"/>
+      <c r="L52" s="7" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="inlineStr"/>
+      <c r="O52" s="7" t="inlineStr"/>
+      <c r="P52" s="7" t="inlineStr"/>
+      <c r="Q52" s="7" t="inlineStr"/>
+      <c r="R52" s="6" t="inlineStr"/>
+      <c r="S52" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:34,40-44; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="T52" s="6" t="inlineStr">
+        <is>
+          <t>Kate owns social listening tool maintenance, query hygiene and the weekly retailer new-arrivals scan. A and R both KL. Danielle consulted on what the social signal implies for brand.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Creative Requests intake and design coordination</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>Brand guideline custody (fonts, colors, logos, voice)</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr"/>
       <c r="F53" s="7" t="inlineStr"/>
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr"/>
@@ -3501,40 +3716,47 @@
           <t>C</t>
         </is>
       </c>
-      <c r="J53" s="7" t="inlineStr"/>
-      <c r="K53" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L53" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K53" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
-      <c r="O53" s="6" t="inlineStr"/>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-status-reporter/SKILL.md:352; .claude/skills/asana-pd-manager/references/role-map.md:24; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>Creative Requests Asana project owner is Ivy, Editorial/Design team. Ivy supports Erin and Jan. A and R both IT. Danielle consulted on intake priority.</t>
+      <c r="O53" s="7" t="inlineStr"/>
+      <c r="P53" s="7" t="inlineStr"/>
+      <c r="Q53" s="7" t="inlineStr"/>
+      <c r="R53" s="6" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sweet-july-skin-brand/SKILL.md:1; references/architecture/system_map.md:157; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="T53" s="6" t="inlineStr">
+        <is>
+          <t>Every output-producing skill defers here for canonical brand spec; no skill carries its own copy. President answers for brand custody; Creative Director maintains it. Ayesha consulted - the brand carries her name. Every output-producing skill defers here for canonical spec.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Shopify revenue and channel position read</t>
+          <t>Annual team holiday communications (11 sends across 3 templates)</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr"/>
@@ -3550,147 +3772,200 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
       <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr"/>
-      <c r="J54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J54" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr"/>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="M54" s="7" t="inlineStr"/>
       <c r="N54" s="7" t="inlineStr"/>
-      <c r="O54" s="6" t="inlineStr"/>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>connections.md:7; context/about-business.md:5</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>INFERRED - no source names an owner. Shopify is registered as the revenue connection and named as the primary DTC revenue track, but no skill assigns ownership or a gate. A defaults to AB.</t>
+      <c r="O54" s="7" t="inlineStr"/>
+      <c r="P54" s="7" t="inlineStr"/>
+      <c r="Q54" s="7" t="inlineStr"/>
+      <c r="R54" s="6" t="inlineStr"/>
+      <c r="S54" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/ac-brands-holiday-comms/SKILL.md:26,165</t>
+        </is>
+      </c>
+      <c r="T54" s="6" t="inlineStr">
+        <is>
+          <t>Sends from alvin@ac-brands.com with the team on BCC. Includes the Outlook calendar sync and annual maintenance. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Daily DTC fulfillment KPIs and the SJ Shipping Dashboard</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="inlineStr"/>
-      <c r="D55" s="7" t="inlineStr"/>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="inlineStr">
+          <t>Weekly founder briefing, Slides 5 and 6</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr"/>
       <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
       <c r="J55" s="7" t="inlineStr"/>
       <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="7" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr"/>
-      <c r="O55" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/oc3pl-order-manager/SKILL.md:61,191; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>Ex-Ops-Coordinator scope, now Nicole per the interim split. A and R both NI.</t>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O55" s="7" t="inlineStr"/>
+      <c r="P55" s="7" t="inlineStr"/>
+      <c r="Q55" s="7" t="inlineStr"/>
+      <c r="R55" s="6" t="inlineStr"/>
+      <c r="S55" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:49,72</t>
+        </is>
+      </c>
+      <c r="T55" s="6" t="inlineStr">
+        <is>
+          <t>Alvin owns both Slide 5 (Business Operations) and Slide 6 PD-Ops content; Nicole co-authors Slide 6 with her core PD content. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Margin architecture framework and quarterly portfolio review</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="inlineStr"/>
+          <t>Operational special projects: labels, PR seeding, sampling</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E56" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr"/>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
-      <c r="J56" s="7" t="inlineStr"/>
-      <c r="K56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L56" s="7" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
       <c r="N56" s="7" t="inlineStr"/>
-      <c r="O56" s="6" t="inlineStr"/>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-margin-architect/references/framework.md:209; .claude/skills/sjs-margin-portfolio-review/SKILL.md:1</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>Framework reference plus the quarterly portfolio sweep and traffic-light report. A and R both AB.</t>
+      <c r="O56" s="7" t="inlineStr"/>
+      <c r="P56" s="7" t="inlineStr"/>
+      <c r="Q56" s="7" t="inlineStr"/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="S56" s="6" t="inlineStr">
+        <is>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="T56" s="6" t="inlineStr">
+        <is>
+          <t>Named in the Ops Specialist JD, and in the email as making sure product is where it needs to be for launches, promos, PR seeding and sampling. Danielle consulted - PR seeding and sampling are brand-facing.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Per-SKU margin pressure-test against channel floors</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr"/>
-      <c r="D57" s="7" t="inlineStr">
+          <t>Campaign direction and seasonal brand moments</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -3700,59 +3975,66 @@
       </c>
       <c r="G57" s="7" t="inlineStr"/>
       <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J57" s="7" t="inlineStr"/>
-      <c r="K57" s="7" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J57" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L57" s="7" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
-      <c r="N57" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="O57" s="6" t="inlineStr"/>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-margin-pressure-test/SKILL.md:93</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>Flagged as Perrine and Soraya's call to ratify, with Alvin on admin, Nicole consulting and Danielle approving.</t>
+      <c r="N57" s="7" t="inlineStr"/>
+      <c r="O57" s="7" t="inlineStr"/>
+      <c r="P57" s="7" t="inlineStr"/>
+      <c r="Q57" s="7" t="inlineStr"/>
+      <c r="R57" s="6" t="inlineStr"/>
+      <c r="S57" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (role correction); .claude/skills/sjs-margin-walk-away/SKILL.md:93</t>
+        </is>
+      </c>
+      <c r="T57" s="6" t="inlineStr">
+        <is>
+          <t>Added 2026-07-31. Campaign direction was absent from the matrix, which is why the President and the Founder had almost no Marketing presence. Danielle answers for it - Soraya reports to her and the margin sources already have her approving every repricing and channel call. Ayesha consulted on brand moments.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Walk-away decision when a SKU breaks its channel floor</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr"/>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>Creative direction on packaging, artwork and brand visuals</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr"/>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
       <c r="I58" s="7" t="inlineStr">
@@ -3761,135 +4043,172 @@
         </is>
       </c>
       <c r="J58" s="7" t="inlineStr"/>
-      <c r="K58" s="7" t="inlineStr"/>
-      <c r="L58" s="7" t="inlineStr"/>
+      <c r="K58" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O58" s="6" t="inlineStr"/>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:93,105,118</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>Danielle approves on three of the four paths. Alvin carries the work on all four.</t>
+      <c r="N58" s="7" t="inlineStr"/>
+      <c r="O58" s="7" t="inlineStr"/>
+      <c r="P58" s="7" t="inlineStr"/>
+      <c r="Q58" s="7" t="inlineStr"/>
+      <c r="R58" s="6" t="inlineStr"/>
+      <c r="S58" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:22; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="T58" s="6" t="inlineStr">
+        <is>
+          <t>Creative Director owns packaging, artwork and brand visuals. A and R both EH. Creative Director owns the direction as lead technical authority, and is a contractor. Danielle and Ayesha both consulted. A and R the same person - no second pair of eyes, and no internal backup either.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>SKU archetype and Standard / Acquisition designation</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr"/>
+          <t>Packaging and artwork execution</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr"/>
       <c r="G59" s="7" t="inlineStr"/>
       <c r="H59" s="7" t="inlineStr"/>
       <c r="I59" s="7" t="inlineStr"/>
       <c r="J59" s="7" t="inlineStr"/>
-      <c r="K59" s="7" t="inlineStr"/>
-      <c r="L59" s="7" t="inlineStr"/>
-      <c r="M59" s="7" t="inlineStr"/>
-      <c r="N59" s="9" t="inlineStr">
+      <c r="K59" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="O59" s="6" t="inlineStr"/>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:78</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>Perrine as PD owner with Alvin on PD admin and sourcing; Nicole consults.</t>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M59" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O59" s="7" t="inlineStr"/>
+      <c r="P59" s="7" t="inlineStr"/>
+      <c r="Q59" s="7" t="inlineStr"/>
+      <c r="R59" s="6" t="inlineStr"/>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:23; .claude/skills/sjs-comp-intel/references/team-ownership.md:79; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="T59" s="6" t="inlineStr">
+        <is>
+          <t>Jan is the creative contractor under Erin. Title differs between sources - Packaging Engineer in one, creative contractor in the other. Erin holds technical authority; Jan executes. Both contractors.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Monthly and quarterly vendor cost rollups</t>
+          <t>Creative Requests intake and design coordination</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr"/>
       <c r="D60" s="7" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="E60" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
       <c r="G60" s="7" t="inlineStr"/>
       <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J60" s="7" t="inlineStr"/>
-      <c r="K60" s="7" t="inlineStr"/>
-      <c r="L60" s="7" t="inlineStr"/>
+      <c r="K60" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="7" t="inlineStr"/>
-      <c r="O60" s="6" t="inlineStr"/>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/regulatory-manager/SKILL.md:196; .claude/skills/purchasing-manager/SKILL.md:365</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>regulatory-manager Jobs 8 and 9 read vendor_invoices directly; purchasing-manager has no rollup of its own. A and R both AB.</t>
+      <c r="O60" s="7" t="inlineStr"/>
+      <c r="P60" s="7" t="inlineStr"/>
+      <c r="Q60" s="7" t="inlineStr"/>
+      <c r="R60" s="6" t="inlineStr"/>
+      <c r="S60" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-status-reporter/SKILL.md:352; .claude/skills/asana-pd-manager/references/role-map.md:24; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="T60" s="6" t="inlineStr">
+        <is>
+          <t>Creative Requests Asana project owner is Ivy, Editorial/Design team. Ivy supports Erin and Jan. A and R both IT. Danielle consulted on intake priority.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Accounts payable, bookkeeping and payroll</t>
+          <t>Shopify revenue and channel position read</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr"/>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -3897,7 +4216,11 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="F61" s="7" t="inlineStr"/>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
@@ -3906,46 +4229,49 @@
       <c r="L61" s="7" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="7" t="inlineStr"/>
-      <c r="O61" s="6" t="inlineStr"/>
-      <c r="P61" s="6" t="inlineStr"/>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>INFERRED - no source. Finance appears only as an email-sender category (outlook-plm-bridge/SKILL.md:368) and a briefing heading (ayesha-weekly-briefing/SKILL.md:9). No owner, no approver, no gate anywhere in SJ-OS. A defaults to AB.</t>
+      <c r="O61" s="7" t="inlineStr"/>
+      <c r="P61" s="7" t="inlineStr"/>
+      <c r="Q61" s="7" t="inlineStr"/>
+      <c r="R61" s="6" t="inlineStr"/>
+      <c r="S61" s="6" t="inlineStr">
+        <is>
+          <t>connections.md:7; context/about-business.md:5</t>
+        </is>
+      </c>
+      <c r="T61" s="6" t="inlineStr">
+        <is>
+          <t>INFERRED - no source names an owner. Shopify is registered as the revenue connection and named as the primary DTC revenue track, but no skill assigns ownership or a gate. A defaults to AB.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Hiring the Operations Specialist and the PD Project Manager Specialist</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr"/>
+          <t>Daily DTC fulfillment KPIs and the SJ Shipping Dashboard</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr"/>
+      <c r="D62" s="7" t="inlineStr"/>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H62" s="7" t="inlineStr"/>
       <c r="I62" s="7" t="inlineStr"/>
       <c r="J62" s="7" t="inlineStr"/>
@@ -3953,89 +4279,119 @@
       <c r="L62" s="7" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
       <c r="N62" s="7" t="inlineStr"/>
-      <c r="O62" s="6" t="inlineStr"/>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>decisions/log.md:52,58; context/priorities.md:3</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>Both new roles report to Nicole. Decision owner recorded as Alvin, with Nicole on the two new roles once filled. Priority 1 of 2 this quarter.</t>
+      <c r="O62" s="7" t="inlineStr"/>
+      <c r="P62" s="7" t="inlineStr"/>
+      <c r="Q62" s="7" t="inlineStr"/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="S62" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/oc3pl-order-manager/SKILL.md:61,191; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
+        </is>
+      </c>
+      <c r="T62" s="6" t="inlineStr">
+        <is>
+          <t>Ex-Ops-Coordinator scope, now Nicole per the interim split. A and R both NI.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Tool procurement, vendor renewals and shared-folder admin</t>
+          <t>Channel operations and promo setup across DTC, UBM and Amazon</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr"/>
-      <c r="D63" s="7" t="inlineStr"/>
-      <c r="E63" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr"/>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="7" t="inlineStr"/>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="K63" s="7" t="inlineStr"/>
-      <c r="L63" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="L63" s="7" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
       <c r="N63" s="7" t="inlineStr"/>
-      <c r="O63" s="6" t="inlineStr"/>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:50; .claude/skills/sjs-comp-intel/references/sequencing-plan.md:12</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>Ex-Ops-Coordinator scope. Alvin carries it directly until the Operations Specialist starts. A and R both AB.</t>
+      <c r="O63" s="7" t="inlineStr"/>
+      <c r="P63" s="7" t="inlineStr"/>
+      <c r="Q63" s="7" t="inlineStr"/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="S63" s="6" t="inlineStr">
+        <is>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
+        </is>
+      </c>
+      <c r="T63" s="6" t="inlineStr">
+        <is>
+          <t>Named in the Ops Specialist JD under Order Management &amp; Channel Operations. Nicole holds the channel relationship.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Employee onboarding, offboarding and access deprovisioning</t>
+          <t>Proactive reships and fulfillment-issue resolution</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr"/>
       <c r="D64" s="7" t="inlineStr"/>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H64" s="7" t="inlineStr"/>
       <c r="I64" s="7" t="inlineStr"/>
       <c r="J64" s="7" t="inlineStr"/>
@@ -4043,37 +4399,52 @@
       <c r="L64" s="7" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="7" t="inlineStr"/>
-      <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:48-56</t>
-        </is>
-      </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>INFERRED - no named owner. The departed-role-holder checklist is the only offboarding process documented anywhere in SJ-OS, and it exists because a stale role row broke collaborator resolution. A defaults to AB.</t>
+      <c r="O64" s="7" t="inlineStr"/>
+      <c r="P64" s="7" t="inlineStr"/>
+      <c r="Q64" s="7" t="inlineStr"/>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="S64" s="6" t="inlineStr">
+        <is>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
+        </is>
+      </c>
+      <c r="T64" s="6" t="inlineStr">
+        <is>
+          <t>JD wording: resolve fulfillment issues "before a customer has to follow up." Sits inside Nicole's interim OC3PL coverage. A and R both NI.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>PLM schema, write path, audit log and Supabase wiki custody</t>
+          <t>Margin architecture framework and quarterly portfolio review</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr"/>
-      <c r="D65" s="7" t="inlineStr"/>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E65" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
       <c r="I65" s="7" t="inlineStr"/>
@@ -4081,78 +4452,100 @@
       <c r="K65" s="7" t="inlineStr"/>
       <c r="L65" s="7" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
-      <c r="N65" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O65" s="6" t="inlineStr"/>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/plm-assistant/SKILL.md:292; decisions/wiki-layer-audit-2026-07-29.md:52</t>
-        </is>
-      </c>
-      <c r="Q65" s="6" t="inlineStr">
-        <is>
-          <t>plm-assistant is the sole PLM writer and every write needs Operations sign-off. Job 0 wiki write-back has not fired since 2026-05-26. A and R both AB.</t>
+      <c r="N65" s="7" t="inlineStr"/>
+      <c r="O65" s="7" t="inlineStr"/>
+      <c r="P65" s="7" t="inlineStr"/>
+      <c r="Q65" s="7" t="inlineStr"/>
+      <c r="R65" s="6" t="inlineStr"/>
+      <c r="S65" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-margin-architect/references/framework.md:209; .claude/skills/sjs-margin-portfolio-review/SKILL.md:1</t>
+        </is>
+      </c>
+      <c r="T65" s="6" t="inlineStr">
+        <is>
+          <t>Framework reference plus the quarterly portfolio sweep and traffic-light report. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Landing hub publish and Netlify Function maintenance</t>
+          <t>Per-SKU margin pressure-test against channel floors</t>
         </is>
       </c>
       <c r="C66" s="7" t="inlineStr"/>
-      <c r="D66" s="7" t="inlineStr"/>
-      <c r="E66" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G66" s="7" t="inlineStr"/>
       <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr"/>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J66" s="7" t="inlineStr"/>
       <c r="K66" s="7" t="inlineStr"/>
       <c r="L66" s="7" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
-      <c r="N66" s="7" t="inlineStr"/>
-      <c r="O66" s="6" t="inlineStr"/>
-      <c r="P66" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/quality-status-reporter/SKILL.md:34-50; .claude/skills/quality-status-reporter/references/hub-integration.md:85</t>
-        </is>
-      </c>
-      <c r="Q66" s="6" t="inlineStr">
-        <is>
-          <t>All hub writes go through the landing-hub-publish Function behind an Operator gate. Deploy is commit-and-push only, never Netlify CLI. A and R both AB.</t>
+      <c r="N66" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr"/>
+      <c r="P66" s="7" t="inlineStr"/>
+      <c r="Q66" s="7" t="inlineStr"/>
+      <c r="R66" s="6" t="inlineStr"/>
+      <c r="S66" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-margin-pressure-test/SKILL.md:93</t>
+        </is>
+      </c>
+      <c r="T66" s="6" t="inlineStr">
+        <is>
+          <t>Flagged as Perrine and Soraya's call to ratify, with Alvin on admin, Nicole consulting and Danielle approving.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Asana project, section, custom-field and connector configuration</t>
+          <t>Walk-away decision when a SKU breaks its channel floor</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr"/>
-      <c r="D67" s="7" t="inlineStr"/>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -4162,43 +4555,62 @@
       </c>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J67" s="7" t="inlineStr"/>
       <c r="K67" s="7" t="inlineStr"/>
       <c r="L67" s="7" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr"/>
-      <c r="O67" s="6" t="inlineStr"/>
-      <c r="P67" s="6" t="inlineStr">
-        <is>
-          <t>references/architecture/asana_task_contract.md:227; connections.md:5-13</t>
-        </is>
-      </c>
-      <c r="Q67" s="6" t="inlineStr">
-        <is>
-          <t>An unresolvable role-holder is surfaced for Alvin to decide, not dropped. Seven tool domains registered; iMessage still not connected. A and R both AB.</t>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O67" s="7" t="inlineStr"/>
+      <c r="P67" s="7" t="inlineStr"/>
+      <c r="Q67" s="7" t="inlineStr"/>
+      <c r="R67" s="6" t="inlineStr"/>
+      <c r="S67" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:93,105,118</t>
+        </is>
+      </c>
+      <c r="T67" s="6" t="inlineStr">
+        <is>
+          <t>Danielle approves on three of the four paths. Alvin carries the work on all four.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Skill suite authorship, audit and versioning</t>
+          <t>SKU archetype and Standard / Acquisition designation</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr"/>
-      <c r="D68" s="7" t="inlineStr"/>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr"/>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G68" s="7" t="inlineStr"/>
       <c r="H68" s="7" t="inlineStr"/>
       <c r="I68" s="7" t="inlineStr"/>
@@ -4206,42 +4618,49 @@
       <c r="K68" s="7" t="inlineStr"/>
       <c r="L68" s="7" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
-      <c r="N68" s="7" t="inlineStr"/>
-      <c r="O68" s="6" t="inlineStr"/>
-      <c r="P68" s="6" t="inlineStr">
-        <is>
-          <t>decisions/skills-architecture-tracker.md:4; decisions/log.md:31,45</t>
-        </is>
-      </c>
-      <c r="Q68" s="6" t="inlineStr">
-        <is>
-          <t>Owner recorded as Alvin Belt across the architecture decisions. Priority 2 of 2 this quarter. A and R both AB.</t>
+      <c r="N68" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr"/>
+      <c r="P68" s="7" t="inlineStr"/>
+      <c r="Q68" s="7" t="inlineStr"/>
+      <c r="R68" s="6" t="inlineStr"/>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:78</t>
+        </is>
+      </c>
+      <c r="T68" s="6" t="inlineStr">
+        <is>
+          <t>Perrine as PD owner with Alvin on PD admin and sourcing; Nicole consults.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>The 23 scheduled Routines and their HITL gates</t>
+          <t>Monthly and quarterly vendor cost rollups</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr"/>
-      <c r="D69" s="7" t="inlineStr"/>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E69" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="F69" s="7" t="inlineStr"/>
       <c r="G69" s="7" t="inlineStr"/>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr"/>
@@ -4250,106 +4669,104 @@
       <c r="L69" s="7" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
       <c r="N69" s="7" t="inlineStr"/>
-      <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="6" t="inlineStr">
-        <is>
-          <t>scheduled-prompts/weekly-pd-update.md:91; scheduled-prompts/sjs-purchasing-monthly-rollup-and-snapshot.md:79</t>
-        </is>
-      </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>Nothing commits until Alvin says go. Same pattern across all 23 Routines, including the ones that fire unattended on a schedule. A and R both AB.</t>
+      <c r="O69" s="7" t="inlineStr"/>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q69" s="7" t="inlineStr"/>
+      <c r="R69" s="6" t="inlineStr"/>
+      <c r="S69" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/regulatory-manager/SKILL.md:196; .claude/skills/purchasing-manager/SKILL.md:365; Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T69" s="6" t="inlineStr">
+        <is>
+          <t>regulatory-manager Jobs 8 and 9 read vendor_invoices directly; purchasing-manager has no rollup of its own. A and R both AB. Ironclad consulted - the rollup feeds their books.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Final quality check on product and documentation across every function</t>
-        </is>
-      </c>
-      <c r="C70" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>Accounts payable, bookkeeping and payroll</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr"/>
       <c r="G70" s="7" t="inlineStr"/>
       <c r="H70" s="7" t="inlineStr"/>
-      <c r="I70" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I70" s="7" t="inlineStr"/>
       <c r="J70" s="7" t="inlineStr"/>
-      <c r="K70" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K70" s="7" t="inlineStr"/>
       <c r="L70" s="7" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
-      <c r="N70" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O70" s="6" t="inlineStr"/>
-      <c r="P70" s="6" t="inlineStr">
-        <is>
-          <t>Leadership Business Review 2026-07-30 25:35-26:01</t>
-        </is>
-      </c>
-      <c r="Q70" s="6" t="inlineStr">
-        <is>
-          <t>The new cross-function gate. Verbatim: "anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check... Even with each function having or being the primary owner, we'll still have that quality gate." A and R both NI.</t>
+      <c r="N70" s="7" t="inlineStr"/>
+      <c r="O70" s="7" t="inlineStr"/>
+      <c r="P70" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr"/>
+      <c r="R70" s="6" t="inlineStr"/>
+      <c r="S70" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T70" s="6" t="inlineStr">
+        <is>
+          <t>Ironclad Finance runs AP, bookkeeping and payroll; Dan Bender is the contact. Cost-side accountability sits with Operations because the vendor-invoice pipeline and its five approval gates feed it. No longer an unowned function.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Quality management system framework and monthly quality-trend review</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr"/>
-      <c r="D71" s="7" t="inlineStr">
+          <t>Month-end close and management reporting</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr">
+      <c r="D71" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F71" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr"/>
@@ -4359,102 +4776,108 @@
       <c r="K71" s="7" t="inlineStr"/>
       <c r="L71" s="7" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O71" s="6" t="inlineStr"/>
-      <c r="P71" s="6" t="inlineStr">
-        <is>
-          <t>Leadership Business Review 2026-07-30 25:18-26:17</t>
-        </is>
-      </c>
-      <c r="Q71" s="6" t="inlineStr">
-        <is>
-          <t>Alvin owns the overall framework; Nicole runs it. Monthly trend review so recurring issues (the pump issue was the worked example) can drive packaging or formula decisions. Target: implemented by end of Q3.</t>
+      <c r="N71" s="7" t="inlineStr"/>
+      <c r="O71" s="7" t="inlineStr"/>
+      <c r="P71" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="Q71" s="7" t="inlineStr"/>
+      <c r="R71" s="6" t="inlineStr"/>
+      <c r="S71" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T71" s="6" t="inlineStr">
+        <is>
+          <t>Ironclad Finance closes the books and produces the reporting; Dan Bender is the contact. Reporting accountability sits with the President.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Product Development</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Document control: specifications, dielines, artwork versions, BOMs, landed-cost integrity</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr"/>
-      <c r="D72" s="7" t="inlineStr"/>
-      <c r="E72" s="8" t="inlineStr">
+          <t>Annual budget and forecast consolidation</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr"/>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr"/>
+      <c r="K72" s="7" t="inlineStr"/>
+      <c r="L72" s="7" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+      <c r="N72" s="7" t="inlineStr"/>
+      <c r="O72" s="7" t="inlineStr"/>
+      <c r="P72" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr"/>
-      <c r="H72" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-      <c r="I72" s="7" t="inlineStr"/>
-      <c r="J72" s="7" t="inlineStr"/>
-      <c r="K72" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L72" s="7" t="inlineStr"/>
-      <c r="M72" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N72" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="O72" s="6" t="inlineStr">
-        <is>
-          <t>Product Development Specialist</t>
-        </is>
-      </c>
-      <c r="P72" s="6" t="inlineStr">
-        <is>
-          <t>SharePoint: Sweet July Skin - Product Development Specialist - Job Description.docx</t>
-        </is>
-      </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>Documentation quality is Nicole's gate. The PD Specialist JD names document control as a core responsibility, so this row transitions on hire.</t>
+      <c r="Q72" s="7" t="inlineStr"/>
+      <c r="R72" s="6" t="inlineStr"/>
+      <c r="S72" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T72" s="6" t="inlineStr">
+        <is>
+          <t>President answers for the budget. Operations and Consumer Strategy feed the operating and channel assumptions.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Operations &amp; Supply Chain</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Production scheduling with manufacturing partners</t>
+          <t>Inventory valuation and cost of goods</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr"/>
-      <c r="D73" s="7" t="inlineStr"/>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E73" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -4462,11 +4885,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
       <c r="J73" s="7" t="inlineStr"/>
@@ -4478,204 +4897,184 @@
           <t>C</t>
         </is>
       </c>
-      <c r="O73" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="P73" s="6" t="inlineStr">
-        <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Leadership Business Review 2026-07-30 35:18</t>
-        </is>
-      </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>Named in the Ops Specialist JD under Planning &amp; Special Projects. Today Alvin coordinates KDC scheduling directly. A and R both AB until the seat is filled.</t>
+      <c r="O73" s="7" t="inlineStr"/>
+      <c r="P73" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="Q73" s="7" t="inlineStr"/>
+      <c r="R73" s="6" t="inlineStr"/>
+      <c r="S73" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners); .claude/skills/inventory-manager/SKILL.md:18</t>
+        </is>
+      </c>
+      <c r="T73" s="6" t="inlineStr">
+        <is>
+          <t>Cost side, so accountability sits with Operations - it flows out of purchasing, receiving and the inventory ledger. Ironclad carries it into the books.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Channel operations and promo setup across DTC, UBM and Amazon</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr"/>
+          <t>Hiring the Operations Specialist and the PD Project Manager Specialist</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F74" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="G74" s="7" t="inlineStr"/>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J74" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I74" s="7" t="inlineStr"/>
+      <c r="J74" s="7" t="inlineStr"/>
       <c r="K74" s="7" t="inlineStr"/>
       <c r="L74" s="7" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="7" t="inlineStr"/>
-      <c r="O74" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="P74" s="6" t="inlineStr">
-        <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
-        </is>
-      </c>
-      <c r="Q74" s="6" t="inlineStr">
-        <is>
-          <t>Named in the Ops Specialist JD under Order Management &amp; Channel Operations. Nicole holds the channel relationship.</t>
+      <c r="O74" s="7" t="inlineStr"/>
+      <c r="P74" s="7" t="inlineStr"/>
+      <c r="Q74" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R74" s="6" t="inlineStr"/>
+      <c r="S74" s="6" t="inlineStr">
+        <is>
+          <t>decisions/log.md:52,58; context/priorities.md:3; Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T74" s="6" t="inlineStr">
+        <is>
+          <t>Both new roles report to Nicole. Decision owner recorded as Alvin, with Nicole on the two new roles once filled. Priority 1 of 2 this quarter. Calm HR runs the recruiting process once the RACI clears Danielle.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Proactive reships and fulfillment-issue resolution</t>
+          <t>Tool procurement, vendor renewals and shared-folder admin</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr"/>
       <c r="D75" s="7" t="inlineStr"/>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr">
+      <c r="E75" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr"/>
       <c r="H75" s="7" t="inlineStr"/>
       <c r="I75" s="7" t="inlineStr"/>
       <c r="J75" s="7" t="inlineStr"/>
       <c r="K75" s="7" t="inlineStr"/>
-      <c r="L75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M75" s="7" t="inlineStr"/>
       <c r="N75" s="7" t="inlineStr"/>
-      <c r="O75" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="P75" s="6" t="inlineStr">
-        <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
-        </is>
-      </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>JD wording: resolve fulfillment issues "before a customer has to follow up." Sits inside Nicole's interim OC3PL coverage. A and R both NI.</t>
+      <c r="O75" s="7" t="inlineStr"/>
+      <c r="P75" s="7" t="inlineStr"/>
+      <c r="Q75" s="7" t="inlineStr"/>
+      <c r="R75" s="6" t="inlineStr"/>
+      <c r="S75" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:50; .claude/skills/sjs-comp-intel/references/sequencing-plan.md:12</t>
+        </is>
+      </c>
+      <c r="T75" s="6" t="inlineStr">
+        <is>
+          <t>Ex-Ops-Coordinator scope. Alvin carries it directly until the Operations Specialist starts. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Operational special projects: labels, PR seeding, sampling</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>Employee onboarding, offboarding and access deprovisioning</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
+      <c r="E76" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr"/>
       <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J76" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K76" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I76" s="7" t="inlineStr"/>
+      <c r="J76" s="7" t="inlineStr"/>
+      <c r="K76" s="7" t="inlineStr"/>
       <c r="L76" s="7" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
       <c r="N76" s="7" t="inlineStr"/>
-      <c r="O76" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="P76" s="6" t="inlineStr">
-        <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="Q76" s="6" t="inlineStr">
-        <is>
-          <t>Named in the Ops Specialist JD, and in the email as making sure product is where it needs to be for launches, promos, PR seeding and sampling. Danielle consulted - PR seeding and sampling are brand-facing.</t>
+      <c r="O76" s="7" t="inlineStr"/>
+      <c r="P76" s="7" t="inlineStr"/>
+      <c r="Q76" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R76" s="6" t="inlineStr"/>
+      <c r="S76" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:48-56; Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T76" s="6" t="inlineStr">
+        <is>
+          <t>Calm HR is the PEO and co-employer and runs the process; Alvin is the liaison and answers for it. Danielle consulted. No longer an unowned function - the departed-role-holder checklist in the PD role-map remains the internal system-side counterpart.</t>
         </is>
       </c>
     </row>
@@ -4718,13 +5117,16 @@
       <c r="L77" s="7" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
       <c r="N77" s="7" t="inlineStr"/>
-      <c r="O77" s="6" t="inlineStr"/>
-      <c r="P77" s="6" t="inlineStr">
+      <c r="O77" s="7" t="inlineStr"/>
+      <c r="P77" s="7" t="inlineStr"/>
+      <c r="Q77" s="7" t="inlineStr"/>
+      <c r="R77" s="6" t="inlineStr"/>
+      <c r="S77" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 52:48-53:17; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
         </is>
       </c>
-      <c r="Q77" s="6" t="inlineStr">
+      <c r="T77" s="6" t="inlineStr">
         <is>
           <t>Prioritized first. Danielle: "we're going to prioritize the operations... Specialist." Reports to Nicole. Target in place before Q4. Salary band $72-90K.</t>
         </is>
@@ -4769,13 +5171,16 @@
       <c r="L78" s="7" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
       <c r="N78" s="7" t="inlineStr"/>
-      <c r="O78" s="6" t="inlineStr"/>
-      <c r="P78" s="6" t="inlineStr">
+      <c r="O78" s="7" t="inlineStr"/>
+      <c r="P78" s="7" t="inlineStr"/>
+      <c r="Q78" s="7" t="inlineStr"/>
+      <c r="R78" s="6" t="inlineStr"/>
+      <c r="S78" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 53:17-57:10; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
         </is>
       </c>
-      <c r="Q78" s="6" t="inlineStr">
+      <c r="T78" s="6" t="inlineStr">
         <is>
           <t>Phased in after the Ops Specialist. Danielle scopes it as "air traffic control, holding people accountable" rather than strategy or ideation, and is adding trend-forecasting language to the JD. Reports to Nicole. Salary band $75-95K.</t>
         </is>
@@ -4816,13 +5221,16 @@
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
       <c r="N79" s="7" t="inlineStr"/>
-      <c r="O79" s="6" t="inlineStr"/>
-      <c r="P79" s="6" t="inlineStr">
+      <c r="O79" s="7" t="inlineStr"/>
+      <c r="P79" s="7" t="inlineStr"/>
+      <c r="Q79" s="7" t="inlineStr"/>
+      <c r="R79" s="6" t="inlineStr"/>
+      <c r="S79" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
         </is>
       </c>
-      <c r="Q79" s="6" t="inlineStr">
+      <c r="T79" s="6" t="inlineStr">
         <is>
           <t>Danielle's condition on the hire: clean up the system first so the role can function. Nicole's action item from the review.</t>
         </is>
@@ -4831,15 +5239,19 @@
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>RACI and role framework across Operations and PD</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr"/>
+          <t>Employee handbook and HR policy</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -4850,9 +5262,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F80" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr"/>
@@ -4863,460 +5275,521 @@
       <c r="L80" s="7" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
       <c r="N80" s="7" t="inlineStr"/>
-      <c r="O80" s="6" t="inlineStr"/>
-      <c r="P80" s="6" t="inlineStr">
-        <is>
-          <t>Leadership Business Review 2026-07-30 52:12-52:39</t>
-        </is>
-      </c>
-      <c r="Q80" s="6" t="inlineStr">
-        <is>
-          <t>Alvin owns the framework, built with Nicole in the builder session, then to Danielle for final review before it goes to Calm HR to start recruiting.</t>
+      <c r="O80" s="7" t="inlineStr"/>
+      <c r="P80" s="7" t="inlineStr"/>
+      <c r="Q80" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr"/>
+      <c r="S80" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T80" s="6" t="inlineStr">
+        <is>
+          <t>Calm HR drafts and maintains; Alvin is the liaison and answers for it; Danielle co-approves. Handbook is in flight as of 2026-07-30 and goes to legal review before implementation.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Campaign direction and seasonal brand moments</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
+          <t>Benefits administration and payroll processing</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J81" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K81" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I81" s="7" t="inlineStr"/>
+      <c r="J81" s="7" t="inlineStr"/>
+      <c r="K81" s="7" t="inlineStr"/>
       <c r="L81" s="7" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
       <c r="N81" s="7" t="inlineStr"/>
-      <c r="O81" s="6" t="inlineStr"/>
-      <c r="P81" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (role correction); .claude/skills/sjs-margin-walk-away/SKILL.md:93</t>
-        </is>
-      </c>
-      <c r="Q81" s="6" t="inlineStr">
-        <is>
-          <t>Added 2026-07-31. Campaign direction was absent from the matrix, which is why the President and the Founder had almost no Marketing presence. Danielle answers for it - Soraya reports to her and the margin sources already have her approving every repricing and channel call. Ayesha consulted on brand moments.</t>
+      <c r="O81" s="7" t="inlineStr"/>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R81" s="6" t="inlineStr"/>
+      <c r="S81" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T81" s="6" t="inlineStr">
+        <is>
+          <t>Calm HR administers as co-employer. Ironclad consulted where payroll hits the books.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>People &amp; Admin</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>Employment compliance and separations</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr"/>
+      <c r="G82" s="7" t="inlineStr"/>
+      <c r="H82" s="7" t="inlineStr"/>
+      <c r="I82" s="7" t="inlineStr"/>
+      <c r="J82" s="7" t="inlineStr"/>
+      <c r="K82" s="7" t="inlineStr"/>
+      <c r="L82" s="7" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+      <c r="N82" s="7" t="inlineStr"/>
+      <c r="O82" s="7" t="inlineStr"/>
+      <c r="P82" s="7" t="inlineStr"/>
+      <c r="Q82" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R82" s="6" t="inlineStr"/>
+      <c r="S82" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="T82" s="6" t="inlineStr">
+        <is>
+          <t>Calm HR runs the process with outside counsel where needed. Danielle co-approves every separation.</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="10" t="inlineStr">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>PLM schema, write path, audit log and Supabase wiki custody</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr"/>
+      <c r="D83" s="7" t="inlineStr"/>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr"/>
+      <c r="G83" s="7" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr"/>
+      <c r="J83" s="7" t="inlineStr"/>
+      <c r="K83" s="7" t="inlineStr"/>
+      <c r="L83" s="7" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O83" s="7" t="inlineStr"/>
+      <c r="P83" s="7" t="inlineStr"/>
+      <c r="Q83" s="7" t="inlineStr"/>
+      <c r="R83" s="6" t="inlineStr"/>
+      <c r="S83" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/plm-assistant/SKILL.md:292; decisions/wiki-layer-audit-2026-07-29.md:52</t>
+        </is>
+      </c>
+      <c r="T83" s="6" t="inlineStr">
+        <is>
+          <t>plm-assistant is the sole PLM writer and every write needs Operations sign-off. Job 0 wiki write-back has not fired since 2026-05-26. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>Landing hub publish and Netlify Function maintenance</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr"/>
+      <c r="D84" s="7" t="inlineStr"/>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr"/>
+      <c r="G84" s="7" t="inlineStr"/>
+      <c r="H84" s="7" t="inlineStr"/>
+      <c r="I84" s="7" t="inlineStr"/>
+      <c r="J84" s="7" t="inlineStr"/>
+      <c r="K84" s="7" t="inlineStr"/>
+      <c r="L84" s="7" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+      <c r="N84" s="7" t="inlineStr"/>
+      <c r="O84" s="7" t="inlineStr"/>
+      <c r="P84" s="7" t="inlineStr"/>
+      <c r="Q84" s="7" t="inlineStr"/>
+      <c r="R84" s="6" t="inlineStr"/>
+      <c r="S84" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/quality-status-reporter/SKILL.md:34-50; .claude/skills/quality-status-reporter/references/hub-integration.md:85</t>
+        </is>
+      </c>
+      <c r="T84" s="6" t="inlineStr">
+        <is>
+          <t>All hub writes go through the landing-hub-publish Function behind an Operator gate. Deploy is commit-and-push only, never Netlify CLI. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Asana project, section, custom-field and connector configuration</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr"/>
+      <c r="D85" s="7" t="inlineStr"/>
+      <c r="E85" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="inlineStr"/>
+      <c r="H85" s="7" t="inlineStr"/>
+      <c r="I85" s="7" t="inlineStr"/>
+      <c r="J85" s="7" t="inlineStr"/>
+      <c r="K85" s="7" t="inlineStr"/>
+      <c r="L85" s="7" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+      <c r="N85" s="7" t="inlineStr"/>
+      <c r="O85" s="7" t="inlineStr"/>
+      <c r="P85" s="7" t="inlineStr"/>
+      <c r="Q85" s="7" t="inlineStr"/>
+      <c r="R85" s="6" t="inlineStr"/>
+      <c r="S85" s="6" t="inlineStr">
+        <is>
+          <t>references/architecture/asana_task_contract.md:227; connections.md:5-13</t>
+        </is>
+      </c>
+      <c r="T85" s="6" t="inlineStr">
+        <is>
+          <t>An unresolvable role-holder is surfaced for Alvin to decide, not dropped. Seven tool domains registered; iMessage still not connected. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>Skill suite authorship, audit and versioning</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr"/>
+      <c r="D86" s="7" t="inlineStr"/>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F86" s="7" t="inlineStr"/>
+      <c r="G86" s="7" t="inlineStr"/>
+      <c r="H86" s="7" t="inlineStr"/>
+      <c r="I86" s="7" t="inlineStr"/>
+      <c r="J86" s="7" t="inlineStr"/>
+      <c r="K86" s="7" t="inlineStr"/>
+      <c r="L86" s="7" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+      <c r="N86" s="7" t="inlineStr"/>
+      <c r="O86" s="7" t="inlineStr"/>
+      <c r="P86" s="7" t="inlineStr"/>
+      <c r="Q86" s="7" t="inlineStr"/>
+      <c r="R86" s="6" t="inlineStr"/>
+      <c r="S86" s="6" t="inlineStr">
+        <is>
+          <t>decisions/skills-architecture-tracker.md:4; decisions/log.md:31,45</t>
+        </is>
+      </c>
+      <c r="T86" s="6" t="inlineStr">
+        <is>
+          <t>Owner recorded as Alvin Belt across the architecture decisions. Priority 2 of 2 this quarter. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>The 23 scheduled Routines and their HITL gates</t>
+        </is>
+      </c>
+      <c r="C87" s="7" t="inlineStr"/>
+      <c r="D87" s="7" t="inlineStr"/>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F87" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="7" t="inlineStr"/>
+      <c r="J87" s="7" t="inlineStr"/>
+      <c r="K87" s="7" t="inlineStr"/>
+      <c r="L87" s="7" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+      <c r="N87" s="7" t="inlineStr"/>
+      <c r="O87" s="7" t="inlineStr"/>
+      <c r="P87" s="7" t="inlineStr"/>
+      <c r="Q87" s="7" t="inlineStr"/>
+      <c r="R87" s="6" t="inlineStr"/>
+      <c r="S87" s="6" t="inlineStr">
+        <is>
+          <t>scheduled-prompts/weekly-pd-update.md:91; scheduled-prompts/sjs-purchasing-monthly-rollup-and-snapshot.md:79</t>
+        </is>
+      </c>
+      <c r="T87" s="6" t="inlineStr">
+        <is>
+          <t>Nothing commits until Alvin says go. Same pattern across all 23 Routines, including the ones that fire unattended on a schedule. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>RACI and role framework across Operations and PD</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr"/>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E88" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F88" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="inlineStr"/>
+      <c r="H88" s="7" t="inlineStr"/>
+      <c r="I88" s="7" t="inlineStr"/>
+      <c r="J88" s="7" t="inlineStr"/>
+      <c r="K88" s="7" t="inlineStr"/>
+      <c r="L88" s="7" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+      <c r="N88" s="7" t="inlineStr"/>
+      <c r="O88" s="7" t="inlineStr"/>
+      <c r="P88" s="7" t="inlineStr"/>
+      <c r="Q88" s="7" t="inlineStr"/>
+      <c r="R88" s="6" t="inlineStr"/>
+      <c r="S88" s="6" t="inlineStr">
+        <is>
+          <t>Leadership Business Review 2026-07-30 52:12-52:39</t>
+        </is>
+      </c>
+      <c r="T88" s="6" t="inlineStr">
+        <is>
+          <t>Alvin owns the framework, built with Nicole in the builder session, then to Danielle for final review before it goes to Calm HR to start recruiting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="11" t="n"/>
-      <c r="B84" s="12" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="11" t="n"/>
+      <c r="B91" s="12" t="inlineStr">
         <is>
           <t>A = answers for the outcome (exactly one per row)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="13" t="n"/>
-      <c r="B85" s="12" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="13" t="n"/>
+      <c r="B92" s="12" t="inlineStr">
         <is>
           <t>R = does the work (exactly one per row)</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="11" t="n"/>
-      <c r="B86" s="12" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="11" t="n"/>
+      <c r="B93" s="12" t="inlineStr">
         <is>
           <t>A/R = the same person holds both, so the row has no second pair of eyes</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="B87" s="12" t="inlineStr">
+    <row r="94">
+      <c r="B94" s="12" t="inlineStr">
         <is>
           <t>C = consulted before the decision</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" s="12" t="inlineStr">
+    <row r="95">
+      <c r="B95" s="12" t="inlineStr">
         <is>
           <t>I = informed after it</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="B89" s="12" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="12" t="inlineStr">
         <is>
           <t>-&gt; = the open seat that absorbs R on hire. Open seats never hold A or R.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="10" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
         <is>
           <t>Positions</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="14" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B92" s="14" t="inlineStr">
+      <c r="B99" s="14" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="C92" s="14" t="inlineStr">
+      <c r="C99" s="14" t="inlineStr">
         <is>
           <t>Holder</t>
         </is>
       </c>
-      <c r="D92" s="14" t="inlineStr">
+      <c r="D99" s="14" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E92" s="14" t="inlineStr">
+      <c r="E99" s="14" t="inlineStr">
         <is>
           <t>A count</t>
         </is>
       </c>
-      <c r="F92" s="14" t="inlineStr">
+      <c r="F99" s="14" t="inlineStr">
         <is>
           <t>R count</t>
         </is>
       </c>
-      <c r="G92" s="14" t="inlineStr">
+      <c r="G99" s="14" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H92" s="14" t="inlineStr">
+      <c r="H99" s="14" t="inlineStr">
         <is>
           <t>Hands off</t>
         </is>
       </c>
-      <c r="I92" s="14" t="inlineStr">
+      <c r="I99" s="14" t="inlineStr">
         <is>
           <t>Absorbs</t>
         </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="12" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>Owner / Founder</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>Ayesha Curry</t>
-        </is>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H93" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="12" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="B94" s="12" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="C94" s="12" t="inlineStr">
-        <is>
-          <t>Danielle Iturbe</t>
-        </is>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="12" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="B95" s="12" t="inlineStr">
-        <is>
-          <t>VP of Operations</t>
-        </is>
-      </c>
-      <c r="C95" s="12" t="inlineStr">
-        <is>
-          <t>Alvin Belt</t>
-        </is>
-      </c>
-      <c r="D95" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>39</v>
-      </c>
-      <c r="F95" s="15" t="n">
-        <v>56</v>
-      </c>
-      <c r="G95" s="15" t="n">
-        <v>31</v>
-      </c>
-      <c r="H95" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="I95" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="12" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>Nicole Iturbe</t>
-        </is>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>21</v>
-      </c>
-      <c r="F96" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="G96" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H96" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I96" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="12" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="B97" s="12" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="inlineStr">
-        <is>
-          <t>Open seat</t>
-        </is>
-      </c>
-      <c r="D97" s="16" t="inlineStr">
-        <is>
-          <t>recruiting</t>
-        </is>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G97" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="15" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="12" t="inlineStr">
-        <is>
-          <t>PDS</t>
-        </is>
-      </c>
-      <c r="B98" s="12" t="inlineStr">
-        <is>
-          <t>Product Development Specialist</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="inlineStr">
-        <is>
-          <t>Open seat</t>
-        </is>
-      </c>
-      <c r="D98" s="16" t="inlineStr">
-        <is>
-          <t>phased</t>
-        </is>
-      </c>
-      <c r="E98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="15" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="12" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>Marketing Manager</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="inlineStr">
-        <is>
-          <t>Soraya Salgadoe</t>
-        </is>
-      </c>
-      <c r="D99" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G99" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H99" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="B100" s="12" t="inlineStr">
         <is>
-          <t>Social Media Coordinator</t>
+          <t>Owner / Founder</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>Kate Le</t>
+          <t>Ayesha Curry</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -5328,10 +5801,10 @@
         <v>1</v>
       </c>
       <c r="F100" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H100" s="15" t="n">
         <v>0</v>
@@ -5343,32 +5816,32 @@
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>Creative Director</t>
+          <t>President</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Erin Hover</t>
+          <t>Danielle Iturbe</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>contractor</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E101" s="15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F101" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G101" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" s="15" t="n">
         <v>0</v>
@@ -5380,17 +5853,17 @@
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="B102" s="12" t="inlineStr">
         <is>
-          <t>Creative / Design Coordinator</t>
+          <t>VP of Operations</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>Ivy Tan</t>
+          <t>Alvin Belt</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -5399,16 +5872,16 @@
         </is>
       </c>
       <c r="E102" s="15" t="n">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F102" s="15" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="G102" s="15" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H102" s="15" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I102" s="15" t="n">
         <v>0</v>
@@ -5417,35 +5890,35 @@
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t>Packaging Engineer</t>
+          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Jan Haeck</t>
+          <t>Nicole Iturbe</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>contractor</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E103" s="15" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F103" s="15" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G103" s="15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H103" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I103" s="15" t="n">
         <v>0</v>
@@ -5454,54 +5927,424 @@
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="B104" s="12" t="inlineStr">
         <is>
-          <t>PD / R&amp;D contractor, Milinyc</t>
+          <t>Operations Specialist</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>Perrine Calvet</t>
-        </is>
-      </c>
-      <c r="D104" s="12" t="inlineStr">
-        <is>
-          <t>contractor</t>
+          <t>Open seat</t>
+        </is>
+      </c>
+      <c r="D104" s="16" t="inlineStr">
+        <is>
+          <t>recruiting</t>
         </is>
       </c>
       <c r="E104" s="15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F104" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G104" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I104" s="15" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>PDS</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>Open seat</t>
+        </is>
+      </c>
+      <c r="D105" s="16" t="inlineStr">
+        <is>
+          <t>phased</t>
+        </is>
+      </c>
+      <c r="E105" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="F105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="15" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="14" t="inlineStr">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>Soraya Salgadoe</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G106" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Social Media Coordinator</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>Kate Le</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Creative Director</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>Erin Hover</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>contractor</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F108" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Creative / Design Coordinator</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>Ivy Tan</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>Packaging Engineer</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>Jan Haeck</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>contractor</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G110" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>PD / R&amp;D contractor, Milinyc</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>Perrine Calvet</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>contractor</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>External regulatory partner</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>Pedrero Regulatory</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>IF</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Outsourced finance (Dan Bender)</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>Ironclad Finance</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>PEO and co-employer</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>Calm HR</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="14" t="inlineStr">
         <is>
           <t>Source of truth</t>
         </is>
       </c>
-      <c r="B106" s="17" t="inlineStr">
+      <c r="B116" s="17" t="inlineStr">
         <is>
           <t>Rows citing a path are relative to the SJ-OS repo. Rows citing the 30 July leadership review, the 27 July email to Danielle, or a job description come from those documents directly. Rows marked INFERRED in Notes have no owner named in any source; A defaults to Alvin Belt because the work falls there in practice.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q81"/>
+  <autoFilter ref="A2:T88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5512,7 +6355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -5594,15 +6437,15 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>COUNTIF(RACI!C3:C81,"A")+COUNTIF(RACI!C3:C81,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C88,"A")+COUNTIF(RACI!C3:C88,"A/R")</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>COUNTIF(RACI!C3:C81,"R")+COUNTIF(RACI!C3:C81,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C88,"R")+COUNTIF(RACI!C3:C88,"A/R")</f>
         <v/>
       </c>
       <c r="D6" s="15">
-        <f>COUNTIF(RACI!C3:C81,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C88,"A/R")</f>
         <v/>
       </c>
       <c r="E6" s="15" t="n">
@@ -5627,15 +6470,15 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>COUNTIF(RACI!D3:D81,"A")+COUNTIF(RACI!D3:D81,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D88,"A")+COUNTIF(RACI!D3:D88,"A/R")</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>COUNTIF(RACI!D3:D81,"R")+COUNTIF(RACI!D3:D81,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D88,"R")+COUNTIF(RACI!D3:D88,"A/R")</f>
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>COUNTIF(RACI!D3:D81,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D88,"A/R")</f>
         <v/>
       </c>
       <c r="E7" s="15" t="n">
@@ -5660,15 +6503,15 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>COUNTIF(RACI!E3:E81,"A")+COUNTIF(RACI!E3:E81,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E88,"A")+COUNTIF(RACI!E3:E88,"A/R")</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>COUNTIF(RACI!E3:E81,"R")+COUNTIF(RACI!E3:E81,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E88,"R")+COUNTIF(RACI!E3:E88,"A/R")</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>COUNTIF(RACI!E3:E81,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E88,"A/R")</f>
         <v/>
       </c>
       <c r="E8" s="15" t="n">
@@ -5693,15 +6536,15 @@
         </is>
       </c>
       <c r="B9" s="15">
-        <f>COUNTIF(RACI!F3:F81,"A")+COUNTIF(RACI!F3:F81,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F88,"A")+COUNTIF(RACI!F3:F88,"A/R")</f>
         <v/>
       </c>
       <c r="C9" s="15">
-        <f>COUNTIF(RACI!F3:F81,"R")+COUNTIF(RACI!F3:F81,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F88,"R")+COUNTIF(RACI!F3:F88,"A/R")</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>COUNTIF(RACI!F3:F81,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F88,"A/R")</f>
         <v/>
       </c>
       <c r="E9" s="15" t="n">
@@ -5726,15 +6569,15 @@
         </is>
       </c>
       <c r="B10" s="15">
-        <f>COUNTIF(RACI!G3:G81,"A")+COUNTIF(RACI!G3:G81,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G88,"A")+COUNTIF(RACI!G3:G88,"A/R")</f>
         <v/>
       </c>
       <c r="C10" s="15">
-        <f>COUNTIF(RACI!G3:G81,"R")+COUNTIF(RACI!G3:G81,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G88,"R")+COUNTIF(RACI!G3:G88,"A/R")</f>
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>COUNTIF(RACI!G3:G81,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G88,"A/R")</f>
         <v/>
       </c>
       <c r="E10" s="15" t="n">
@@ -5759,15 +6602,15 @@
         </is>
       </c>
       <c r="B11" s="15">
-        <f>COUNTIF(RACI!H3:H81,"A")+COUNTIF(RACI!H3:H81,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H88,"A")+COUNTIF(RACI!H3:H88,"A/R")</f>
         <v/>
       </c>
       <c r="C11" s="15">
-        <f>COUNTIF(RACI!H3:H81,"R")+COUNTIF(RACI!H3:H81,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H88,"R")+COUNTIF(RACI!H3:H88,"A/R")</f>
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>COUNTIF(RACI!H3:H81,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H88,"A/R")</f>
         <v/>
       </c>
       <c r="E11" s="15" t="n">
@@ -5792,15 +6635,15 @@
         </is>
       </c>
       <c r="B12" s="15">
-        <f>COUNTIF(RACI!I3:I81,"A")+COUNTIF(RACI!I3:I81,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I88,"A")+COUNTIF(RACI!I3:I88,"A/R")</f>
         <v/>
       </c>
       <c r="C12" s="15">
-        <f>COUNTIF(RACI!I3:I81,"R")+COUNTIF(RACI!I3:I81,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I88,"R")+COUNTIF(RACI!I3:I88,"A/R")</f>
         <v/>
       </c>
       <c r="D12" s="15">
-        <f>COUNTIF(RACI!I3:I81,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I88,"A/R")</f>
         <v/>
       </c>
       <c r="E12" s="15" t="n">
@@ -5825,15 +6668,15 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>COUNTIF(RACI!J3:J81,"A")+COUNTIF(RACI!J3:J81,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J88,"A")+COUNTIF(RACI!J3:J88,"A/R")</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>COUNTIF(RACI!J3:J81,"R")+COUNTIF(RACI!J3:J81,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J88,"R")+COUNTIF(RACI!J3:J88,"A/R")</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>COUNTIF(RACI!J3:J81,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J88,"A/R")</f>
         <v/>
       </c>
       <c r="E13" s="15" t="n">
@@ -5858,15 +6701,15 @@
         </is>
       </c>
       <c r="B14" s="15">
-        <f>COUNTIF(RACI!K3:K81,"A")+COUNTIF(RACI!K3:K81,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K88,"A")+COUNTIF(RACI!K3:K88,"A/R")</f>
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>COUNTIF(RACI!K3:K81,"R")+COUNTIF(RACI!K3:K81,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K88,"R")+COUNTIF(RACI!K3:K88,"A/R")</f>
         <v/>
       </c>
       <c r="D14" s="15">
-        <f>COUNTIF(RACI!K3:K81,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K88,"A/R")</f>
         <v/>
       </c>
       <c r="E14" s="15" t="n">
@@ -5891,15 +6734,15 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF(RACI!L3:L81,"A")+COUNTIF(RACI!L3:L81,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L88,"A")+COUNTIF(RACI!L3:L88,"A/R")</f>
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>COUNTIF(RACI!L3:L81,"R")+COUNTIF(RACI!L3:L81,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L88,"R")+COUNTIF(RACI!L3:L88,"A/R")</f>
         <v/>
       </c>
       <c r="D15" s="15">
-        <f>COUNTIF(RACI!L3:L81,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L88,"A/R")</f>
         <v/>
       </c>
       <c r="E15" s="15" t="n">
@@ -5924,15 +6767,15 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF(RACI!M3:M81,"A")+COUNTIF(RACI!M3:M81,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M88,"A")+COUNTIF(RACI!M3:M88,"A/R")</f>
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>COUNTIF(RACI!M3:M81,"R")+COUNTIF(RACI!M3:M81,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M88,"R")+COUNTIF(RACI!M3:M88,"A/R")</f>
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>COUNTIF(RACI!M3:M81,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M88,"A/R")</f>
         <v/>
       </c>
       <c r="E16" s="15" t="n">
@@ -5957,15 +6800,15 @@
         </is>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF(RACI!N3:N81,"A")+COUNTIF(RACI!N3:N81,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N88,"A")+COUNTIF(RACI!N3:N88,"A/R")</f>
         <v/>
       </c>
       <c r="C17" s="15">
-        <f>COUNTIF(RACI!N3:N81,"R")+COUNTIF(RACI!N3:N81,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N88,"R")+COUNTIF(RACI!N3:N88,"A/R")</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>COUNTIF(RACI!N3:N81,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N88,"A/R")</f>
         <v/>
       </c>
       <c r="E17" s="15" t="n">
@@ -5984,228 +6827,367 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>PR — External regulatory partner (Pedrero Regulatory)</t>
+        </is>
+      </c>
+      <c r="B18" s="15">
+        <f>COUNTIF(RACI!O3:O88,"A")+COUNTIF(RACI!O3:O88,"A/R")</f>
+        <v/>
+      </c>
+      <c r="C18" s="15">
+        <f>COUNTIF(RACI!O3:O88,"R")+COUNTIF(RACI!O3:O88,"A/R")</f>
+        <v/>
+      </c>
+      <c r="D18" s="15">
+        <f>COUNTIF(RACI!O3:O88,"A/R")</f>
+        <v/>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="15">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="H18" s="15">
+        <f>C18-E18+F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>IF — Outsourced finance (Dan Bender) (Ironclad Finance)</t>
+        </is>
+      </c>
+      <c r="B19" s="15">
+        <f>COUNTIF(RACI!P3:P88,"A")+COUNTIF(RACI!P3:P88,"A/R")</f>
+        <v/>
+      </c>
+      <c r="C19" s="15">
+        <f>COUNTIF(RACI!P3:P88,"R")+COUNTIF(RACI!P3:P88,"A/R")</f>
+        <v/>
+      </c>
+      <c r="D19" s="15">
+        <f>COUNTIF(RACI!P3:P88,"A/R")</f>
+        <v/>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="15">
+        <f>B19</f>
+        <v/>
+      </c>
+      <c r="H19" s="15">
+        <f>C19-E19+F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>CH — PEO and co-employer (Calm HR)</t>
+        </is>
+      </c>
+      <c r="B20" s="15">
+        <f>COUNTIF(RACI!Q3:Q88,"A")+COUNTIF(RACI!Q3:Q88,"A/R")</f>
+        <v/>
+      </c>
+      <c r="C20" s="15">
+        <f>COUNTIF(RACI!Q3:Q88,"R")+COUNTIF(RACI!Q3:Q88,"A/R")</f>
+        <v/>
+      </c>
+      <c r="D20" s="15">
+        <f>COUNTIF(RACI!Q3:Q88,"A/R")</f>
+        <v/>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="15">
+        <f>B20</f>
+        <v/>
+      </c>
+      <c r="H20" s="15">
+        <f>C20-E20+F20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Total activities</t>
         </is>
       </c>
-      <c r="B18" s="21">
-        <f>COUNTA(RACI!B3:B81)</f>
+      <c r="B21" s="21">
+        <f>COUNTA(RACI!B3:B88)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>"A after" and "R after" project the book once both specialist seats are filled. Hands off counts rows where this position does the work today and an incoming seat takes it. Absorbs counts rows arriving on hire.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>Quality now has a gate, and it is not the VP</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-    </row>
-    <row r="24" ht="78" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+    </row>
+    <row r="27" ht="78" customHeight="1">
+      <c r="A27" s="17" t="inlineStr">
         <is>
           <t>The 30 July leadership review moved the quality function onto Nicole. Verbatim from the recording: "Nicole taking the primary focus on the quality management side of things with quality control... anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check... Even with each function having or being the primary owner, we'll still have that quality gate." That shows up as 10 of the 13 Quality rows accountable to Nicole, against 2 for Alvin and 1 for Perrine. Her total book of accountability goes from 8 rows to 21.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>Perrine moves to technical guidance</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-    </row>
-    <row r="28" ht="117" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+    </row>
+    <row r="31" ht="117" customHeight="1">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>She keeps A on the 7 rows where the judgment is genuinely formulation - formula stage-gate, compatibility and stability and RIPT and PET, in-market stability testing, reformulation, PD-linked receipt, and the two margin rows that turn on formulation cost. Packaging development moved to Erin Hover as the lead technical authority on packaging and artwork. She moves to consulted on everything process-shaped: NCR and CAPA lifecycle, batch hold and release, vendor quality flags, lab finding classification, SOP ratification. Danielle's framing in the review was that there were things the team had assumed Perrine would manage or organize that she is not, and that leadership can pull the plug even when she has submitted an approval. Splitting technical judgment from process ownership is what that means in practice.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="23" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>Three contractors hold accountability, and two of them hold it alone</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr"/>
-    </row>
-    <row r="32" ht="104" customHeight="1">
-      <c r="A32" s="17" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+    </row>
+    <row r="35" ht="104" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>Erin Hover is the lead technical authority on packaging and artwork and is accountable for 4 rows - creative direction, packaging development, artwork execution, and the label artwork archive. She is also a contractor, and on creative direction she is both A and R with no internal counterpart. Jan Haeck, who executes under her, is a contractor too, so the whole packaging and artwork chain runs through people outside the company. Perrine Calvet is the third, accountable for 7 formulation rows. Between them that is 11 of 79 activities where nobody on staff can check the work or continue it. Neither specialist job description covers creative or formulation authority, so the two hires do not close this.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr"/>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>Where the President and the Founder sit</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr"/>
-    </row>
-    <row r="36" ht="104" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39" ht="104" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Danielle Iturbe is accountable for 4 rows - direction-changing PD decisions, the margin walk-away call, brand guideline custody, and campaign direction - and is consulted on 13 more. She now appears on all 9 Marketing rows and all 3 Creative rows, which she did not before. Campaign direction was missing from the matrix entirely; adding it is what gave the President somewhere to sit in Marketing rather than only receiving finished work. Ayesha Curry keeps sole accountability for brand-line moves and is consulted on 6 rows where the brand carries her name - brand guideline custody, creative direction, campaign direction, claim substantiation, retailer attestations, and packaging. Informed on the rest.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>Alvin owns the framework, and still does most of the work</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-    </row>
-    <row r="40" ht="65" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Accountable for 39 of 79 activities and doing the work on 56. The framework rows are deliberate - quality management system, SOP framework, this RACI, the skill suite, the 23 scheduled Routines. The problem is not the A column. It is that 31 rows have him as both A and R, and that he does the work on 11 of the 12 Operations rows and 5 of the 8 Product Development rows. He holds the gates and does the work behind them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+    </row>
+    <row r="43" ht="65" customHeight="1">
+      <c r="A43" s="17" t="inlineStr">
+        <is>
+          <t>Accountable for 44 of 86 activities and doing the work on 55. The framework rows are deliberate - quality management system, SOP framework, this RACI, the skill suite, the 23 scheduled Routines. The problem is not the A column. It is that 31 rows have him as both A and R, and that he does the work on 11 of the 12 Operations rows and 5 of the 8 Product Development rows. He holds the gates and does the work behind them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>What the two seats actually move</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-    </row>
-    <row r="44" ht="65" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+    </row>
+    <row r="47" ht="65" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
         <is>
           <t>32 rows transition on hire: 16 to the Operations Specialist and 16 to the Product Development Specialist. 29 of those come off Alvin, 3 off Nicole. His R book drops from 55 to 26. Rows with no second pair of eyes drop from 42 to 25 across the whole matrix. Both seats report to Nicole, which is the point Danielle made in the review - moving day-to-day management off the VP seat is the succession outcome the system is being built for.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>Ops first is the right order, and the matrix says why</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-    </row>
-    <row r="48" ht="91" customHeight="1">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51" ht="91" customHeight="1">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Alvin does the work on 11 of 12 Operations rows. The Operations Specialist job description covers almost exactly that list: daily order operations and the third-party logistics relationship, channel operations across the direct store and Ulta Beauty Marketplace and Amazon, inventory reconciliation and FEFO and out-of-stock signals, receiving, purchase-to-pay, freight and customs and broker relationships, routing-guide and advance-ship-notice compliance, sales and operations planning support, production scheduling, and the label and seeding and sampling projects. That is a defined function sitting on one person today.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="23" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>The PD seat is the one that closes the quality loop</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-    </row>
-    <row r="52" ht="104" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+    </row>
+    <row r="55" ht="104" customHeight="1">
+      <c r="A55" s="17" t="inlineStr">
         <is>
           <t>Its job description names running the quality system outright - corrective and preventive actions, non-conformances, complaint intake and trend monitoring, lab results, supplier quality flags, batch lifecycle including stability and hold-release, and the quality dashboard - plus pre-launch ingredient and label review, claim substantiation, retailer compliance responses and the registration tracker, and document control across specifications and dielines and artwork versions and bills of materials. Until it is filled, Nicole gates quality and Alvin executes it. That works, and it is the reason the gate is worth having now rather than after the hire, but it is two people covering a role that was written as one.</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="23" t="inlineStr">
-        <is>
-          <t>What is still unowned</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-    </row>
-    <row r="56" ht="65" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
-        <is>
-          <t>Three rows have no documented owner anywhere and default to Alvin as an inference rather than a sourced claim: accounts payable and bookkeeping and payroll, employee onboarding and offboarding and access deprovisioning, and Shopify revenue ownership. Finance appears in the operating documentation only as an email-sender category and a briefing heading. The function closest to the top line is the least specified.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr"/>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="23" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>Three functions run entirely outside the company</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+    </row>
+    <row r="59" ht="91" customHeight="1">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>Regulatory goes through Pedrero Regulatory, Finance through Ironclad (Dan Bender), HR through Calm HR as PEO and co-employer. Adding them resolved two of the three unowned functions - Finance and HR were only unowned because the partners were missing from the matrix, not because nobody was doing the work. Between the three partner organisations and the three contractors on packaging, creative and formulation, six external parties hold the execution of six functions. For a team of nine that is a reasonable shape. What it means is that continuity rests on six engagements rather than on employment, and each is a renewal decision rather than a retention one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>Regulatory is the odd one, and it cuts both ways</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+    </row>
+    <row r="63" ht="78" customHeight="1">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Pedrero is consulted on 11 rows and responsible for none. That is not an undervaluation - our own procedures make them consult-only with no Asana access and no internal authority, and Amy Pedrero holds the binding regulatory calls. The consequence is a split bottleneck: Pedrero forms every regulatory opinion, and Alvin performs every regulatory action, because the Operator and Reg Lead gates are both his and Pedrero cannot act inside our systems. Either the Reg Lead gate gets an alternate or Pedrero's remit widens; the current shape means regulatory work stops if either side is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="23" t="inlineStr">
+        <is>
+          <t>One row is still unowned</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+    </row>
+    <row r="67" ht="52" customHeight="1">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>Shopify revenue and channel position. It is registered as the revenue connection and named as the primary direct-to-consumer revenue track, but no process assigns ownership or an approval step, so it shows Alvin by inference rather than by source. The function closest to the top line is the least specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="23" t="inlineStr">
         <is>
           <t>Single points of failure that remain after both hires</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr"/>
-    </row>
-    <row r="60" ht="91" customHeight="1">
-      <c r="A60" s="17" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71" ht="91" customHeight="1">
+      <c r="A71" s="17" t="inlineStr">
         <is>
           <t>Perrine is an external contractor holding A on 8 rows with no internal counterpart, and one of those - compatibility and stability and RIPT and PET - has her as both A and R. Nobody inside AC Brands can check that work or continue it. Alvin is the other: the Operator gate has no alternate anywhere in the suite, and all 23 scheduled Routines stop at a human approval only he can clear. Succession is documented exactly once in the entire system, for competitive intelligence. Nothing comparable exists for the quality gate, the technical advisor, or the framework owner. That gap costs hours to close, not headcount, and it is the one I would fix first.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr"/>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6218,7 +7200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6340,7 +7322,7 @@
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>Unowned function</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -6350,32 +7332,32 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Accounts payable, bookkeeping and payroll have no owner, approver or gate anywhere.</t>
+          <t>Finance is owned. Ironclad Finance (Dan Bender) runs AP, bookkeeping, payroll, month-end close and reporting. Danielle accountable for reporting, Alvin for cost.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Spend is captured through vendor invoices behind five approval gates, but nothing downstream of it is owned. The cost ledger has a custodian; the books do not.</t>
+          <t>Was flagged as unowned before the external partners were added to the matrix. The remaining question is not ownership but coverage: no internal finance headcount exists, so continuity depends on the Ironclad engagement.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Fractional controller or bookkeeper; Alvin approves</t>
+          <t>No action - confirm engagement terms and renewal date</t>
         </is>
       </c>
       <c r="F4" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>outlook-plm-bridge/SKILL.md:368; ayesha-weekly-briefing/SKILL.md:9</t>
+          <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>Unowned function</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -6385,25 +7367,25 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Employee onboarding, offboarding and access deprovisioning has no named owner.</t>
+          <t>HR is owned. Calm HR is the PEO and co-employer and runs handbook, policy, benefits, payroll admin, onboarding, offboarding and separations. Alvin accountable as liaison, Danielle co-approves.</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>The only documented process is a departed-role-holder checklist written after a stale role record broke task assignment. Reactive, and not owned.</t>
+          <t>Was flagged as unowned before the external partners were added. What remains internal is the system-side half of offboarding - Asana reassignment, wiki contact state, access deprovisioning - which the departed-role-holder checklist covers and which is still on Alvin.</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Operations Specialist once hired; Alvin interim</t>
+          <t>No action on HR; system-side offboarding to the Ops Specialist</t>
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>asana-pd-manager/references/role-map.md:48-56</t>
+          <t>Alvin, 2026-07-31 (external partners); asana-pd-manager/references/role-map.md:48-56</t>
         </is>
       </c>
     </row>
@@ -6480,27 +7462,27 @@
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>Single point of failure</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>All functions</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Erin Hover is a contractor and the lead technical authority on packaging and artwork, accountable for 4 rows with no internal backup. On creative direction she is both A and R.</t>
+          <t>Three whole functions run through external partners: Regulatory (Pedrero), Finance (Ironclad), HR (Calm HR). Plus three contractors on packaging, creative and formulation.</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Jan Haeck executes under her and is also a contractor, so the entire packaging and artwork chain sits outside the company. Neither approved job description covers creative authority.</t>
+          <t>Six external parties hold the execution of Regulatory, Finance, HR, packaging, creative and formulation. Not a fault - it is how a team of nine covers this surface - but it means continuity rests on six engagements rather than on employment, and every one of them is a renewal decision.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Name an internal creative counterpart, or scope it into a future role</t>
+          <t>Confirm engagement terms and renewal dates for all six</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
@@ -6508,7 +7490,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (role correction); asana-pd-manager/references/role-map.md:22-23</t>
+          <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
     </row>
@@ -6520,22 +7502,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Perrine holds A on 7 formulation rows as a contractor, with no named backup.</t>
+          <t>Pedrero forms every regulatory opinion but holds no accountability, and Alvin performs every regulatory action. Consulted on 11 rows, responsible for none.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Reduced from 11 by moving process gates to Nicole and packaging to Erin, which is real progress. What remains is genuinely formulation and genuinely single-threaded.</t>
+          <t>Our own procedures make Pedrero consult-only with no Asana access and no internal authority, so the binding external call and the internal execution are both bottlenecks in different ways: their opinion gates the work, and only Alvin can act on it.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Name a backup technical reviewer</t>
+          <t>Give the Reg Lead gate an alternate, or widen Pedrero's remit</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
@@ -6543,7 +7525,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 25:18-25:50; quality-manager/references/role-map.md:14</t>
+          <t>regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
     </row>
@@ -6555,22 +7537,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Compliance</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Operator and Reg Lead are the same person, so two gates designed to be independent fire against one approver.</t>
+          <t>Erin Hover is a contractor and the lead technical authority on packaging and artwork, accountable for 4 rows with no internal backup. On creative direction she is both A and R.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>On ingredient-list packets, retailer attestations and FDA filings the second approval adds an audit entry but no second judgment. The 15-day reporting clock has no alternate.</t>
+          <t>Jan Haeck executes under her and is also a contractor, so the entire packaging and artwork chain sits outside the company. Neither approved job description covers creative authority.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Split Reg Lead, or route the second gate to Pedrero</t>
+          <t>Name an internal creative counterpart, or scope it into a future role</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
@@ -6578,7 +7560,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>regulatory-manager/references/role-map.md:14; adverse-event-and-recall-reporter/SKILL.md:108</t>
+          <t>Alvin, 2026-07-31 (role correction); asana-pd-manager/references/role-map.md:22-23</t>
         </is>
       </c>
     </row>
@@ -6590,22 +7572,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>All 23 scheduled Routines stop at a human approval only Alvin can clear.</t>
+          <t>Perrine holds A on 7 formulation rows as a contractor, with no named backup.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Automation that fires unattended still needs him to commit. A week away queues the work rather than pausing it, and the Routines keep firing.</t>
+          <t>Reduced from 11 by moving process gates to Nicole and packaging to Erin, which is real progress. What remains is genuinely formulation and genuinely single-threaded.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Delegate publish gates to the new specialists</t>
+          <t>Name a backup technical reviewer</t>
         </is>
       </c>
       <c r="F11" s="7" t="n">
@@ -6613,7 +7595,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>scheduled-prompts/weekly-pd-update.md:91</t>
+          <t>Leadership Business Review 2026-07-30 25:18-25:50; quality-manager/references/role-map.md:14</t>
         </is>
       </c>
     </row>
@@ -6625,100 +7607,100 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>All functions</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Succession is documented once in the whole system - Soraya as interim CI lead if Nicole is out.</t>
+          <t>Operator and Reg Lead are the same person, so two gates designed to be independent fire against one approver.</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Nothing comparable exists for the quality gate, the technical advisor, the Reg Lead or Creative. The repo's stated purpose is succession.</t>
+          <t>On ingredient-list packets, retailer attestations and FDA filings the second approval adds an audit entry but no second judgment. The 15-day reporting clock has no alternate.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Alvin to write per-role backups into each role-map</t>
+          <t>Split Reg Lead, or route the second gate to Pedrero</t>
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>sjs-comp-intel/references/team-ownership.md:95; decisions/log.md:41</t>
+          <t>regulatory-manager/references/role-map.md:14; adverse-event-and-recall-reporter/SKILL.md:108</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>Open item</t>
+          <t>Single point of failure</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Quality management system and monthly trend review not yet stood up. Target end of Q3.</t>
+          <t>All 23 scheduled Routines stop at a human approval only Alvin can clear.</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>The gate is assigned but the reporting cadence behind it is not built. Without trend data a recurring issue like the pump defect cannot drive a packaging decision.</t>
+          <t>Automation that fires unattended still needs him to commit. A week away queues the work rather than pausing it, and the Routines keep firing.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Alvin owns framework, Nicole runs it</t>
+          <t>Delegate publish gates to the new specialists</t>
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 26:02-26:17</t>
+          <t>scheduled-prompts/weekly-pd-update.md:91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>Open item</t>
+          <t>Single point of failure</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Operations &amp; Supply Chain</t>
+          <t>All functions</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>22 tasks from the retired coordinator seat sit unassigned in an archived holding project; 4 overdue.</t>
+          <t>Succession is documented once in the whole system - Soraya as interim CI lead if Nicole is out.</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>An unassigned task drops out of every per-person sweep and goes stale silently. Concrete cost of running the interim split for a quarter.</t>
+          <t>Nothing comparable exists for the quality gate, the technical advisor, the Reg Lead or Creative. The repo's stated purpose is succession.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Alvin to reassign under the interim split</t>
+          <t>Alvin to write per-role backups into each role-map</t>
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>decisions/log.md:60</t>
+          <t>sjs-comp-intel/references/team-ownership.md:95; decisions/log.md:41</t>
         </is>
       </c>
     </row>
@@ -6730,30 +7712,30 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>SOP cleanup and operational prep before onboarding is not done.</t>
+          <t>Quality management system and monthly trend review not yet stood up. Target end of Q3.</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Danielle's stated condition on the hire: clean up the system first so the role can function. Onboarding into the current state recreates the too-broad seat.</t>
+          <t>The gate is assigned but the reporting cadence behind it is not built. Without trend data a recurring issue like the pump defect cannot drive a packaging decision.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Alvin and Nicole, before the Ops seat starts</t>
+          <t>Alvin owns framework, Nicole runs it</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
+          <t>Leadership Business Review 2026-07-30 26:02-26:17</t>
         </is>
       </c>
     </row>
@@ -6765,30 +7747,30 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Operations &amp; Supply Chain</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Wiki write-back has not fired since 2026-05-26. 123 of 133 pages are untouched seed content.</t>
+          <t>22 tasks from the retired coordinator seat sit unassigned in an archived holding project; 4 overdue.</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>The bridges' runtime lexicon reads stale seed data, degrading vendor, contact and product recognition on every sweep.</t>
+          <t>An unassigned task drops out of every per-person sweep and goes stale silently. Concrete cost of running the interim split for a quarter.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Alvin; part of the skills-architecture backlog</t>
+          <t>Alvin to reassign under the interim split</t>
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>decisions/wiki-layer-audit-2026-07-29.md:52; decisions/log.md:75</t>
+          <t>decisions/log.md:60</t>
         </is>
       </c>
     </row>
@@ -6800,82 +7782,152 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Nine SOPs and forms are 29 days overdue on annual review.</t>
+          <t>SOP cleanup and operational prep before onboarding is not done.</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Review dates were null so the annual sweep had nothing to fire on. Dates are restored; the reviews are not done, and each needs sign-off.</t>
+          <t>Danielle's stated condition on the hire: clean up the system first so the role can function. Onboarding into the current state recreates the too-broad seat.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Nicole approves as the quality gate; Alvin stages</t>
+          <t>Alvin and Nicole, before the Ops seat starts</t>
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>decisions/log.md:69</t>
+          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
+          <t>Open item</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Wiki write-back has not fired since 2026-05-26. 123 of 133 pages are untouched seed content.</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>The bridges' runtime lexicon reads stale seed data, degrading vendor, contact and product recognition on every sweep.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Alvin; part of the skills-architecture backlog</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>decisions/wiki-layer-audit-2026-07-29.md:52; decisions/log.md:75</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>Open item</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Nine SOPs and forms are 29 days overdue on annual review.</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Review dates were null so the annual sweep had nothing to fire on. Dates are restored; the reviews are not done, and each needs sign-off.</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Nicole approves as the quality gate; Alvin stages</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>decisions/log.md:69</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="inlineStr">
+        <is>
           <t>Uncovered brand</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>All functions</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>Sweet July, the lifestyle brand, has no coverage. The suite is Sweet July Skin plus company-wide work.</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>Merch, licensing and non-skincare retail are run somewhere, but nothing documents who owns them. They cannot be put on a RACI from these sources.</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Danielle to confirm scope for the next version</t>
         </is>
       </c>
-      <c r="F18" s="7" t="n">
+      <c r="F20" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>references/architecture/system_map.md:3; context/about-business.md:3</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Hours per month</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
         <is>
           <t>Rough estimates. Open-seat rows are full-time-equivalent load, not incremental. Zero means the gap is a structural exposure rather than unbilled hours.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G18"/>
+  <autoFilter ref="A1:G20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/deliverables/AC-Brands-RACI.xlsx
+++ b/deliverables/AC-Brands-RACI.xlsx
@@ -12,8 +12,8 @@
     <sheet name="Gaps" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$T$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$V$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T116"/>
+  <dimension ref="A1:V131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -581,9 +581,11 @@
     <col width="6" customWidth="1" min="15" max="15"/>
     <col width="6" customWidth="1" min="16" max="16"/>
     <col width="6" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
-    <col width="58" customWidth="1" min="19" max="19"/>
-    <col width="82" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="18" max="18"/>
+    <col width="6" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="20" max="20"/>
+    <col width="58" customWidth="1" min="21" max="21"/>
+    <col width="82" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -672,17 +674,27 @@
           <t>CH</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Transitions to</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -766,9 +778,19 @@
           <t>Calm HR</t>
         </is>
       </c>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>WITHIN</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>Teknologics</t>
+        </is>
+      </c>
       <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr"/>
+      <c r="V2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -816,17 +838,19 @@
       <c r="O3" s="7" t="inlineStr"/>
       <c r="P3" s="7" t="inlineStr"/>
       <c r="Q3" s="7" t="inlineStr"/>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="7" t="inlineStr"/>
+      <c r="S3" s="7" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="U3" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/asana-pd-manager/SKILL.md:60</t>
         </is>
       </c>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="V3" s="6" t="inlineStr">
         <is>
           <t>PD Lead holds technical sign-off on formula stage moves. Operator confirms every move (Rule 1 preview); reversals get a stronger intent check.</t>
         </is>
@@ -870,13 +894,15 @@
       <c r="O4" s="7" t="inlineStr"/>
       <c r="P4" s="7" t="inlineStr"/>
       <c r="Q4" s="7" t="inlineStr"/>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="6" t="inlineStr">
+      <c r="R4" s="7" t="inlineStr"/>
+      <c r="S4" s="7" t="inlineStr"/>
+      <c r="T4" s="6" t="inlineStr"/>
+      <c r="U4" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:16</t>
         </is>
       </c>
-      <c r="T4" s="6" t="inlineStr">
+      <c r="V4" s="6" t="inlineStr">
         <is>
           <t>PD Lead owns the technical call outright. A and R the same person, and PC is an external contractor.</t>
         </is>
@@ -936,13 +962,15 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="6" t="inlineStr">
+      <c r="R5" s="7" t="inlineStr"/>
+      <c r="S5" s="7" t="inlineStr"/>
+      <c r="T5" s="6" t="inlineStr"/>
+      <c r="U5" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:16,23; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
-      <c r="T5" s="6" t="inlineStr">
+      <c r="V5" s="6" t="inlineStr">
         <is>
           <t>PD Lead owns packaging dev calls; Jan executes packaging and artwork under Erin. Both are contractors. Erin is the lead technical authority on packaging and artwork and answers for the outcome; Jan executes under her. Perrine consults where formula contact or compatibility is in play. Both Erin and Jan are contractors.</t>
         </is>
@@ -994,13 +1022,15 @@
       <c r="O6" s="7" t="inlineStr"/>
       <c r="P6" s="7" t="inlineStr"/>
       <c r="Q6" s="7" t="inlineStr"/>
-      <c r="R6" s="6" t="inlineStr"/>
-      <c r="S6" s="6" t="inlineStr">
+      <c r="R6" s="7" t="inlineStr"/>
+      <c r="S6" s="7" t="inlineStr"/>
+      <c r="T6" s="6" t="inlineStr"/>
+      <c r="U6" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:17,18</t>
         </is>
       </c>
-      <c r="T6" s="6" t="inlineStr">
+      <c r="V6" s="6" t="inlineStr">
         <is>
           <t>President approves. PD Consult is final-line approver alongside the President.</t>
         </is>
@@ -1048,13 +1078,15 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="6" t="inlineStr"/>
-      <c r="S7" s="6" t="inlineStr">
+      <c r="R7" s="7" t="inlineStr"/>
+      <c r="S7" s="7" t="inlineStr"/>
+      <c r="T7" s="6" t="inlineStr"/>
+      <c r="U7" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:19</t>
         </is>
       </c>
-      <c r="T7" s="6" t="inlineStr">
+      <c r="V7" s="6" t="inlineStr">
         <is>
           <t>Founder gate. Ayesha receives weekly PD signal through the Friday briefing.</t>
         </is>
@@ -1106,17 +1138,19 @@
       <c r="O8" s="7" t="inlineStr"/>
       <c r="P8" s="7" t="inlineStr"/>
       <c r="Q8" s="7" t="inlineStr"/>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="7" t="inlineStr"/>
+      <c r="S8" s="7" t="inlineStr"/>
+      <c r="T8" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S8" s="6" t="inlineStr">
+      <c r="U8" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/fireflies-asana-bridge/SKILL.md:287; .claude/skills/outlook-plm-bridge/SKILL.md:191; .claude/skills/sjs-status-reporter/SKILL.md:331,385</t>
         </is>
       </c>
-      <c r="T8" s="6" t="inlineStr">
+      <c r="V8" s="6" t="inlineStr">
         <is>
           <t>Alvin is the named approver on Flow D formula-approval decisions and classifies every meeting item. Covers the three PD hub dashboards. A and R both AB.</t>
         </is>
@@ -1164,13 +1198,15 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="6" t="inlineStr"/>
-      <c r="S9" s="6" t="inlineStr">
+      <c r="R9" s="7" t="inlineStr"/>
+      <c r="S9" s="7" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/capa-coordinator/SKILL.md:85</t>
         </is>
       </c>
-      <c r="T9" s="6" t="inlineStr">
+      <c r="V9" s="6" t="inlineStr">
         <is>
           <t>PD Lead is cross-flagged for any PD-side reformulation. Reformulation handoff rides the root-cause approval - no separate gate.</t>
         </is>
@@ -1226,17 +1262,19 @@
       <c r="O10" s="7" t="inlineStr"/>
       <c r="P10" s="7" t="inlineStr"/>
       <c r="Q10" s="7" t="inlineStr"/>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="7" t="inlineStr"/>
+      <c r="S10" s="7" t="inlineStr"/>
+      <c r="T10" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S10" s="6" t="inlineStr">
+      <c r="U10" s="6" t="inlineStr">
         <is>
           <t>SharePoint: Sweet July Skin - Product Development Specialist - Job Description.docx</t>
         </is>
       </c>
-      <c r="T10" s="6" t="inlineStr">
+      <c r="V10" s="6" t="inlineStr">
         <is>
           <t>Documentation quality is Nicole's gate. The PD Specialist JD names document control as a core responsibility, so this row transitions on hire.</t>
         </is>
@@ -1288,17 +1326,19 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="7" t="inlineStr"/>
+      <c r="S11" s="7" t="inlineStr"/>
+      <c r="T11" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
+      <c r="U11" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:42,46,75,154,158</t>
         </is>
       </c>
-      <c r="T11" s="6" t="inlineStr">
+      <c r="V11" s="6" t="inlineStr">
         <is>
           <t>PLM vendor record created only after Operations approves at 2D. First-contact routing varies by vendor_type (SKILL.md:50-56) but the approval gate does not. A and R both AB.</t>
         </is>
@@ -1342,17 +1382,19 @@
       <c r="O12" s="7" t="inlineStr"/>
       <c r="P12" s="7" t="inlineStr"/>
       <c r="Q12" s="7" t="inlineStr"/>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="7" t="inlineStr"/>
+      <c r="S12" s="7" t="inlineStr"/>
+      <c r="T12" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S12" s="6" t="inlineStr">
+      <c r="U12" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:108,116,140,248</t>
         </is>
       </c>
-      <c r="T12" s="6" t="inlineStr">
+      <c r="V12" s="6" t="inlineStr">
         <is>
           <t>Six sub-flows from draft to close, plus Job 10 discrepancy investigation. Every gate is Operations. A and R both AB.</t>
         </is>
@@ -1396,13 +1438,15 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="6" t="inlineStr"/>
-      <c r="S13" s="6" t="inlineStr">
+      <c r="R13" s="7" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr"/>
+      <c r="T13" s="6" t="inlineStr"/>
+      <c r="U13" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:130</t>
         </is>
       </c>
-      <c r="T13" s="6" t="inlineStr">
+      <c r="V13" s="6" t="inlineStr">
         <is>
           <t>PD owns the close on PD-linked receipts; Purchasing carries the receipt signal only. The one Ops row where accountability sits off the VP seat.</t>
         </is>
@@ -1446,17 +1490,19 @@
       <c r="O14" s="7" t="inlineStr"/>
       <c r="P14" s="7" t="inlineStr"/>
       <c r="Q14" s="7" t="inlineStr"/>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="7" t="inlineStr"/>
+      <c r="S14" s="7" t="inlineStr"/>
+      <c r="T14" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S14" s="6" t="inlineStr">
+      <c r="U14" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/inventory-manager/SKILL.md:68</t>
         </is>
       </c>
-      <c r="T14" s="6" t="inlineStr">
+      <c r="V14" s="6" t="inlineStr">
         <is>
           <t>Operations decides the correction direction, usually trusting Logiwa as physical reality. A and R both AB.</t>
         </is>
@@ -1512,17 +1558,19 @@
         </is>
       </c>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="7" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr"/>
+      <c r="T15" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S15" s="6" t="inlineStr">
+      <c r="U15" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:234,235,238; Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="T15" s="6" t="inlineStr">
+      <c r="V15" s="6" t="inlineStr">
         <is>
           <t>Operator confirms cost_category, regulatory_driver, linked SKU and multi-home routing before any PLM write, and approves the dispute branch. A and R both AB. Ironclad consulted - classified invoices land in their ledger.</t>
         </is>
@@ -1570,17 +1618,19 @@
       <c r="O16" s="7" t="inlineStr"/>
       <c r="P16" s="7" t="inlineStr"/>
       <c r="Q16" s="7" t="inlineStr"/>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr"/>
+      <c r="T16" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S16" s="6" t="inlineStr">
+      <c r="U16" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/inventory-manager/SKILL.md:18,52,60</t>
         </is>
       </c>
-      <c r="T16" s="6" t="inlineStr">
+      <c r="V16" s="6" t="inlineStr">
         <is>
           <t>Ex-Ops-Coordinator scope. Alvin took inventory under the 2026-07-17 interim split. A and R both AB.</t>
         </is>
@@ -1624,17 +1674,19 @@
       <c r="O17" s="7" t="inlineStr"/>
       <c r="P17" s="7" t="inlineStr"/>
       <c r="Q17" s="7" t="inlineStr"/>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="7" t="inlineStr"/>
+      <c r="S17" s="7" t="inlineStr"/>
+      <c r="T17" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S17" s="6" t="inlineStr">
+      <c r="U17" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/inventory-manager/SKILL.md:94</t>
         </is>
       </c>
-      <c r="T17" s="6" t="inlineStr">
+      <c r="V17" s="6" t="inlineStr">
         <is>
           <t>Operations approves. Near-expiry write-offs wait on the quality call first. A and R both AB.</t>
         </is>
@@ -1682,17 +1734,19 @@
       <c r="O18" s="7" t="inlineStr"/>
       <c r="P18" s="7" t="inlineStr"/>
       <c r="Q18" s="7" t="inlineStr"/>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr"/>
+      <c r="T18" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S18" s="6" t="inlineStr">
+      <c r="U18" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/supply-demand-planner/SKILL.md:30-52; .claude/skills/supply-demand-planner/references/plm-schema-additions.md:139</t>
         </is>
       </c>
-      <c r="T18" s="6" t="inlineStr">
+      <c r="V18" s="6" t="inlineStr">
         <is>
           <t>Operations approves; plm-assistant executes the SQL. Four intertwined jobs on one person. A and R both AB.</t>
         </is>
@@ -1736,17 +1790,19 @@
       <c r="O19" s="7" t="inlineStr"/>
       <c r="P19" s="7" t="inlineStr"/>
       <c r="Q19" s="7" t="inlineStr"/>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="7" t="inlineStr"/>
+      <c r="S19" s="7" t="inlineStr"/>
+      <c r="T19" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S19" s="6" t="inlineStr">
+      <c r="U19" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/logistics-manager/SKILL.md:59,186; .claude/skills/logistics-manager/forms/international-dtc-shipment.md:11</t>
         </is>
       </c>
-      <c r="T19" s="6" t="inlineStr">
+      <c r="V19" s="6" t="inlineStr">
         <is>
           <t>Nothing created or updated until Operations signs off. Ex-Ops-Coordinator logistics scope, now Alvin. HCT and Impress origin Asia so customs is routine. A and R both AB.</t>
         </is>
@@ -1790,17 +1846,19 @@
       <c r="O20" s="7" t="inlineStr"/>
       <c r="P20" s="7" t="inlineStr"/>
       <c r="Q20" s="7" t="inlineStr"/>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="7" t="inlineStr"/>
+      <c r="S20" s="7" t="inlineStr"/>
+      <c r="T20" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S20" s="6" t="inlineStr">
+      <c r="U20" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:123; .claude/skills/oc3pl-order-manager/SKILL.md:109,191</t>
         </is>
       </c>
-      <c r="T20" s="6" t="inlineStr">
+      <c r="V20" s="6" t="inlineStr">
         <is>
           <t>Ex-Ops-Coordinator scope. Nicole covers order management and OC3PL under the 2026-07-17 interim split. A and R both NI.</t>
         </is>
@@ -1844,17 +1902,19 @@
       <c r="O21" s="7" t="inlineStr"/>
       <c r="P21" s="7" t="inlineStr"/>
       <c r="Q21" s="7" t="inlineStr"/>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr"/>
+      <c r="T21" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S21" s="6" t="inlineStr">
+      <c r="U21" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/oc3pl-order-manager/SKILL.md:201; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
         </is>
       </c>
-      <c r="T21" s="6" t="inlineStr">
+      <c r="V21" s="6" t="inlineStr">
         <is>
           <t>Order-side holds sit with Nicole; SKU-level shortage routing belongs to inventory-manager, so Alvin does the work.</t>
         </is>
@@ -1902,17 +1962,19 @@
       <c r="O22" s="7" t="inlineStr"/>
       <c r="P22" s="7" t="inlineStr"/>
       <c r="Q22" s="7" t="inlineStr"/>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr"/>
+      <c r="T22" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S22" s="6" t="inlineStr">
+      <c r="U22" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/logistics-manager/SKILL.md:80; .claude/skills/purchasing-manager/SKILL.md:55</t>
         </is>
       </c>
-      <c r="T22" s="6" t="inlineStr">
+      <c r="V22" s="6" t="inlineStr">
         <is>
           <t>Operations or Order Ops reviews. UBM launch June 2026 is the deadline driver on this lane.</t>
         </is>
@@ -1960,17 +2022,19 @@
       <c r="O23" s="7" t="inlineStr"/>
       <c r="P23" s="7" t="inlineStr"/>
       <c r="Q23" s="7" t="inlineStr"/>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr"/>
+      <c r="T23" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="S23" s="6" t="inlineStr">
+      <c r="U23" s="6" t="inlineStr">
         <is>
           <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Leadership Business Review 2026-07-30 35:18</t>
         </is>
       </c>
-      <c r="T23" s="6" t="inlineStr">
+      <c r="V23" s="6" t="inlineStr">
         <is>
           <t>Named in the Ops Specialist JD under Planning &amp; Special Projects. Today Alvin coordinates KDC scheduling directly. A and R both AB until the seat is filled.</t>
         </is>
@@ -2018,17 +2082,19 @@
       <c r="O24" s="7" t="inlineStr"/>
       <c r="P24" s="7" t="inlineStr"/>
       <c r="Q24" s="7" t="inlineStr"/>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="7" t="inlineStr"/>
+      <c r="S24" s="7" t="inlineStr"/>
+      <c r="T24" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S24" s="6" t="inlineStr">
+      <c r="U24" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/complaint-and-event-handler/SKILL.md:20,53</t>
         </is>
       </c>
-      <c r="T24" s="6" t="inlineStr">
+      <c r="V24" s="6" t="inlineStr">
         <is>
           <t>HITL on every write. Operator approves classification plus first response. A and R both AB. Gate moved to Nicole as the final quality check per Leadership Business Review 2026-07-30 25:18-26:01.</t>
         </is>
@@ -2076,17 +2142,19 @@
       <c r="O25" s="7" t="inlineStr"/>
       <c r="P25" s="7" t="inlineStr"/>
       <c r="Q25" s="7" t="inlineStr"/>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr"/>
+      <c r="T25" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S25" s="6" t="inlineStr">
+      <c r="U25" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-manager/references/role-map.md:15</t>
         </is>
       </c>
-      <c r="T25" s="6" t="inlineStr">
+      <c r="V25" s="6" t="inlineStr">
         <is>
           <t>Voice of Customer holds gates on complaint classification and complaint-driven escalations. Nicole already held this gate; monthly trend review formalizes it per Leadership Business Review 2026-07-30 26:02-26:17.</t>
         </is>
@@ -2138,17 +2206,19 @@
       <c r="O26" s="7" t="inlineStr"/>
       <c r="P26" s="7" t="inlineStr"/>
       <c r="Q26" s="7" t="inlineStr"/>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="7" t="inlineStr"/>
+      <c r="S26" s="7" t="inlineStr"/>
+      <c r="T26" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S26" s="6" t="inlineStr">
+      <c r="U26" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/capa-coordinator/SKILL.md:54,136; .claude/skills/capa-coordinator/references/ncr-procedure.md:135; .claude/skills/capa-coordinator/references/skn-ops-001.md:64,102</t>
         </is>
       </c>
-      <c r="T26" s="6" t="inlineStr">
+      <c r="V26" s="6" t="inlineStr">
         <is>
           <t>Operator approves intake and both action plans; QA Lead approves conversion, root cause, verification, effectiveness and close. Six SOP phases, one external contractor on every technical gate. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults on technical root cause.</t>
         </is>
@@ -2196,17 +2266,19 @@
       <c r="O27" s="7" t="inlineStr"/>
       <c r="P27" s="7" t="inlineStr"/>
       <c r="Q27" s="7" t="inlineStr"/>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="7" t="inlineStr"/>
+      <c r="S27" s="7" t="inlineStr"/>
+      <c r="T27" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S27" s="6" t="inlineStr">
+      <c r="U27" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-lab-coordinator/SKILL.md:48,56</t>
         </is>
       </c>
-      <c r="T27" s="6" t="inlineStr">
+      <c r="V27" s="6" t="inlineStr">
         <is>
           <t>Operator approves intake and the single-versus-systemic classification. A and R both AB. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:35-25:50. Perrine consults on the technical call.</t>
         </is>
@@ -2254,17 +2326,19 @@
       <c r="O28" s="7" t="inlineStr"/>
       <c r="P28" s="7" t="inlineStr"/>
       <c r="Q28" s="7" t="inlineStr"/>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="7" t="inlineStr"/>
+      <c r="S28" s="7" t="inlineStr"/>
+      <c r="T28" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S28" s="6" t="inlineStr">
+      <c r="U28" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-lab-coordinator/SKILL.md:76; .claude/skills/quality-lab-coordinator/references/vendor-scorecard-signal.md:103</t>
         </is>
       </c>
-      <c r="T28" s="6" t="inlineStr">
+      <c r="V28" s="6" t="inlineStr">
         <is>
           <t>QA Lead approves any vendor flag and the scorecard band. Operator can stage but not commit. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults.</t>
         </is>
@@ -2316,17 +2390,19 @@
       <c r="O29" s="7" t="inlineStr"/>
       <c r="P29" s="7" t="inlineStr"/>
       <c r="Q29" s="7" t="inlineStr"/>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="7" t="inlineStr"/>
+      <c r="S29" s="7" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S29" s="6" t="inlineStr">
+      <c r="U29" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/batch-lifecycle-tracker/references/batch-lifecycle-procedure.md:208; .claude/skills/batch-lifecycle-tracker/SKILL.md:86</t>
         </is>
       </c>
-      <c r="T29" s="6" t="inlineStr">
+      <c r="V29" s="6" t="inlineStr">
         <is>
           <t>QA Lead approves every hold and every release. No exceptions at v5.4. Releases need a CAPA close or clean retest plus QA Lead judgment. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:35-26:01. Perrine consults on the technical basis.</t>
         </is>
@@ -2374,17 +2450,19 @@
       <c r="O30" s="7" t="inlineStr"/>
       <c r="P30" s="7" t="inlineStr"/>
       <c r="Q30" s="7" t="inlineStr"/>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="7" t="inlineStr"/>
+      <c r="S30" s="7" t="inlineStr"/>
+      <c r="T30" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S30" s="6" t="inlineStr">
+      <c r="U30" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
         </is>
       </c>
-      <c r="T30" s="6" t="inlineStr">
+      <c r="V30" s="6" t="inlineStr">
         <is>
           <t>Technical testing call stays with Perrine as the R&amp;D and quality technical advisor. Operator approves schedule edits. Per Leadership Business Review 2026-07-30 25:18-25:35 the process gate moved to Nicole but the technical judgment did not.</t>
         </is>
@@ -2432,17 +2510,19 @@
       <c r="O31" s="7" t="inlineStr"/>
       <c r="P31" s="7" t="inlineStr"/>
       <c r="Q31" s="7" t="inlineStr"/>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="7" t="inlineStr"/>
+      <c r="S31" s="7" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S31" s="6" t="inlineStr">
+      <c r="U31" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
         </is>
       </c>
-      <c r="T31" s="6" t="inlineStr">
+      <c r="V31" s="6" t="inlineStr">
         <is>
           <t>Disposition is a quality gate, so it moves to Nicole. Posts back to inventory before any write-off.</t>
         </is>
@@ -2498,13 +2578,15 @@
       </c>
       <c r="P32" s="7" t="inlineStr"/>
       <c r="Q32" s="7" t="inlineStr"/>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="6" t="inlineStr">
+      <c r="R32" s="7" t="inlineStr"/>
+      <c r="S32" s="7" t="inlineStr"/>
+      <c r="T32" s="6" t="inlineStr"/>
+      <c r="U32" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/complaint-and-event-handler/SKILL.md:85,89,95; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T32" s="6" t="inlineStr">
+      <c r="V32" s="6" t="inlineStr">
         <is>
           <t>The strictest gate in the suite: explicit approval at every step, §4.A through §4.F each a separate gate. Operator decides severity, team and whether external reporting is needed. A and R both AB. Stays with Alvin as Reg Lead — legal and agency exposure. Nicole consults. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -2548,13 +2630,15 @@
       <c r="O33" s="7" t="inlineStr"/>
       <c r="P33" s="7" t="inlineStr"/>
       <c r="Q33" s="7" t="inlineStr"/>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="6" t="inlineStr">
+      <c r="R33" s="7" t="inlineStr"/>
+      <c r="S33" s="7" t="inlineStr"/>
+      <c r="T33" s="6" t="inlineStr"/>
+      <c r="U33" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-manager/SKILL.md:66,135; .claude/skills/quality-manager/references/sop-catalog.md:120; .claude/skills/quality-manager/references/qos-thresholds.md:52</t>
         </is>
       </c>
-      <c r="T33" s="6" t="inlineStr">
+      <c r="V33" s="6" t="inlineStr">
         <is>
           <t>QA Lead approves every ratification, review outcome, cross-cutting task and QoS threshold task. SOP §7 names a QA Manager for this; that seat is vacant and Perrine is filling it. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:18-25:50.</t>
         </is>
@@ -2602,17 +2686,19 @@
       <c r="O34" s="7" t="inlineStr"/>
       <c r="P34" s="7" t="inlineStr"/>
       <c r="Q34" s="7" t="inlineStr"/>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="7" t="inlineStr"/>
+      <c r="S34" s="7" t="inlineStr"/>
+      <c r="T34" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S34" s="6" t="inlineStr">
+      <c r="U34" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-status-reporter/SKILL.md:78</t>
         </is>
       </c>
-      <c r="T34" s="6" t="inlineStr">
+      <c r="V34" s="6" t="inlineStr">
         <is>
           <t>Operator approves the commit before push. Never commit without confirmation. A and R both AB. Nicole gates the content; Alvin retains the publish mechanics. Per Leadership Business Review 2026-07-30 26:02-26:17.</t>
         </is>
@@ -2672,13 +2758,15 @@
       <c r="O35" s="7" t="inlineStr"/>
       <c r="P35" s="7" t="inlineStr"/>
       <c r="Q35" s="7" t="inlineStr"/>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="6" t="inlineStr">
+      <c r="R35" s="7" t="inlineStr"/>
+      <c r="S35" s="7" t="inlineStr"/>
+      <c r="T35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 25:35-26:01</t>
         </is>
       </c>
-      <c r="T35" s="6" t="inlineStr">
+      <c r="V35" s="6" t="inlineStr">
         <is>
           <t>The new cross-function gate. Verbatim: "anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check... Even with each function having or being the primary owner, we'll still have that quality gate." A and R both NI.</t>
         </is>
@@ -2726,13 +2814,15 @@
       <c r="O36" s="7" t="inlineStr"/>
       <c r="P36" s="7" t="inlineStr"/>
       <c r="Q36" s="7" t="inlineStr"/>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="6" t="inlineStr">
+      <c r="R36" s="7" t="inlineStr"/>
+      <c r="S36" s="7" t="inlineStr"/>
+      <c r="T36" s="6" t="inlineStr"/>
+      <c r="U36" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 25:18-26:17</t>
         </is>
       </c>
-      <c r="T36" s="6" t="inlineStr">
+      <c r="V36" s="6" t="inlineStr">
         <is>
           <t>Alvin owns the overall framework; Nicole runs it. Monthly trend review so recurring issues (the pump issue was the worked example) can drive packaging or formula decisions. Target: implemented by end of Q3.</t>
         </is>
@@ -2784,17 +2874,19 @@
       </c>
       <c r="P37" s="7" t="inlineStr"/>
       <c r="Q37" s="7" t="inlineStr"/>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="7" t="inlineStr"/>
+      <c r="S37" s="7" t="inlineStr"/>
+      <c r="T37" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S37" s="6" t="inlineStr">
+      <c r="U37" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:50; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:62; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T37" s="6" t="inlineStr">
+      <c r="V37" s="6" t="inlineStr">
         <is>
           <t>Operator approves intake. Reg Lead is the same person at v6.6, so the gate fires twice against one person. Pedrero holds the binding external call. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -2838,13 +2930,15 @@
       </c>
       <c r="P38" s="7" t="inlineStr"/>
       <c r="Q38" s="7" t="inlineStr"/>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="6" t="inlineStr">
+      <c r="R38" s="7" t="inlineStr"/>
+      <c r="S38" s="7" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
+      <c r="U38" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:60; .claude/skills/regulatory-manager/SKILL.md:140; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T38" s="6" t="inlineStr">
+      <c r="V38" s="6" t="inlineStr">
         <is>
           <t>Reg Lead approves every Pedrero send; Operator hits send manually. Both roles are Alvin. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -2908,17 +3002,19 @@
       </c>
       <c r="P39" s="7" t="inlineStr"/>
       <c r="Q39" s="7" t="inlineStr"/>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="7" t="inlineStr"/>
+      <c r="S39" s="7" t="inlineStr"/>
+      <c r="T39" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S39" s="6" t="inlineStr">
+      <c r="U39" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:97; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:29; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T39" s="6" t="inlineStr">
+      <c r="V39" s="6" t="inlineStr">
         <is>
           <t>Operator approves the path; Reg Lead approves the Pedrero stage. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off. A and R both AB. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off, so both are consulted rather than bypassed. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -2982,13 +3078,15 @@
       </c>
       <c r="P40" s="7" t="inlineStr"/>
       <c r="Q40" s="7" t="inlineStr"/>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="6" t="inlineStr">
+      <c r="R40" s="7" t="inlineStr"/>
+      <c r="S40" s="7" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+      <c r="U40" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:85; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:93; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T40" s="6" t="inlineStr">
+      <c r="V40" s="6" t="inlineStr">
         <is>
           <t>Operator approves each pass outcome; Reg Lead approves any archive entry. Creative produces the artwork under review. Erin answers for the artwork being right as lead technical authority. Alvin runs the IL cross-check and the label-law passes and holds the Reg Lead gate on archive entries, so the regulatory approval and the artwork authority are separate people. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3036,13 +3134,15 @@
       </c>
       <c r="P41" s="7" t="inlineStr"/>
       <c r="Q41" s="7" t="inlineStr"/>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="6" t="inlineStr">
+      <c r="R41" s="7" t="inlineStr"/>
+      <c r="S41" s="7" t="inlineStr"/>
+      <c r="T41" s="6" t="inlineStr"/>
+      <c r="U41" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:281; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T41" s="6" t="inlineStr">
+      <c r="V41" s="6" t="inlineStr">
         <is>
           <t>Reg Lead approves the QIL recovery ask to the prior manufacturer; PD Lead does the formulation work. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3102,17 +3202,19 @@
       </c>
       <c r="P42" s="7" t="inlineStr"/>
       <c r="Q42" s="7" t="inlineStr"/>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="7" t="inlineStr"/>
+      <c r="S42" s="7" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S42" s="6" t="inlineStr">
+      <c r="U42" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:105; .claude/skills/regulatory-manager/SKILL.md:122; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T42" s="6" t="inlineStr">
+      <c r="V42" s="6" t="inlineStr">
         <is>
           <t>Reg Lead approves the retailer submission after Pedrero approval. Voice of Customer consults where customer-perceived attributes matter. A and R both AB. Ayesha consulted - retailer clean-standard positioning is a brand claim. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3164,17 +3266,19 @@
       </c>
       <c r="P43" s="7" t="inlineStr"/>
       <c r="Q43" s="7" t="inlineStr"/>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="7" t="inlineStr"/>
+      <c r="S43" s="7" t="inlineStr"/>
+      <c r="T43" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="S43" s="6" t="inlineStr">
+      <c r="U43" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/regulatory-manager/SKILL.md:114,367; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T43" s="6" t="inlineStr">
+      <c r="V43" s="6" t="inlineStr">
         <is>
           <t>Operator approves the filing draft; Reg Lead approves every registration record write. Both roles are Alvin. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3230,13 +3334,15 @@
       </c>
       <c r="P44" s="7" t="inlineStr"/>
       <c r="Q44" s="7" t="inlineStr"/>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="6" t="inlineStr">
+      <c r="R44" s="7" t="inlineStr"/>
+      <c r="S44" s="7" t="inlineStr"/>
+      <c r="T44" s="6" t="inlineStr"/>
+      <c r="U44" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/adverse-event-and-recall-reporter/SKILL.md:65,108; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T44" s="6" t="inlineStr">
+      <c r="V44" s="6" t="inlineStr">
         <is>
           <t>Two distinct gates per filing - Pedrero send approval and agency submission approval - both held by Alvin. Statutory clock with no named backup. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3284,13 +3390,15 @@
       </c>
       <c r="P45" s="7" t="inlineStr"/>
       <c r="Q45" s="7" t="inlineStr"/>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" s="6" t="inlineStr">
+      <c r="R45" s="7" t="inlineStr"/>
+      <c r="S45" s="7" t="inlineStr"/>
+      <c r="T45" s="6" t="inlineStr"/>
+      <c r="U45" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/regulatory-manager/SKILL.md:60; .claude/skills/regulatory-status-reporter/SKILL.md:90; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="T45" s="6" t="inlineStr">
+      <c r="V45" s="6" t="inlineStr">
         <is>
           <t>Two gates per fan-out (Operator for the routing call, Reg Lead for task creation), both Alvin. Operator approves the dashboard commit before push. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3338,13 +3446,15 @@
       </c>
       <c r="P46" s="7" t="inlineStr"/>
       <c r="Q46" s="7" t="inlineStr"/>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="6" t="inlineStr">
+      <c r="R46" s="7" t="inlineStr"/>
+      <c r="S46" s="7" t="inlineStr"/>
+      <c r="T46" s="6" t="inlineStr"/>
+      <c r="U46" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/regulatory-manager/references/pedrero-contacts.md:50; Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="T46" s="6" t="inlineStr">
+      <c r="V46" s="6" t="inlineStr">
         <is>
           <t>The engagement letter governs scope, retainer, response windows and dispute resolution. Annual renewal. A and R both AB - the only person managing the regulatory partner relationship.</t>
         </is>
@@ -3388,15 +3498,17 @@
       <c r="O47" s="7" t="inlineStr"/>
       <c r="P47" s="7" t="inlineStr"/>
       <c r="Q47" s="7" t="inlineStr"/>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:55</t>
-        </is>
-      </c>
-      <c r="T47" s="6" t="inlineStr">
-        <is>
-          <t>First-contact owner for retailer, promotional_goods and accessories vendor types is the Sr. Director Consumer Strategy &amp; Ops. A and R both NI.</t>
+      <c r="R47" s="7" t="inlineStr"/>
+      <c r="S47" s="7" t="inlineStr"/>
+      <c r="T47" s="6" t="inlineStr"/>
+      <c r="U47" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/purchasing-manager/SKILL.md:55; acb-thelanding: data/links.json</t>
+        </is>
+      </c>
+      <c r="V47" s="6" t="inlineStr">
+        <is>
+          <t>First-contact owner for retailer, promotional_goods and accessories vendor types is the Sr. Director Consumer Strategy &amp; Ops. A and R both NI. Consistent with Nicole's all-channel accountability.</t>
         </is>
       </c>
     </row>
@@ -3442,27 +3554,29 @@
       <c r="O48" s="7" t="inlineStr"/>
       <c r="P48" s="7" t="inlineStr"/>
       <c r="Q48" s="7" t="inlineStr"/>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:55; .claude/skills/sjs-retail-intel/SKILL.md:52; .claude/skills/logistics-manager/SKILL.md:80</t>
-        </is>
-      </c>
-      <c r="T48" s="6" t="inlineStr">
-        <is>
-          <t>UBM launch June 2026. Nicole holds the channel relationship; Alvin runs the positioning and outbound work.</t>
+      <c r="R48" s="7" t="inlineStr"/>
+      <c r="S48" s="7" t="inlineStr"/>
+      <c r="T48" s="6" t="inlineStr"/>
+      <c r="U48" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/purchasing-manager/SKILL.md:55; .claude/skills/sjs-retail-intel/SKILL.md:52; .claude/skills/logistics-manager/SKILL.md:80; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V48" s="6" t="inlineStr">
+        <is>
+          <t>UBM launch June 2026. Nicole holds the channel relationship; Alvin runs the positioning and outbound work. Hub lists wholesale as "Owned by TBD" (links.json, Sales &amp; Commerce lead). Resolved to Nicole as part of all-channel accountability.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Retail &amp; Wholesale</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Quarterly competitive teardowns across the five comp brands</t>
+          <t>Wholesale pipeline and new retail partner development</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -3472,31 +3586,27 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="J49" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J49" s="7" t="inlineStr"/>
       <c r="K49" s="7" t="inlineStr"/>
       <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -3504,81 +3614,93 @@
       <c r="O49" s="7" t="inlineStr"/>
       <c r="P49" s="7" t="inlineStr"/>
       <c r="Q49" s="7" t="inlineStr"/>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:19,23-30; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="T49" s="6" t="inlineStr">
-        <is>
-          <t>Soraya owns teardown production and comp brand profile maintenance. A and R both SS. Danielle consulted rather than only receiving the finished teardown.</t>
+      <c r="R49" s="7" t="inlineStr"/>
+      <c r="S49" s="7" t="inlineStr"/>
+      <c r="T49" s="6" t="inlineStr"/>
+      <c r="U49" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json (Sales &amp; Commerce lead: "TBD (wholesale)"); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V49" s="6" t="inlineStr">
+        <is>
+          <t>Hub left wholesale unowned. Resolved to Nicole with all-channel accountability. A and R both Nicole - no second pair of eyes on new-partner decisions.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Retail &amp; Wholesale</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Quarterly teardown sign-off before circulation</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr"/>
+          <t>Retail price architecture and the pricing matrix</t>
+        </is>
+      </c>
+      <c r="C50" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E50" s="9" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
         <is>
           <t>A</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr"/>
       <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr"/>
       <c r="K50" s="7" t="inlineStr"/>
       <c r="L50" s="7" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O50" s="7" t="inlineStr"/>
       <c r="P50" s="7" t="inlineStr"/>
       <c r="Q50" s="7" t="inlineStr"/>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:65; .claude/skills/sjs-comp-intel/SKILL.md:50</t>
-        </is>
-      </c>
-      <c r="T50" s="6" t="inlineStr">
-        <is>
-          <t>Alvin signs off before it circulates to Danielle and the SJS brand team.</t>
+      <c r="R50" s="7" t="inlineStr"/>
+      <c r="S50" s="7" t="inlineStr"/>
+      <c r="T50" s="6" t="inlineStr"/>
+      <c r="U50" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json (Sales &amp; Commerce / Retail Price Architecture, SJS Pricing Matrix); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V50" s="6" t="inlineStr">
+        <is>
+          <t>Live pricing matrix on the hub carries retail, wholesale and subscription prices with margin colouring. Ties to the margin framework, so Danielle consulted as the walk-away approver.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Retail &amp; Wholesale</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Monthly competitive trend digest and cross-stream signal routing</t>
+          <t>Retailer promo calendar (Sephora, Ulta) and promo planning</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -3588,24 +3710,24 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
@@ -3620,15 +3742,17 @@
       <c r="O51" s="7" t="inlineStr"/>
       <c r="P51" s="7" t="inlineStr"/>
       <c r="Q51" s="7" t="inlineStr"/>
-      <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:3,9-15; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="T51" s="6" t="inlineStr">
-        <is>
-          <t>Stream DRI owns digest production and the 'what it means for SJS' analytical layer. Named as the stream's heartbeat - first thing protected under capacity pressure. A and R both NI. Danielle consulted on the digest's read.</t>
+      <c r="R51" s="7" t="inlineStr"/>
+      <c r="S51" s="7" t="inlineStr"/>
+      <c r="T51" s="6" t="inlineStr"/>
+      <c r="U51" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json (Market Intelligence / Promo Landscape); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V51" s="6" t="inlineStr">
+        <is>
+          <t>Promo Landscape tracks the Sephora and Ulta promo calendar. Marketing runs the planning; Nicole answers for the channel commitment.</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3764,7 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Social listening and comp brand monitoring (TikTok, IG, Pinterest, retailer new arrivals)</t>
+          <t>Quarterly competitive teardowns across the five comp brands</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
@@ -3653,18 +3777,26 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr"/>
-      <c r="F52" s="7" t="inlineStr"/>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G52" s="7" t="inlineStr"/>
       <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J52" s="9" t="inlineStr">
+      <c r="I52" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
+        </is>
+      </c>
+      <c r="J52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr"/>
@@ -3674,15 +3806,17 @@
       <c r="O52" s="7" t="inlineStr"/>
       <c r="P52" s="7" t="inlineStr"/>
       <c r="Q52" s="7" t="inlineStr"/>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:34,40-44; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="T52" s="6" t="inlineStr">
-        <is>
-          <t>Kate owns social listening tool maintenance, query hygiene and the weekly retailer new-arrivals scan. A and R both KL. Danielle consulted on what the social signal implies for brand.</t>
+      <c r="R52" s="7" t="inlineStr"/>
+      <c r="S52" s="7" t="inlineStr"/>
+      <c r="T52" s="6" t="inlineStr"/>
+      <c r="U52" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:19,23-30; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="V52" s="6" t="inlineStr">
+        <is>
+          <t>Soraya owns teardown production and comp brand profile maintenance. A and R both SS. Danielle consulted rather than only receiving the finished teardown.</t>
         </is>
       </c>
     </row>
@@ -3694,57 +3828,51 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Brand guideline custody (fonts, colors, logos, voice)</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
+          <t>Quarterly teardown sign-off before circulation</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr"/>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr"/>
-      <c r="F53" s="7" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K53" s="8" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="L53" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J53" s="7" t="inlineStr"/>
+      <c r="K53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
       <c r="O53" s="7" t="inlineStr"/>
       <c r="P53" s="7" t="inlineStr"/>
       <c r="Q53" s="7" t="inlineStr"/>
-      <c r="R53" s="6" t="inlineStr"/>
-      <c r="S53" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sweet-july-skin-brand/SKILL.md:1; references/architecture/system_map.md:157; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="T53" s="6" t="inlineStr">
-        <is>
-          <t>Every output-producing skill defers here for canonical brand spec; no skill carries its own copy. President answers for brand custody; Creative Director maintains it. Ayesha consulted - the brand carries her name. Every output-producing skill defers here for canonical spec.</t>
+      <c r="R53" s="7" t="inlineStr"/>
+      <c r="S53" s="7" t="inlineStr"/>
+      <c r="T53" s="6" t="inlineStr"/>
+      <c r="U53" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:65; .claude/skills/sjs-comp-intel/SKILL.md:50</t>
+        </is>
+      </c>
+      <c r="V53" s="6" t="inlineStr">
+        <is>
+          <t>Alvin signs off before it circulates to Danielle and the SJS brand team.</t>
         </is>
       </c>
     </row>
@@ -3756,57 +3884,59 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Annual team holiday communications (11 sends across 3 templates)</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="inlineStr"/>
+          <t>Monthly competitive trend digest and cross-stream signal routing</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="F54" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
       <c r="H54" s="7" t="inlineStr"/>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="L54" s="7" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
       <c r="N54" s="7" t="inlineStr"/>
       <c r="O54" s="7" t="inlineStr"/>
       <c r="P54" s="7" t="inlineStr"/>
       <c r="Q54" s="7" t="inlineStr"/>
-      <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/ac-brands-holiday-comms/SKILL.md:26,165</t>
-        </is>
-      </c>
-      <c r="T54" s="6" t="inlineStr">
-        <is>
-          <t>Sends from alvin@ac-brands.com with the team on BCC. Includes the Outlook calendar sync and annual maintenance. A and R both AB.</t>
+      <c r="R54" s="7" t="inlineStr"/>
+      <c r="S54" s="7" t="inlineStr"/>
+      <c r="T54" s="6" t="inlineStr"/>
+      <c r="U54" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:3,9-15; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="V54" s="6" t="inlineStr">
+        <is>
+          <t>Stream DRI owns digest production and the 'what it means for SJS' analytical layer. Named as the stream's heartbeat - first thing protected under capacity pressure. A and R both NI. Danielle consulted on the digest's read.</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3948,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Weekly founder briefing, Slides 5 and 6</t>
+          <t>Social listening and comp brand monitoring (TikTok, IG, Pinterest, retailer new arrivals)</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
@@ -3828,43 +3958,41 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E55" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr"/>
       <c r="G55" s="7" t="inlineStr"/>
       <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr"/>
-      <c r="J55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
       <c r="K55" s="7" t="inlineStr"/>
       <c r="L55" s="7" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
-      <c r="N55" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N55" s="7" t="inlineStr"/>
       <c r="O55" s="7" t="inlineStr"/>
       <c r="P55" s="7" t="inlineStr"/>
       <c r="Q55" s="7" t="inlineStr"/>
-      <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:49,72</t>
-        </is>
-      </c>
-      <c r="T55" s="6" t="inlineStr">
-        <is>
-          <t>Alvin owns both Slide 5 (Business Operations) and Slide 6 PD-Ops content; Nicole co-authors Slide 6 with her core PD content. A and R both AB.</t>
+      <c r="R55" s="7" t="inlineStr"/>
+      <c r="S55" s="7" t="inlineStr"/>
+      <c r="T55" s="6" t="inlineStr"/>
+      <c r="U55" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:34,40-44; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="V55" s="6" t="inlineStr">
+        <is>
+          <t>Kate owns social listening tool maintenance, query hygiene and the weekly retailer new-arrivals scan. A and R both KL. Danielle consulted on what the social signal implies for brand.</t>
         </is>
       </c>
     </row>
@@ -3876,34 +4004,22 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Operational special projects: labels, PR seeding, sampling</t>
+          <t>Brand guideline custody (fonts, colors, logos, voice)</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F56" s="9" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="E56" s="7" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="7" t="inlineStr"/>
       <c r="I56" s="7" t="inlineStr">
         <is>
@@ -3912,33 +4028,35 @@
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K56" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr"/>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K56" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M56" s="7" t="inlineStr"/>
       <c r="N56" s="7" t="inlineStr"/>
       <c r="O56" s="7" t="inlineStr"/>
       <c r="P56" s="7" t="inlineStr"/>
       <c r="Q56" s="7" t="inlineStr"/>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="S56" s="6" t="inlineStr">
-        <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="T56" s="6" t="inlineStr">
-        <is>
-          <t>Named in the Ops Specialist JD, and in the email as making sure product is where it needs to be for launches, promos, PR seeding and sampling. Danielle consulted - PR seeding and sampling are brand-facing.</t>
+      <c r="R56" s="7" t="inlineStr"/>
+      <c r="S56" s="7" t="inlineStr"/>
+      <c r="T56" s="6" t="inlineStr"/>
+      <c r="U56" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sweet-july-skin-brand/SKILL.md:1; references/architecture/system_map.md:157; Alvin, 2026-07-31 (role correction); acb-thelanding: data/links.json</t>
+        </is>
+      </c>
+      <c r="V56" s="6" t="inlineStr">
+        <is>
+          <t>Every output-producing skill defers here for canonical brand spec; no skill carries its own copy. President answers for brand custody; Creative Director maintains it. Ayesha consulted - the brand carries her name. Every output-producing skill defers here for canonical spec. Hub lists Brand &amp; Creative as "Owned by Soraya" as function lead; custody accountability sits with the President per the 31 July correction. Both hold: Soraya runs the function, Danielle answers for the brand standard.</t>
         </is>
       </c>
     </row>
@@ -3950,135 +4068,131 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Campaign direction and seasonal brand moments</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D57" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
+          <t>Annual team holiday communications (11 sends across 3 templates)</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr"/>
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
+      <c r="E57" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr"/>
       <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="I57" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K57" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L57" s="7" t="inlineStr"/>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K57" s="7" t="inlineStr"/>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="7" t="inlineStr"/>
       <c r="O57" s="7" t="inlineStr"/>
       <c r="P57" s="7" t="inlineStr"/>
       <c r="Q57" s="7" t="inlineStr"/>
-      <c r="R57" s="6" t="inlineStr"/>
-      <c r="S57" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (role correction); .claude/skills/sjs-margin-walk-away/SKILL.md:93</t>
-        </is>
-      </c>
-      <c r="T57" s="6" t="inlineStr">
-        <is>
-          <t>Added 2026-07-31. Campaign direction was absent from the matrix, which is why the President and the Founder had almost no Marketing presence. Danielle answers for it - Soraya reports to her and the margin sources already have her approving every repricing and channel call. Ayesha consulted on brand moments.</t>
+      <c r="R57" s="7" t="inlineStr"/>
+      <c r="S57" s="7" t="inlineStr"/>
+      <c r="T57" s="6" t="inlineStr"/>
+      <c r="U57" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/ac-brands-holiday-comms/SKILL.md:26,165</t>
+        </is>
+      </c>
+      <c r="V57" s="6" t="inlineStr">
+        <is>
+          <t>Sends from alvin@ac-brands.com with the team on BCC. Includes the Outlook calendar sync and annual maintenance. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Creative direction on packaging, artwork and brand visuals</t>
+          <t>Weekly founder briefing, Slides 5 and 6</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
           <t>I</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I58" s="7" t="inlineStr"/>
       <c r="J58" s="7" t="inlineStr"/>
-      <c r="K58" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="L58" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K58" s="7" t="inlineStr"/>
+      <c r="L58" s="7" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr"/>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O58" s="7" t="inlineStr"/>
       <c r="P58" s="7" t="inlineStr"/>
       <c r="Q58" s="7" t="inlineStr"/>
-      <c r="R58" s="6" t="inlineStr"/>
-      <c r="S58" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:22; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="T58" s="6" t="inlineStr">
-        <is>
-          <t>Creative Director owns packaging, artwork and brand visuals. A and R both EH. Creative Director owns the direction as lead technical authority, and is a contractor. Danielle and Ayesha both consulted. A and R the same person - no second pair of eyes, and no internal backup either.</t>
+      <c r="R58" s="7" t="inlineStr"/>
+      <c r="S58" s="7" t="inlineStr"/>
+      <c r="T58" s="6" t="inlineStr"/>
+      <c r="U58" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:49,72</t>
+        </is>
+      </c>
+      <c r="V58" s="6" t="inlineStr">
+        <is>
+          <t>Alvin owns both Slide 5 (Business Operations) and Slide 6 PD-Ops content; Nicole co-authors Slide 6 with her core PD content. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Packaging and artwork execution</t>
+          <t>Operational special projects: labels, PR seeding, sampling</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -4088,69 +4202,83 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr"/>
-      <c r="G59" s="7" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="7" t="inlineStr"/>
-      <c r="K59" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L59" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M59" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N59" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L59" s="7" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+      <c r="N59" s="7" t="inlineStr"/>
       <c r="O59" s="7" t="inlineStr"/>
       <c r="P59" s="7" t="inlineStr"/>
       <c r="Q59" s="7" t="inlineStr"/>
-      <c r="R59" s="6" t="inlineStr"/>
-      <c r="S59" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:23; .claude/skills/sjs-comp-intel/references/team-ownership.md:79; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
+      <c r="R59" s="7" t="inlineStr"/>
+      <c r="S59" s="7" t="inlineStr"/>
       <c r="T59" s="6" t="inlineStr">
         <is>
-          <t>Jan is the creative contractor under Erin. Title differs between sources - Packaging Engineer in one, creative contractor in the other. Erin holds technical authority; Jan executes. Both contractors.</t>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="U59" s="6" t="inlineStr">
+        <is>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="V59" s="6" t="inlineStr">
+        <is>
+          <t>Named in the Ops Specialist JD, and in the email as making sure product is where it needs to be for launches, promos, PR seeding and sampling. Danielle consulted - PR seeding and sampling are brand-facing.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Creative Requests intake and design coordination</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>Campaign direction and seasonal brand moments</t>
+        </is>
+      </c>
+      <c r="C60" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -4158,62 +4286,72 @@
           <t>I</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G60" s="7" t="inlineStr"/>
       <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J60" s="7" t="inlineStr"/>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J60" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L60" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
+      <c r="L60" s="7" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="7" t="inlineStr"/>
       <c r="O60" s="7" t="inlineStr"/>
       <c r="P60" s="7" t="inlineStr"/>
       <c r="Q60" s="7" t="inlineStr"/>
-      <c r="R60" s="6" t="inlineStr"/>
-      <c r="S60" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-status-reporter/SKILL.md:352; .claude/skills/asana-pd-manager/references/role-map.md:24; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
-      <c r="T60" s="6" t="inlineStr">
-        <is>
-          <t>Creative Requests Asana project owner is Ivy, Editorial/Design team. Ivy supports Erin and Jan. A and R both IT. Danielle consulted on intake priority.</t>
+      <c r="R60" s="7" t="inlineStr"/>
+      <c r="S60" s="7" t="inlineStr"/>
+      <c r="T60" s="6" t="inlineStr"/>
+      <c r="U60" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (role correction); .claude/skills/sjs-margin-walk-away/SKILL.md:93</t>
+        </is>
+      </c>
+      <c r="V60" s="6" t="inlineStr">
+        <is>
+          <t>Added 2026-07-31. Campaign direction was absent from the matrix, which is why the President and the Founder had almost no Marketing presence. Danielle answers for it - Soraya reports to her and the margin sources already have her approving every repricing and channel call. Ayesha consulted on brand moments.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Shopify revenue and channel position read</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr"/>
+          <t>Editorial and content calendar</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="E61" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -4223,58 +4361,84 @@
       </c>
       <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr"/>
-      <c r="I61" s="7" t="inlineStr"/>
-      <c r="J61" s="7" t="inlineStr"/>
-      <c r="K61" s="7" t="inlineStr"/>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L61" s="7" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="7" t="inlineStr"/>
       <c r="O61" s="7" t="inlineStr"/>
       <c r="P61" s="7" t="inlineStr"/>
       <c r="Q61" s="7" t="inlineStr"/>
-      <c r="R61" s="6" t="inlineStr"/>
-      <c r="S61" s="6" t="inlineStr">
-        <is>
-          <t>connections.md:7; context/about-business.md:5</t>
-        </is>
-      </c>
-      <c r="T61" s="6" t="inlineStr">
-        <is>
-          <t>INFERRED - no source names an owner. Shopify is registered as the revenue connection and named as the primary DTC revenue track, but no skill assigns ownership or a gate. A defaults to AB.</t>
+      <c r="R61" s="7" t="inlineStr"/>
+      <c r="S61" s="7" t="inlineStr"/>
+      <c r="T61" s="6" t="inlineStr"/>
+      <c r="U61" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json (Marketing / Owned Channels); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V61" s="6" t="inlineStr">
+        <is>
+          <t>Hub lists Marketing as "Owned by TBD"; resolved to Soraya as Marketing Manager. Editorial Calendar is a named tool under Owned Channels.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Daily DTC fulfillment KPIs and the SJ Shipping Dashboard</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr"/>
-      <c r="D62" s="7" t="inlineStr"/>
+          <t>Email marketing: Klaviyo flows and campaign sends</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F62" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="inlineStr"/>
       <c r="H62" s="7" t="inlineStr"/>
-      <c r="I62" s="7" t="inlineStr"/>
-      <c r="J62" s="7" t="inlineStr"/>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="K62" s="7" t="inlineStr"/>
       <c r="L62" s="7" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -4282,65 +4446,63 @@
       <c r="O62" s="7" t="inlineStr"/>
       <c r="P62" s="7" t="inlineStr"/>
       <c r="Q62" s="7" t="inlineStr"/>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="S62" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/oc3pl-order-manager/SKILL.md:61,191; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
-        </is>
-      </c>
-      <c r="T62" s="6" t="inlineStr">
-        <is>
-          <t>Ex-Ops-Coordinator scope, now Nicole per the interim split. A and R both NI.</t>
+      <c r="R62" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr"/>
+      <c r="T62" s="6" t="inlineStr"/>
+      <c r="U62" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json (Marketing / Klaviyo Performance); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V62" s="6" t="inlineStr">
+        <is>
+          <t>WITHIN runs most of our digital marketing including email execution. Soraya answers for the channel. Klaviyo Performance is a named tool on the hub.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Channel operations and promo setup across DTC, UBM and Amazon</t>
-        </is>
-      </c>
-      <c r="C63" s="7" t="inlineStr"/>
+          <t>Paid media: Meta, Google and channel spend</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="7" t="inlineStr"/>
+      <c r="I63" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J63" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J63" s="7" t="inlineStr"/>
       <c r="K63" s="7" t="inlineStr"/>
       <c r="L63" s="7" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -4348,96 +4510,112 @@
       <c r="O63" s="7" t="inlineStr"/>
       <c r="P63" s="7" t="inlineStr"/>
       <c r="Q63" s="7" t="inlineStr"/>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="S63" s="6" t="inlineStr">
-        <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
-        </is>
-      </c>
-      <c r="T63" s="6" t="inlineStr">
-        <is>
-          <t>Named in the Ops Specialist JD under Order Management &amp; Channel Operations. Nicole holds the channel relationship.</t>
+      <c r="R63" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr"/>
+      <c r="T63" s="6" t="inlineStr"/>
+      <c r="U63" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json (Marketing / Paid Media Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V63" s="6" t="inlineStr">
+        <is>
+          <t>WITHIN is the digital marketing agency and runs paid execution. Alvin consulted on spend against margin floors. Quarterly business reviews with WITHIN - the most recent was 20 July.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Proactive reships and fulfillment-issue resolution</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr"/>
-      <c r="D64" s="7" t="inlineStr"/>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F64" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+          <t>Social media content and publishing</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
       <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="7" t="inlineStr"/>
-      <c r="K64" s="7" t="inlineStr"/>
-      <c r="L64" s="7" t="inlineStr"/>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J64" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M64" s="7" t="inlineStr"/>
       <c r="N64" s="7" t="inlineStr"/>
       <c r="O64" s="7" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr"/>
       <c r="Q64" s="7" t="inlineStr"/>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="S64" s="6" t="inlineStr">
-        <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
-        </is>
-      </c>
-      <c r="T64" s="6" t="inlineStr">
-        <is>
-          <t>JD wording: resolve fulfillment issues "before a customer has to follow up." Sits inside Nicole's interim OC3PL coverage. A and R both NI.</t>
+      <c r="R64" s="7" t="inlineStr"/>
+      <c r="S64" s="7" t="inlineStr"/>
+      <c r="T64" s="6" t="inlineStr"/>
+      <c r="U64" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json (Marketing / Social Media Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V64" s="6" t="inlineStr">
+        <is>
+          <t>Distinct from social listening, which Kate is accountable for. Here she does the publishing work and Soraya answers for the channel.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Margin architecture framework and quarterly portfolio review</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr"/>
+          <t>Influencer and earned media programs</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -4447,8 +4625,16 @@
       </c>
       <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="K65" s="7" t="inlineStr"/>
       <c r="L65" s="7" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -4456,38 +4642,44 @@
       <c r="O65" s="7" t="inlineStr"/>
       <c r="P65" s="7" t="inlineStr"/>
       <c r="Q65" s="7" t="inlineStr"/>
-      <c r="R65" s="6" t="inlineStr"/>
-      <c r="S65" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-margin-architect/references/framework.md:209; .claude/skills/sjs-margin-portfolio-review/SKILL.md:1</t>
-        </is>
-      </c>
-      <c r="T65" s="6" t="inlineStr">
-        <is>
-          <t>Framework reference plus the quarterly portfolio sweep and traffic-light report. A and R both AB.</t>
+      <c r="R65" s="7" t="inlineStr"/>
+      <c r="S65" s="7" t="inlineStr"/>
+      <c r="T65" s="6" t="inlineStr"/>
+      <c r="U65" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V65" s="6" t="inlineStr">
+        <is>
+          <t>Brand-facing and founder-adjacent, so Danielle consulted and Ayesha informed. The physical seeding logistics sit on the Operations special-projects row.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>Per-SKU margin pressure-test against channel floors</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr"/>
+          <t>WITHIN agency relationship and quarterly business reviews</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -4497,62 +4689,60 @@
       </c>
       <c r="G66" s="7" t="inlineStr"/>
       <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr"/>
       <c r="K66" s="7" t="inlineStr"/>
       <c r="L66" s="7" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
-      <c r="N66" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="N66" s="7" t="inlineStr"/>
       <c r="O66" s="7" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr"/>
       <c r="Q66" s="7" t="inlineStr"/>
-      <c r="R66" s="6" t="inlineStr"/>
-      <c r="S66" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-margin-pressure-test/SKILL.md:93</t>
-        </is>
-      </c>
-      <c r="T66" s="6" t="inlineStr">
-        <is>
-          <t>Flagged as Perrine and Soraya's call to ratify, with Alvin on admin, Nicole consulting and Danielle approving.</t>
+      <c r="R66" s="7" t="inlineStr"/>
+      <c r="S66" s="7" t="inlineStr"/>
+      <c r="T66" s="6" t="inlineStr"/>
+      <c r="U66" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V66" s="6" t="inlineStr">
+        <is>
+          <t>A and R both Soraya. WITHIN holds most of our digital marketing execution, so the engagement is a single point of dependency - same shape as the other five external parties.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Walk-away decision when a SKU breaks its channel floor</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr"/>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>Creative direction on packaging, artwork and brand visuals</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr"/>
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr">
@@ -4561,215 +4751,247 @@
         </is>
       </c>
       <c r="J67" s="7" t="inlineStr"/>
-      <c r="K67" s="7" t="inlineStr"/>
-      <c r="L67" s="7" t="inlineStr"/>
+      <c r="K67" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M67" s="7" t="inlineStr"/>
-      <c r="N67" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N67" s="7" t="inlineStr"/>
       <c r="O67" s="7" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr"/>
       <c r="Q67" s="7" t="inlineStr"/>
-      <c r="R67" s="6" t="inlineStr"/>
-      <c r="S67" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:93,105,118</t>
-        </is>
-      </c>
-      <c r="T67" s="6" t="inlineStr">
-        <is>
-          <t>Danielle approves on three of the four paths. Alvin carries the work on all four.</t>
+      <c r="R67" s="7" t="inlineStr"/>
+      <c r="S67" s="7" t="inlineStr"/>
+      <c r="T67" s="6" t="inlineStr"/>
+      <c r="U67" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:22; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="V67" s="6" t="inlineStr">
+        <is>
+          <t>Creative Director owns packaging, artwork and brand visuals. A and R both EH. Creative Director owns the direction as lead technical authority, and is a contractor. Danielle and Ayesha both consulted. A and R the same person - no second pair of eyes, and no internal backup either.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>SKU archetype and Standard / Acquisition designation</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr"/>
+          <t>Packaging and artwork execution</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr"/>
       <c r="G68" s="7" t="inlineStr"/>
       <c r="H68" s="7" t="inlineStr"/>
       <c r="I68" s="7" t="inlineStr"/>
       <c r="J68" s="7" t="inlineStr"/>
-      <c r="K68" s="7" t="inlineStr"/>
-      <c r="L68" s="7" t="inlineStr"/>
-      <c r="M68" s="7" t="inlineStr"/>
-      <c r="N68" s="9" t="inlineStr">
+      <c r="K68" s="9" t="inlineStr">
         <is>
           <t>A</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M68" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="O68" s="7" t="inlineStr"/>
       <c r="P68" s="7" t="inlineStr"/>
       <c r="Q68" s="7" t="inlineStr"/>
-      <c r="R68" s="6" t="inlineStr"/>
-      <c r="S68" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:78</t>
-        </is>
-      </c>
-      <c r="T68" s="6" t="inlineStr">
-        <is>
-          <t>Perrine as PD owner with Alvin on PD admin and sourcing; Nicole consults.</t>
+      <c r="R68" s="7" t="inlineStr"/>
+      <c r="S68" s="7" t="inlineStr"/>
+      <c r="T68" s="6" t="inlineStr"/>
+      <c r="U68" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:23; .claude/skills/sjs-comp-intel/references/team-ownership.md:79; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="V68" s="6" t="inlineStr">
+        <is>
+          <t>Jan is the creative contractor under Erin. Title differs between sources - Packaging Engineer in one, creative contractor in the other. Erin holds technical authority; Jan executes. Both contractors.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Monthly and quarterly vendor cost rollups</t>
+          <t>Creative Requests intake and design coordination</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr"/>
       <c r="D69" s="7" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
           <t>I</t>
-        </is>
-      </c>
-      <c r="E69" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
       <c r="G69" s="7" t="inlineStr"/>
       <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J69" s="7" t="inlineStr"/>
-      <c r="K69" s="7" t="inlineStr"/>
-      <c r="L69" s="7" t="inlineStr"/>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
       <c r="M69" s="7" t="inlineStr"/>
       <c r="N69" s="7" t="inlineStr"/>
       <c r="O69" s="7" t="inlineStr"/>
-      <c r="P69" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="P69" s="7" t="inlineStr"/>
       <c r="Q69" s="7" t="inlineStr"/>
-      <c r="R69" s="6" t="inlineStr"/>
-      <c r="S69" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/regulatory-manager/SKILL.md:196; .claude/skills/purchasing-manager/SKILL.md:365; Alvin, 2026-07-31 (external partners)</t>
-        </is>
-      </c>
-      <c r="T69" s="6" t="inlineStr">
-        <is>
-          <t>regulatory-manager Jobs 8 and 9 read vendor_invoices directly; purchasing-manager has no rollup of its own. A and R both AB. Ironclad consulted - the rollup feeds their books.</t>
+      <c r="R69" s="7" t="inlineStr"/>
+      <c r="S69" s="7" t="inlineStr"/>
+      <c r="T69" s="6" t="inlineStr"/>
+      <c r="U69" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-status-reporter/SKILL.md:352; .claude/skills/asana-pd-manager/references/role-map.md:24; Alvin, 2026-07-31 (role correction)</t>
+        </is>
+      </c>
+      <c r="V69" s="6" t="inlineStr">
+        <is>
+          <t>Creative Requests Asana project owner is Ivy, Editorial/Design team. Ivy supports Erin and Jan. A and R both IT. Danielle consulted on intake priority.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Accounts payable, bookkeeping and payroll</t>
+          <t>Shopify revenue and channel position read</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr"/>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E70" s="9" t="inlineStr">
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr"/>
       <c r="G70" s="7" t="inlineStr"/>
       <c r="H70" s="7" t="inlineStr"/>
-      <c r="I70" s="7" t="inlineStr"/>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J70" s="7" t="inlineStr"/>
       <c r="K70" s="7" t="inlineStr"/>
       <c r="L70" s="7" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
       <c r="N70" s="7" t="inlineStr"/>
       <c r="O70" s="7" t="inlineStr"/>
-      <c r="P70" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="P70" s="7" t="inlineStr"/>
       <c r="Q70" s="7" t="inlineStr"/>
-      <c r="R70" s="6" t="inlineStr"/>
-      <c r="S70" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
-        </is>
-      </c>
-      <c r="T70" s="6" t="inlineStr">
-        <is>
-          <t>Ironclad Finance runs AP, bookkeeping and payroll; Dan Bender is the contact. Cost-side accountability sits with Operations because the vendor-invoice pipeline and its five approval gates feed it. No longer an unowned function.</t>
+      <c r="R70" s="7" t="inlineStr"/>
+      <c r="S70" s="7" t="inlineStr"/>
+      <c r="T70" s="6" t="inlineStr"/>
+      <c r="U70" s="6" t="inlineStr">
+        <is>
+          <t>connections.md:7; context/about-business.md:5; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V70" s="6" t="inlineStr">
+        <is>
+          <t>Nicole is accountable for all channels - DTC, Amazon and wholesale - with Alvin consulted and Danielle informed. This was the last row on the matrix with no owner; it now has one.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Month-end close and management reporting</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D71" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+          <t>Daily DTC fulfillment KPIs and the SJ Shipping Dashboard</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr"/>
+      <c r="D71" s="7" t="inlineStr"/>
       <c r="E71" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr"/>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr"/>
@@ -4778,153 +5000,159 @@
       <c r="M71" s="7" t="inlineStr"/>
       <c r="N71" s="7" t="inlineStr"/>
       <c r="O71" s="7" t="inlineStr"/>
-      <c r="P71" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="P71" s="7" t="inlineStr"/>
       <c r="Q71" s="7" t="inlineStr"/>
-      <c r="R71" s="6" t="inlineStr"/>
-      <c r="S71" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
-        </is>
-      </c>
+      <c r="R71" s="7" t="inlineStr"/>
+      <c r="S71" s="7" t="inlineStr"/>
       <c r="T71" s="6" t="inlineStr">
         <is>
-          <t>Ironclad Finance closes the books and produces the reporting; Dan Bender is the contact. Reporting accountability sits with the President.</t>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="U71" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/oc3pl-order-manager/SKILL.md:61,191; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
+        </is>
+      </c>
+      <c r="V71" s="6" t="inlineStr">
+        <is>
+          <t>Ex-Ops-Coordinator scope, now Nicole per the interim split. A and R both NI.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Annual budget and forecast consolidation</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
+          <t>Channel operations and promo setup across DTC, UBM and Amazon</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr"/>
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D72" s="9" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J72" s="7" t="inlineStr"/>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="K72" s="7" t="inlineStr"/>
       <c r="L72" s="7" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="7" t="inlineStr"/>
       <c r="O72" s="7" t="inlineStr"/>
-      <c r="P72" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="P72" s="7" t="inlineStr"/>
       <c r="Q72" s="7" t="inlineStr"/>
-      <c r="R72" s="6" t="inlineStr"/>
-      <c r="S72" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
-        </is>
-      </c>
+      <c r="R72" s="7" t="inlineStr"/>
+      <c r="S72" s="7" t="inlineStr"/>
       <c r="T72" s="6" t="inlineStr">
         <is>
-          <t>President answers for the budget. Operations and Consumer Strategy feed the operating and channel assumptions.</t>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="U72" s="6" t="inlineStr">
+        <is>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V72" s="6" t="inlineStr">
+        <is>
+          <t>Named in the Ops Specialist JD under Order Management &amp; Channel Operations. Nicole holds the channel relationship. Part of Nicole's all-channel accountability.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Inventory valuation and cost of goods</t>
+          <t>Proactive reships and fulfillment-issue resolution</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr"/>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E73" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr"/>
+      <c r="D73" s="7" t="inlineStr"/>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
       <c r="J73" s="7" t="inlineStr"/>
       <c r="K73" s="7" t="inlineStr"/>
       <c r="L73" s="7" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
-      <c r="N73" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N73" s="7" t="inlineStr"/>
       <c r="O73" s="7" t="inlineStr"/>
-      <c r="P73" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="P73" s="7" t="inlineStr"/>
       <c r="Q73" s="7" t="inlineStr"/>
-      <c r="R73" s="6" t="inlineStr"/>
-      <c r="S73" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (external partners); .claude/skills/inventory-manager/SKILL.md:18</t>
-        </is>
-      </c>
+      <c r="R73" s="7" t="inlineStr"/>
+      <c r="S73" s="7" t="inlineStr"/>
       <c r="T73" s="6" t="inlineStr">
         <is>
-          <t>Cost side, so accountability sits with Operations - it flows out of purchasing, receiving and the inventory ledger. Ironclad carries it into the books.</t>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="U73" s="6" t="inlineStr">
+        <is>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
+        </is>
+      </c>
+      <c r="V73" s="6" t="inlineStr">
+        <is>
+          <t>JD wording: resolve fulfillment issues "before a customer has to follow up." Sits inside Nicole's interim OC3PL coverage. A and R both NI.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Hiring the Operations Specialist and the PD Project Manager Specialist</t>
+          <t>Amazon channel management (FBA, AWD, Seller Central)</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -4934,22 +5162,30 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E74" s="9" t="inlineStr">
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F74" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J74" s="7" t="inlineStr"/>
       <c r="K74" s="7" t="inlineStr"/>
       <c r="L74" s="7" t="inlineStr"/>
@@ -4957,39 +5193,45 @@
       <c r="N74" s="7" t="inlineStr"/>
       <c r="O74" s="7" t="inlineStr"/>
       <c r="P74" s="7" t="inlineStr"/>
-      <c r="Q74" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="R74" s="6" t="inlineStr"/>
-      <c r="S74" s="6" t="inlineStr">
-        <is>
-          <t>decisions/log.md:52,58; context/priorities.md:3; Alvin, 2026-07-31 (external partners)</t>
-        </is>
-      </c>
+      <c r="Q74" s="7" t="inlineStr"/>
+      <c r="R74" s="7" t="inlineStr"/>
+      <c r="S74" s="7" t="inlineStr"/>
       <c r="T74" s="6" t="inlineStr">
         <is>
-          <t>Both new roles report to Nicole. Decision owner recorded as Alvin, with Nicole on the two new roles once filled. Priority 1 of 2 this quarter. Calm HR runs the recruiting process once the RACI clears Danielle.</t>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="U74" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json (Sales &amp; Commerce / Amazon Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V74" s="6" t="inlineStr">
+        <is>
+          <t>Hub gave Amazon to Alvin; resolved to Nicole under all-channel accountability with Alvin doing the work. Inventory and inbound pipeline transition to the Ops Specialist.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Tool procurement, vendor renewals and shared-folder admin</t>
+          <t>Product detail page content and product copy</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr"/>
-      <c r="D75" s="7" t="inlineStr"/>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -4999,40 +5241,54 @@
       </c>
       <c r="G75" s="7" t="inlineStr"/>
       <c r="H75" s="7" t="inlineStr"/>
-      <c r="I75" s="7" t="inlineStr"/>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
       <c r="J75" s="7" t="inlineStr"/>
-      <c r="K75" s="7" t="inlineStr"/>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr"/>
-      <c r="N75" s="7" t="inlineStr"/>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O75" s="7" t="inlineStr"/>
       <c r="P75" s="7" t="inlineStr"/>
       <c r="Q75" s="7" t="inlineStr"/>
-      <c r="R75" s="6" t="inlineStr"/>
-      <c r="S75" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:50; .claude/skills/sjs-comp-intel/references/sequencing-plan.md:12</t>
-        </is>
-      </c>
-      <c r="T75" s="6" t="inlineStr">
-        <is>
-          <t>Ex-Ops-Coordinator scope. Alvin carries it directly until the Operations Specialist starts. A and R both AB.</t>
+      <c r="R75" s="7" t="inlineStr"/>
+      <c r="S75" s="7" t="inlineStr"/>
+      <c r="T75" s="6" t="inlineStr"/>
+      <c r="U75" s="6" t="inlineStr">
+        <is>
+          <t>acb-thelanding: data/links.json (Sales &amp; Commerce / SJS Product Copy Database); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V75" s="6" t="inlineStr">
+        <is>
+          <t>Product Copy Database is live from PLM and carries every claim, ingredient line, FAQ and Amazon title across DTC, Amazon and wholesale. Perrine and Regulatory consulted because claims on a PDP are claims. A and R both Soraya.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Employee onboarding, offboarding and access deprovisioning</t>
+          <t>Margin architecture framework and quarterly portfolio review</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr"/>
@@ -5043,7 +5299,7 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A/R</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -5061,140 +5317,150 @@
       <c r="N76" s="7" t="inlineStr"/>
       <c r="O76" s="7" t="inlineStr"/>
       <c r="P76" s="7" t="inlineStr"/>
-      <c r="Q76" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="R76" s="6" t="inlineStr"/>
-      <c r="S76" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:48-56; Alvin, 2026-07-31 (external partners)</t>
-        </is>
-      </c>
-      <c r="T76" s="6" t="inlineStr">
-        <is>
-          <t>Calm HR is the PEO and co-employer and runs the process; Alvin is the liaison and answers for it. Danielle consulted. No longer an unowned function - the departed-role-holder checklist in the PD role-map remains the internal system-side counterpart.</t>
+      <c r="Q76" s="7" t="inlineStr"/>
+      <c r="R76" s="7" t="inlineStr"/>
+      <c r="S76" s="7" t="inlineStr"/>
+      <c r="T76" s="6" t="inlineStr"/>
+      <c r="U76" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-margin-architect/references/framework.md:209; .claude/skills/sjs-margin-portfolio-review/SKILL.md:1</t>
+        </is>
+      </c>
+      <c r="V76" s="6" t="inlineStr">
+        <is>
+          <t>Framework reference plus the quarterly portfolio sweep and traffic-light report. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Operations Specialist recruiting</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
+          <t>Per-SKU margin pressure-test against channel floors</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr"/>
+      <c r="D77" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E77" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="inlineStr">
+      <c r="E77" s="8" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr"/>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J77" s="7" t="inlineStr"/>
       <c r="K77" s="7" t="inlineStr"/>
       <c r="L77" s="7" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
-      <c r="N77" s="7" t="inlineStr"/>
+      <c r="N77" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="O77" s="7" t="inlineStr"/>
       <c r="P77" s="7" t="inlineStr"/>
       <c r="Q77" s="7" t="inlineStr"/>
-      <c r="R77" s="6" t="inlineStr"/>
-      <c r="S77" s="6" t="inlineStr">
-        <is>
-          <t>Leadership Business Review 2026-07-30 52:48-53:17; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
-        </is>
-      </c>
-      <c r="T77" s="6" t="inlineStr">
-        <is>
-          <t>Prioritized first. Danielle: "we're going to prioritize the operations... Specialist." Reports to Nicole. Target in place before Q4. Salary band $72-90K.</t>
+      <c r="R77" s="7" t="inlineStr"/>
+      <c r="S77" s="7" t="inlineStr"/>
+      <c r="T77" s="6" t="inlineStr"/>
+      <c r="U77" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-margin-pressure-test/SKILL.md:93</t>
+        </is>
+      </c>
+      <c r="V77" s="6" t="inlineStr">
+        <is>
+          <t>Flagged as Perrine and Soraya's call to ratify, with Alvin on admin, Nicole consulting and Danielle approving.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>PD Specialist role definition and phased recruiting</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
+          <t>Walk-away decision when a SKU breaks its channel floor</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr"/>
+      <c r="D78" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F78" s="8" t="inlineStr">
+      <c r="E78" s="8" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J78" s="7" t="inlineStr"/>
       <c r="K78" s="7" t="inlineStr"/>
       <c r="L78" s="7" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
-      <c r="N78" s="7" t="inlineStr"/>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O78" s="7" t="inlineStr"/>
       <c r="P78" s="7" t="inlineStr"/>
       <c r="Q78" s="7" t="inlineStr"/>
-      <c r="R78" s="6" t="inlineStr"/>
-      <c r="S78" s="6" t="inlineStr">
-        <is>
-          <t>Leadership Business Review 2026-07-30 53:17-57:10; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
-        </is>
-      </c>
-      <c r="T78" s="6" t="inlineStr">
-        <is>
-          <t>Phased in after the Ops Specialist. Danielle scopes it as "air traffic control, holding people accountable" rather than strategy or ideation, and is adding trend-forecasting language to the JD. Reports to Nicole. Salary band $75-95K.</t>
+      <c r="R78" s="7" t="inlineStr"/>
+      <c r="S78" s="7" t="inlineStr"/>
+      <c r="T78" s="6" t="inlineStr"/>
+      <c r="U78" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:93,105,118</t>
+        </is>
+      </c>
+      <c r="V78" s="6" t="inlineStr">
+        <is>
+          <t>Danielle approves on three of the four paths. Alvin carries the work on all four.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>SOP cleanup and operational prep before new-hire onboarding</t>
+          <t>SKU archetype and Standard / Acquisition designation</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr"/>
@@ -5203,14 +5469,14 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="inlineStr">
+      <c r="E79" s="8" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -5220,53 +5486,51 @@
       <c r="K79" s="7" t="inlineStr"/>
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
-      <c r="N79" s="7" t="inlineStr"/>
+      <c r="N79" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="O79" s="7" t="inlineStr"/>
       <c r="P79" s="7" t="inlineStr"/>
       <c r="Q79" s="7" t="inlineStr"/>
-      <c r="R79" s="6" t="inlineStr"/>
-      <c r="S79" s="6" t="inlineStr">
-        <is>
-          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
-        </is>
-      </c>
-      <c r="T79" s="6" t="inlineStr">
-        <is>
-          <t>Danielle's condition on the hire: clean up the system first so the role can function. Nicole's action item from the review.</t>
+      <c r="R79" s="7" t="inlineStr"/>
+      <c r="S79" s="7" t="inlineStr"/>
+      <c r="T79" s="6" t="inlineStr"/>
+      <c r="U79" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:78</t>
+        </is>
+      </c>
+      <c r="V79" s="6" t="inlineStr">
+        <is>
+          <t>Perrine as PD owner with Alvin on PD admin and sourcing; Nicole consults.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Employee handbook and HR policy</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
+          <t>Monthly and quarterly vendor cost rollups</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr"/>
+      <c r="D80" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="7" t="inlineStr"/>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr"/>
@@ -5276,33 +5540,35 @@
       <c r="M80" s="7" t="inlineStr"/>
       <c r="N80" s="7" t="inlineStr"/>
       <c r="O80" s="7" t="inlineStr"/>
-      <c r="P80" s="7" t="inlineStr"/>
-      <c r="Q80" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="R80" s="6" t="inlineStr"/>
-      <c r="S80" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
-        </is>
-      </c>
-      <c r="T80" s="6" t="inlineStr">
-        <is>
-          <t>Calm HR drafts and maintains; Alvin is the liaison and answers for it; Danielle co-approves. Handbook is in flight as of 2026-07-30 and goes to legal review before implementation.</t>
+      <c r="P80" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q80" s="7" t="inlineStr"/>
+      <c r="R80" s="7" t="inlineStr"/>
+      <c r="S80" s="7" t="inlineStr"/>
+      <c r="T80" s="6" t="inlineStr"/>
+      <c r="U80" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/regulatory-manager/SKILL.md:196; .claude/skills/purchasing-manager/SKILL.md:365; Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="V80" s="6" t="inlineStr">
+        <is>
+          <t>regulatory-manager Jobs 8 and 9 read vendor_invoices directly; purchasing-manager has no rollup of its own. A and R both AB. Ironclad consulted - the rollup feeds their books.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Benefits administration and payroll processing</t>
+          <t>Accounts payable, bookkeeping and payroll</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr"/>
@@ -5326,51 +5592,57 @@
       <c r="M81" s="7" t="inlineStr"/>
       <c r="N81" s="7" t="inlineStr"/>
       <c r="O81" s="7" t="inlineStr"/>
-      <c r="P81" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q81" s="8" t="inlineStr">
+      <c r="P81" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="R81" s="6" t="inlineStr"/>
-      <c r="S81" s="6" t="inlineStr">
+      <c r="Q81" s="7" t="inlineStr"/>
+      <c r="R81" s="7" t="inlineStr"/>
+      <c r="S81" s="7" t="inlineStr"/>
+      <c r="T81" s="6" t="inlineStr"/>
+      <c r="U81" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="T81" s="6" t="inlineStr">
-        <is>
-          <t>Calm HR administers as co-employer. Ironclad consulted where payroll hits the books.</t>
+      <c r="V81" s="6" t="inlineStr">
+        <is>
+          <t>Ironclad Finance runs AP, bookkeeping and payroll; Dan Bender is the contact. Cost-side accountability sits with Operations because the vendor-invoice pipeline and its five approval gates feed it. No longer an unowned function.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Employment compliance and separations</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr"/>
-      <c r="D82" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr">
+          <t>Month-end close and management reporting</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr"/>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G82" s="7" t="inlineStr"/>
       <c r="H82" s="7" t="inlineStr"/>
       <c r="I82" s="7" t="inlineStr"/>
@@ -5380,89 +5652,117 @@
       <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="7" t="inlineStr"/>
       <c r="O82" s="7" t="inlineStr"/>
-      <c r="P82" s="7" t="inlineStr"/>
-      <c r="Q82" s="8" t="inlineStr">
+      <c r="P82" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="R82" s="6" t="inlineStr"/>
-      <c r="S82" s="6" t="inlineStr">
+      <c r="Q82" s="7" t="inlineStr"/>
+      <c r="R82" s="7" t="inlineStr"/>
+      <c r="S82" s="7" t="inlineStr"/>
+      <c r="T82" s="6" t="inlineStr"/>
+      <c r="U82" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="T82" s="6" t="inlineStr">
-        <is>
-          <t>Calm HR runs the process with outside counsel where needed. Danielle co-approves every separation.</t>
+      <c r="V82" s="6" t="inlineStr">
+        <is>
+          <t>Ironclad Finance closes the books and produces the reporting; Dan Bender is the contact. Reporting accountability sits with the President.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>PLM schema, write path, audit log and Supabase wiki custody</t>
-        </is>
-      </c>
-      <c r="C83" s="7" t="inlineStr"/>
-      <c r="D83" s="7" t="inlineStr"/>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F83" s="7" t="inlineStr"/>
+          <t>Annual budget and forecast consolidation</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G83" s="7" t="inlineStr"/>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J83" s="7" t="inlineStr"/>
       <c r="K83" s="7" t="inlineStr"/>
       <c r="L83" s="7" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
-      <c r="N83" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N83" s="7" t="inlineStr"/>
       <c r="O83" s="7" t="inlineStr"/>
-      <c r="P83" s="7" t="inlineStr"/>
+      <c r="P83" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="Q83" s="7" t="inlineStr"/>
-      <c r="R83" s="6" t="inlineStr"/>
-      <c r="S83" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/plm-assistant/SKILL.md:292; decisions/wiki-layer-audit-2026-07-29.md:52</t>
-        </is>
-      </c>
-      <c r="T83" s="6" t="inlineStr">
-        <is>
-          <t>plm-assistant is the sole PLM writer and every write needs Operations sign-off. Job 0 wiki write-back has not fired since 2026-05-26. A and R both AB.</t>
+      <c r="R83" s="7" t="inlineStr"/>
+      <c r="S83" s="7" t="inlineStr"/>
+      <c r="T83" s="6" t="inlineStr"/>
+      <c r="U83" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="V83" s="6" t="inlineStr">
+        <is>
+          <t>President answers for the budget. Operations and Consumer Strategy feed the operating and channel assumptions.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Landing hub publish and Netlify Function maintenance</t>
+          <t>Inventory valuation and cost of goods</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr"/>
-      <c r="D84" s="7" t="inlineStr"/>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E84" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F84" s="7" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G84" s="7" t="inlineStr"/>
       <c r="H84" s="7" t="inlineStr"/>
       <c r="I84" s="7" t="inlineStr"/>
@@ -5470,43 +5770,61 @@
       <c r="K84" s="7" t="inlineStr"/>
       <c r="L84" s="7" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
-      <c r="N84" s="7" t="inlineStr"/>
+      <c r="N84" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O84" s="7" t="inlineStr"/>
-      <c r="P84" s="7" t="inlineStr"/>
+      <c r="P84" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="Q84" s="7" t="inlineStr"/>
-      <c r="R84" s="6" t="inlineStr"/>
-      <c r="S84" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/quality-status-reporter/SKILL.md:34-50; .claude/skills/quality-status-reporter/references/hub-integration.md:85</t>
-        </is>
-      </c>
-      <c r="T84" s="6" t="inlineStr">
-        <is>
-          <t>All hub writes go through the landing-hub-publish Function behind an Operator gate. Deploy is commit-and-push only, never Netlify CLI. A and R both AB.</t>
+      <c r="R84" s="7" t="inlineStr"/>
+      <c r="S84" s="7" t="inlineStr"/>
+      <c r="T84" s="6" t="inlineStr"/>
+      <c r="U84" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners); .claude/skills/inventory-manager/SKILL.md:18</t>
+        </is>
+      </c>
+      <c r="V84" s="6" t="inlineStr">
+        <is>
+          <t>Cost side, so accountability sits with Operations - it flows out of purchasing, receiving and the inventory ledger. Ironclad carries it into the books.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Asana project, section, custom-field and connector configuration</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr"/>
-      <c r="D85" s="7" t="inlineStr"/>
+          <t>Hiring the Operations Specialist and the PD Project Manager Specialist</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E85" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr"/>
@@ -5519,28 +5837,34 @@
       <c r="N85" s="7" t="inlineStr"/>
       <c r="O85" s="7" t="inlineStr"/>
       <c r="P85" s="7" t="inlineStr"/>
-      <c r="Q85" s="7" t="inlineStr"/>
-      <c r="R85" s="6" t="inlineStr"/>
-      <c r="S85" s="6" t="inlineStr">
-        <is>
-          <t>references/architecture/asana_task_contract.md:227; connections.md:5-13</t>
-        </is>
-      </c>
-      <c r="T85" s="6" t="inlineStr">
-        <is>
-          <t>An unresolvable role-holder is surfaced for Alvin to decide, not dropped. Seven tool domains registered; iMessage still not connected. A and R both AB.</t>
+      <c r="Q85" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R85" s="7" t="inlineStr"/>
+      <c r="S85" s="7" t="inlineStr"/>
+      <c r="T85" s="6" t="inlineStr"/>
+      <c r="U85" s="6" t="inlineStr">
+        <is>
+          <t>decisions/log.md:52,58; context/priorities.md:3; Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="V85" s="6" t="inlineStr">
+        <is>
+          <t>Both new roles report to Nicole. Decision owner recorded as Alvin, with Nicole on the two new roles once filled. Priority 1 of 2 this quarter. Calm HR runs the recruiting process once the RACI clears Danielle.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Skill suite authorship, audit and versioning</t>
+          <t>Tool procurement, vendor renewals and shared-folder admin</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr"/>
@@ -5550,51 +5874,65 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="F86" s="7" t="inlineStr"/>
+      <c r="F86" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G86" s="7" t="inlineStr"/>
       <c r="H86" s="7" t="inlineStr"/>
       <c r="I86" s="7" t="inlineStr"/>
       <c r="J86" s="7" t="inlineStr"/>
       <c r="K86" s="7" t="inlineStr"/>
-      <c r="L86" s="7" t="inlineStr"/>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M86" s="7" t="inlineStr"/>
       <c r="N86" s="7" t="inlineStr"/>
       <c r="O86" s="7" t="inlineStr"/>
       <c r="P86" s="7" t="inlineStr"/>
       <c r="Q86" s="7" t="inlineStr"/>
-      <c r="R86" s="6" t="inlineStr"/>
-      <c r="S86" s="6" t="inlineStr">
-        <is>
-          <t>decisions/skills-architecture-tracker.md:4; decisions/log.md:31,45</t>
-        </is>
-      </c>
-      <c r="T86" s="6" t="inlineStr">
-        <is>
-          <t>Owner recorded as Alvin Belt across the architecture decisions. Priority 2 of 2 this quarter. A and R both AB.</t>
+      <c r="R86" s="7" t="inlineStr"/>
+      <c r="S86" s="7" t="inlineStr"/>
+      <c r="T86" s="6" t="inlineStr"/>
+      <c r="U86" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:50; .claude/skills/sjs-comp-intel/references/sequencing-plan.md:12</t>
+        </is>
+      </c>
+      <c r="V86" s="6" t="inlineStr">
+        <is>
+          <t>Ex-Ops-Coordinator scope. Alvin carries it directly until the Operations Specialist starts. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>The 23 scheduled Routines and their HITL gates</t>
+          <t>Employee onboarding, offboarding and access deprovisioning</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr"/>
-      <c r="D87" s="7" t="inlineStr"/>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr"/>
@@ -5607,31 +5945,41 @@
       <c r="N87" s="7" t="inlineStr"/>
       <c r="O87" s="7" t="inlineStr"/>
       <c r="P87" s="7" t="inlineStr"/>
-      <c r="Q87" s="7" t="inlineStr"/>
-      <c r="R87" s="6" t="inlineStr"/>
-      <c r="S87" s="6" t="inlineStr">
-        <is>
-          <t>scheduled-prompts/weekly-pd-update.md:91; scheduled-prompts/sjs-purchasing-monthly-rollup-and-snapshot.md:79</t>
-        </is>
-      </c>
-      <c r="T87" s="6" t="inlineStr">
-        <is>
-          <t>Nothing commits until Alvin says go. Same pattern across all 23 Routines, including the ones that fire unattended on a schedule. A and R both AB.</t>
+      <c r="Q87" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R87" s="7" t="inlineStr"/>
+      <c r="S87" s="7" t="inlineStr"/>
+      <c r="T87" s="6" t="inlineStr"/>
+      <c r="U87" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:48-56; Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="V87" s="6" t="inlineStr">
+        <is>
+          <t>Calm HR is the PEO and co-employer and runs the process; Alvin is the liaison and answers for it. Danielle consulted. No longer an unowned function - the departed-role-holder checklist in the PD role-map remains the internal system-side counterpart.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>RACI and role framework across Operations and PD</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr"/>
+          <t>Operations Specialist recruiting</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -5658,631 +6006,844 @@
       <c r="O88" s="7" t="inlineStr"/>
       <c r="P88" s="7" t="inlineStr"/>
       <c r="Q88" s="7" t="inlineStr"/>
-      <c r="R88" s="6" t="inlineStr"/>
-      <c r="S88" s="6" t="inlineStr">
+      <c r="R88" s="7" t="inlineStr"/>
+      <c r="S88" s="7" t="inlineStr"/>
+      <c r="T88" s="6" t="inlineStr"/>
+      <c r="U88" s="6" t="inlineStr">
+        <is>
+          <t>Leadership Business Review 2026-07-30 52:48-53:17; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
+        </is>
+      </c>
+      <c r="V88" s="6" t="inlineStr">
+        <is>
+          <t>Prioritized first. Danielle: "we're going to prioritize the operations... Specialist." Reports to Nicole. Target in place before Q4. Salary band $72-90K.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>People &amp; Admin</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>PD Specialist role definition and phased recruiting</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="inlineStr"/>
+      <c r="H89" s="7" t="inlineStr"/>
+      <c r="I89" s="7" t="inlineStr"/>
+      <c r="J89" s="7" t="inlineStr"/>
+      <c r="K89" s="7" t="inlineStr"/>
+      <c r="L89" s="7" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+      <c r="N89" s="7" t="inlineStr"/>
+      <c r="O89" s="7" t="inlineStr"/>
+      <c r="P89" s="7" t="inlineStr"/>
+      <c r="Q89" s="7" t="inlineStr"/>
+      <c r="R89" s="7" t="inlineStr"/>
+      <c r="S89" s="7" t="inlineStr"/>
+      <c r="T89" s="6" t="inlineStr"/>
+      <c r="U89" s="6" t="inlineStr">
+        <is>
+          <t>Leadership Business Review 2026-07-30 53:17-57:10; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
+        </is>
+      </c>
+      <c r="V89" s="6" t="inlineStr">
+        <is>
+          <t>Phased in after the Ops Specialist. Danielle scopes it as "air traffic control, holding people accountable" rather than strategy or ideation, and is adding trend-forecasting language to the JD. Reports to Nicole. Salary band $75-95K.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>People &amp; Admin</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>SOP cleanup and operational prep before new-hire onboarding</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr"/>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F90" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr"/>
+      <c r="I90" s="7" t="inlineStr"/>
+      <c r="J90" s="7" t="inlineStr"/>
+      <c r="K90" s="7" t="inlineStr"/>
+      <c r="L90" s="7" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+      <c r="N90" s="7" t="inlineStr"/>
+      <c r="O90" s="7" t="inlineStr"/>
+      <c r="P90" s="7" t="inlineStr"/>
+      <c r="Q90" s="7" t="inlineStr"/>
+      <c r="R90" s="7" t="inlineStr"/>
+      <c r="S90" s="7" t="inlineStr"/>
+      <c r="T90" s="6" t="inlineStr"/>
+      <c r="U90" s="6" t="inlineStr">
+        <is>
+          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
+        </is>
+      </c>
+      <c r="V90" s="6" t="inlineStr">
+        <is>
+          <t>Danielle's condition on the hire: clean up the system first so the role can function. Nicole's action item from the review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>People &amp; Admin</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Employee handbook and HR policy</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr"/>
+      <c r="I91" s="7" t="inlineStr"/>
+      <c r="J91" s="7" t="inlineStr"/>
+      <c r="K91" s="7" t="inlineStr"/>
+      <c r="L91" s="7" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+      <c r="N91" s="7" t="inlineStr"/>
+      <c r="O91" s="7" t="inlineStr"/>
+      <c r="P91" s="7" t="inlineStr"/>
+      <c r="Q91" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R91" s="7" t="inlineStr"/>
+      <c r="S91" s="7" t="inlineStr"/>
+      <c r="T91" s="6" t="inlineStr"/>
+      <c r="U91" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="V91" s="6" t="inlineStr">
+        <is>
+          <t>Calm HR drafts and maintains; Alvin is the liaison and answers for it; Danielle co-approves. Handbook is in flight as of 2026-07-30 and goes to legal review before implementation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>People &amp; Admin</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>Benefits administration and payroll processing</t>
+        </is>
+      </c>
+      <c r="C92" s="7" t="inlineStr"/>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr"/>
+      <c r="H92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr"/>
+      <c r="J92" s="7" t="inlineStr"/>
+      <c r="K92" s="7" t="inlineStr"/>
+      <c r="L92" s="7" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+      <c r="N92" s="7" t="inlineStr"/>
+      <c r="O92" s="7" t="inlineStr"/>
+      <c r="P92" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q92" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R92" s="7" t="inlineStr"/>
+      <c r="S92" s="7" t="inlineStr"/>
+      <c r="T92" s="6" t="inlineStr"/>
+      <c r="U92" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="V92" s="6" t="inlineStr">
+        <is>
+          <t>Calm HR administers as co-employer. Ironclad consulted where payroll hits the books.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="inlineStr">
+        <is>
+          <t>People &amp; Admin</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>Employment compliance and separations</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr"/>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E93" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr"/>
+      <c r="J93" s="7" t="inlineStr"/>
+      <c r="K93" s="7" t="inlineStr"/>
+      <c r="L93" s="7" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+      <c r="N93" s="7" t="inlineStr"/>
+      <c r="O93" s="7" t="inlineStr"/>
+      <c r="P93" s="7" t="inlineStr"/>
+      <c r="Q93" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="R93" s="7" t="inlineStr"/>
+      <c r="S93" s="7" t="inlineStr"/>
+      <c r="T93" s="6" t="inlineStr"/>
+      <c r="U93" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (external partners)</t>
+        </is>
+      </c>
+      <c r="V93" s="6" t="inlineStr">
+        <is>
+          <t>Calm HR runs the process with outside counsel where needed. Danielle co-approves every separation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>PLM schema, write path, audit log and Supabase wiki custody</t>
+        </is>
+      </c>
+      <c r="C94" s="7" t="inlineStr"/>
+      <c r="D94" s="7" t="inlineStr"/>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr"/>
+      <c r="H94" s="7" t="inlineStr"/>
+      <c r="I94" s="7" t="inlineStr"/>
+      <c r="J94" s="7" t="inlineStr"/>
+      <c r="K94" s="7" t="inlineStr"/>
+      <c r="L94" s="7" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O94" s="7" t="inlineStr"/>
+      <c r="P94" s="7" t="inlineStr"/>
+      <c r="Q94" s="7" t="inlineStr"/>
+      <c r="R94" s="7" t="inlineStr"/>
+      <c r="S94" s="7" t="inlineStr"/>
+      <c r="T94" s="6" t="inlineStr"/>
+      <c r="U94" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/plm-assistant/SKILL.md:292; decisions/wiki-layer-audit-2026-07-29.md:52</t>
+        </is>
+      </c>
+      <c r="V94" s="6" t="inlineStr">
+        <is>
+          <t>plm-assistant is the sole PLM writer and every write needs Operations sign-off. Job 0 wiki write-back has not fired since 2026-05-26. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>Landing hub publish and Netlify Function maintenance</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr"/>
+      <c r="D95" s="7" t="inlineStr"/>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="7" t="inlineStr"/>
+      <c r="J95" s="7" t="inlineStr"/>
+      <c r="K95" s="7" t="inlineStr"/>
+      <c r="L95" s="7" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+      <c r="N95" s="7" t="inlineStr"/>
+      <c r="O95" s="7" t="inlineStr"/>
+      <c r="P95" s="7" t="inlineStr"/>
+      <c r="Q95" s="7" t="inlineStr"/>
+      <c r="R95" s="7" t="inlineStr"/>
+      <c r="S95" s="7" t="inlineStr"/>
+      <c r="T95" s="6" t="inlineStr"/>
+      <c r="U95" s="6" t="inlineStr">
+        <is>
+          <t>.claude/skills/quality-status-reporter/SKILL.md:34-50; .claude/skills/quality-status-reporter/references/hub-integration.md:85</t>
+        </is>
+      </c>
+      <c r="V95" s="6" t="inlineStr">
+        <is>
+          <t>All hub writes go through the landing-hub-publish Function behind an Operator gate. Deploy is commit-and-push only, never Netlify CLI. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>Asana project, section, custom-field and connector configuration</t>
+        </is>
+      </c>
+      <c r="C96" s="7" t="inlineStr"/>
+      <c r="D96" s="7" t="inlineStr"/>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="7" t="inlineStr"/>
+      <c r="J96" s="7" t="inlineStr"/>
+      <c r="K96" s="7" t="inlineStr"/>
+      <c r="L96" s="7" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+      <c r="N96" s="7" t="inlineStr"/>
+      <c r="O96" s="7" t="inlineStr"/>
+      <c r="P96" s="7" t="inlineStr"/>
+      <c r="Q96" s="7" t="inlineStr"/>
+      <c r="R96" s="7" t="inlineStr"/>
+      <c r="S96" s="7" t="inlineStr"/>
+      <c r="T96" s="6" t="inlineStr"/>
+      <c r="U96" s="6" t="inlineStr">
+        <is>
+          <t>references/architecture/asana_task_contract.md:227; connections.md:5-13</t>
+        </is>
+      </c>
+      <c r="V96" s="6" t="inlineStr">
+        <is>
+          <t>An unresolvable role-holder is surfaced for Alvin to decide, not dropped. Seven tool domains registered; iMessage still not connected. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>Skill suite authorship, audit and versioning</t>
+        </is>
+      </c>
+      <c r="C97" s="7" t="inlineStr"/>
+      <c r="D97" s="7" t="inlineStr"/>
+      <c r="E97" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr"/>
+      <c r="G97" s="7" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr"/>
+      <c r="I97" s="7" t="inlineStr"/>
+      <c r="J97" s="7" t="inlineStr"/>
+      <c r="K97" s="7" t="inlineStr"/>
+      <c r="L97" s="7" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+      <c r="N97" s="7" t="inlineStr"/>
+      <c r="O97" s="7" t="inlineStr"/>
+      <c r="P97" s="7" t="inlineStr"/>
+      <c r="Q97" s="7" t="inlineStr"/>
+      <c r="R97" s="7" t="inlineStr"/>
+      <c r="S97" s="7" t="inlineStr"/>
+      <c r="T97" s="6" t="inlineStr"/>
+      <c r="U97" s="6" t="inlineStr">
+        <is>
+          <t>decisions/skills-architecture-tracker.md:4; decisions/log.md:31,45</t>
+        </is>
+      </c>
+      <c r="V97" s="6" t="inlineStr">
+        <is>
+          <t>Owner recorded as Alvin Belt across the architecture decisions. Priority 2 of 2 this quarter. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>The 23 scheduled Routines and their HITL gates</t>
+        </is>
+      </c>
+      <c r="C98" s="7" t="inlineStr"/>
+      <c r="D98" s="7" t="inlineStr"/>
+      <c r="E98" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr"/>
+      <c r="H98" s="7" t="inlineStr"/>
+      <c r="I98" s="7" t="inlineStr"/>
+      <c r="J98" s="7" t="inlineStr"/>
+      <c r="K98" s="7" t="inlineStr"/>
+      <c r="L98" s="7" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+      <c r="N98" s="7" t="inlineStr"/>
+      <c r="O98" s="7" t="inlineStr"/>
+      <c r="P98" s="7" t="inlineStr"/>
+      <c r="Q98" s="7" t="inlineStr"/>
+      <c r="R98" s="7" t="inlineStr"/>
+      <c r="S98" s="7" t="inlineStr"/>
+      <c r="T98" s="6" t="inlineStr"/>
+      <c r="U98" s="6" t="inlineStr">
+        <is>
+          <t>scheduled-prompts/weekly-pd-update.md:91; scheduled-prompts/sjs-purchasing-monthly-rollup-and-snapshot.md:79</t>
+        </is>
+      </c>
+      <c r="V98" s="6" t="inlineStr">
+        <is>
+          <t>Nothing commits until Alvin says go. Same pattern across all 23 Routines, including the ones that fire unattended on a schedule. A and R both AB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>RACI and role framework across Operations and PD</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr"/>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E99" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="7" t="inlineStr"/>
+      <c r="J99" s="7" t="inlineStr"/>
+      <c r="K99" s="7" t="inlineStr"/>
+      <c r="L99" s="7" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+      <c r="N99" s="7" t="inlineStr"/>
+      <c r="O99" s="7" t="inlineStr"/>
+      <c r="P99" s="7" t="inlineStr"/>
+      <c r="Q99" s="7" t="inlineStr"/>
+      <c r="R99" s="7" t="inlineStr"/>
+      <c r="S99" s="7" t="inlineStr"/>
+      <c r="T99" s="6" t="inlineStr"/>
+      <c r="U99" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 52:12-52:39</t>
         </is>
       </c>
-      <c r="T88" s="6" t="inlineStr">
+      <c r="V99" s="6" t="inlineStr">
         <is>
           <t>Alvin owns the framework, built with Nicole in the builder session, then to Danielle for final review before it goes to Calm HR to start recruiting.</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="10" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>Website platform, Shopify storefront and web releases</t>
+        </is>
+      </c>
+      <c r="C100" s="7" t="inlineStr"/>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr"/>
+      <c r="H100" s="7" t="inlineStr"/>
+      <c r="I100" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J100" s="7" t="inlineStr"/>
+      <c r="K100" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M100" s="7" t="inlineStr"/>
+      <c r="N100" s="7" t="inlineStr"/>
+      <c r="O100" s="7" t="inlineStr"/>
+      <c r="P100" s="7" t="inlineStr"/>
+      <c r="Q100" s="7" t="inlineStr"/>
+      <c r="R100" s="7" t="inlineStr"/>
+      <c r="S100" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="T100" s="6" t="inlineStr"/>
+      <c r="U100" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V100" s="6" t="inlineStr">
+        <is>
+          <t>Teknologics is the web development partner. Danielle accountable; Nicole is the systems and tech owner; Erin and Ivy on visual design; Soraya consulted on merchandising and content; Alvin informed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>Web and digital systems ownership, including the Teknologics engagement</t>
+        </is>
+      </c>
+      <c r="C101" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr"/>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J101" s="7" t="inlineStr"/>
+      <c r="K101" s="7" t="inlineStr"/>
+      <c r="L101" s="7" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+      <c r="N101" s="7" t="inlineStr"/>
+      <c r="O101" s="7" t="inlineStr"/>
+      <c r="P101" s="7" t="inlineStr"/>
+      <c r="Q101" s="7" t="inlineStr"/>
+      <c r="R101" s="7" t="inlineStr"/>
+      <c r="S101" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T101" s="6" t="inlineStr"/>
+      <c r="U101" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+        </is>
+      </c>
+      <c r="V101" s="6" t="inlineStr">
+        <is>
+          <t>Nicole is the systems and tech owner for the web and digital stack. Scoped here to web and digital rather than the whole IT function - the PLM, Asana, hub-publish and Routine rows still sit with Alvin. Confirm whether that should widen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="11" t="n"/>
-      <c r="B91" s="12" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="11" t="n"/>
+      <c r="B104" s="12" t="inlineStr">
         <is>
           <t>A = answers for the outcome (exactly one per row)</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="13" t="n"/>
-      <c r="B92" s="12" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="13" t="n"/>
+      <c r="B105" s="12" t="inlineStr">
         <is>
           <t>R = does the work (exactly one per row)</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="11" t="n"/>
-      <c r="B93" s="12" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="11" t="n"/>
+      <c r="B106" s="12" t="inlineStr">
         <is>
           <t>A/R = the same person holds both, so the row has no second pair of eyes</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="B94" s="12" t="inlineStr">
+    <row r="107">
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>C = consulted before the decision</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="B95" s="12" t="inlineStr">
+    <row r="108">
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>I = informed after it</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="B96" s="12" t="inlineStr">
+    <row r="109">
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>-&gt; = the open seat that absorbs R on hire. Open seats never hold A or R.</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="10" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="10" t="inlineStr">
         <is>
           <t>Positions</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="14" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B99" s="14" t="inlineStr">
+      <c r="B112" s="14" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="C99" s="14" t="inlineStr">
+      <c r="C112" s="14" t="inlineStr">
         <is>
           <t>Holder</t>
         </is>
       </c>
-      <c r="D99" s="14" t="inlineStr">
+      <c r="D112" s="14" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E99" s="14" t="inlineStr">
+      <c r="E112" s="14" t="inlineStr">
         <is>
           <t>A count</t>
         </is>
       </c>
-      <c r="F99" s="14" t="inlineStr">
+      <c r="F112" s="14" t="inlineStr">
         <is>
           <t>R count</t>
         </is>
       </c>
-      <c r="G99" s="14" t="inlineStr">
+      <c r="G112" s="14" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H99" s="14" t="inlineStr">
+      <c r="H112" s="14" t="inlineStr">
         <is>
           <t>Hands off</t>
         </is>
       </c>
-      <c r="I99" s="14" t="inlineStr">
+      <c r="I112" s="14" t="inlineStr">
         <is>
           <t>Absorbs</t>
         </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="12" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="B100" s="12" t="inlineStr">
-        <is>
-          <t>Owner / Founder</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="inlineStr">
-        <is>
-          <t>Ayesha Curry</t>
-        </is>
-      </c>
-      <c r="D100" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="12" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="B101" s="12" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="inlineStr">
-        <is>
-          <t>Danielle Iturbe</t>
-        </is>
-      </c>
-      <c r="D101" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E101" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="F101" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="12" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="B102" s="12" t="inlineStr">
-        <is>
-          <t>VP of Operations</t>
-        </is>
-      </c>
-      <c r="C102" s="12" t="inlineStr">
-        <is>
-          <t>Alvin Belt</t>
-        </is>
-      </c>
-      <c r="D102" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>44</v>
-      </c>
-      <c r="F102" s="15" t="n">
-        <v>55</v>
-      </c>
-      <c r="G102" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="H102" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="I102" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="12" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B103" s="12" t="inlineStr">
-        <is>
-          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
-        </is>
-      </c>
-      <c r="C103" s="12" t="inlineStr">
-        <is>
-          <t>Nicole Iturbe</t>
-        </is>
-      </c>
-      <c r="D103" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>21</v>
-      </c>
-      <c r="F103" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="G103" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="H103" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I103" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="12" t="inlineStr">
-        <is>
-          <t>OPS</t>
-        </is>
-      </c>
-      <c r="B104" s="12" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="C104" s="12" t="inlineStr">
-        <is>
-          <t>Open seat</t>
-        </is>
-      </c>
-      <c r="D104" s="16" t="inlineStr">
-        <is>
-          <t>recruiting</t>
-        </is>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="15" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="12" t="inlineStr">
-        <is>
-          <t>PDS</t>
-        </is>
-      </c>
-      <c r="B105" s="12" t="inlineStr">
-        <is>
-          <t>Product Development Specialist</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="inlineStr">
-        <is>
-          <t>Open seat</t>
-        </is>
-      </c>
-      <c r="D105" s="16" t="inlineStr">
-        <is>
-          <t>phased</t>
-        </is>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="15" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="12" t="inlineStr">
-        <is>
-          <t>SS</t>
-        </is>
-      </c>
-      <c r="B106" s="12" t="inlineStr">
-        <is>
-          <t>Marketing Manager</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="inlineStr">
-        <is>
-          <t>Soraya Salgadoe</t>
-        </is>
-      </c>
-      <c r="D106" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E106" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F106" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="G106" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t>KL</t>
-        </is>
-      </c>
-      <c r="B107" s="12" t="inlineStr">
-        <is>
-          <t>Social Media Coordinator</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="inlineStr">
-        <is>
-          <t>Kate Le</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G107" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="12" t="inlineStr">
-        <is>
-          <t>EH</t>
-        </is>
-      </c>
-      <c r="B108" s="12" t="inlineStr">
-        <is>
-          <t>Creative Director</t>
-        </is>
-      </c>
-      <c r="C108" s="12" t="inlineStr">
-        <is>
-          <t>Erin Hover</t>
-        </is>
-      </c>
-      <c r="D108" s="12" t="inlineStr">
-        <is>
-          <t>contractor</t>
-        </is>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="F108" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G108" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H108" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="12" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="B109" s="12" t="inlineStr">
-        <is>
-          <t>Creative / Design Coordinator</t>
-        </is>
-      </c>
-      <c r="C109" s="12" t="inlineStr">
-        <is>
-          <t>Ivy Tan</t>
-        </is>
-      </c>
-      <c r="D109" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G109" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H109" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="12" t="inlineStr">
-        <is>
-          <t>JH</t>
-        </is>
-      </c>
-      <c r="B110" s="12" t="inlineStr">
-        <is>
-          <t>Packaging Engineer</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="inlineStr">
-        <is>
-          <t>Jan Haeck</t>
-        </is>
-      </c>
-      <c r="D110" s="12" t="inlineStr">
-        <is>
-          <t>contractor</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="12" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="B111" s="12" t="inlineStr">
-        <is>
-          <t>PD / R&amp;D contractor, Milinyc</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="inlineStr">
-        <is>
-          <t>Perrine Calvet</t>
-        </is>
-      </c>
-      <c r="D111" s="12" t="inlineStr">
-        <is>
-          <t>contractor</t>
-        </is>
-      </c>
-      <c r="E111" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F111" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G111" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H111" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="12" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="B112" s="12" t="inlineStr">
-        <is>
-          <t>External regulatory partner</t>
-        </is>
-      </c>
-      <c r="C112" s="12" t="inlineStr">
-        <is>
-          <t>Pedrero Regulatory</t>
-        </is>
-      </c>
-      <c r="D112" s="12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>IF</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>Outsourced finance (Dan Bender)</t>
+          <t>Owner / Founder</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Ironclad Finance</t>
+          <t>Ayesha Curry</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E113" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G113" s="15" t="n">
         <v>0</v>
@@ -6297,54 +6858,609 @@
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
+          <t>DI</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>Danielle Iturbe</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>VP of Operations</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>Alvin Belt</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>43</v>
+      </c>
+      <c r="F115" s="15" t="n">
+        <v>57</v>
+      </c>
+      <c r="G115" s="15" t="n">
+        <v>29</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>30</v>
+      </c>
+      <c r="I115" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>Nicole Iturbe</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>26</v>
+      </c>
+      <c r="F116" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="G116" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H116" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="I116" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>Open seat</t>
+        </is>
+      </c>
+      <c r="D117" s="16" t="inlineStr">
+        <is>
+          <t>recruiting</t>
+        </is>
+      </c>
+      <c r="E117" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="15" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>PDS</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>Open seat</t>
+        </is>
+      </c>
+      <c r="D118" s="16" t="inlineStr">
+        <is>
+          <t>phased</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="15" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>Soraya Salgadoe</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>8</v>
+      </c>
+      <c r="F119" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G119" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>Social Media Coordinator</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>Kate Le</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G120" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>EH</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Creative Director</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>Erin Hover</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>contractor</t>
+        </is>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F121" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G121" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>Creative / Design Coordinator</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>Ivy Tan</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>JH</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Packaging Engineer</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>Jan Haeck</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>contractor</t>
+        </is>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G123" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>PD / R&amp;D contractor, Milinyc</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>Perrine Calvet</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>contractor</t>
+        </is>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F124" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G124" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>External regulatory partner</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>Pedrero Regulatory</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>IF</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>Outsourced finance (Dan Bender)</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>Ironclad Finance</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="B114" s="12" t="inlineStr">
+      <c r="B127" s="12" t="inlineStr">
         <is>
           <t>PEO and co-employer</t>
         </is>
       </c>
-      <c r="C114" s="12" t="inlineStr">
+      <c r="C127" s="12" t="inlineStr">
         <is>
           <t>Calm HR</t>
         </is>
       </c>
-      <c r="D114" s="12" t="inlineStr">
+      <c r="D127" s="12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="E114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="15" t="n">
+      <c r="E127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="G114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="14" t="inlineStr">
+      <c r="G127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>Digital marketing agency</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>WITHIN</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G128" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>TK</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Web development</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>Teknologics</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="inlineStr">
         <is>
           <t>Source of truth</t>
         </is>
       </c>
-      <c r="B116" s="17" t="inlineStr">
-        <is>
-          <t>Rows citing a path are relative to the SJ-OS repo. Rows citing the 30 July leadership review, the 27 July email to Danielle, or a job description come from those documents directly. Rows marked INFERRED in Notes have no owner named in any source; A defaults to Alvin Belt because the work falls there in practice.</t>
+      <c r="B131" s="17" t="inlineStr">
+        <is>
+          <t>Rows citing a path are relative to the SJ-OS repo. Rows prefixed acb-thelanding cite the AC Brands landing hub, whose links.json defines eleven functions with a named lead each. Rows citing the 30 July leadership review, the 27 July email to Danielle, a job description, or Alvin directly come from those sources. Every row on this matrix has an owner - there are no inferred owners left.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:T88"/>
+  <autoFilter ref="A2:V101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6355,7 +7471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -6437,15 +7553,15 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>COUNTIF(RACI!C3:C88,"A")+COUNTIF(RACI!C3:C88,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C101,"A")+COUNTIF(RACI!C3:C101,"A/R")</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>COUNTIF(RACI!C3:C88,"R")+COUNTIF(RACI!C3:C88,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C101,"R")+COUNTIF(RACI!C3:C101,"A/R")</f>
         <v/>
       </c>
       <c r="D6" s="15">
-        <f>COUNTIF(RACI!C3:C88,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C101,"A/R")</f>
         <v/>
       </c>
       <c r="E6" s="15" t="n">
@@ -6470,15 +7586,15 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>COUNTIF(RACI!D3:D88,"A")+COUNTIF(RACI!D3:D88,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D101,"A")+COUNTIF(RACI!D3:D101,"A/R")</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>COUNTIF(RACI!D3:D88,"R")+COUNTIF(RACI!D3:D88,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D101,"R")+COUNTIF(RACI!D3:D101,"A/R")</f>
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>COUNTIF(RACI!D3:D88,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D101,"A/R")</f>
         <v/>
       </c>
       <c r="E7" s="15" t="n">
@@ -6503,19 +7619,19 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>COUNTIF(RACI!E3:E88,"A")+COUNTIF(RACI!E3:E88,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E101,"A")+COUNTIF(RACI!E3:E101,"A/R")</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>COUNTIF(RACI!E3:E88,"R")+COUNTIF(RACI!E3:E88,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E101,"R")+COUNTIF(RACI!E3:E101,"A/R")</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>COUNTIF(RACI!E3:E88,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E101,"A/R")</f>
         <v/>
       </c>
       <c r="E8" s="15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0</v>
@@ -6536,15 +7652,15 @@
         </is>
       </c>
       <c r="B9" s="15">
-        <f>COUNTIF(RACI!F3:F88,"A")+COUNTIF(RACI!F3:F88,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F101,"A")+COUNTIF(RACI!F3:F101,"A/R")</f>
         <v/>
       </c>
       <c r="C9" s="15">
-        <f>COUNTIF(RACI!F3:F88,"R")+COUNTIF(RACI!F3:F88,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F101,"R")+COUNTIF(RACI!F3:F101,"A/R")</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>COUNTIF(RACI!F3:F88,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F101,"A/R")</f>
         <v/>
       </c>
       <c r="E9" s="15" t="n">
@@ -6569,22 +7685,22 @@
         </is>
       </c>
       <c r="B10" s="15">
-        <f>COUNTIF(RACI!G3:G88,"A")+COUNTIF(RACI!G3:G88,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G101,"A")+COUNTIF(RACI!G3:G101,"A/R")</f>
         <v/>
       </c>
       <c r="C10" s="15">
-        <f>COUNTIF(RACI!G3:G88,"R")+COUNTIF(RACI!G3:G88,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G101,"R")+COUNTIF(RACI!G3:G101,"A/R")</f>
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>COUNTIF(RACI!G3:G88,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G101,"A/R")</f>
         <v/>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" s="15">
         <f>B10</f>
@@ -6602,15 +7718,15 @@
         </is>
       </c>
       <c r="B11" s="15">
-        <f>COUNTIF(RACI!H3:H88,"A")+COUNTIF(RACI!H3:H88,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H101,"A")+COUNTIF(RACI!H3:H101,"A/R")</f>
         <v/>
       </c>
       <c r="C11" s="15">
-        <f>COUNTIF(RACI!H3:H88,"R")+COUNTIF(RACI!H3:H88,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H101,"R")+COUNTIF(RACI!H3:H101,"A/R")</f>
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>COUNTIF(RACI!H3:H88,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H101,"A/R")</f>
         <v/>
       </c>
       <c r="E11" s="15" t="n">
@@ -6635,15 +7751,15 @@
         </is>
       </c>
       <c r="B12" s="15">
-        <f>COUNTIF(RACI!I3:I88,"A")+COUNTIF(RACI!I3:I88,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I101,"A")+COUNTIF(RACI!I3:I101,"A/R")</f>
         <v/>
       </c>
       <c r="C12" s="15">
-        <f>COUNTIF(RACI!I3:I88,"R")+COUNTIF(RACI!I3:I88,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I101,"R")+COUNTIF(RACI!I3:I101,"A/R")</f>
         <v/>
       </c>
       <c r="D12" s="15">
-        <f>COUNTIF(RACI!I3:I88,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I101,"A/R")</f>
         <v/>
       </c>
       <c r="E12" s="15" t="n">
@@ -6668,15 +7784,15 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>COUNTIF(RACI!J3:J88,"A")+COUNTIF(RACI!J3:J88,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J101,"A")+COUNTIF(RACI!J3:J101,"A/R")</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>COUNTIF(RACI!J3:J88,"R")+COUNTIF(RACI!J3:J88,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J101,"R")+COUNTIF(RACI!J3:J101,"A/R")</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>COUNTIF(RACI!J3:J88,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J101,"A/R")</f>
         <v/>
       </c>
       <c r="E13" s="15" t="n">
@@ -6701,15 +7817,15 @@
         </is>
       </c>
       <c r="B14" s="15">
-        <f>COUNTIF(RACI!K3:K88,"A")+COUNTIF(RACI!K3:K88,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K101,"A")+COUNTIF(RACI!K3:K101,"A/R")</f>
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>COUNTIF(RACI!K3:K88,"R")+COUNTIF(RACI!K3:K88,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K101,"R")+COUNTIF(RACI!K3:K101,"A/R")</f>
         <v/>
       </c>
       <c r="D14" s="15">
-        <f>COUNTIF(RACI!K3:K88,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K101,"A/R")</f>
         <v/>
       </c>
       <c r="E14" s="15" t="n">
@@ -6734,15 +7850,15 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF(RACI!L3:L88,"A")+COUNTIF(RACI!L3:L88,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L101,"A")+COUNTIF(RACI!L3:L101,"A/R")</f>
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>COUNTIF(RACI!L3:L88,"R")+COUNTIF(RACI!L3:L88,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L101,"R")+COUNTIF(RACI!L3:L101,"A/R")</f>
         <v/>
       </c>
       <c r="D15" s="15">
-        <f>COUNTIF(RACI!L3:L88,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L101,"A/R")</f>
         <v/>
       </c>
       <c r="E15" s="15" t="n">
@@ -6767,15 +7883,15 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF(RACI!M3:M88,"A")+COUNTIF(RACI!M3:M88,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M101,"A")+COUNTIF(RACI!M3:M101,"A/R")</f>
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>COUNTIF(RACI!M3:M88,"R")+COUNTIF(RACI!M3:M88,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M101,"R")+COUNTIF(RACI!M3:M101,"A/R")</f>
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>COUNTIF(RACI!M3:M88,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M101,"A/R")</f>
         <v/>
       </c>
       <c r="E16" s="15" t="n">
@@ -6800,15 +7916,15 @@
         </is>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF(RACI!N3:N88,"A")+COUNTIF(RACI!N3:N88,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N101,"A")+COUNTIF(RACI!N3:N101,"A/R")</f>
         <v/>
       </c>
       <c r="C17" s="15">
-        <f>COUNTIF(RACI!N3:N88,"R")+COUNTIF(RACI!N3:N88,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N101,"R")+COUNTIF(RACI!N3:N101,"A/R")</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>COUNTIF(RACI!N3:N88,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N101,"A/R")</f>
         <v/>
       </c>
       <c r="E17" s="15" t="n">
@@ -6833,15 +7949,15 @@
         </is>
       </c>
       <c r="B18" s="15">
-        <f>COUNTIF(RACI!O3:O88,"A")+COUNTIF(RACI!O3:O88,"A/R")</f>
+        <f>COUNTIF(RACI!O3:O101,"A")+COUNTIF(RACI!O3:O101,"A/R")</f>
         <v/>
       </c>
       <c r="C18" s="15">
-        <f>COUNTIF(RACI!O3:O88,"R")+COUNTIF(RACI!O3:O88,"A/R")</f>
+        <f>COUNTIF(RACI!O3:O101,"R")+COUNTIF(RACI!O3:O101,"A/R")</f>
         <v/>
       </c>
       <c r="D18" s="15">
-        <f>COUNTIF(RACI!O3:O88,"A/R")</f>
+        <f>COUNTIF(RACI!O3:O101,"A/R")</f>
         <v/>
       </c>
       <c r="E18" s="15" t="n">
@@ -6866,15 +7982,15 @@
         </is>
       </c>
       <c r="B19" s="15">
-        <f>COUNTIF(RACI!P3:P88,"A")+COUNTIF(RACI!P3:P88,"A/R")</f>
+        <f>COUNTIF(RACI!P3:P101,"A")+COUNTIF(RACI!P3:P101,"A/R")</f>
         <v/>
       </c>
       <c r="C19" s="15">
-        <f>COUNTIF(RACI!P3:P88,"R")+COUNTIF(RACI!P3:P88,"A/R")</f>
+        <f>COUNTIF(RACI!P3:P101,"R")+COUNTIF(RACI!P3:P101,"A/R")</f>
         <v/>
       </c>
       <c r="D19" s="15">
-        <f>COUNTIF(RACI!P3:P88,"A/R")</f>
+        <f>COUNTIF(RACI!P3:P101,"A/R")</f>
         <v/>
       </c>
       <c r="E19" s="15" t="n">
@@ -6899,15 +8015,15 @@
         </is>
       </c>
       <c r="B20" s="15">
-        <f>COUNTIF(RACI!Q3:Q88,"A")+COUNTIF(RACI!Q3:Q88,"A/R")</f>
+        <f>COUNTIF(RACI!Q3:Q101,"A")+COUNTIF(RACI!Q3:Q101,"A/R")</f>
         <v/>
       </c>
       <c r="C20" s="15">
-        <f>COUNTIF(RACI!Q3:Q88,"R")+COUNTIF(RACI!Q3:Q88,"A/R")</f>
+        <f>COUNTIF(RACI!Q3:Q101,"R")+COUNTIF(RACI!Q3:Q101,"A/R")</f>
         <v/>
       </c>
       <c r="D20" s="15">
-        <f>COUNTIF(RACI!Q3:Q88,"A/R")</f>
+        <f>COUNTIF(RACI!Q3:Q101,"A/R")</f>
         <v/>
       </c>
       <c r="E20" s="15" t="n">
@@ -6926,268 +8042,374 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>WI — Digital marketing agency (WITHIN)</t>
+        </is>
+      </c>
+      <c r="B21" s="15">
+        <f>COUNTIF(RACI!R3:R101,"A")+COUNTIF(RACI!R3:R101,"A/R")</f>
+        <v/>
+      </c>
+      <c r="C21" s="15">
+        <f>COUNTIF(RACI!R3:R101,"R")+COUNTIF(RACI!R3:R101,"A/R")</f>
+        <v/>
+      </c>
+      <c r="D21" s="15">
+        <f>COUNTIF(RACI!R3:R101,"A/R")</f>
+        <v/>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="15">
+        <f>B21</f>
+        <v/>
+      </c>
+      <c r="H21" s="15">
+        <f>C21-E21+F21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>TK — Web development (Teknologics)</t>
+        </is>
+      </c>
+      <c r="B22" s="15">
+        <f>COUNTIF(RACI!S3:S101,"A")+COUNTIF(RACI!S3:S101,"A/R")</f>
+        <v/>
+      </c>
+      <c r="C22" s="15">
+        <f>COUNTIF(RACI!S3:S101,"R")+COUNTIF(RACI!S3:S101,"A/R")</f>
+        <v/>
+      </c>
+      <c r="D22" s="15">
+        <f>COUNTIF(RACI!S3:S101,"A/R")</f>
+        <v/>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="15">
+        <f>B22</f>
+        <v/>
+      </c>
+      <c r="H22" s="15">
+        <f>C22-E22+F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Total activities</t>
         </is>
       </c>
-      <c r="B21" s="21">
-        <f>COUNTA(RACI!B3:B88)</f>
+      <c r="B23" s="21">
+        <f>COUNTA(RACI!B3:B101)</f>
         <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>"A after" and "R after" project the book once both specialist seats are filled. Hands off counts rows where this position does the work today and an incoming seat takes it. Absorbs counts rows arriving on hire.</t>
-        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>Quality now has a gate, and it is not the VP</t>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>"A after" and "R after" project the book once both specialist seats are filled. Hands off counts rows where this position does the work today and an incoming seat takes it. Absorbs counts rows arriving on hire.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
     </row>
-    <row r="27" ht="78" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>The 30 July leadership review moved the quality function onto Nicole. Verbatim from the recording: "Nicole taking the primary focus on the quality management side of things with quality control... anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check... Even with each function having or being the primary owner, we'll still have that quality gate." That shows up as 10 of the 13 Quality rows accountable to Nicole, against 2 for Alvin and 1 for Perrine. Her total book of accountability goes from 8 rows to 21.</t>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>Quality now has a gate, and it is not the VP</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="23" t="inlineStr">
-        <is>
-          <t>Perrine moves to technical guidance</t>
+    <row r="29" ht="78" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>The 30 July leadership review moved the quality function onto Nicole. Verbatim from the recording: "Nicole taking the primary focus on the quality management side of things with quality control... anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check... Even with each function having or being the primary owner, we'll still have that quality gate." That shows up as 10 of the 13 Quality rows accountable to Nicole, against 2 for Alvin and 1 for Perrine. Her total book of accountability goes from 8 rows to 21.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
     </row>
-    <row r="31" ht="117" customHeight="1">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>She keeps A on the 7 rows where the judgment is genuinely formulation - formula stage-gate, compatibility and stability and RIPT and PET, in-market stability testing, reformulation, PD-linked receipt, and the two margin rows that turn on formulation cost. Packaging development moved to Erin Hover as the lead technical authority on packaging and artwork. She moves to consulted on everything process-shaped: NCR and CAPA lifecycle, batch hold and release, vendor quality flags, lab finding classification, SOP ratification. Danielle's framing in the review was that there were things the team had assumed Perrine would manage or organize that she is not, and that leadership can pull the plug even when she has submitted an approval. Splitting technical judgment from process ownership is what that means in practice.</t>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Perrine moves to technical guidance</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
-        <is>
-          <t>Three contractors hold accountability, and two of them hold it alone</t>
+    <row r="33" ht="117" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>She keeps A on the 7 rows where the judgment is genuinely formulation - formula stage-gate, compatibility and stability and RIPT and PET, in-market stability testing, reformulation, PD-linked receipt, and the two margin rows that turn on formulation cost. Packaging development moved to Erin Hover as the lead technical authority on packaging and artwork. She moves to consulted on everything process-shaped: NCR and CAPA lifecycle, batch hold and release, vendor quality flags, lab finding classification, SOP ratification. Danielle's framing in the review was that there were things the team had assumed Perrine would manage or organize that she is not, and that leadership can pull the plug even when she has submitted an approval. Splitting technical judgment from process ownership is what that means in practice.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
     </row>
-    <row r="35" ht="104" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>Erin Hover is the lead technical authority on packaging and artwork and is accountable for 4 rows - creative direction, packaging development, artwork execution, and the label artwork archive. She is also a contractor, and on creative direction she is both A and R with no internal counterpart. Jan Haeck, who executes under her, is a contractor too, so the whole packaging and artwork chain runs through people outside the company. Perrine Calvet is the third, accountable for 7 formulation rows. Between them that is 11 of 79 activities where nobody on staff can check the work or continue it. Neither specialist job description covers creative or formulation authority, so the two hires do not close this.</t>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>Three contractors hold accountability, and two of them hold it alone</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
     </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
-        <is>
-          <t>Where the President and the Founder sit</t>
+    <row r="37" ht="104" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>Erin Hover is the lead technical authority on packaging and artwork and is accountable for 4 rows - creative direction, packaging development, artwork execution, and the label artwork archive. She is also a contractor, and on creative direction she is both A and R with no internal counterpart. Jan Haeck, who executes under her, is a contractor too, so the whole packaging and artwork chain runs through people outside the company. Perrine Calvet is the third, accountable for 7 formulation rows. Between them that is 11 of 79 activities where nobody on staff can check the work or continue it. Neither specialist job description covers creative or formulation authority, so the two hires do not close this.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
     </row>
-    <row r="39" ht="104" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Danielle Iturbe is accountable for 4 rows - direction-changing PD decisions, the margin walk-away call, brand guideline custody, and campaign direction - and is consulted on 13 more. She now appears on all 9 Marketing rows and all 3 Creative rows, which she did not before. Campaign direction was missing from the matrix entirely; adding it is what gave the President somewhere to sit in Marketing rather than only receiving finished work. Ayesha Curry keeps sole accountability for brand-line moves and is consulted on 6 rows where the brand carries her name - brand guideline custody, creative direction, campaign direction, claim substantiation, retailer attestations, and packaging. Informed on the rest.</t>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>Marketing and the channels finally have owners with real activities under them</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
     </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>Alvin owns the framework, and still does most of the work</t>
+    <row r="41" ht="91" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>Soraya goes from 1 accountable row to 8. Marketing now carries editorial calendar, Klaviyo email, paid media, social content, influencer and earned media, the WITHIN relationship, product copy and PDP content - none of which existed on the matrix before, because none of it has a skill behind it. Nicole goes from 21 to 26 with all-channel accountability plus wholesale pipeline, retail price architecture and the retailer promo calendar. Retail &amp; Wholesale went from 2 rows to 5, Marketing from 9 to 15. A skill suite is a good source for what is automated; it is a poor source for what a business does.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
     </row>
-    <row r="43" ht="65" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Accountable for 44 of 86 activities and doing the work on 55. The framework rows are deliberate - quality management system, SOP framework, this RACI, the skill suite, the 23 scheduled Routines. The problem is not the A column. It is that 31 rows have him as both A and R, and that he does the work on 11 of the 12 Operations rows and 5 of the 8 Product Development rows. He holds the gates and does the work behind them.</t>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>Where the President and the Founder sit</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
     </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="23" t="inlineStr">
-        <is>
-          <t>What the two seats actually move</t>
+    <row r="45" ht="104" customHeight="1">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>Danielle Iturbe is accountable for 8 rows - direction-changing PD decisions, the margin walk-away call, brand guideline custody, campaign direction, month-end close, the annual budget, and the two web rows - and is consulted on 25 more. She now appears on all 9 Marketing rows and all 3 Creative rows, which she did not before. Campaign direction was missing from the matrix entirely; adding it is what gave the President somewhere to sit in Marketing rather than only receiving finished work. Ayesha Curry keeps sole accountability for brand-line moves and is consulted on 6 rows where the brand carries her name - brand guideline custody, creative direction, campaign direction, claim substantiation, retailer attestations, and packaging. Informed on the rest.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
     </row>
-    <row r="47" ht="65" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
-        <is>
-          <t>32 rows transition on hire: 16 to the Operations Specialist and 16 to the Product Development Specialist. 29 of those come off Alvin, 3 off Nicole. His R book drops from 55 to 26. Rows with no second pair of eyes drop from 42 to 25 across the whole matrix. Both seats report to Nicole, which is the point Danielle made in the review - moving day-to-day management off the VP seat is the succession outcome the system is being built for.</t>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>Alvin owns the framework, and still does most of the work</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
     </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="23" t="inlineStr">
-        <is>
-          <t>Ops first is the right order, and the matrix says why</t>
+    <row r="49" ht="65" customHeight="1">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Accountable for 43 of 99 activities and doing the work on 57. The framework rows are deliberate - quality management system, SOP framework, this RACI, the skill suite, the 23 scheduled Routines. The problem is not the A column. It is that 31 rows have him as both A and R, and that he does the work on 11 of the 12 Operations rows and 5 of the 8 Product Development rows. He holds the gates and does the work behind them.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
     </row>
-    <row r="51" ht="91" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
-        <is>
-          <t>Alvin does the work on 11 of 12 Operations rows. The Operations Specialist job description covers almost exactly that list: daily order operations and the third-party logistics relationship, channel operations across the direct store and Ulta Beauty Marketplace and Amazon, inventory reconciliation and FEFO and out-of-stock signals, receiving, purchase-to-pay, freight and customs and broker relationships, routing-guide and advance-ship-notice compliance, sales and operations planning support, production scheduling, and the label and seeding and sampling projects. That is a defined function sitting on one person today.</t>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>What the two seats actually move</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
     </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="23" t="inlineStr">
-        <is>
-          <t>The PD seat is the one that closes the quality loop</t>
+    <row r="53" ht="65" customHeight="1">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>32 rows transition on hire: 16 to the Operations Specialist and 16 to the Product Development Specialist. 29 of those come off Alvin, 3 off Nicole. His R book drops from 55 to 26. Rows with no second pair of eyes drop from 42 to 25 across the whole matrix. Both seats report to Nicole, which is the point Danielle made in the review - moving day-to-day management off the VP seat is the succession outcome the system is being built for.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
     </row>
-    <row r="55" ht="104" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
-        <is>
-          <t>Its job description names running the quality system outright - corrective and preventive actions, non-conformances, complaint intake and trend monitoring, lab results, supplier quality flags, batch lifecycle including stability and hold-release, and the quality dashboard - plus pre-launch ingredient and label review, claim substantiation, retailer compliance responses and the registration tracker, and document control across specifications and dielines and artwork versions and bills of materials. Until it is filled, Nicole gates quality and Alvin executes it. That works, and it is the reason the gate is worth having now rather than after the hire, but it is two people covering a role that was written as one.</t>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>Ops first is the right order, and the matrix says why</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
     </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="23" t="inlineStr">
-        <is>
-          <t>Three functions run entirely outside the company</t>
+    <row r="57" ht="91" customHeight="1">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>Alvin does the work on 11 of 12 Operations rows. The Operations Specialist job description covers almost exactly that list: daily order operations and the third-party logistics relationship, channel operations across the direct store and Ulta Beauty Marketplace and Amazon, inventory reconciliation and FEFO and out-of-stock signals, receiving, purchase-to-pay, freight and customs and broker relationships, routing-guide and advance-ship-notice compliance, sales and operations planning support, production scheduling, and the label and seeding and sampling projects. That is a defined function sitting on one person today.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
     </row>
-    <row r="59" ht="91" customHeight="1">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t>Regulatory goes through Pedrero Regulatory, Finance through Ironclad (Dan Bender), HR through Calm HR as PEO and co-employer. Adding them resolved two of the three unowned functions - Finance and HR were only unowned because the partners were missing from the matrix, not because nobody was doing the work. Between the three partner organisations and the three contractors on packaging, creative and formulation, six external parties hold the execution of six functions. For a team of nine that is a reasonable shape. What it means is that continuity rests on six engagements rather than on employment, and each is a renewal decision rather than a retention one.</t>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>The PD seat is the one that closes the quality loop</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
     </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="23" t="inlineStr">
-        <is>
-          <t>Regulatory is the odd one, and it cuts both ways</t>
+    <row r="61" ht="104" customHeight="1">
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>Its job description names running the quality system outright - corrective and preventive actions, non-conformances, complaint intake and trend monitoring, lab results, supplier quality flags, batch lifecycle including stability and hold-release, and the quality dashboard - plus pre-launch ingredient and label review, claim substantiation, retailer compliance responses and the registration tracker, and document control across specifications and dielines and artwork versions and bills of materials. Until it is filled, Nicole gates quality and Alvin executes it. That works, and it is the reason the gate is worth having now rather than after the hire, but it is two people covering a role that was written as one.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
     </row>
-    <row r="63" ht="78" customHeight="1">
-      <c r="A63" s="17" t="inlineStr">
-        <is>
-          <t>Pedrero is consulted on 11 rows and responsible for none. That is not an undervaluation - our own procedures make them consult-only with no Asana access and no internal authority, and Amy Pedrero holds the binding regulatory calls. The consequence is a split bottleneck: Pedrero forms every regulatory opinion, and Alvin performs every regulatory action, because the Operator and Reg Lead gates are both his and Pedrero cannot act inside our systems. Either the Reg Lead gate gets an alternate or Pedrero's remit widens; the current shape means regulatory work stops if either side is unavailable.</t>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="23" t="inlineStr">
+        <is>
+          <t>Nothing on this matrix is unowned any more</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
     </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="23" t="inlineStr">
-        <is>
-          <t>One row is still unowned</t>
+    <row r="65" ht="117" customHeight="1">
+      <c r="A65" s="17" t="inlineStr">
+        <is>
+          <t>The first pass reported three unowned functions. All three are now owned, and none of them were ever actually ownerless - they were missing from the sources. Finance and HR needed the partner organisations added. Marketing, wholesale and Shopify revenue needed the AC Brands landing hub, which defines eleven functions with an explicit lead per function and had three reading "Owned by TBD": Marketing, Finance, and the wholesale half of Sales &amp; Commerce. Resolving those took three decisions rather than three hires. Soraya is accountable for Marketing. Nicole is accountable for all channels - DTC, Amazon and wholesale together, which is broader than the hub had it. Danielle is accountable for web with Nicole as the systems and tech owner. That is 99 activities across eleven functions with an owner on every row.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
     </row>
-    <row r="67" ht="52" customHeight="1">
-      <c r="A67" s="17" t="inlineStr">
-        <is>
-          <t>Shopify revenue and channel position. It is registered as the revenue connection and named as the primary direct-to-consumer revenue track, but no process assigns ownership or an approval step, so it shows Alvin by inference rather than by source. The function closest to the top line is the least specified.</t>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="23" t="inlineStr">
+        <is>
+          <t>Five functions run entirely outside the company</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
     </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="23" t="inlineStr">
-        <is>
-          <t>Single points of failure that remain after both hires</t>
+    <row r="69" ht="91" customHeight="1">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>Regulatory goes through Pedrero, Finance through Ironclad (Dan Bender), HR through Calm HR as PEO and co-employer, digital marketing and email through WITHIN, web development through Teknologics. Add the three contractors on packaging, creative and formulation and that is eight external parties holding the execution of eight functions. For a team of nine it is a reasonable shape - it is how this surface gets covered at all. What it means is that continuity rests on eight engagements rather than on employment, and each is a renewal decision rather than a retention one. Engagement terms are recorded for Pedrero only.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
     </row>
-    <row r="71" ht="91" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
-        <is>
-          <t>Perrine is an external contractor holding A on 8 rows with no internal counterpart, and one of those - compatibility and stability and RIPT and PET - has her as both A and R. Nobody inside AC Brands can check that work or continue it. Alvin is the other: the Operator gate has no alternate anywhere in the suite, and all 23 scheduled Routines stop at a human approval only he can clear. Succession is documented exactly once in the entire system, for competitive intelligence. Nothing comparable exists for the quality gate, the technical advisor, or the framework owner. That gap costs hours to close, not headcount, and it is the one I would fix first.</t>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="23" t="inlineStr">
+        <is>
+          <t>Regulatory is the odd one, and it cuts both ways</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73" ht="78" customHeight="1">
+      <c r="A73" s="17" t="inlineStr">
+        <is>
+          <t>Pedrero is consulted on 11 rows and responsible for none. That is not an undervaluation - our own procedures make them consult-only with no Asana access and no internal authority, and Amy Pedrero holds the binding regulatory calls. The consequence is a split bottleneck: Pedrero forms every regulatory opinion, and Alvin performs every regulatory action, because the Operator and Reg Lead gates are both his and Pedrero cannot act inside our systems. Either the Reg Lead gate gets an alternate or Pedrero's remit widens; the current shape means regulatory work stops if either side is unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>One row is still unowned</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77" ht="52" customHeight="1">
+      <c r="A77" s="17" t="inlineStr">
+        <is>
+          <t>Shopify revenue and channel position. It is registered as the revenue connection and named as the primary direct-to-consumer revenue track, but no process assigns ownership or an approval step, so it shows Alvin by inference rather than by source. The function closest to the top line is the least specified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>Single points of failure that remain after both hires</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+    </row>
+    <row r="81" ht="91" customHeight="1">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>Perrine is an external contractor holding A on 8 rows with no internal counterpart, and one of those - compatibility and stability and RIPT and PET - has her as both A and R. Nobody inside AC Brands can check that work or continue it. Alvin is the other: the Operator gate has no alternate anywhere in the suite, and all 23 scheduled Routines stop at a human approval only he can clear. Succession is documented exactly once in the entire system, for competitive intelligence. Nothing comparable exists for the quality gate, the technical advisor, or the framework owner. That gap costs hours to close, not headcount, and it is the one I would fix first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7200,7 +8422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7392,7 +8614,7 @@
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>Unowned function</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -7402,52 +8624,52 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Shopify revenue and channel position has no owner or gate.</t>
+          <t>Shopify revenue and channel position is owned. Nicole is accountable for all channels - DTC, Amazon and wholesale - with Alvin doing the work and Danielle informed.</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Registered as the revenue connection and named as the primary direct-to-consumer revenue track, but no process assigns ownership. The function closest to the top line is the least specified.</t>
+          <t>Was the last row on the matrix with no owner. The landing hub had split DTC and Amazon to Alvin and left wholesale as TBD; consolidating all channels under one accountability closes it.</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Nicole on channel, Alvin on data - needs a decision</t>
+          <t>No action - every row on the matrix now has an owner</t>
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>connections.md:7; context/about-business.md:5</t>
+          <t>acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>Single point of failure</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Product Development</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Compatibility, stability, RIPT and PET decisions sit with an external contractor as both A and R.</t>
+          <t>Marketing is owned. Soraya is accountable across editorial, email, paid media and social. WITHIN responsible for paid and email execution, Kate for social content.</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>No internal counterpart can check the work or continue it. Pre-launch technical decisions have no second reader.</t>
+          <t>The landing hub listed Marketing as "Owned by TBD" with four named tools and nobody against them. Fifteen Marketing rows now have an owner.</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>PD Specialist as internal counterpart on hire</t>
+          <t>No action - confirm WITHIN engagement terms and renewal</t>
         </is>
       </c>
       <c r="F7" s="7" t="n">
@@ -7455,34 +8677,34 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>asana-pd-manager/references/role-map.md:16</t>
+          <t>acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>Concentration</t>
+          <t>Single point of failure</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>All functions</t>
+          <t>Product Development</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Three whole functions run through external partners: Regulatory (Pedrero), Finance (Ironclad), HR (Calm HR). Plus three contractors on packaging, creative and formulation.</t>
+          <t>Compatibility, stability, RIPT and PET decisions sit with an external contractor as both A and R.</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Six external parties hold the execution of Regulatory, Finance, HR, packaging, creative and formulation. Not a fault - it is how a team of nine covers this surface - but it means continuity rests on six engagements rather than on employment, and every one of them is a renewal decision.</t>
+          <t>No internal counterpart can check the work or continue it. Pre-launch technical decisions have no second reader.</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Confirm engagement terms and renewal dates for all six</t>
+          <t>PD Specialist as internal counterpart on hire</t>
         </is>
       </c>
       <c r="F8" s="7" t="n">
@@ -7490,34 +8712,34 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
+          <t>asana-pd-manager/references/role-map.md:16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>Single point of failure</t>
+          <t>Concentration</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Compliance</t>
+          <t>All functions</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Pedrero forms every regulatory opinion but holds no accountability, and Alvin performs every regulatory action. Consulted on 11 rows, responsible for none.</t>
+          <t>Five whole functions run through external partner organisations: Regulatory (Pedrero), Finance (Ironclad), HR (Calm HR), digital marketing (WITHIN), web development (Teknologics). Plus three contractors on packaging, creative and formulation.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Our own procedures make Pedrero consult-only with no Asana access and no internal authority, so the binding external call and the internal execution are both bottlenecks in different ways: their opinion gates the work, and only Alvin can act on it.</t>
+          <t>Eight external parties hold the execution of Regulatory, Finance, HR, digital marketing, web development, packaging, creative and formulation. Not a fault - it is how a team of nine covers this surface - but continuity rests on eight engagements rather than on employment, and each one is a renewal decision. Engagement terms are recorded for Pedrero only.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Give the Reg Lead gate an alternate, or widen Pedrero's remit</t>
+          <t>Record engagement terms and renewal dates for all eight</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">
@@ -7525,7 +8747,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
     </row>
@@ -7537,22 +8759,22 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Erin Hover is a contractor and the lead technical authority on packaging and artwork, accountable for 4 rows with no internal backup. On creative direction she is both A and R.</t>
+          <t>Pedrero forms every regulatory opinion but holds no accountability, and Alvin performs every regulatory action. Consulted on 11 rows, responsible for none.</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Jan Haeck executes under her and is also a contractor, so the entire packaging and artwork chain sits outside the company. Neither approved job description covers creative authority.</t>
+          <t>Our own procedures make Pedrero consult-only with no Asana access and no internal authority, so the binding external call and the internal execution are both bottlenecks in different ways: their opinion gates the work, and only Alvin can act on it.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Name an internal creative counterpart, or scope it into a future role</t>
+          <t>Give the Reg Lead gate an alternate, or widen Pedrero's remit</t>
         </is>
       </c>
       <c r="F10" s="7" t="n">
@@ -7560,7 +8782,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (role correction); asana-pd-manager/references/role-map.md:22-23</t>
+          <t>regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
     </row>
@@ -7572,22 +8794,22 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Perrine holds A on 7 formulation rows as a contractor, with no named backup.</t>
+          <t>Erin Hover is a contractor and the lead technical authority on packaging and artwork, accountable for 4 rows with no internal backup. On creative direction she is both A and R.</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Reduced from 11 by moving process gates to Nicole and packaging to Erin, which is real progress. What remains is genuinely formulation and genuinely single-threaded.</t>
+          <t>Jan Haeck executes under her and is also a contractor, so the entire packaging and artwork chain sits outside the company. Neither approved job description covers creative authority.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Name a backup technical reviewer</t>
+          <t>Name an internal creative counterpart, or scope it into a future role</t>
         </is>
       </c>
       <c r="F11" s="7" t="n">
@@ -7595,7 +8817,7 @@
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 25:18-25:50; quality-manager/references/role-map.md:14</t>
+          <t>Alvin, 2026-07-31 (role correction); asana-pd-manager/references/role-map.md:22-23</t>
         </is>
       </c>
     </row>
@@ -7607,22 +8829,22 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Regulatory &amp; Compliance</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Operator and Reg Lead are the same person, so two gates designed to be independent fire against one approver.</t>
+          <t>Perrine holds A on 7 formulation rows as a contractor, with no named backup.</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>On ingredient-list packets, retailer attestations and FDA filings the second approval adds an audit entry but no second judgment. The 15-day reporting clock has no alternate.</t>
+          <t>Reduced from 11 by moving process gates to Nicole and packaging to Erin, which is real progress. What remains is genuinely formulation and genuinely single-threaded.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Split Reg Lead, or route the second gate to Pedrero</t>
+          <t>Name a backup technical reviewer</t>
         </is>
       </c>
       <c r="F12" s="7" t="n">
@@ -7630,7 +8852,7 @@
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>regulatory-manager/references/role-map.md:14; adverse-event-and-recall-reporter/SKILL.md:108</t>
+          <t>Leadership Business Review 2026-07-30 25:18-25:50; quality-manager/references/role-map.md:14</t>
         </is>
       </c>
     </row>
@@ -7642,22 +8864,22 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>Regulatory &amp; Compliance</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>All 23 scheduled Routines stop at a human approval only Alvin can clear.</t>
+          <t>Operator and Reg Lead are the same person, so two gates designed to be independent fire against one approver.</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Automation that fires unattended still needs him to commit. A week away queues the work rather than pausing it, and the Routines keep firing.</t>
+          <t>On ingredient-list packets, retailer attestations and FDA filings the second approval adds an audit entry but no second judgment. The 15-day reporting clock has no alternate.</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Delegate publish gates to the new specialists</t>
+          <t>Split Reg Lead, or route the second gate to Pedrero</t>
         </is>
       </c>
       <c r="F13" s="7" t="n">
@@ -7665,7 +8887,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>scheduled-prompts/weekly-pd-update.md:91</t>
+          <t>regulatory-manager/references/role-map.md:14; adverse-event-and-recall-reporter/SKILL.md:108</t>
         </is>
       </c>
     </row>
@@ -7677,65 +8899,65 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>All functions</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Succession is documented once in the whole system - Soraya as interim CI lead if Nicole is out.</t>
+          <t>All 23 scheduled Routines stop at a human approval only Alvin can clear.</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Nothing comparable exists for the quality gate, the technical advisor, the Reg Lead or Creative. The repo's stated purpose is succession.</t>
+          <t>Automation that fires unattended still needs him to commit. A week away queues the work rather than pausing it, and the Routines keep firing.</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Alvin to write per-role backups into each role-map</t>
+          <t>Delegate publish gates to the new specialists</t>
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>sjs-comp-intel/references/team-ownership.md:95; decisions/log.md:41</t>
+          <t>scheduled-prompts/weekly-pd-update.md:91</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>Open item</t>
+          <t>Single point of failure</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>All functions</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Quality management system and monthly trend review not yet stood up. Target end of Q3.</t>
+          <t>Succession is documented once in the whole system - Soraya as interim CI lead if Nicole is out.</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>The gate is assigned but the reporting cadence behind it is not built. Without trend data a recurring issue like the pump defect cannot drive a packaging decision.</t>
+          <t>Nothing comparable exists for the quality gate, the technical advisor, the Reg Lead or Creative. The repo's stated purpose is succession.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Alvin owns framework, Nicole runs it</t>
+          <t>Alvin to write per-role backups into each role-map</t>
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 26:02-26:17</t>
+          <t>sjs-comp-intel/references/team-ownership.md:95; decisions/log.md:41</t>
         </is>
       </c>
     </row>
@@ -7747,30 +8969,30 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Operations &amp; Supply Chain</t>
+          <t>Quality</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>22 tasks from the retired coordinator seat sit unassigned in an archived holding project; 4 overdue.</t>
+          <t>Quality management system and monthly trend review not yet stood up. Target end of Q3.</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>An unassigned task drops out of every per-person sweep and goes stale silently. Concrete cost of running the interim split for a quarter.</t>
+          <t>The gate is assigned but the reporting cadence behind it is not built. Without trend data a recurring issue like the pump defect cannot drive a packaging decision.</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Alvin to reassign under the interim split</t>
+          <t>Alvin owns framework, Nicole runs it</t>
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>decisions/log.md:60</t>
+          <t>Leadership Business Review 2026-07-30 26:02-26:17</t>
         </is>
       </c>
     </row>
@@ -7782,30 +9004,30 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>Operations &amp; Supply Chain</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>SOP cleanup and operational prep before onboarding is not done.</t>
+          <t>22 tasks from the retired coordinator seat sit unassigned in an archived holding project; 4 overdue.</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Danielle's stated condition on the hire: clean up the system first so the role can function. Onboarding into the current state recreates the too-broad seat.</t>
+          <t>An unassigned task drops out of every per-person sweep and goes stale silently. Concrete cost of running the interim split for a quarter.</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Alvin and Nicole, before the Ops seat starts</t>
+          <t>Alvin to reassign under the interim split</t>
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
+          <t>decisions/log.md:60</t>
         </is>
       </c>
     </row>
@@ -7817,30 +9039,30 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>IT / Systems &amp; Data</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Wiki write-back has not fired since 2026-05-26. 123 of 133 pages are untouched seed content.</t>
+          <t>SOP cleanup and operational prep before onboarding is not done.</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>The bridges' runtime lexicon reads stale seed data, degrading vendor, contact and product recognition on every sweep.</t>
+          <t>Danielle's stated condition on the hire: clean up the system first so the role can function. Onboarding into the current state recreates the too-broad seat.</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Alvin; part of the skills-architecture backlog</t>
+          <t>Alvin and Nicole, before the Ops seat starts</t>
         </is>
       </c>
       <c r="F18" s="7" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>decisions/wiki-layer-audit-2026-07-29.md:52; decisions/log.md:75</t>
+          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
         </is>
       </c>
     </row>
@@ -7852,82 +9074,117 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Quality</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Nine SOPs and forms are 29 days overdue on annual review.</t>
+          <t>Wiki write-back has not fired since 2026-05-26. 123 of 133 pages are untouched seed content.</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Review dates were null so the annual sweep had nothing to fire on. Dates are restored; the reviews are not done, and each needs sign-off.</t>
+          <t>The bridges' runtime lexicon reads stale seed data, degrading vendor, contact and product recognition on every sweep.</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Nicole approves as the quality gate; Alvin stages</t>
+          <t>Alvin; part of the skills-architecture backlog</t>
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>decisions/log.md:69</t>
+          <t>decisions/wiki-layer-audit-2026-07-29.md:52; decisions/log.md:75</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
         <is>
+          <t>Open item</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Nine SOPs and forms are 29 days overdue on annual review.</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Review dates were null so the annual sweep had nothing to fire on. Dates are restored; the reviews are not done, and each needs sign-off.</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Nicole approves as the quality gate; Alvin stages</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>decisions/log.md:69</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
           <t>Uncovered brand</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>All functions</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>Sweet July, the lifestyle brand, has no coverage. The suite is Sweet July Skin plus company-wide work.</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Merch, licensing and non-skincare retail are run somewhere, but nothing documents who owns them. They cannot be put on a RACI from these sources.</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>Danielle to confirm scope for the next version</t>
         </is>
       </c>
-      <c r="F20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="F21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>references/architecture/system_map.md:3; context/about-business.md:3</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Hours per month</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
+      <c r="C23" s="17" t="inlineStr">
         <is>
           <t>Rough estimates. Open-seat rows are full-time-equivalent load, not incremental. Zero means the gap is a structural exposure rather than unbilled hours.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G20"/>
+  <autoFilter ref="A1:G21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/deliverables/AC-Brands-RACI.xlsx
+++ b/deliverables/AC-Brands-RACI.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Gaps" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$V$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$W$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V131"/>
+  <dimension ref="A1:W135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -583,9 +583,10 @@
     <col width="6" customWidth="1" min="17" max="17"/>
     <col width="6" customWidth="1" min="18" max="18"/>
     <col width="6" customWidth="1" min="19" max="19"/>
-    <col width="26" customWidth="1" min="20" max="20"/>
-    <col width="58" customWidth="1" min="21" max="21"/>
-    <col width="82" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="20" max="20"/>
+    <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="58" customWidth="1" min="22" max="22"/>
+    <col width="82" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -684,17 +685,22 @@
           <t>TK</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Transitions to</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -788,9 +794,14 @@
           <t>Teknologics</t>
         </is>
       </c>
-      <c r="T2" s="3" t="inlineStr"/>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>Coastal Interactive</t>
+        </is>
+      </c>
       <c r="U2" s="3" t="inlineStr"/>
       <c r="V2" s="3" t="inlineStr"/>
+      <c r="W2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -825,7 +836,11 @@
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I3" s="7" t="inlineStr"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J3" s="7" t="inlineStr"/>
       <c r="K3" s="7" t="inlineStr"/>
       <c r="L3" s="7" t="inlineStr"/>
@@ -840,19 +855,20 @@
       <c r="Q3" s="7" t="inlineStr"/>
       <c r="R3" s="7" t="inlineStr"/>
       <c r="S3" s="7" t="inlineStr"/>
-      <c r="T3" s="6" t="inlineStr">
+      <c r="T3" s="7" t="inlineStr"/>
+      <c r="U3" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U3" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/asana-pd-manager/SKILL.md:60</t>
-        </is>
-      </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>PD Lead holds technical sign-off on formula stage moves. Operator confirms every move (Rule 1 preview); reversals get a stronger intent check.</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/asana-pd-manager/SKILL.md:60; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W3" s="6" t="inlineStr">
+        <is>
+          <t>PD Lead holds technical sign-off on formula stage moves. Operator confirms every move (Rule 1 preview); reversals get a stronger intent check. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
         </is>
       </c>
     </row>
@@ -881,7 +897,11 @@
       </c>
       <c r="G4" s="7" t="inlineStr"/>
       <c r="H4" s="7" t="inlineStr"/>
-      <c r="I4" s="7" t="inlineStr"/>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J4" s="7" t="inlineStr"/>
       <c r="K4" s="7" t="inlineStr"/>
       <c r="L4" s="7" t="inlineStr"/>
@@ -896,15 +916,16 @@
       <c r="Q4" s="7" t="inlineStr"/>
       <c r="R4" s="7" t="inlineStr"/>
       <c r="S4" s="7" t="inlineStr"/>
-      <c r="T4" s="6" t="inlineStr"/>
-      <c r="U4" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:16</t>
-        </is>
-      </c>
+      <c r="T4" s="7" t="inlineStr"/>
+      <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>PD Lead owns the technical call outright. A and R the same person, and PC is an external contractor.</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W4" s="6" t="inlineStr">
+        <is>
+          <t>PD Lead owns the technical call outright. A and R the same person, and PC is an external contractor. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
         </is>
       </c>
     </row>
@@ -937,7 +958,11 @@
       <c r="F5" s="7" t="inlineStr"/>
       <c r="G5" s="7" t="inlineStr"/>
       <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J5" s="7" t="inlineStr"/>
       <c r="K5" s="9" t="inlineStr">
         <is>
@@ -964,15 +989,16 @@
       <c r="Q5" s="7" t="inlineStr"/>
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="7" t="inlineStr"/>
-      <c r="T5" s="6" t="inlineStr"/>
-      <c r="U5" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:16,23; Alvin, 2026-07-31 (role correction)</t>
-        </is>
-      </c>
+      <c r="T5" s="7" t="inlineStr"/>
+      <c r="U5" s="6" t="inlineStr"/>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>PD Lead owns packaging dev calls; Jan executes packaging and artwork under Erin. Both are contractors. Erin is the lead technical authority on packaging and artwork and answers for the outcome; Jan executes under her. Perrine consults where formula contact or compatibility is in play. Both Erin and Jan are contractors.</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:16,23; Alvin, 2026-07-31 (role correction); Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W5" s="6" t="inlineStr">
+        <is>
+          <t>PD Lead owns packaging dev calls; Jan executes packaging and artwork under Erin. Both are contractors. Erin is the lead technical authority on packaging and artwork and answers for the outcome; Jan executes under her. Perrine consults where formula contact or compatibility is in play. Both Erin and Jan are contractors. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1035,11 @@
       </c>
       <c r="G6" s="7" t="inlineStr"/>
       <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="7" t="inlineStr"/>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J6" s="7" t="inlineStr"/>
       <c r="K6" s="7" t="inlineStr"/>
       <c r="L6" s="7" t="inlineStr"/>
@@ -1024,15 +1054,16 @@
       <c r="Q6" s="7" t="inlineStr"/>
       <c r="R6" s="7" t="inlineStr"/>
       <c r="S6" s="7" t="inlineStr"/>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:17,18</t>
-        </is>
-      </c>
+      <c r="T6" s="7" t="inlineStr"/>
+      <c r="U6" s="6" t="inlineStr"/>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>President approves. PD Consult is final-line approver alongside the President.</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:17,18; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W6" s="6" t="inlineStr">
+        <is>
+          <t>President approves. PD Consult is final-line approver alongside the President. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
         </is>
       </c>
     </row>
@@ -1069,26 +1100,35 @@
       </c>
       <c r="G7" s="7" t="inlineStr"/>
       <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J7" s="7" t="inlineStr"/>
       <c r="K7" s="7" t="inlineStr"/>
       <c r="L7" s="7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
       <c r="R7" s="7" t="inlineStr"/>
       <c r="S7" s="7" t="inlineStr"/>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:19</t>
-        </is>
-      </c>
+      <c r="T7" s="7" t="inlineStr"/>
+      <c r="U7" s="6" t="inlineStr"/>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>Founder gate. Ayesha receives weekly PD signal through the Friday briefing.</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:19; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>Founder gate. Ayesha receives weekly PD signal through the Friday briefing. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1165,11 @@
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr"/>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J8" s="7" t="inlineStr"/>
       <c r="K8" s="7" t="inlineStr"/>
       <c r="L8" s="7" t="inlineStr"/>
@@ -1140,19 +1184,20 @@
       <c r="Q8" s="7" t="inlineStr"/>
       <c r="R8" s="7" t="inlineStr"/>
       <c r="S8" s="7" t="inlineStr"/>
-      <c r="T8" s="6" t="inlineStr">
+      <c r="T8" s="7" t="inlineStr"/>
+      <c r="U8" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U8" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/fireflies-asana-bridge/SKILL.md:287; .claude/skills/outlook-plm-bridge/SKILL.md:191; .claude/skills/sjs-status-reporter/SKILL.md:331,385</t>
-        </is>
-      </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>Alvin is the named approver on Flow D formula-approval decisions and classifies every meeting item. Covers the three PD hub dashboards. A and R both AB.</t>
+          <t>.claude/skills/fireflies-asana-bridge/SKILL.md:287; .claude/skills/outlook-plm-bridge/SKILL.md:191; .claude/skills/sjs-status-reporter/SKILL.md:331,385; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W8" s="6" t="inlineStr">
+        <is>
+          <t>Alvin is the named approver on Flow D formula-approval decisions and classifies every meeting item. Covers the three PD hub dashboards. A and R both AB. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1230,11 @@
       </c>
       <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr"/>
@@ -1200,15 +1249,16 @@
       <c r="Q9" s="7" t="inlineStr"/>
       <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="7" t="inlineStr"/>
-      <c r="T9" s="6" t="inlineStr"/>
-      <c r="U9" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/capa-coordinator/SKILL.md:85</t>
-        </is>
-      </c>
+      <c r="T9" s="7" t="inlineStr"/>
+      <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>PD Lead is cross-flagged for any PD-side reformulation. Reformulation handoff rides the root-cause approval - no separate gate.</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/capa-coordinator/SKILL.md:85; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
+        <is>
+          <t>PD Lead is cross-flagged for any PD-side reformulation. Reformulation handoff rides the root-cause approval - no separate gate. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1291,11 @@
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J10" s="7" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr">
         <is>
@@ -1264,19 +1318,20 @@
       <c r="Q10" s="7" t="inlineStr"/>
       <c r="R10" s="7" t="inlineStr"/>
       <c r="S10" s="7" t="inlineStr"/>
-      <c r="T10" s="6" t="inlineStr">
+      <c r="T10" s="7" t="inlineStr"/>
+      <c r="U10" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U10" s="6" t="inlineStr">
-        <is>
-          <t>SharePoint: Sweet July Skin - Product Development Specialist - Job Description.docx</t>
-        </is>
-      </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>Documentation quality is Nicole's gate. The PD Specialist JD names document control as a core responsibility, so this row transitions on hire.</t>
+          <t>SharePoint: Sweet July Skin - Product Development Specialist - Job Description.docx; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W10" s="6" t="inlineStr">
+        <is>
+          <t>Documentation quality is Nicole's gate. The PD Specialist JD names document control as a core responsibility, so this row transitions on hire. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
         </is>
       </c>
     </row>
@@ -1328,17 +1383,18 @@
       <c r="Q11" s="7" t="inlineStr"/>
       <c r="R11" s="7" t="inlineStr"/>
       <c r="S11" s="7" t="inlineStr"/>
-      <c r="T11" s="6" t="inlineStr">
+      <c r="T11" s="7" t="inlineStr"/>
+      <c r="U11" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U11" s="6" t="inlineStr">
+      <c r="V11" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:42,46,75,154,158</t>
         </is>
       </c>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="W11" s="6" t="inlineStr">
         <is>
           <t>PLM vendor record created only after Operations approves at 2D. First-contact routing varies by vendor_type (SKILL.md:50-56) but the approval gate does not. A and R both AB.</t>
         </is>
@@ -1384,17 +1440,18 @@
       <c r="Q12" s="7" t="inlineStr"/>
       <c r="R12" s="7" t="inlineStr"/>
       <c r="S12" s="7" t="inlineStr"/>
-      <c r="T12" s="6" t="inlineStr">
+      <c r="T12" s="7" t="inlineStr"/>
+      <c r="U12" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U12" s="6" t="inlineStr">
+      <c r="V12" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:108,116,140,248</t>
         </is>
       </c>
-      <c r="V12" s="6" t="inlineStr">
+      <c r="W12" s="6" t="inlineStr">
         <is>
           <t>Six sub-flows from draft to close, plus Job 10 discrepancy investigation. Every gate is Operations. A and R both AB.</t>
         </is>
@@ -1440,13 +1497,14 @@
       <c r="Q13" s="7" t="inlineStr"/>
       <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="7" t="inlineStr"/>
-      <c r="T13" s="6" t="inlineStr"/>
-      <c r="U13" s="6" t="inlineStr">
+      <c r="T13" s="7" t="inlineStr"/>
+      <c r="U13" s="6" t="inlineStr"/>
+      <c r="V13" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:130</t>
         </is>
       </c>
-      <c r="V13" s="6" t="inlineStr">
+      <c r="W13" s="6" t="inlineStr">
         <is>
           <t>PD owns the close on PD-linked receipts; Purchasing carries the receipt signal only. The one Ops row where accountability sits off the VP seat.</t>
         </is>
@@ -1492,17 +1550,18 @@
       <c r="Q14" s="7" t="inlineStr"/>
       <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="7" t="inlineStr"/>
-      <c r="T14" s="6" t="inlineStr">
+      <c r="T14" s="7" t="inlineStr"/>
+      <c r="U14" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
+      <c r="V14" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/inventory-manager/SKILL.md:68</t>
         </is>
       </c>
-      <c r="V14" s="6" t="inlineStr">
+      <c r="W14" s="6" t="inlineStr">
         <is>
           <t>Operations decides the correction direction, usually trusting Logiwa as physical reality. A and R both AB.</t>
         </is>
@@ -1560,17 +1619,18 @@
       <c r="Q15" s="7" t="inlineStr"/>
       <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="7" t="inlineStr"/>
-      <c r="T15" s="6" t="inlineStr">
+      <c r="T15" s="7" t="inlineStr"/>
+      <c r="U15" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
+      <c r="V15" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:234,235,238; Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V15" s="6" t="inlineStr">
+      <c r="W15" s="6" t="inlineStr">
         <is>
           <t>Operator confirms cost_category, regulatory_driver, linked SKU and multi-home routing before any PLM write, and approves the dispute branch. A and R both AB. Ironclad consulted - classified invoices land in their ledger.</t>
         </is>
@@ -1620,17 +1680,18 @@
       <c r="Q16" s="7" t="inlineStr"/>
       <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="7" t="inlineStr"/>
-      <c r="T16" s="6" t="inlineStr">
+      <c r="T16" s="7" t="inlineStr"/>
+      <c r="U16" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
+      <c r="V16" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/inventory-manager/SKILL.md:18,52,60</t>
         </is>
       </c>
-      <c r="V16" s="6" t="inlineStr">
+      <c r="W16" s="6" t="inlineStr">
         <is>
           <t>Ex-Ops-Coordinator scope. Alvin took inventory under the 2026-07-17 interim split. A and R both AB.</t>
         </is>
@@ -1676,17 +1737,18 @@
       <c r="Q17" s="7" t="inlineStr"/>
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr"/>
-      <c r="T17" s="6" t="inlineStr">
+      <c r="T17" s="7" t="inlineStr"/>
+      <c r="U17" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
+      <c r="V17" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/inventory-manager/SKILL.md:94</t>
         </is>
       </c>
-      <c r="V17" s="6" t="inlineStr">
+      <c r="W17" s="6" t="inlineStr">
         <is>
           <t>Operations approves. Near-expiry write-offs wait on the quality call first. A and R both AB.</t>
         </is>
@@ -1736,17 +1798,18 @@
       <c r="Q18" s="7" t="inlineStr"/>
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="7" t="inlineStr"/>
-      <c r="T18" s="6" t="inlineStr">
+      <c r="T18" s="7" t="inlineStr"/>
+      <c r="U18" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U18" s="6" t="inlineStr">
+      <c r="V18" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/supply-demand-planner/SKILL.md:30-52; .claude/skills/supply-demand-planner/references/plm-schema-additions.md:139</t>
         </is>
       </c>
-      <c r="V18" s="6" t="inlineStr">
+      <c r="W18" s="6" t="inlineStr">
         <is>
           <t>Operations approves; plm-assistant executes the SQL. Four intertwined jobs on one person. A and R both AB.</t>
         </is>
@@ -1792,17 +1855,18 @@
       <c r="Q19" s="7" t="inlineStr"/>
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr"/>
-      <c r="T19" s="6" t="inlineStr">
+      <c r="T19" s="7" t="inlineStr"/>
+      <c r="U19" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
+      <c r="V19" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/logistics-manager/SKILL.md:59,186; .claude/skills/logistics-manager/forms/international-dtc-shipment.md:11</t>
         </is>
       </c>
-      <c r="V19" s="6" t="inlineStr">
+      <c r="W19" s="6" t="inlineStr">
         <is>
           <t>Nothing created or updated until Operations signs off. Ex-Ops-Coordinator logistics scope, now Alvin. HCT and Impress origin Asia so customs is routine. A and R both AB.</t>
         </is>
@@ -1848,17 +1912,18 @@
       <c r="Q20" s="7" t="inlineStr"/>
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr"/>
-      <c r="T20" s="6" t="inlineStr">
+      <c r="T20" s="7" t="inlineStr"/>
+      <c r="U20" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U20" s="6" t="inlineStr">
+      <c r="V20" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:123; .claude/skills/oc3pl-order-manager/SKILL.md:109,191</t>
         </is>
       </c>
-      <c r="V20" s="6" t="inlineStr">
+      <c r="W20" s="6" t="inlineStr">
         <is>
           <t>Ex-Ops-Coordinator scope. Nicole covers order management and OC3PL under the 2026-07-17 interim split. A and R both NI.</t>
         </is>
@@ -1904,17 +1969,18 @@
       <c r="Q21" s="7" t="inlineStr"/>
       <c r="R21" s="7" t="inlineStr"/>
       <c r="S21" s="7" t="inlineStr"/>
-      <c r="T21" s="6" t="inlineStr">
+      <c r="T21" s="7" t="inlineStr"/>
+      <c r="U21" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U21" s="6" t="inlineStr">
+      <c r="V21" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/oc3pl-order-manager/SKILL.md:201; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
         </is>
       </c>
-      <c r="V21" s="6" t="inlineStr">
+      <c r="W21" s="6" t="inlineStr">
         <is>
           <t>Order-side holds sit with Nicole; SKU-level shortage routing belongs to inventory-manager, so Alvin does the work.</t>
         </is>
@@ -1964,17 +2030,18 @@
       <c r="Q22" s="7" t="inlineStr"/>
       <c r="R22" s="7" t="inlineStr"/>
       <c r="S22" s="7" t="inlineStr"/>
-      <c r="T22" s="6" t="inlineStr">
+      <c r="T22" s="7" t="inlineStr"/>
+      <c r="U22" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U22" s="6" t="inlineStr">
+      <c r="V22" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/logistics-manager/SKILL.md:80; .claude/skills/purchasing-manager/SKILL.md:55</t>
         </is>
       </c>
-      <c r="V22" s="6" t="inlineStr">
+      <c r="W22" s="6" t="inlineStr">
         <is>
           <t>Operations or Order Ops reviews. UBM launch June 2026 is the deadline driver on this lane.</t>
         </is>
@@ -2024,17 +2091,18 @@
       <c r="Q23" s="7" t="inlineStr"/>
       <c r="R23" s="7" t="inlineStr"/>
       <c r="S23" s="7" t="inlineStr"/>
-      <c r="T23" s="6" t="inlineStr">
+      <c r="T23" s="7" t="inlineStr"/>
+      <c r="U23" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U23" s="6" t="inlineStr">
+      <c r="V23" s="6" t="inlineStr">
         <is>
           <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Leadership Business Review 2026-07-30 35:18</t>
         </is>
       </c>
-      <c r="V23" s="6" t="inlineStr">
+      <c r="W23" s="6" t="inlineStr">
         <is>
           <t>Named in the Ops Specialist JD under Planning &amp; Special Projects. Today Alvin coordinates KDC scheduling directly. A and R both AB until the seat is filled.</t>
         </is>
@@ -2084,17 +2152,18 @@
       <c r="Q24" s="7" t="inlineStr"/>
       <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="7" t="inlineStr"/>
-      <c r="T24" s="6" t="inlineStr">
+      <c r="T24" s="7" t="inlineStr"/>
+      <c r="U24" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U24" s="6" t="inlineStr">
+      <c r="V24" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/complaint-and-event-handler/SKILL.md:20,53</t>
         </is>
       </c>
-      <c r="V24" s="6" t="inlineStr">
+      <c r="W24" s="6" t="inlineStr">
         <is>
           <t>HITL on every write. Operator approves classification plus first response. A and R both AB. Gate moved to Nicole as the final quality check per Leadership Business Review 2026-07-30 25:18-26:01.</t>
         </is>
@@ -2144,17 +2213,18 @@
       <c r="Q25" s="7" t="inlineStr"/>
       <c r="R25" s="7" t="inlineStr"/>
       <c r="S25" s="7" t="inlineStr"/>
-      <c r="T25" s="6" t="inlineStr">
+      <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U25" s="6" t="inlineStr">
+      <c r="V25" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-manager/references/role-map.md:15</t>
         </is>
       </c>
-      <c r="V25" s="6" t="inlineStr">
+      <c r="W25" s="6" t="inlineStr">
         <is>
           <t>Voice of Customer holds gates on complaint classification and complaint-driven escalations. Nicole already held this gate; monthly trend review formalizes it per Leadership Business Review 2026-07-30 26:02-26:17.</t>
         </is>
@@ -2208,17 +2278,18 @@
       <c r="Q26" s="7" t="inlineStr"/>
       <c r="R26" s="7" t="inlineStr"/>
       <c r="S26" s="7" t="inlineStr"/>
-      <c r="T26" s="6" t="inlineStr">
+      <c r="T26" s="7" t="inlineStr"/>
+      <c r="U26" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U26" s="6" t="inlineStr">
+      <c r="V26" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/capa-coordinator/SKILL.md:54,136; .claude/skills/capa-coordinator/references/ncr-procedure.md:135; .claude/skills/capa-coordinator/references/skn-ops-001.md:64,102</t>
         </is>
       </c>
-      <c r="V26" s="6" t="inlineStr">
+      <c r="W26" s="6" t="inlineStr">
         <is>
           <t>Operator approves intake and both action plans; QA Lead approves conversion, root cause, verification, effectiveness and close. Six SOP phases, one external contractor on every technical gate. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults on technical root cause.</t>
         </is>
@@ -2268,17 +2339,18 @@
       <c r="Q27" s="7" t="inlineStr"/>
       <c r="R27" s="7" t="inlineStr"/>
       <c r="S27" s="7" t="inlineStr"/>
-      <c r="T27" s="6" t="inlineStr">
+      <c r="T27" s="7" t="inlineStr"/>
+      <c r="U27" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U27" s="6" t="inlineStr">
+      <c r="V27" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-lab-coordinator/SKILL.md:48,56</t>
         </is>
       </c>
-      <c r="V27" s="6" t="inlineStr">
+      <c r="W27" s="6" t="inlineStr">
         <is>
           <t>Operator approves intake and the single-versus-systemic classification. A and R both AB. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:35-25:50. Perrine consults on the technical call.</t>
         </is>
@@ -2328,17 +2400,18 @@
       <c r="Q28" s="7" t="inlineStr"/>
       <c r="R28" s="7" t="inlineStr"/>
       <c r="S28" s="7" t="inlineStr"/>
-      <c r="T28" s="6" t="inlineStr">
+      <c r="T28" s="7" t="inlineStr"/>
+      <c r="U28" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U28" s="6" t="inlineStr">
+      <c r="V28" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-lab-coordinator/SKILL.md:76; .claude/skills/quality-lab-coordinator/references/vendor-scorecard-signal.md:103</t>
         </is>
       </c>
-      <c r="V28" s="6" t="inlineStr">
+      <c r="W28" s="6" t="inlineStr">
         <is>
           <t>QA Lead approves any vendor flag and the scorecard band. Operator can stage but not commit. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults.</t>
         </is>
@@ -2392,17 +2465,18 @@
       <c r="Q29" s="7" t="inlineStr"/>
       <c r="R29" s="7" t="inlineStr"/>
       <c r="S29" s="7" t="inlineStr"/>
-      <c r="T29" s="6" t="inlineStr">
+      <c r="T29" s="7" t="inlineStr"/>
+      <c r="U29" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U29" s="6" t="inlineStr">
+      <c r="V29" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/batch-lifecycle-tracker/references/batch-lifecycle-procedure.md:208; .claude/skills/batch-lifecycle-tracker/SKILL.md:86</t>
         </is>
       </c>
-      <c r="V29" s="6" t="inlineStr">
+      <c r="W29" s="6" t="inlineStr">
         <is>
           <t>QA Lead approves every hold and every release. No exceptions at v5.4. Releases need a CAPA close or clean retest plus QA Lead judgment. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:35-26:01. Perrine consults on the technical basis.</t>
         </is>
@@ -2452,17 +2526,18 @@
       <c r="Q30" s="7" t="inlineStr"/>
       <c r="R30" s="7" t="inlineStr"/>
       <c r="S30" s="7" t="inlineStr"/>
-      <c r="T30" s="6" t="inlineStr">
+      <c r="T30" s="7" t="inlineStr"/>
+      <c r="U30" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U30" s="6" t="inlineStr">
+      <c r="V30" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
         </is>
       </c>
-      <c r="V30" s="6" t="inlineStr">
+      <c r="W30" s="6" t="inlineStr">
         <is>
           <t>Technical testing call stays with Perrine as the R&amp;D and quality technical advisor. Operator approves schedule edits. Per Leadership Business Review 2026-07-30 25:18-25:35 the process gate moved to Nicole but the technical judgment did not.</t>
         </is>
@@ -2512,17 +2587,18 @@
       <c r="Q31" s="7" t="inlineStr"/>
       <c r="R31" s="7" t="inlineStr"/>
       <c r="S31" s="7" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr">
+      <c r="T31" s="7" t="inlineStr"/>
+      <c r="U31" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U31" s="6" t="inlineStr">
+      <c r="V31" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
         </is>
       </c>
-      <c r="V31" s="6" t="inlineStr">
+      <c r="W31" s="6" t="inlineStr">
         <is>
           <t>Disposition is a quality gate, so it moves to Nicole. Posts back to inventory before any write-off.</t>
         </is>
@@ -2580,13 +2656,14 @@
       <c r="Q32" s="7" t="inlineStr"/>
       <c r="R32" s="7" t="inlineStr"/>
       <c r="S32" s="7" t="inlineStr"/>
-      <c r="T32" s="6" t="inlineStr"/>
-      <c r="U32" s="6" t="inlineStr">
+      <c r="T32" s="7" t="inlineStr"/>
+      <c r="U32" s="6" t="inlineStr"/>
+      <c r="V32" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/complaint-and-event-handler/SKILL.md:85,89,95; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V32" s="6" t="inlineStr">
+      <c r="W32" s="6" t="inlineStr">
         <is>
           <t>The strictest gate in the suite: explicit approval at every step, §4.A through §4.F each a separate gate. Operator decides severity, team and whether external reporting is needed. A and R both AB. Stays with Alvin as Reg Lead — legal and agency exposure. Nicole consults. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -2632,13 +2709,14 @@
       <c r="Q33" s="7" t="inlineStr"/>
       <c r="R33" s="7" t="inlineStr"/>
       <c r="S33" s="7" t="inlineStr"/>
-      <c r="T33" s="6" t="inlineStr"/>
-      <c r="U33" s="6" t="inlineStr">
+      <c r="T33" s="7" t="inlineStr"/>
+      <c r="U33" s="6" t="inlineStr"/>
+      <c r="V33" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-manager/SKILL.md:66,135; .claude/skills/quality-manager/references/sop-catalog.md:120; .claude/skills/quality-manager/references/qos-thresholds.md:52</t>
         </is>
       </c>
-      <c r="V33" s="6" t="inlineStr">
+      <c r="W33" s="6" t="inlineStr">
         <is>
           <t>QA Lead approves every ratification, review outcome, cross-cutting task and QoS threshold task. SOP §7 names a QA Manager for this; that seat is vacant and Perrine is filling it. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:18-25:50.</t>
         </is>
@@ -2688,17 +2766,18 @@
       <c r="Q34" s="7" t="inlineStr"/>
       <c r="R34" s="7" t="inlineStr"/>
       <c r="S34" s="7" t="inlineStr"/>
-      <c r="T34" s="6" t="inlineStr">
+      <c r="T34" s="7" t="inlineStr"/>
+      <c r="U34" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U34" s="6" t="inlineStr">
+      <c r="V34" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-status-reporter/SKILL.md:78</t>
         </is>
       </c>
-      <c r="V34" s="6" t="inlineStr">
+      <c r="W34" s="6" t="inlineStr">
         <is>
           <t>Operator approves the commit before push. Never commit without confirmation. A and R both AB. Nicole gates the content; Alvin retains the publish mechanics. Per Leadership Business Review 2026-07-30 26:02-26:17.</t>
         </is>
@@ -2760,13 +2839,14 @@
       <c r="Q35" s="7" t="inlineStr"/>
       <c r="R35" s="7" t="inlineStr"/>
       <c r="S35" s="7" t="inlineStr"/>
-      <c r="T35" s="6" t="inlineStr"/>
-      <c r="U35" s="6" t="inlineStr">
+      <c r="T35" s="7" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr"/>
+      <c r="V35" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 25:35-26:01</t>
         </is>
       </c>
-      <c r="V35" s="6" t="inlineStr">
+      <c r="W35" s="6" t="inlineStr">
         <is>
           <t>The new cross-function gate. Verbatim: "anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check... Even with each function having or being the primary owner, we'll still have that quality gate." A and R both NI.</t>
         </is>
@@ -2816,13 +2896,14 @@
       <c r="Q36" s="7" t="inlineStr"/>
       <c r="R36" s="7" t="inlineStr"/>
       <c r="S36" s="7" t="inlineStr"/>
-      <c r="T36" s="6" t="inlineStr"/>
-      <c r="U36" s="6" t="inlineStr">
+      <c r="T36" s="7" t="inlineStr"/>
+      <c r="U36" s="6" t="inlineStr"/>
+      <c r="V36" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 25:18-26:17</t>
         </is>
       </c>
-      <c r="V36" s="6" t="inlineStr">
+      <c r="W36" s="6" t="inlineStr">
         <is>
           <t>Alvin owns the overall framework; Nicole runs it. Monthly trend review so recurring issues (the pump issue was the worked example) can drive packaging or formula decisions. Target: implemented by end of Q3.</t>
         </is>
@@ -2876,17 +2957,18 @@
       <c r="Q37" s="7" t="inlineStr"/>
       <c r="R37" s="7" t="inlineStr"/>
       <c r="S37" s="7" t="inlineStr"/>
-      <c r="T37" s="6" t="inlineStr">
+      <c r="T37" s="7" t="inlineStr"/>
+      <c r="U37" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U37" s="6" t="inlineStr">
+      <c r="V37" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:50; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:62; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V37" s="6" t="inlineStr">
+      <c r="W37" s="6" t="inlineStr">
         <is>
           <t>Operator approves intake. Reg Lead is the same person at v6.6, so the gate fires twice against one person. Pedrero holds the binding external call. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -2932,13 +3014,14 @@
       <c r="Q38" s="7" t="inlineStr"/>
       <c r="R38" s="7" t="inlineStr"/>
       <c r="S38" s="7" t="inlineStr"/>
-      <c r="T38" s="6" t="inlineStr"/>
-      <c r="U38" s="6" t="inlineStr">
+      <c r="T38" s="7" t="inlineStr"/>
+      <c r="U38" s="6" t="inlineStr"/>
+      <c r="V38" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:60; .claude/skills/regulatory-manager/SKILL.md:140; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V38" s="6" t="inlineStr">
+      <c r="W38" s="6" t="inlineStr">
         <is>
           <t>Reg Lead approves every Pedrero send; Operator hits send manually. Both roles are Alvin. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3004,17 +3087,18 @@
       <c r="Q39" s="7" t="inlineStr"/>
       <c r="R39" s="7" t="inlineStr"/>
       <c r="S39" s="7" t="inlineStr"/>
-      <c r="T39" s="6" t="inlineStr">
+      <c r="T39" s="7" t="inlineStr"/>
+      <c r="U39" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U39" s="6" t="inlineStr">
+      <c r="V39" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:97; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:29; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V39" s="6" t="inlineStr">
+      <c r="W39" s="6" t="inlineStr">
         <is>
           <t>Operator approves the path; Reg Lead approves the Pedrero stage. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off. A and R both AB. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off, so both are consulted rather than bypassed. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3080,13 +3164,14 @@
       <c r="Q40" s="7" t="inlineStr"/>
       <c r="R40" s="7" t="inlineStr"/>
       <c r="S40" s="7" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr">
+      <c r="T40" s="7" t="inlineStr"/>
+      <c r="U40" s="6" t="inlineStr"/>
+      <c r="V40" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:85; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:93; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V40" s="6" t="inlineStr">
+      <c r="W40" s="6" t="inlineStr">
         <is>
           <t>Operator approves each pass outcome; Reg Lead approves any archive entry. Creative produces the artwork under review. Erin answers for the artwork being right as lead technical authority. Alvin runs the IL cross-check and the label-law passes and holds the Reg Lead gate on archive entries, so the regulatory approval and the artwork authority are separate people. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3136,13 +3221,14 @@
       <c r="Q41" s="7" t="inlineStr"/>
       <c r="R41" s="7" t="inlineStr"/>
       <c r="S41" s="7" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
-      <c r="U41" s="6" t="inlineStr">
+      <c r="T41" s="7" t="inlineStr"/>
+      <c r="U41" s="6" t="inlineStr"/>
+      <c r="V41" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:281; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V41" s="6" t="inlineStr">
+      <c r="W41" s="6" t="inlineStr">
         <is>
           <t>Reg Lead approves the QIL recovery ask to the prior manufacturer; PD Lead does the formulation work. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3204,17 +3290,18 @@
       <c r="Q42" s="7" t="inlineStr"/>
       <c r="R42" s="7" t="inlineStr"/>
       <c r="S42" s="7" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr">
+      <c r="T42" s="7" t="inlineStr"/>
+      <c r="U42" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U42" s="6" t="inlineStr">
+      <c r="V42" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:105; .claude/skills/regulatory-manager/SKILL.md:122; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V42" s="6" t="inlineStr">
+      <c r="W42" s="6" t="inlineStr">
         <is>
           <t>Reg Lead approves the retailer submission after Pedrero approval. Voice of Customer consults where customer-perceived attributes matter. A and R both AB. Ayesha consulted - retailer clean-standard positioning is a brand claim. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3268,17 +3355,18 @@
       <c r="Q43" s="7" t="inlineStr"/>
       <c r="R43" s="7" t="inlineStr"/>
       <c r="S43" s="7" t="inlineStr"/>
-      <c r="T43" s="6" t="inlineStr">
+      <c r="T43" s="7" t="inlineStr"/>
+      <c r="U43" s="6" t="inlineStr">
         <is>
           <t>Product Development Specialist</t>
         </is>
       </c>
-      <c r="U43" s="6" t="inlineStr">
+      <c r="V43" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/regulatory-manager/SKILL.md:114,367; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V43" s="6" t="inlineStr">
+      <c r="W43" s="6" t="inlineStr">
         <is>
           <t>Operator approves the filing draft; Reg Lead approves every registration record write. Both roles are Alvin. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3336,13 +3424,14 @@
       <c r="Q44" s="7" t="inlineStr"/>
       <c r="R44" s="7" t="inlineStr"/>
       <c r="S44" s="7" t="inlineStr"/>
-      <c r="T44" s="6" t="inlineStr"/>
-      <c r="U44" s="6" t="inlineStr">
+      <c r="T44" s="7" t="inlineStr"/>
+      <c r="U44" s="6" t="inlineStr"/>
+      <c r="V44" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/adverse-event-and-recall-reporter/SKILL.md:65,108; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V44" s="6" t="inlineStr">
+      <c r="W44" s="6" t="inlineStr">
         <is>
           <t>Two distinct gates per filing - Pedrero send approval and agency submission approval - both held by Alvin. Statutory clock with no named backup. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3392,13 +3481,14 @@
       <c r="Q45" s="7" t="inlineStr"/>
       <c r="R45" s="7" t="inlineStr"/>
       <c r="S45" s="7" t="inlineStr"/>
-      <c r="T45" s="6" t="inlineStr"/>
-      <c r="U45" s="6" t="inlineStr">
+      <c r="T45" s="7" t="inlineStr"/>
+      <c r="U45" s="6" t="inlineStr"/>
+      <c r="V45" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/regulatory-manager/SKILL.md:60; .claude/skills/regulatory-status-reporter/SKILL.md:90; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
         </is>
       </c>
-      <c r="V45" s="6" t="inlineStr">
+      <c r="W45" s="6" t="inlineStr">
         <is>
           <t>Two gates per fan-out (Operator for the routing call, Reg Lead for task creation), both Alvin. Operator approves the dashboard commit before push. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
@@ -3448,13 +3538,14 @@
       <c r="Q46" s="7" t="inlineStr"/>
       <c r="R46" s="7" t="inlineStr"/>
       <c r="S46" s="7" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
-      <c r="U46" s="6" t="inlineStr">
+      <c r="T46" s="7" t="inlineStr"/>
+      <c r="U46" s="6" t="inlineStr"/>
+      <c r="V46" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/regulatory-manager/references/pedrero-contacts.md:50; Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V46" s="6" t="inlineStr">
+      <c r="W46" s="6" t="inlineStr">
         <is>
           <t>The engagement letter governs scope, retainer, response windows and dispute resolution. Annual renewal. A and R both AB - the only person managing the regulatory partner relationship.</t>
         </is>
@@ -3500,13 +3591,14 @@
       <c r="Q47" s="7" t="inlineStr"/>
       <c r="R47" s="7" t="inlineStr"/>
       <c r="S47" s="7" t="inlineStr"/>
-      <c r="T47" s="6" t="inlineStr"/>
-      <c r="U47" s="6" t="inlineStr">
+      <c r="T47" s="7" t="inlineStr"/>
+      <c r="U47" s="6" t="inlineStr"/>
+      <c r="V47" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:55; acb-thelanding: data/links.json</t>
         </is>
       </c>
-      <c r="V47" s="6" t="inlineStr">
+      <c r="W47" s="6" t="inlineStr">
         <is>
           <t>First-contact owner for retailer, promotional_goods and accessories vendor types is the Sr. Director Consumer Strategy &amp; Ops. A and R both NI. Consistent with Nicole's all-channel accountability.</t>
         </is>
@@ -3556,13 +3648,14 @@
       <c r="Q48" s="7" t="inlineStr"/>
       <c r="R48" s="7" t="inlineStr"/>
       <c r="S48" s="7" t="inlineStr"/>
-      <c r="T48" s="6" t="inlineStr"/>
-      <c r="U48" s="6" t="inlineStr">
+      <c r="T48" s="7" t="inlineStr"/>
+      <c r="U48" s="6" t="inlineStr"/>
+      <c r="V48" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/purchasing-manager/SKILL.md:55; .claude/skills/sjs-retail-intel/SKILL.md:52; .claude/skills/logistics-manager/SKILL.md:80; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V48" s="6" t="inlineStr">
+      <c r="W48" s="6" t="inlineStr">
         <is>
           <t>UBM launch June 2026. Nicole holds the channel relationship; Alvin runs the positioning and outbound work. Hub lists wholesale as "Owned by TBD" (links.json, Sales &amp; Commerce lead). Resolved to Nicole as part of all-channel accountability.</t>
         </is>
@@ -3616,13 +3709,14 @@
       <c r="Q49" s="7" t="inlineStr"/>
       <c r="R49" s="7" t="inlineStr"/>
       <c r="S49" s="7" t="inlineStr"/>
-      <c r="T49" s="6" t="inlineStr"/>
-      <c r="U49" s="6" t="inlineStr">
+      <c r="T49" s="7" t="inlineStr"/>
+      <c r="U49" s="6" t="inlineStr"/>
+      <c r="V49" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json (Sales &amp; Commerce lead: "TBD (wholesale)"); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V49" s="6" t="inlineStr">
+      <c r="W49" s="6" t="inlineStr">
         <is>
           <t>Hub left wholesale unowned. Resolved to Nicole with all-channel accountability. A and R both Nicole - no second pair of eyes on new-partner decisions.</t>
         </is>
@@ -3680,13 +3774,14 @@
       <c r="Q50" s="7" t="inlineStr"/>
       <c r="R50" s="7" t="inlineStr"/>
       <c r="S50" s="7" t="inlineStr"/>
-      <c r="T50" s="6" t="inlineStr"/>
-      <c r="U50" s="6" t="inlineStr">
+      <c r="T50" s="7" t="inlineStr"/>
+      <c r="U50" s="6" t="inlineStr"/>
+      <c r="V50" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json (Sales &amp; Commerce / Retail Price Architecture, SJS Pricing Matrix); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V50" s="6" t="inlineStr">
+      <c r="W50" s="6" t="inlineStr">
         <is>
           <t>Live pricing matrix on the hub carries retail, wholesale and subscription prices with margin colouring. Ties to the margin framework, so Danielle consulted as the walk-away approver.</t>
         </is>
@@ -3744,13 +3839,14 @@
       <c r="Q51" s="7" t="inlineStr"/>
       <c r="R51" s="7" t="inlineStr"/>
       <c r="S51" s="7" t="inlineStr"/>
-      <c r="T51" s="6" t="inlineStr"/>
-      <c r="U51" s="6" t="inlineStr">
+      <c r="T51" s="7" t="inlineStr"/>
+      <c r="U51" s="6" t="inlineStr"/>
+      <c r="V51" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json (Market Intelligence / Promo Landscape); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V51" s="6" t="inlineStr">
+      <c r="W51" s="6" t="inlineStr">
         <is>
           <t>Promo Landscape tracks the Sephora and Ulta promo calendar. Marketing runs the planning; Nicole answers for the channel commitment.</t>
         </is>
@@ -3808,13 +3904,14 @@
       <c r="Q52" s="7" t="inlineStr"/>
       <c r="R52" s="7" t="inlineStr"/>
       <c r="S52" s="7" t="inlineStr"/>
-      <c r="T52" s="6" t="inlineStr"/>
-      <c r="U52" s="6" t="inlineStr">
+      <c r="T52" s="7" t="inlineStr"/>
+      <c r="U52" s="6" t="inlineStr"/>
+      <c r="V52" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:19,23-30; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
-      <c r="V52" s="6" t="inlineStr">
+      <c r="W52" s="6" t="inlineStr">
         <is>
           <t>Soraya owns teardown production and comp brand profile maintenance. A and R both SS. Danielle consulted rather than only receiving the finished teardown.</t>
         </is>
@@ -3864,13 +3961,14 @@
       <c r="Q53" s="7" t="inlineStr"/>
       <c r="R53" s="7" t="inlineStr"/>
       <c r="S53" s="7" t="inlineStr"/>
-      <c r="T53" s="6" t="inlineStr"/>
-      <c r="U53" s="6" t="inlineStr">
+      <c r="T53" s="7" t="inlineStr"/>
+      <c r="U53" s="6" t="inlineStr"/>
+      <c r="V53" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:65; .claude/skills/sjs-comp-intel/SKILL.md:50</t>
         </is>
       </c>
-      <c r="V53" s="6" t="inlineStr">
+      <c r="W53" s="6" t="inlineStr">
         <is>
           <t>Alvin signs off before it circulates to Danielle and the SJS brand team.</t>
         </is>
@@ -3928,13 +4026,14 @@
       <c r="Q54" s="7" t="inlineStr"/>
       <c r="R54" s="7" t="inlineStr"/>
       <c r="S54" s="7" t="inlineStr"/>
-      <c r="T54" s="6" t="inlineStr"/>
-      <c r="U54" s="6" t="inlineStr">
+      <c r="T54" s="7" t="inlineStr"/>
+      <c r="U54" s="6" t="inlineStr"/>
+      <c r="V54" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:3,9-15; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
-      <c r="V54" s="6" t="inlineStr">
+      <c r="W54" s="6" t="inlineStr">
         <is>
           <t>Stream DRI owns digest production and the 'what it means for SJS' analytical layer. Named as the stream's heartbeat - first thing protected under capacity pressure. A and R both NI. Danielle consulted on the digest's read.</t>
         </is>
@@ -3984,13 +4083,14 @@
       <c r="Q55" s="7" t="inlineStr"/>
       <c r="R55" s="7" t="inlineStr"/>
       <c r="S55" s="7" t="inlineStr"/>
-      <c r="T55" s="6" t="inlineStr"/>
-      <c r="U55" s="6" t="inlineStr">
+      <c r="T55" s="7" t="inlineStr"/>
+      <c r="U55" s="6" t="inlineStr"/>
+      <c r="V55" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:34,40-44; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
-      <c r="V55" s="6" t="inlineStr">
+      <c r="W55" s="6" t="inlineStr">
         <is>
           <t>Kate owns social listening tool maintenance, query hygiene and the weekly retailer new-arrivals scan. A and R both KL. Danielle consulted on what the social signal implies for brand.</t>
         </is>
@@ -4048,13 +4148,14 @@
       <c r="Q56" s="7" t="inlineStr"/>
       <c r="R56" s="7" t="inlineStr"/>
       <c r="S56" s="7" t="inlineStr"/>
-      <c r="T56" s="6" t="inlineStr"/>
-      <c r="U56" s="6" t="inlineStr">
+      <c r="T56" s="7" t="inlineStr"/>
+      <c r="U56" s="6" t="inlineStr"/>
+      <c r="V56" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sweet-july-skin-brand/SKILL.md:1; references/architecture/system_map.md:157; Alvin, 2026-07-31 (role correction); acb-thelanding: data/links.json</t>
         </is>
       </c>
-      <c r="V56" s="6" t="inlineStr">
+      <c r="W56" s="6" t="inlineStr">
         <is>
           <t>Every output-producing skill defers here for canonical brand spec; no skill carries its own copy. President answers for brand custody; Creative Director maintains it. Ayesha consulted - the brand carries her name. Every output-producing skill defers here for canonical spec. Hub lists Brand &amp; Creative as "Owned by Soraya" as function lead; custody accountability sits with the President per the 31 July correction. Both hold: Soraya runs the function, Danielle answers for the brand standard.</t>
         </is>
@@ -4112,13 +4213,14 @@
       <c r="Q57" s="7" t="inlineStr"/>
       <c r="R57" s="7" t="inlineStr"/>
       <c r="S57" s="7" t="inlineStr"/>
-      <c r="T57" s="6" t="inlineStr"/>
-      <c r="U57" s="6" t="inlineStr">
+      <c r="T57" s="7" t="inlineStr"/>
+      <c r="U57" s="6" t="inlineStr"/>
+      <c r="V57" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/ac-brands-holiday-comms/SKILL.md:26,165</t>
         </is>
       </c>
-      <c r="V57" s="6" t="inlineStr">
+      <c r="W57" s="6" t="inlineStr">
         <is>
           <t>Sends from alvin@ac-brands.com with the team on BCC. Includes the Outlook calendar sync and annual maintenance. A and R both AB.</t>
         </is>
@@ -4172,13 +4274,14 @@
       <c r="Q58" s="7" t="inlineStr"/>
       <c r="R58" s="7" t="inlineStr"/>
       <c r="S58" s="7" t="inlineStr"/>
-      <c r="T58" s="6" t="inlineStr"/>
-      <c r="U58" s="6" t="inlineStr">
+      <c r="T58" s="7" t="inlineStr"/>
+      <c r="U58" s="6" t="inlineStr"/>
+      <c r="V58" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:49,72</t>
         </is>
       </c>
-      <c r="V58" s="6" t="inlineStr">
+      <c r="W58" s="6" t="inlineStr">
         <is>
           <t>Alvin owns both Slide 5 (Business Operations) and Slide 6 PD-Ops content; Nicole co-authors Slide 6 with her core PD content. A and R both AB.</t>
         </is>
@@ -4244,17 +4347,18 @@
       <c r="Q59" s="7" t="inlineStr"/>
       <c r="R59" s="7" t="inlineStr"/>
       <c r="S59" s="7" t="inlineStr"/>
-      <c r="T59" s="6" t="inlineStr">
+      <c r="T59" s="7" t="inlineStr"/>
+      <c r="U59" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U59" s="6" t="inlineStr">
+      <c r="V59" s="6" t="inlineStr">
         <is>
           <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
-      <c r="V59" s="6" t="inlineStr">
+      <c r="W59" s="6" t="inlineStr">
         <is>
           <t>Named in the Ops Specialist JD, and in the email as making sure product is where it needs to be for launches, promos, PR seeding and sampling. Danielle consulted - PR seeding and sampling are brand-facing.</t>
         </is>
@@ -4316,13 +4420,14 @@
       <c r="Q60" s="7" t="inlineStr"/>
       <c r="R60" s="7" t="inlineStr"/>
       <c r="S60" s="7" t="inlineStr"/>
-      <c r="T60" s="6" t="inlineStr"/>
-      <c r="U60" s="6" t="inlineStr">
+      <c r="T60" s="7" t="inlineStr"/>
+      <c r="U60" s="6" t="inlineStr"/>
+      <c r="V60" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (role correction); .claude/skills/sjs-margin-walk-away/SKILL.md:93</t>
         </is>
       </c>
-      <c r="V60" s="6" t="inlineStr">
+      <c r="W60" s="6" t="inlineStr">
         <is>
           <t>Added 2026-07-31. Campaign direction was absent from the matrix, which is why the President and the Founder had almost no Marketing presence. Danielle answers for it - Soraya reports to her and the margin sources already have her approving every repricing and channel call. Ayesha consulted on brand moments.</t>
         </is>
@@ -4384,13 +4489,14 @@
       <c r="Q61" s="7" t="inlineStr"/>
       <c r="R61" s="7" t="inlineStr"/>
       <c r="S61" s="7" t="inlineStr"/>
-      <c r="T61" s="6" t="inlineStr"/>
-      <c r="U61" s="6" t="inlineStr">
+      <c r="T61" s="7" t="inlineStr"/>
+      <c r="U61" s="6" t="inlineStr"/>
+      <c r="V61" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json (Marketing / Owned Channels); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V61" s="6" t="inlineStr">
+      <c r="W61" s="6" t="inlineStr">
         <is>
           <t>Hub lists Marketing as "Owned by TBD"; resolved to Soraya as Marketing Manager. Editorial Calendar is a named tool under Owned Channels.</t>
         </is>
@@ -4452,13 +4558,14 @@
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr"/>
-      <c r="T62" s="6" t="inlineStr"/>
-      <c r="U62" s="6" t="inlineStr">
+      <c r="T62" s="7" t="inlineStr"/>
+      <c r="U62" s="6" t="inlineStr"/>
+      <c r="V62" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json (Marketing / Klaviyo Performance); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V62" s="6" t="inlineStr">
+      <c r="W62" s="6" t="inlineStr">
         <is>
           <t>WITHIN runs most of our digital marketing including email execution. Soraya answers for the channel. Klaviyo Performance is a named tool on the hub.</t>
         </is>
@@ -4516,13 +4623,14 @@
         </is>
       </c>
       <c r="S63" s="7" t="inlineStr"/>
-      <c r="T63" s="6" t="inlineStr"/>
-      <c r="U63" s="6" t="inlineStr">
+      <c r="T63" s="7" t="inlineStr"/>
+      <c r="U63" s="6" t="inlineStr"/>
+      <c r="V63" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json (Marketing / Paid Media Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V63" s="6" t="inlineStr">
+      <c r="W63" s="6" t="inlineStr">
         <is>
           <t>WITHIN is the digital marketing agency and runs paid execution. Alvin consulted on spend against margin floors. Quarterly business reviews with WITHIN - the most recent was 20 July.</t>
         </is>
@@ -4580,13 +4688,14 @@
       <c r="Q64" s="7" t="inlineStr"/>
       <c r="R64" s="7" t="inlineStr"/>
       <c r="S64" s="7" t="inlineStr"/>
-      <c r="T64" s="6" t="inlineStr"/>
-      <c r="U64" s="6" t="inlineStr">
+      <c r="T64" s="7" t="inlineStr"/>
+      <c r="U64" s="6" t="inlineStr"/>
+      <c r="V64" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json (Marketing / Social Media Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V64" s="6" t="inlineStr">
+      <c r="W64" s="6" t="inlineStr">
         <is>
           <t>Distinct from social listening, which Kate is accountable for. Here she does the publishing work and Soraya answers for the channel.</t>
         </is>
@@ -4644,13 +4753,14 @@
       <c r="Q65" s="7" t="inlineStr"/>
       <c r="R65" s="7" t="inlineStr"/>
       <c r="S65" s="7" t="inlineStr"/>
-      <c r="T65" s="6" t="inlineStr"/>
-      <c r="U65" s="6" t="inlineStr">
+      <c r="T65" s="7" t="inlineStr"/>
+      <c r="U65" s="6" t="inlineStr"/>
+      <c r="V65" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V65" s="6" t="inlineStr">
+      <c r="W65" s="6" t="inlineStr">
         <is>
           <t>Brand-facing and founder-adjacent, so Danielle consulted and Ayesha informed. The physical seeding logistics sit on the Operations special-projects row.</t>
         </is>
@@ -4704,13 +4814,14 @@
       <c r="Q66" s="7" t="inlineStr"/>
       <c r="R66" s="7" t="inlineStr"/>
       <c r="S66" s="7" t="inlineStr"/>
-      <c r="T66" s="6" t="inlineStr"/>
-      <c r="U66" s="6" t="inlineStr">
+      <c r="T66" s="7" t="inlineStr"/>
+      <c r="U66" s="6" t="inlineStr"/>
+      <c r="V66" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V66" s="6" t="inlineStr">
+      <c r="W66" s="6" t="inlineStr">
         <is>
           <t>A and R both Soraya. WITHIN holds most of our digital marketing execution, so the engagement is a single point of dependency - same shape as the other five external parties.</t>
         </is>
@@ -4768,13 +4879,14 @@
       <c r="Q67" s="7" t="inlineStr"/>
       <c r="R67" s="7" t="inlineStr"/>
       <c r="S67" s="7" t="inlineStr"/>
-      <c r="T67" s="6" t="inlineStr"/>
-      <c r="U67" s="6" t="inlineStr">
+      <c r="T67" s="7" t="inlineStr"/>
+      <c r="U67" s="6" t="inlineStr"/>
+      <c r="V67" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:22; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
-      <c r="V67" s="6" t="inlineStr">
+      <c r="W67" s="6" t="inlineStr">
         <is>
           <t>Creative Director owns packaging, artwork and brand visuals. A and R both EH. Creative Director owns the direction as lead technical authority, and is a contractor. Danielle and Ayesha both consulted. A and R the same person - no second pair of eyes, and no internal backup either.</t>
         </is>
@@ -4836,13 +4948,14 @@
       <c r="Q68" s="7" t="inlineStr"/>
       <c r="R68" s="7" t="inlineStr"/>
       <c r="S68" s="7" t="inlineStr"/>
-      <c r="T68" s="6" t="inlineStr"/>
-      <c r="U68" s="6" t="inlineStr">
+      <c r="T68" s="7" t="inlineStr"/>
+      <c r="U68" s="6" t="inlineStr"/>
+      <c r="V68" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/asana-pd-manager/references/role-map.md:23; .claude/skills/sjs-comp-intel/references/team-ownership.md:79; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
-      <c r="V68" s="6" t="inlineStr">
+      <c r="W68" s="6" t="inlineStr">
         <is>
           <t>Jan is the creative contractor under Erin. Title differs between sources - Packaging Engineer in one, creative contractor in the other. Erin holds technical authority; Jan executes. Both contractors.</t>
         </is>
@@ -4896,13 +5009,14 @@
       <c r="Q69" s="7" t="inlineStr"/>
       <c r="R69" s="7" t="inlineStr"/>
       <c r="S69" s="7" t="inlineStr"/>
-      <c r="T69" s="6" t="inlineStr"/>
-      <c r="U69" s="6" t="inlineStr">
+      <c r="T69" s="7" t="inlineStr"/>
+      <c r="U69" s="6" t="inlineStr"/>
+      <c r="V69" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-status-reporter/SKILL.md:352; .claude/skills/asana-pd-manager/references/role-map.md:24; Alvin, 2026-07-31 (role correction)</t>
         </is>
       </c>
-      <c r="V69" s="6" t="inlineStr">
+      <c r="W69" s="6" t="inlineStr">
         <is>
           <t>Creative Requests Asana project owner is Ivy, Editorial/Design team. Ivy supports Erin and Jan. A and R both IT. Danielle consulted on intake priority.</t>
         </is>
@@ -4952,13 +5066,14 @@
       <c r="Q70" s="7" t="inlineStr"/>
       <c r="R70" s="7" t="inlineStr"/>
       <c r="S70" s="7" t="inlineStr"/>
-      <c r="T70" s="6" t="inlineStr"/>
-      <c r="U70" s="6" t="inlineStr">
+      <c r="T70" s="7" t="inlineStr"/>
+      <c r="U70" s="6" t="inlineStr"/>
+      <c r="V70" s="6" t="inlineStr">
         <is>
           <t>connections.md:7; context/about-business.md:5; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V70" s="6" t="inlineStr">
+      <c r="W70" s="6" t="inlineStr">
         <is>
           <t>Nicole is accountable for all channels - DTC, Amazon and wholesale - with Alvin consulted and Danielle informed. This was the last row on the matrix with no owner; it now has one.</t>
         </is>
@@ -5004,17 +5119,18 @@
       <c r="Q71" s="7" t="inlineStr"/>
       <c r="R71" s="7" t="inlineStr"/>
       <c r="S71" s="7" t="inlineStr"/>
-      <c r="T71" s="6" t="inlineStr">
+      <c r="T71" s="7" t="inlineStr"/>
+      <c r="U71" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U71" s="6" t="inlineStr">
+      <c r="V71" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/oc3pl-order-manager/SKILL.md:61,191; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
         </is>
       </c>
-      <c r="V71" s="6" t="inlineStr">
+      <c r="W71" s="6" t="inlineStr">
         <is>
           <t>Ex-Ops-Coordinator scope, now Nicole per the interim split. A and R both NI.</t>
         </is>
@@ -5072,17 +5188,18 @@
       <c r="Q72" s="7" t="inlineStr"/>
       <c r="R72" s="7" t="inlineStr"/>
       <c r="S72" s="7" t="inlineStr"/>
-      <c r="T72" s="6" t="inlineStr">
+      <c r="T72" s="7" t="inlineStr"/>
+      <c r="U72" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U72" s="6" t="inlineStr">
+      <c r="V72" s="6" t="inlineStr">
         <is>
           <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V72" s="6" t="inlineStr">
+      <c r="W72" s="6" t="inlineStr">
         <is>
           <t>Named in the Ops Specialist JD under Order Management &amp; Channel Operations. Nicole holds the channel relationship. Part of Nicole's all-channel accountability.</t>
         </is>
@@ -5128,17 +5245,18 @@
       <c r="Q73" s="7" t="inlineStr"/>
       <c r="R73" s="7" t="inlineStr"/>
       <c r="S73" s="7" t="inlineStr"/>
-      <c r="T73" s="6" t="inlineStr">
+      <c r="T73" s="7" t="inlineStr"/>
+      <c r="U73" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U73" s="6" t="inlineStr">
+      <c r="V73" s="6" t="inlineStr">
         <is>
           <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
         </is>
       </c>
-      <c r="V73" s="6" t="inlineStr">
+      <c r="W73" s="6" t="inlineStr">
         <is>
           <t>JD wording: resolve fulfillment issues "before a customer has to follow up." Sits inside Nicole's interim OC3PL coverage. A and R both NI.</t>
         </is>
@@ -5196,17 +5314,18 @@
       <c r="Q74" s="7" t="inlineStr"/>
       <c r="R74" s="7" t="inlineStr"/>
       <c r="S74" s="7" t="inlineStr"/>
-      <c r="T74" s="6" t="inlineStr">
+      <c r="T74" s="7" t="inlineStr"/>
+      <c r="U74" s="6" t="inlineStr">
         <is>
           <t>Operations Specialist</t>
         </is>
       </c>
-      <c r="U74" s="6" t="inlineStr">
+      <c r="V74" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json (Sales &amp; Commerce / Amazon Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V74" s="6" t="inlineStr">
+      <c r="W74" s="6" t="inlineStr">
         <is>
           <t>Hub gave Amazon to Alvin; resolved to Nicole under all-channel accountability with Alvin doing the work. Inventory and inbound pipeline transition to the Ops Specialist.</t>
         </is>
@@ -5268,13 +5387,14 @@
       <c r="Q75" s="7" t="inlineStr"/>
       <c r="R75" s="7" t="inlineStr"/>
       <c r="S75" s="7" t="inlineStr"/>
-      <c r="T75" s="6" t="inlineStr"/>
-      <c r="U75" s="6" t="inlineStr">
+      <c r="T75" s="7" t="inlineStr"/>
+      <c r="U75" s="6" t="inlineStr"/>
+      <c r="V75" s="6" t="inlineStr">
         <is>
           <t>acb-thelanding: data/links.json (Sales &amp; Commerce / SJS Product Copy Database); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V75" s="6" t="inlineStr">
+      <c r="W75" s="6" t="inlineStr">
         <is>
           <t>Product Copy Database is live from PLM and carries every claim, ingredient line, FAQ and Amazon title across DTC, Amazon and wholesale. Perrine and Regulatory consulted because claims on a PDP are claims. A and R both Soraya.</t>
         </is>
@@ -5320,13 +5440,14 @@
       <c r="Q76" s="7" t="inlineStr"/>
       <c r="R76" s="7" t="inlineStr"/>
       <c r="S76" s="7" t="inlineStr"/>
-      <c r="T76" s="6" t="inlineStr"/>
-      <c r="U76" s="6" t="inlineStr">
+      <c r="T76" s="7" t="inlineStr"/>
+      <c r="U76" s="6" t="inlineStr"/>
+      <c r="V76" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-margin-architect/references/framework.md:209; .claude/skills/sjs-margin-portfolio-review/SKILL.md:1</t>
         </is>
       </c>
-      <c r="V76" s="6" t="inlineStr">
+      <c r="W76" s="6" t="inlineStr">
         <is>
           <t>Framework reference plus the quarterly portfolio sweep and traffic-light report. A and R both AB.</t>
         </is>
@@ -5380,13 +5501,14 @@
       <c r="Q77" s="7" t="inlineStr"/>
       <c r="R77" s="7" t="inlineStr"/>
       <c r="S77" s="7" t="inlineStr"/>
-      <c r="T77" s="6" t="inlineStr"/>
-      <c r="U77" s="6" t="inlineStr">
+      <c r="T77" s="7" t="inlineStr"/>
+      <c r="U77" s="6" t="inlineStr"/>
+      <c r="V77" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-margin-pressure-test/SKILL.md:93</t>
         </is>
       </c>
-      <c r="V77" s="6" t="inlineStr">
+      <c r="W77" s="6" t="inlineStr">
         <is>
           <t>Flagged as Perrine and Soraya's call to ratify, with Alvin on admin, Nicole consulting and Danielle approving.</t>
         </is>
@@ -5440,13 +5562,14 @@
       <c r="Q78" s="7" t="inlineStr"/>
       <c r="R78" s="7" t="inlineStr"/>
       <c r="S78" s="7" t="inlineStr"/>
-      <c r="T78" s="6" t="inlineStr"/>
-      <c r="U78" s="6" t="inlineStr">
+      <c r="T78" s="7" t="inlineStr"/>
+      <c r="U78" s="6" t="inlineStr"/>
+      <c r="V78" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-margin-walk-away/SKILL.md:93,105,118</t>
         </is>
       </c>
-      <c r="V78" s="6" t="inlineStr">
+      <c r="W78" s="6" t="inlineStr">
         <is>
           <t>Danielle approves on three of the four paths. Alvin carries the work on all four.</t>
         </is>
@@ -5496,13 +5619,14 @@
       <c r="Q79" s="7" t="inlineStr"/>
       <c r="R79" s="7" t="inlineStr"/>
       <c r="S79" s="7" t="inlineStr"/>
-      <c r="T79" s="6" t="inlineStr"/>
-      <c r="U79" s="6" t="inlineStr">
+      <c r="T79" s="7" t="inlineStr"/>
+      <c r="U79" s="6" t="inlineStr"/>
+      <c r="V79" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-margin-walk-away/SKILL.md:78</t>
         </is>
       </c>
-      <c r="V79" s="6" t="inlineStr">
+      <c r="W79" s="6" t="inlineStr">
         <is>
           <t>Perrine as PD owner with Alvin on PD admin and sourcing; Nicole consults.</t>
         </is>
@@ -5548,13 +5672,14 @@
       <c r="Q80" s="7" t="inlineStr"/>
       <c r="R80" s="7" t="inlineStr"/>
       <c r="S80" s="7" t="inlineStr"/>
-      <c r="T80" s="6" t="inlineStr"/>
-      <c r="U80" s="6" t="inlineStr">
+      <c r="T80" s="7" t="inlineStr"/>
+      <c r="U80" s="6" t="inlineStr"/>
+      <c r="V80" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/regulatory-manager/SKILL.md:196; .claude/skills/purchasing-manager/SKILL.md:365; Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V80" s="6" t="inlineStr">
+      <c r="W80" s="6" t="inlineStr">
         <is>
           <t>regulatory-manager Jobs 8 and 9 read vendor_invoices directly; purchasing-manager has no rollup of its own. A and R both AB. Ironclad consulted - the rollup feeds their books.</t>
         </is>
@@ -5600,13 +5725,14 @@
       <c r="Q81" s="7" t="inlineStr"/>
       <c r="R81" s="7" t="inlineStr"/>
       <c r="S81" s="7" t="inlineStr"/>
-      <c r="T81" s="6" t="inlineStr"/>
-      <c r="U81" s="6" t="inlineStr">
+      <c r="T81" s="7" t="inlineStr"/>
+      <c r="U81" s="6" t="inlineStr"/>
+      <c r="V81" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V81" s="6" t="inlineStr">
+      <c r="W81" s="6" t="inlineStr">
         <is>
           <t>Ironclad Finance runs AP, bookkeeping and payroll; Dan Bender is the contact. Cost-side accountability sits with Operations because the vendor-invoice pipeline and its five approval gates feed it. No longer an unowned function.</t>
         </is>
@@ -5660,13 +5786,14 @@
       <c r="Q82" s="7" t="inlineStr"/>
       <c r="R82" s="7" t="inlineStr"/>
       <c r="S82" s="7" t="inlineStr"/>
-      <c r="T82" s="6" t="inlineStr"/>
-      <c r="U82" s="6" t="inlineStr">
+      <c r="T82" s="7" t="inlineStr"/>
+      <c r="U82" s="6" t="inlineStr"/>
+      <c r="V82" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V82" s="6" t="inlineStr">
+      <c r="W82" s="6" t="inlineStr">
         <is>
           <t>Ironclad Finance closes the books and produces the reporting; Dan Bender is the contact. Reporting accountability sits with the President.</t>
         </is>
@@ -5724,13 +5851,14 @@
       <c r="Q83" s="7" t="inlineStr"/>
       <c r="R83" s="7" t="inlineStr"/>
       <c r="S83" s="7" t="inlineStr"/>
-      <c r="T83" s="6" t="inlineStr"/>
-      <c r="U83" s="6" t="inlineStr">
+      <c r="T83" s="7" t="inlineStr"/>
+      <c r="U83" s="6" t="inlineStr"/>
+      <c r="V83" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V83" s="6" t="inlineStr">
+      <c r="W83" s="6" t="inlineStr">
         <is>
           <t>President answers for the budget. Operations and Consumer Strategy feed the operating and channel assumptions.</t>
         </is>
@@ -5784,13 +5912,14 @@
       <c r="Q84" s="7" t="inlineStr"/>
       <c r="R84" s="7" t="inlineStr"/>
       <c r="S84" s="7" t="inlineStr"/>
-      <c r="T84" s="6" t="inlineStr"/>
-      <c r="U84" s="6" t="inlineStr">
+      <c r="T84" s="7" t="inlineStr"/>
+      <c r="U84" s="6" t="inlineStr"/>
+      <c r="V84" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (external partners); .claude/skills/inventory-manager/SKILL.md:18</t>
         </is>
       </c>
-      <c r="V84" s="6" t="inlineStr">
+      <c r="W84" s="6" t="inlineStr">
         <is>
           <t>Cost side, so accountability sits with Operations - it flows out of purchasing, receiving and the inventory ledger. Ironclad carries it into the books.</t>
         </is>
@@ -5844,13 +5973,14 @@
       </c>
       <c r="R85" s="7" t="inlineStr"/>
       <c r="S85" s="7" t="inlineStr"/>
-      <c r="T85" s="6" t="inlineStr"/>
-      <c r="U85" s="6" t="inlineStr">
+      <c r="T85" s="7" t="inlineStr"/>
+      <c r="U85" s="6" t="inlineStr"/>
+      <c r="V85" s="6" t="inlineStr">
         <is>
           <t>decisions/log.md:52,58; context/priorities.md:3; Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V85" s="6" t="inlineStr">
+      <c r="W85" s="6" t="inlineStr">
         <is>
           <t>Both new roles report to Nicole. Decision owner recorded as Alvin, with Nicole on the two new roles once filled. Priority 1 of 2 this quarter. Calm HR runs the recruiting process once the RACI clears Danielle.</t>
         </is>
@@ -5896,13 +6026,14 @@
       <c r="Q86" s="7" t="inlineStr"/>
       <c r="R86" s="7" t="inlineStr"/>
       <c r="S86" s="7" t="inlineStr"/>
-      <c r="T86" s="6" t="inlineStr"/>
-      <c r="U86" s="6" t="inlineStr">
+      <c r="T86" s="7" t="inlineStr"/>
+      <c r="U86" s="6" t="inlineStr"/>
+      <c r="V86" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:50; .claude/skills/sjs-comp-intel/references/sequencing-plan.md:12</t>
         </is>
       </c>
-      <c r="V86" s="6" t="inlineStr">
+      <c r="W86" s="6" t="inlineStr">
         <is>
           <t>Ex-Ops-Coordinator scope. Alvin carries it directly until the Operations Specialist starts. A and R both AB.</t>
         </is>
@@ -5952,15 +6083,20 @@
       </c>
       <c r="R87" s="7" t="inlineStr"/>
       <c r="S87" s="7" t="inlineStr"/>
-      <c r="T87" s="6" t="inlineStr"/>
-      <c r="U87" s="6" t="inlineStr">
-        <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:48-56; Alvin, 2026-07-31 (external partners)</t>
-        </is>
-      </c>
+      <c r="T87" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U87" s="6" t="inlineStr"/>
       <c r="V87" s="6" t="inlineStr">
         <is>
-          <t>Calm HR is the PEO and co-employer and runs the process; Alvin is the liaison and answers for it. Danielle consulted. No longer an unowned function - the departed-role-holder checklist in the PD role-map remains the internal system-side counterpart.</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:48-56; Alvin, 2026-07-31 (external partners); Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W87" s="6" t="inlineStr">
+        <is>
+          <t>Calm HR is the PEO and co-employer and runs the process; Alvin is the liaison and answers for it. Danielle consulted. No longer an unowned function - the departed-role-holder checklist in the PD role-map remains the internal system-side counterpart. Two partners split this: Calm HR runs the employment side, Coastal Interactive runs equipment and account provisioning. Alvin is the liaison to both and answers for the whole.</t>
         </is>
       </c>
     </row>
@@ -6008,13 +6144,14 @@
       <c r="Q88" s="7" t="inlineStr"/>
       <c r="R88" s="7" t="inlineStr"/>
       <c r="S88" s="7" t="inlineStr"/>
-      <c r="T88" s="6" t="inlineStr"/>
-      <c r="U88" s="6" t="inlineStr">
+      <c r="T88" s="7" t="inlineStr"/>
+      <c r="U88" s="6" t="inlineStr"/>
+      <c r="V88" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 52:48-53:17; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
         </is>
       </c>
-      <c r="V88" s="6" t="inlineStr">
+      <c r="W88" s="6" t="inlineStr">
         <is>
           <t>Prioritized first. Danielle: "we're going to prioritize the operations... Specialist." Reports to Nicole. Target in place before Q4. Salary band $72-90K.</t>
         </is>
@@ -6064,13 +6201,14 @@
       <c r="Q89" s="7" t="inlineStr"/>
       <c r="R89" s="7" t="inlineStr"/>
       <c r="S89" s="7" t="inlineStr"/>
-      <c r="T89" s="6" t="inlineStr"/>
-      <c r="U89" s="6" t="inlineStr">
+      <c r="T89" s="7" t="inlineStr"/>
+      <c r="U89" s="6" t="inlineStr"/>
+      <c r="V89" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 53:17-57:10; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
         </is>
       </c>
-      <c r="V89" s="6" t="inlineStr">
+      <c r="W89" s="6" t="inlineStr">
         <is>
           <t>Phased in after the Ops Specialist. Danielle scopes it as "air traffic control, holding people accountable" rather than strategy or ideation, and is adding trend-forecasting language to the JD. Reports to Nicole. Salary band $75-95K.</t>
         </is>
@@ -6116,13 +6254,14 @@
       <c r="Q90" s="7" t="inlineStr"/>
       <c r="R90" s="7" t="inlineStr"/>
       <c r="S90" s="7" t="inlineStr"/>
-      <c r="T90" s="6" t="inlineStr"/>
-      <c r="U90" s="6" t="inlineStr">
+      <c r="T90" s="7" t="inlineStr"/>
+      <c r="U90" s="6" t="inlineStr"/>
+      <c r="V90" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
         </is>
       </c>
-      <c r="V90" s="6" t="inlineStr">
+      <c r="W90" s="6" t="inlineStr">
         <is>
           <t>Danielle's condition on the hire: clean up the system first so the role can function. Nicole's action item from the review.</t>
         </is>
@@ -6176,13 +6315,14 @@
       </c>
       <c r="R91" s="7" t="inlineStr"/>
       <c r="S91" s="7" t="inlineStr"/>
-      <c r="T91" s="6" t="inlineStr"/>
-      <c r="U91" s="6" t="inlineStr">
+      <c r="T91" s="7" t="inlineStr"/>
+      <c r="U91" s="6" t="inlineStr"/>
+      <c r="V91" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V91" s="6" t="inlineStr">
+      <c r="W91" s="6" t="inlineStr">
         <is>
           <t>Calm HR drafts and maintains; Alvin is the liaison and answers for it; Danielle co-approves. Handbook is in flight as of 2026-07-30 and goes to legal review before implementation.</t>
         </is>
@@ -6232,13 +6372,14 @@
       </c>
       <c r="R92" s="7" t="inlineStr"/>
       <c r="S92" s="7" t="inlineStr"/>
-      <c r="T92" s="6" t="inlineStr"/>
-      <c r="U92" s="6" t="inlineStr">
+      <c r="T92" s="7" t="inlineStr"/>
+      <c r="U92" s="6" t="inlineStr"/>
+      <c r="V92" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V92" s="6" t="inlineStr">
+      <c r="W92" s="6" t="inlineStr">
         <is>
           <t>Calm HR administers as co-employer. Ironclad consulted where payroll hits the books.</t>
         </is>
@@ -6284,13 +6425,14 @@
       </c>
       <c r="R93" s="7" t="inlineStr"/>
       <c r="S93" s="7" t="inlineStr"/>
-      <c r="T93" s="6" t="inlineStr"/>
-      <c r="U93" s="6" t="inlineStr">
+      <c r="T93" s="7" t="inlineStr"/>
+      <c r="U93" s="6" t="inlineStr"/>
+      <c r="V93" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
-      <c r="V93" s="6" t="inlineStr">
+      <c r="W93" s="6" t="inlineStr">
         <is>
           <t>Calm HR runs the process with outside counsel where needed. Danielle co-approves every separation.</t>
         </is>
@@ -6332,13 +6474,14 @@
       <c r="Q94" s="7" t="inlineStr"/>
       <c r="R94" s="7" t="inlineStr"/>
       <c r="S94" s="7" t="inlineStr"/>
-      <c r="T94" s="6" t="inlineStr"/>
-      <c r="U94" s="6" t="inlineStr">
+      <c r="T94" s="7" t="inlineStr"/>
+      <c r="U94" s="6" t="inlineStr"/>
+      <c r="V94" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/plm-assistant/SKILL.md:292; decisions/wiki-layer-audit-2026-07-29.md:52</t>
         </is>
       </c>
-      <c r="V94" s="6" t="inlineStr">
+      <c r="W94" s="6" t="inlineStr">
         <is>
           <t>plm-assistant is the sole PLM writer and every write needs Operations sign-off. Job 0 wiki write-back has not fired since 2026-05-26. A and R both AB.</t>
         </is>
@@ -6376,13 +6519,14 @@
       <c r="Q95" s="7" t="inlineStr"/>
       <c r="R95" s="7" t="inlineStr"/>
       <c r="S95" s="7" t="inlineStr"/>
-      <c r="T95" s="6" t="inlineStr"/>
-      <c r="U95" s="6" t="inlineStr">
+      <c r="T95" s="7" t="inlineStr"/>
+      <c r="U95" s="6" t="inlineStr"/>
+      <c r="V95" s="6" t="inlineStr">
         <is>
           <t>.claude/skills/quality-status-reporter/SKILL.md:34-50; .claude/skills/quality-status-reporter/references/hub-integration.md:85</t>
         </is>
       </c>
-      <c r="V95" s="6" t="inlineStr">
+      <c r="W95" s="6" t="inlineStr">
         <is>
           <t>All hub writes go through the landing-hub-publish Function behind an Operator gate. Deploy is commit-and-push only, never Netlify CLI. A and R both AB.</t>
         </is>
@@ -6424,15 +6568,20 @@
       <c r="Q96" s="7" t="inlineStr"/>
       <c r="R96" s="7" t="inlineStr"/>
       <c r="S96" s="7" t="inlineStr"/>
-      <c r="T96" s="6" t="inlineStr"/>
-      <c r="U96" s="6" t="inlineStr">
-        <is>
-          <t>references/architecture/asana_task_contract.md:227; connections.md:5-13</t>
-        </is>
-      </c>
+      <c r="T96" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U96" s="6" t="inlineStr"/>
       <c r="V96" s="6" t="inlineStr">
         <is>
-          <t>An unresolvable role-holder is surfaced for Alvin to decide, not dropped. Seven tool domains registered; iMessage still not connected. A and R both AB.</t>
+          <t>references/architecture/asana_task_contract.md:227; connections.md:5-13; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W96" s="6" t="inlineStr">
+        <is>
+          <t>An unresolvable role-holder is surfaced for Alvin to decide, not dropped. Seven tool domains registered; iMessage still not connected. A and R both AB. Coastal Interactive consulted on identity, access and integration plumbing behind the connectors.</t>
         </is>
       </c>
     </row>
@@ -6468,13 +6617,14 @@
       <c r="Q97" s="7" t="inlineStr"/>
       <c r="R97" s="7" t="inlineStr"/>
       <c r="S97" s="7" t="inlineStr"/>
-      <c r="T97" s="6" t="inlineStr"/>
-      <c r="U97" s="6" t="inlineStr">
+      <c r="T97" s="7" t="inlineStr"/>
+      <c r="U97" s="6" t="inlineStr"/>
+      <c r="V97" s="6" t="inlineStr">
         <is>
           <t>decisions/skills-architecture-tracker.md:4; decisions/log.md:31,45</t>
         </is>
       </c>
-      <c r="V97" s="6" t="inlineStr">
+      <c r="W97" s="6" t="inlineStr">
         <is>
           <t>Owner recorded as Alvin Belt across the architecture decisions. Priority 2 of 2 this quarter. A and R both AB.</t>
         </is>
@@ -6516,13 +6666,14 @@
       <c r="Q98" s="7" t="inlineStr"/>
       <c r="R98" s="7" t="inlineStr"/>
       <c r="S98" s="7" t="inlineStr"/>
-      <c r="T98" s="6" t="inlineStr"/>
-      <c r="U98" s="6" t="inlineStr">
+      <c r="T98" s="7" t="inlineStr"/>
+      <c r="U98" s="6" t="inlineStr"/>
+      <c r="V98" s="6" t="inlineStr">
         <is>
           <t>scheduled-prompts/weekly-pd-update.md:91; scheduled-prompts/sjs-purchasing-monthly-rollup-and-snapshot.md:79</t>
         </is>
       </c>
-      <c r="V98" s="6" t="inlineStr">
+      <c r="W98" s="6" t="inlineStr">
         <is>
           <t>Nothing commits until Alvin says go. Same pattern across all 23 Routines, including the ones that fire unattended on a schedule. A and R both AB.</t>
         </is>
@@ -6568,13 +6719,14 @@
       <c r="Q99" s="7" t="inlineStr"/>
       <c r="R99" s="7" t="inlineStr"/>
       <c r="S99" s="7" t="inlineStr"/>
-      <c r="T99" s="6" t="inlineStr"/>
-      <c r="U99" s="6" t="inlineStr">
+      <c r="T99" s="7" t="inlineStr"/>
+      <c r="U99" s="6" t="inlineStr"/>
+      <c r="V99" s="6" t="inlineStr">
         <is>
           <t>Leadership Business Review 2026-07-30 52:12-52:39</t>
         </is>
       </c>
-      <c r="V99" s="6" t="inlineStr">
+      <c r="W99" s="6" t="inlineStr">
         <is>
           <t>Alvin owns the framework, built with Nicole in the builder session, then to Danielle for final review before it goes to Calm HR to start recruiting.</t>
         </is>
@@ -6636,13 +6788,14 @@
           <t>R</t>
         </is>
       </c>
-      <c r="T100" s="6" t="inlineStr"/>
-      <c r="U100" s="6" t="inlineStr">
+      <c r="T100" s="7" t="inlineStr"/>
+      <c r="U100" s="6" t="inlineStr"/>
+      <c r="V100" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V100" s="6" t="inlineStr">
+      <c r="W100" s="6" t="inlineStr">
         <is>
           <t>Teknologics is the web development partner. Danielle accountable; Nicole is the systems and tech owner; Erin and Ivy on visual design; Soraya consulted on merchandising and content; Alvin informed.</t>
         </is>
@@ -6700,249 +6853,322 @@
           <t>C</t>
         </is>
       </c>
-      <c r="T101" s="6" t="inlineStr"/>
-      <c r="U101" s="6" t="inlineStr">
+      <c r="T101" s="7" t="inlineStr"/>
+      <c r="U101" s="6" t="inlineStr"/>
+      <c r="V101" s="6" t="inlineStr">
         <is>
           <t>Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
-      <c r="V101" s="6" t="inlineStr">
+      <c r="W101" s="6" t="inlineStr">
         <is>
           <t>Nicole is the systems and tech owner for the web and digital stack. Scoped here to web and digital rather than the whole IT function - the PLM, Asana, hub-publish and Routine rows still sit with Alvin. Confirm whether that should widen.</t>
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>Back-end IT infrastructure, identity and endpoint management</t>
+        </is>
+      </c>
+      <c r="C102" s="7" t="inlineStr"/>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E102" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr"/>
+      <c r="H102" s="7" t="inlineStr"/>
+      <c r="I102" s="7" t="inlineStr"/>
+      <c r="J102" s="7" t="inlineStr"/>
+      <c r="K102" s="7" t="inlineStr"/>
+      <c r="L102" s="7" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+      <c r="N102" s="7" t="inlineStr"/>
+      <c r="O102" s="7" t="inlineStr"/>
+      <c r="P102" s="7" t="inlineStr"/>
+      <c r="Q102" s="7" t="inlineStr"/>
+      <c r="R102" s="7" t="inlineStr"/>
+      <c r="S102" s="7" t="inlineStr"/>
+      <c r="T102" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="U102" s="6" t="inlineStr"/>
+      <c r="V102" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W102" s="6" t="inlineStr">
+        <is>
+          <t>Coastal Interactive is the managed service provider and handles the higher-level IT and systems work. Alvin is the liaison and answers for it. Distinct from the web and digital stack, which sits with Danielle and Nicole.</t>
+        </is>
+      </c>
+    </row>
     <row r="103">
-      <c r="A103" s="10" t="inlineStr">
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>Equipment procurement, onboarding and asset lifecycle</t>
+        </is>
+      </c>
+      <c r="C103" s="7" t="inlineStr"/>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr"/>
+      <c r="I103" s="7" t="inlineStr"/>
+      <c r="J103" s="7" t="inlineStr"/>
+      <c r="K103" s="7" t="inlineStr"/>
+      <c r="L103" s="7" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+      <c r="N103" s="7" t="inlineStr"/>
+      <c r="O103" s="7" t="inlineStr"/>
+      <c r="P103" s="7" t="inlineStr"/>
+      <c r="Q103" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R103" s="7" t="inlineStr"/>
+      <c r="S103" s="7" t="inlineStr"/>
+      <c r="T103" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="U103" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="V103" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W103" s="6" t="inlineStr">
+        <is>
+          <t>Coastal Interactive provisions and recovers equipment. Pairs with the Calm HR employment side on every start and every exit - the departed-role-holder checklist covers the systems half. Transitions to the Operations Specialist on hire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>IT / Systems &amp; Data</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>Coastal Interactive managed-service engagement and escalation</t>
+        </is>
+      </c>
+      <c r="C104" s="7" t="inlineStr"/>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E104" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="7" t="inlineStr"/>
+      <c r="J104" s="7" t="inlineStr"/>
+      <c r="K104" s="7" t="inlineStr"/>
+      <c r="L104" s="7" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+      <c r="N104" s="7" t="inlineStr"/>
+      <c r="O104" s="7" t="inlineStr"/>
+      <c r="P104" s="7" t="inlineStr"/>
+      <c r="Q104" s="7" t="inlineStr"/>
+      <c r="R104" s="7" t="inlineStr"/>
+      <c r="S104" s="7" t="inlineStr"/>
+      <c r="T104" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U104" s="6" t="inlineStr"/>
+      <c r="V104" s="6" t="inlineStr">
+        <is>
+          <t>Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+        </is>
+      </c>
+      <c r="W104" s="6" t="inlineStr">
+        <is>
+          <t>A and R both Alvin - he is the sole liaison to the IT managed-service partner. Same single-point shape as the other partner relationships.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="11" t="n"/>
-      <c r="B104" s="12" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="11" t="n"/>
+      <c r="B107" s="12" t="inlineStr">
         <is>
           <t>A = answers for the outcome (exactly one per row)</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="13" t="n"/>
-      <c r="B105" s="12" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="13" t="n"/>
+      <c r="B108" s="12" t="inlineStr">
         <is>
           <t>R = does the work (exactly one per row)</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="11" t="n"/>
-      <c r="B106" s="12" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="11" t="n"/>
+      <c r="B109" s="12" t="inlineStr">
         <is>
           <t>A/R = the same person holds both, so the row has no second pair of eyes</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="B107" s="12" t="inlineStr">
+    <row r="110">
+      <c r="B110" s="12" t="inlineStr">
         <is>
           <t>C = consulted before the decision</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="B108" s="12" t="inlineStr">
+    <row r="111">
+      <c r="B111" s="12" t="inlineStr">
         <is>
           <t>I = informed after it</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="B109" s="12" t="inlineStr">
+    <row r="112">
+      <c r="B112" s="12" t="inlineStr">
         <is>
           <t>-&gt; = the open seat that absorbs R on hire. Open seats never hold A or R.</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="10" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
         <is>
           <t>Positions</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="14" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="14" t="inlineStr">
         <is>
           <t>Code</t>
         </is>
       </c>
-      <c r="B112" s="14" t="inlineStr">
+      <c r="B115" s="14" t="inlineStr">
         <is>
           <t>Position</t>
         </is>
       </c>
-      <c r="C112" s="14" t="inlineStr">
+      <c r="C115" s="14" t="inlineStr">
         <is>
           <t>Holder</t>
         </is>
       </c>
-      <c r="D112" s="14" t="inlineStr">
+      <c r="D115" s="14" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E112" s="14" t="inlineStr">
+      <c r="E115" s="14" t="inlineStr">
         <is>
           <t>A count</t>
         </is>
       </c>
-      <c r="F112" s="14" t="inlineStr">
+      <c r="F115" s="14" t="inlineStr">
         <is>
           <t>R count</t>
         </is>
       </c>
-      <c r="G112" s="14" t="inlineStr">
+      <c r="G115" s="14" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="H112" s="14" t="inlineStr">
+      <c r="H115" s="14" t="inlineStr">
         <is>
           <t>Hands off</t>
         </is>
       </c>
-      <c r="I112" s="14" t="inlineStr">
+      <c r="I115" s="14" t="inlineStr">
         <is>
           <t>Absorbs</t>
         </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="12" t="inlineStr">
-        <is>
-          <t>AC</t>
-        </is>
-      </c>
-      <c r="B113" s="12" t="inlineStr">
-        <is>
-          <t>Owner / Founder</t>
-        </is>
-      </c>
-      <c r="C113" s="12" t="inlineStr">
-        <is>
-          <t>Ayesha Curry</t>
-        </is>
-      </c>
-      <c r="D113" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E113" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F113" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H113" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="12" t="inlineStr">
-        <is>
-          <t>DI</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="inlineStr">
-        <is>
-          <t>President</t>
-        </is>
-      </c>
-      <c r="C114" s="12" t="inlineStr">
-        <is>
-          <t>Danielle Iturbe</t>
-        </is>
-      </c>
-      <c r="D114" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="F114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="12" t="inlineStr">
-        <is>
-          <t>AB</t>
-        </is>
-      </c>
-      <c r="B115" s="12" t="inlineStr">
-        <is>
-          <t>VP of Operations</t>
-        </is>
-      </c>
-      <c r="C115" s="12" t="inlineStr">
-        <is>
-          <t>Alvin Belt</t>
-        </is>
-      </c>
-      <c r="D115" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
-        </is>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>43</v>
-      </c>
-      <c r="F115" s="15" t="n">
-        <v>57</v>
-      </c>
-      <c r="G115" s="15" t="n">
-        <v>29</v>
-      </c>
-      <c r="H115" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="I115" s="15" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>AC</t>
         </is>
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
+          <t>Owner / Founder</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>Nicole Iturbe</t>
+          <t>Ayesha Curry</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -6951,16 +7177,16 @@
         </is>
       </c>
       <c r="E116" s="15" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F116" s="15" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G116" s="15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I116" s="15" t="n">
         <v>0</v>
@@ -6969,26 +7195,26 @@
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
-          <t>OPS</t>
+          <t>DI</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Operations Specialist</t>
+          <t>President</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Open seat</t>
-        </is>
-      </c>
-      <c r="D117" s="16" t="inlineStr">
-        <is>
-          <t>recruiting</t>
+          <t>Danielle Iturbe</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
         </is>
       </c>
       <c r="E117" s="15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F117" s="15" t="n">
         <v>0</v>
@@ -7000,60 +7226,60 @@
         <v>0</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t>PDS</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>Product Development Specialist</t>
+          <t>VP of Operations</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>Open seat</t>
-        </is>
-      </c>
-      <c r="D118" s="16" t="inlineStr">
-        <is>
-          <t>phased</t>
+          <t>Alvin Belt</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Soraya Salgadoe</t>
+          <t>Nicole Iturbe</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -7062,16 +7288,16 @@
         </is>
       </c>
       <c r="E119" s="15" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G119" s="15" t="n">
+        <v>7</v>
+      </c>
+      <c r="H119" s="15" t="n">
         <v>3</v>
-      </c>
-      <c r="H119" s="15" t="n">
-        <v>0</v>
       </c>
       <c r="I119" s="15" t="n">
         <v>0</v>
@@ -7080,91 +7306,91 @@
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>OPS</t>
         </is>
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>Social Media Coordinator</t>
+          <t>Operations Specialist</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>Kate Le</t>
-        </is>
-      </c>
-      <c r="D120" s="12" t="inlineStr">
-        <is>
-          <t>filled</t>
+          <t>Open seat</t>
+        </is>
+      </c>
+      <c r="D120" s="16" t="inlineStr">
+        <is>
+          <t>recruiting</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G120" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I120" s="15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>PDS</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Creative Director</t>
+          <t>Product Development Specialist</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Erin Hover</t>
-        </is>
-      </c>
-      <c r="D121" s="12" t="inlineStr">
-        <is>
-          <t>contractor</t>
+          <t>Open seat</t>
+        </is>
+      </c>
+      <c r="D121" s="16" t="inlineStr">
+        <is>
+          <t>phased</t>
         </is>
       </c>
       <c r="E121" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G121" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>Creative / Design Coordinator</t>
+          <t>Marketing Manager</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>Ivy Tan</t>
+          <t>Soraya Salgadoe</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
@@ -7173,13 +7399,13 @@
         </is>
       </c>
       <c r="E122" s="15" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H122" s="15" t="n">
         <v>0</v>
@@ -7191,32 +7417,32 @@
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
         <is>
-          <t>JH</t>
+          <t>KL</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Packaging Engineer</t>
+          <t>Social Media Coordinator</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Jan Haeck</t>
+          <t>Kate Le</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>contractor</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E123" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>0</v>
@@ -7228,17 +7454,17 @@
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
         <is>
-          <t>PC</t>
+          <t>EH</t>
         </is>
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>PD / R&amp;D contractor, Milinyc</t>
+          <t>Creative Director</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>Perrine Calvet</t>
+          <t>Erin Hover</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
@@ -7247,7 +7473,7 @@
         </is>
       </c>
       <c r="E124" s="15" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F124" s="15" t="n">
         <v>2</v>
@@ -7265,32 +7491,32 @@
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>External regulatory partner</t>
+          <t>Creative / Design Coordinator</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Pedrero Regulatory</t>
+          <t>Ivy Tan</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>filled</t>
         </is>
       </c>
       <c r="E125" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G125" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" s="15" t="n">
         <v>0</v>
@@ -7302,29 +7528,29 @@
     <row r="126">
       <c r="A126" s="12" t="inlineStr">
         <is>
-          <t>IF</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="B126" s="12" t="inlineStr">
         <is>
-          <t>Outsourced finance (Dan Bender)</t>
+          <t>Packaging Engineer</t>
         </is>
       </c>
       <c r="C126" s="12" t="inlineStr">
         <is>
-          <t>Ironclad Finance</t>
+          <t>Jan Haeck</t>
         </is>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G126" s="15" t="n">
         <v>0</v>
@@ -7339,32 +7565,32 @@
     <row r="127">
       <c r="A127" s="12" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>PEO and co-employer</t>
+          <t>PD / R&amp;D contractor, Milinyc</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Calm HR</t>
+          <t>Perrine Calvet</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>partner</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="E127" s="15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F127" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G127" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H127" s="15" t="n">
         <v>0</v>
@@ -7376,17 +7602,17 @@
     <row r="128">
       <c r="A128" s="12" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B128" s="12" t="inlineStr">
         <is>
-          <t>Digital marketing agency</t>
+          <t>External regulatory partner</t>
         </is>
       </c>
       <c r="C128" s="12" t="inlineStr">
         <is>
-          <t>WITHIN</t>
+          <t>Pedrero Regulatory</t>
         </is>
       </c>
       <c r="D128" s="12" t="inlineStr">
@@ -7398,7 +7624,7 @@
         <v>0</v>
       </c>
       <c r="F128" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G128" s="15" t="n">
         <v>0</v>
@@ -7413,54 +7639,202 @@
     <row r="129">
       <c r="A129" s="12" t="inlineStr">
         <is>
+          <t>IF</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Outsourced finance (Dan Bender)</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>Ironclad Finance</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G129" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>PEO and co-employer</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>Calm HR</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Digital marketing agency</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>WITHIN</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G131" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
+        <is>
           <t>TK</t>
         </is>
       </c>
-      <c r="B129" s="12" t="inlineStr">
+      <c r="B132" s="12" t="inlineStr">
         <is>
           <t>Web development</t>
         </is>
       </c>
-      <c r="C129" s="12" t="inlineStr">
+      <c r="C132" s="12" t="inlineStr">
         <is>
           <t>Teknologics</t>
         </is>
       </c>
-      <c r="D129" s="12" t="inlineStr">
+      <c r="D132" s="12" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="E129" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="15" t="n">
+      <c r="E132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G129" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="14" t="inlineStr">
+      <c r="G132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>CI</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>Managed IT service provider</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>Coastal Interactive</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G133" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I133" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="inlineStr">
         <is>
           <t>Source of truth</t>
         </is>
       </c>
-      <c r="B131" s="17" t="inlineStr">
+      <c r="B135" s="17" t="inlineStr">
         <is>
           <t>Rows citing a path are relative to the SJ-OS repo. Rows prefixed acb-thelanding cite the AC Brands landing hub, whose links.json defines eleven functions with a named lead each. Rows citing the 30 July leadership review, the 27 July email to Danielle, a job description, or Alvin directly come from those sources. Every row on this matrix has an owner - there are no inferred owners left.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V101"/>
+  <autoFilter ref="A2:W104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7471,7 +7845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -7553,15 +7927,15 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>COUNTIF(RACI!C3:C101,"A")+COUNTIF(RACI!C3:C101,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C104,"A")+COUNTIF(RACI!C3:C104,"A/R")</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>COUNTIF(RACI!C3:C101,"R")+COUNTIF(RACI!C3:C101,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C104,"R")+COUNTIF(RACI!C3:C104,"A/R")</f>
         <v/>
       </c>
       <c r="D6" s="15">
-        <f>COUNTIF(RACI!C3:C101,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C104,"A/R")</f>
         <v/>
       </c>
       <c r="E6" s="15" t="n">
@@ -7586,15 +7960,15 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>COUNTIF(RACI!D3:D101,"A")+COUNTIF(RACI!D3:D101,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D104,"A")+COUNTIF(RACI!D3:D104,"A/R")</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>COUNTIF(RACI!D3:D101,"R")+COUNTIF(RACI!D3:D101,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D104,"R")+COUNTIF(RACI!D3:D104,"A/R")</f>
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>COUNTIF(RACI!D3:D101,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D104,"A/R")</f>
         <v/>
       </c>
       <c r="E7" s="15" t="n">
@@ -7619,15 +7993,15 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>COUNTIF(RACI!E3:E101,"A")+COUNTIF(RACI!E3:E101,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E104,"A")+COUNTIF(RACI!E3:E104,"A/R")</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>COUNTIF(RACI!E3:E101,"R")+COUNTIF(RACI!E3:E101,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E104,"R")+COUNTIF(RACI!E3:E104,"A/R")</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>COUNTIF(RACI!E3:E101,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E104,"A/R")</f>
         <v/>
       </c>
       <c r="E8" s="15" t="n">
@@ -7652,15 +8026,15 @@
         </is>
       </c>
       <c r="B9" s="15">
-        <f>COUNTIF(RACI!F3:F101,"A")+COUNTIF(RACI!F3:F101,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F104,"A")+COUNTIF(RACI!F3:F104,"A/R")</f>
         <v/>
       </c>
       <c r="C9" s="15">
-        <f>COUNTIF(RACI!F3:F101,"R")+COUNTIF(RACI!F3:F101,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F104,"R")+COUNTIF(RACI!F3:F104,"A/R")</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>COUNTIF(RACI!F3:F101,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F104,"A/R")</f>
         <v/>
       </c>
       <c r="E9" s="15" t="n">
@@ -7685,22 +8059,22 @@
         </is>
       </c>
       <c r="B10" s="15">
-        <f>COUNTIF(RACI!G3:G101,"A")+COUNTIF(RACI!G3:G101,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G104,"A")+COUNTIF(RACI!G3:G104,"A/R")</f>
         <v/>
       </c>
       <c r="C10" s="15">
-        <f>COUNTIF(RACI!G3:G101,"R")+COUNTIF(RACI!G3:G101,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G104,"R")+COUNTIF(RACI!G3:G104,"A/R")</f>
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>COUNTIF(RACI!G3:G101,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G104,"A/R")</f>
         <v/>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G10" s="15">
         <f>B10</f>
@@ -7718,15 +8092,15 @@
         </is>
       </c>
       <c r="B11" s="15">
-        <f>COUNTIF(RACI!H3:H101,"A")+COUNTIF(RACI!H3:H101,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H104,"A")+COUNTIF(RACI!H3:H104,"A/R")</f>
         <v/>
       </c>
       <c r="C11" s="15">
-        <f>COUNTIF(RACI!H3:H101,"R")+COUNTIF(RACI!H3:H101,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H104,"R")+COUNTIF(RACI!H3:H104,"A/R")</f>
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>COUNTIF(RACI!H3:H101,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H104,"A/R")</f>
         <v/>
       </c>
       <c r="E11" s="15" t="n">
@@ -7751,15 +8125,15 @@
         </is>
       </c>
       <c r="B12" s="15">
-        <f>COUNTIF(RACI!I3:I101,"A")+COUNTIF(RACI!I3:I101,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I104,"A")+COUNTIF(RACI!I3:I104,"A/R")</f>
         <v/>
       </c>
       <c r="C12" s="15">
-        <f>COUNTIF(RACI!I3:I101,"R")+COUNTIF(RACI!I3:I101,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I104,"R")+COUNTIF(RACI!I3:I104,"A/R")</f>
         <v/>
       </c>
       <c r="D12" s="15">
-        <f>COUNTIF(RACI!I3:I101,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I104,"A/R")</f>
         <v/>
       </c>
       <c r="E12" s="15" t="n">
@@ -7784,15 +8158,15 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>COUNTIF(RACI!J3:J101,"A")+COUNTIF(RACI!J3:J101,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J104,"A")+COUNTIF(RACI!J3:J104,"A/R")</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>COUNTIF(RACI!J3:J101,"R")+COUNTIF(RACI!J3:J101,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J104,"R")+COUNTIF(RACI!J3:J104,"A/R")</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>COUNTIF(RACI!J3:J101,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J104,"A/R")</f>
         <v/>
       </c>
       <c r="E13" s="15" t="n">
@@ -7817,15 +8191,15 @@
         </is>
       </c>
       <c r="B14" s="15">
-        <f>COUNTIF(RACI!K3:K101,"A")+COUNTIF(RACI!K3:K101,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K104,"A")+COUNTIF(RACI!K3:K104,"A/R")</f>
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>COUNTIF(RACI!K3:K101,"R")+COUNTIF(RACI!K3:K101,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K104,"R")+COUNTIF(RACI!K3:K104,"A/R")</f>
         <v/>
       </c>
       <c r="D14" s="15">
-        <f>COUNTIF(RACI!K3:K101,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K104,"A/R")</f>
         <v/>
       </c>
       <c r="E14" s="15" t="n">
@@ -7850,15 +8224,15 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF(RACI!L3:L101,"A")+COUNTIF(RACI!L3:L101,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L104,"A")+COUNTIF(RACI!L3:L104,"A/R")</f>
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>COUNTIF(RACI!L3:L101,"R")+COUNTIF(RACI!L3:L101,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L104,"R")+COUNTIF(RACI!L3:L104,"A/R")</f>
         <v/>
       </c>
       <c r="D15" s="15">
-        <f>COUNTIF(RACI!L3:L101,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L104,"A/R")</f>
         <v/>
       </c>
       <c r="E15" s="15" t="n">
@@ -7883,15 +8257,15 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF(RACI!M3:M101,"A")+COUNTIF(RACI!M3:M101,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M104,"A")+COUNTIF(RACI!M3:M104,"A/R")</f>
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>COUNTIF(RACI!M3:M101,"R")+COUNTIF(RACI!M3:M101,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M104,"R")+COUNTIF(RACI!M3:M104,"A/R")</f>
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>COUNTIF(RACI!M3:M101,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M104,"A/R")</f>
         <v/>
       </c>
       <c r="E16" s="15" t="n">
@@ -7916,15 +8290,15 @@
         </is>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF(RACI!N3:N101,"A")+COUNTIF(RACI!N3:N101,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N104,"A")+COUNTIF(RACI!N3:N104,"A/R")</f>
         <v/>
       </c>
       <c r="C17" s="15">
-        <f>COUNTIF(RACI!N3:N101,"R")+COUNTIF(RACI!N3:N101,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N104,"R")+COUNTIF(RACI!N3:N104,"A/R")</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>COUNTIF(RACI!N3:N101,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N104,"A/R")</f>
         <v/>
       </c>
       <c r="E17" s="15" t="n">
@@ -7949,15 +8323,15 @@
         </is>
       </c>
       <c r="B18" s="15">
-        <f>COUNTIF(RACI!O3:O101,"A")+COUNTIF(RACI!O3:O101,"A/R")</f>
+        <f>COUNTIF(RACI!O3:O104,"A")+COUNTIF(RACI!O3:O104,"A/R")</f>
         <v/>
       </c>
       <c r="C18" s="15">
-        <f>COUNTIF(RACI!O3:O101,"R")+COUNTIF(RACI!O3:O101,"A/R")</f>
+        <f>COUNTIF(RACI!O3:O104,"R")+COUNTIF(RACI!O3:O104,"A/R")</f>
         <v/>
       </c>
       <c r="D18" s="15">
-        <f>COUNTIF(RACI!O3:O101,"A/R")</f>
+        <f>COUNTIF(RACI!O3:O104,"A/R")</f>
         <v/>
       </c>
       <c r="E18" s="15" t="n">
@@ -7982,15 +8356,15 @@
         </is>
       </c>
       <c r="B19" s="15">
-        <f>COUNTIF(RACI!P3:P101,"A")+COUNTIF(RACI!P3:P101,"A/R")</f>
+        <f>COUNTIF(RACI!P3:P104,"A")+COUNTIF(RACI!P3:P104,"A/R")</f>
         <v/>
       </c>
       <c r="C19" s="15">
-        <f>COUNTIF(RACI!P3:P101,"R")+COUNTIF(RACI!P3:P101,"A/R")</f>
+        <f>COUNTIF(RACI!P3:P104,"R")+COUNTIF(RACI!P3:P104,"A/R")</f>
         <v/>
       </c>
       <c r="D19" s="15">
-        <f>COUNTIF(RACI!P3:P101,"A/R")</f>
+        <f>COUNTIF(RACI!P3:P104,"A/R")</f>
         <v/>
       </c>
       <c r="E19" s="15" t="n">
@@ -8015,15 +8389,15 @@
         </is>
       </c>
       <c r="B20" s="15">
-        <f>COUNTIF(RACI!Q3:Q101,"A")+COUNTIF(RACI!Q3:Q101,"A/R")</f>
+        <f>COUNTIF(RACI!Q3:Q104,"A")+COUNTIF(RACI!Q3:Q104,"A/R")</f>
         <v/>
       </c>
       <c r="C20" s="15">
-        <f>COUNTIF(RACI!Q3:Q101,"R")+COUNTIF(RACI!Q3:Q101,"A/R")</f>
+        <f>COUNTIF(RACI!Q3:Q104,"R")+COUNTIF(RACI!Q3:Q104,"A/R")</f>
         <v/>
       </c>
       <c r="D20" s="15">
-        <f>COUNTIF(RACI!Q3:Q101,"A/R")</f>
+        <f>COUNTIF(RACI!Q3:Q104,"A/R")</f>
         <v/>
       </c>
       <c r="E20" s="15" t="n">
@@ -8048,15 +8422,15 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>COUNTIF(RACI!R3:R101,"A")+COUNTIF(RACI!R3:R101,"A/R")</f>
+        <f>COUNTIF(RACI!R3:R104,"A")+COUNTIF(RACI!R3:R104,"A/R")</f>
         <v/>
       </c>
       <c r="C21" s="15">
-        <f>COUNTIF(RACI!R3:R101,"R")+COUNTIF(RACI!R3:R101,"A/R")</f>
+        <f>COUNTIF(RACI!R3:R104,"R")+COUNTIF(RACI!R3:R104,"A/R")</f>
         <v/>
       </c>
       <c r="D21" s="15">
-        <f>COUNTIF(RACI!R3:R101,"A/R")</f>
+        <f>COUNTIF(RACI!R3:R104,"A/R")</f>
         <v/>
       </c>
       <c r="E21" s="15" t="n">
@@ -8081,15 +8455,15 @@
         </is>
       </c>
       <c r="B22" s="15">
-        <f>COUNTIF(RACI!S3:S101,"A")+COUNTIF(RACI!S3:S101,"A/R")</f>
+        <f>COUNTIF(RACI!S3:S104,"A")+COUNTIF(RACI!S3:S104,"A/R")</f>
         <v/>
       </c>
       <c r="C22" s="15">
-        <f>COUNTIF(RACI!S3:S101,"R")+COUNTIF(RACI!S3:S101,"A/R")</f>
+        <f>COUNTIF(RACI!S3:S104,"R")+COUNTIF(RACI!S3:S104,"A/R")</f>
         <v/>
       </c>
       <c r="D22" s="15">
-        <f>COUNTIF(RACI!S3:S101,"A/R")</f>
+        <f>COUNTIF(RACI!S3:S104,"A/R")</f>
         <v/>
       </c>
       <c r="E22" s="15" t="n">
@@ -8108,308 +8482,361 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>CI — Managed IT service provider (Coastal Interactive)</t>
+        </is>
+      </c>
+      <c r="B23" s="15">
+        <f>COUNTIF(RACI!T3:T104,"A")+COUNTIF(RACI!T3:T104,"A/R")</f>
+        <v/>
+      </c>
+      <c r="C23" s="15">
+        <f>COUNTIF(RACI!T3:T104,"R")+COUNTIF(RACI!T3:T104,"A/R")</f>
+        <v/>
+      </c>
+      <c r="D23" s="15">
+        <f>COUNTIF(RACI!T3:T104,"A/R")</f>
+        <v/>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="15">
+        <f>B23</f>
+        <v/>
+      </c>
+      <c r="H23" s="15">
+        <f>C23-E23+F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>Total activities</t>
         </is>
       </c>
-      <c r="B23" s="21">
-        <f>COUNTA(RACI!B3:B101)</f>
+      <c r="B24" s="21">
+        <f>COUNTA(RACI!B3:B104)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
     <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>"A after" and "R after" project the book once both specialist seats are filled. Hands off counts rows where this position does the work today and an incoming seat takes it. Absorbs counts rows arriving on hire.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>Quality now has a gate, and it is not the VP</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-    </row>
-    <row r="29" ht="78" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+    </row>
+    <row r="30" ht="78" customHeight="1">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>The 30 July leadership review moved the quality function onto Nicole. Verbatim from the recording: "Nicole taking the primary focus on the quality management side of things with quality control... anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check... Even with each function having or being the primary owner, we'll still have that quality gate." That shows up as 10 of the 13 Quality rows accountable to Nicole, against 2 for Alvin and 1 for Perrine. Her total book of accountability goes from 8 rows to 21.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>Perrine moves to technical guidance</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr"/>
-    </row>
-    <row r="33" ht="117" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+    </row>
+    <row r="34" ht="117" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>She keeps A on the 7 rows where the judgment is genuinely formulation - formula stage-gate, compatibility and stability and RIPT and PET, in-market stability testing, reformulation, PD-linked receipt, and the two margin rows that turn on formulation cost. Packaging development moved to Erin Hover as the lead technical authority on packaging and artwork. She moves to consulted on everything process-shaped: NCR and CAPA lifecycle, batch hold and release, vendor quality flags, lab finding classification, SOP ratification. Danielle's framing in the review was that there were things the team had assumed Perrine would manage or organize that she is not, and that leadership can pull the plug even when she has submitted an approval. Splitting technical judgment from process ownership is what that means in practice.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>Three contractors hold accountability, and two of them hold it alone</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr"/>
-    </row>
-    <row r="37" ht="104" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+    </row>
+    <row r="38" ht="104" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Erin Hover is the lead technical authority on packaging and artwork and is accountable for 4 rows - creative direction, packaging development, artwork execution, and the label artwork archive. She is also a contractor, and on creative direction she is both A and R with no internal counterpart. Jan Haeck, who executes under her, is a contractor too, so the whole packaging and artwork chain runs through people outside the company. Perrine Calvet is the third, accountable for 7 formulation rows. Between them that is 11 of 79 activities where nobody on staff can check the work or continue it. Neither specialist job description covers creative or formulation authority, so the two hires do not close this.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Nobody is blank on a product decision</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+    </row>
+    <row r="42" ht="65" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>Perrine and Soraya now hold a letter on all eight Product Development rows. Perrine was blank on one - founder brand-line approval - and Soraya was blank on all eight, which meant the marketing read had no formal visibility into any product decision. Both are Informed at minimum now. That is a small change with a real effect: a blank cell on a RACI is ambiguous in a way that Informed is not, because blank does not tell you whether the omission was deliberate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>Marketing and the channels finally have owners with real activities under them</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-    </row>
-    <row r="41" ht="91" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46" ht="91" customHeight="1">
+      <c r="A46" s="17" t="inlineStr">
         <is>
           <t>Soraya goes from 1 accountable row to 8. Marketing now carries editorial calendar, Klaviyo email, paid media, social content, influencer and earned media, the WITHIN relationship, product copy and PDP content - none of which existed on the matrix before, because none of it has a skill behind it. Nicole goes from 21 to 26 with all-channel accountability plus wholesale pipeline, retail price architecture and the retailer promo calendar. Retail &amp; Wholesale went from 2 rows to 5, Marketing from 9 to 15. A skill suite is a good source for what is automated; it is a poor source for what a business does.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="23" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="23" t="inlineStr">
         <is>
           <t>Where the President and the Founder sit</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-    </row>
-    <row r="45" ht="104" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+    </row>
+    <row r="50" ht="104" customHeight="1">
+      <c r="A50" s="17" t="inlineStr">
         <is>
           <t>Danielle Iturbe is accountable for 8 rows - direction-changing PD decisions, the margin walk-away call, brand guideline custody, campaign direction, month-end close, the annual budget, and the two web rows - and is consulted on 25 more. She now appears on all 9 Marketing rows and all 3 Creative rows, which she did not before. Campaign direction was missing from the matrix entirely; adding it is what gave the President somewhere to sit in Marketing rather than only receiving finished work. Ayesha Curry keeps sole accountability for brand-line moves and is consulted on 6 rows where the brand carries her name - brand guideline custody, creative direction, campaign direction, claim substantiation, retailer attestations, and packaging. Informed on the rest.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="23" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="23" t="inlineStr">
         <is>
           <t>Alvin owns the framework, and still does most of the work</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-    </row>
-    <row r="49" ht="65" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
-        <is>
-          <t>Accountable for 43 of 99 activities and doing the work on 57. The framework rows are deliberate - quality management system, SOP framework, this RACI, the skill suite, the 23 scheduled Routines. The problem is not the A column. It is that 31 rows have him as both A and R, and that he does the work on 11 of the 12 Operations rows and 5 of the 8 Product Development rows. He holds the gates and does the work behind them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="23" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+    </row>
+    <row r="54" ht="65" customHeight="1">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Accountable for 46 of 102 activities and doing the work on 58. The framework rows are deliberate - quality management system, SOP framework, this RACI, the skill suite, the 23 scheduled Routines. The problem is not the A column. It is that 31 rows have him as both A and R, and that he does the work on 11 of the 12 Operations rows and 5 of the 8 Product Development rows. He holds the gates and does the work behind them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="23" t="inlineStr">
         <is>
           <t>What the two seats actually move</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
-    <row r="53" ht="65" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+    </row>
+    <row r="58" ht="65" customHeight="1">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>32 rows transition on hire: 16 to the Operations Specialist and 16 to the Product Development Specialist. 29 of those come off Alvin, 3 off Nicole. His R book drops from 55 to 26. Rows with no second pair of eyes drop from 42 to 25 across the whole matrix. Both seats report to Nicole, which is the point Danielle made in the review - moving day-to-day management off the VP seat is the succession outcome the system is being built for.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="23" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
         <is>
           <t>Ops first is the right order, and the matrix says why</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-    </row>
-    <row r="57" ht="91" customHeight="1">
-      <c r="A57" s="17" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+    </row>
+    <row r="62" ht="91" customHeight="1">
+      <c r="A62" s="17" t="inlineStr">
         <is>
           <t>Alvin does the work on 11 of 12 Operations rows. The Operations Specialist job description covers almost exactly that list: daily order operations and the third-party logistics relationship, channel operations across the direct store and Ulta Beauty Marketplace and Amazon, inventory reconciliation and FEFO and out-of-stock signals, receiving, purchase-to-pay, freight and customs and broker relationships, routing-guide and advance-ship-notice compliance, sales and operations planning support, production scheduling, and the label and seeding and sampling projects. That is a defined function sitting on one person today.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="23" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="23" t="inlineStr">
         <is>
           <t>The PD seat is the one that closes the quality loop</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr"/>
-    </row>
-    <row r="61" ht="104" customHeight="1">
-      <c r="A61" s="17" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+    </row>
+    <row r="66" ht="104" customHeight="1">
+      <c r="A66" s="17" t="inlineStr">
         <is>
           <t>Its job description names running the quality system outright - corrective and preventive actions, non-conformances, complaint intake and trend monitoring, lab results, supplier quality flags, batch lifecycle including stability and hold-release, and the quality dashboard - plus pre-launch ingredient and label review, claim substantiation, retailer compliance responses and the registration tracker, and document control across specifications and dielines and artwork versions and bills of materials. Until it is filled, Nicole gates quality and Alvin executes it. That works, and it is the reason the gate is worth having now rather than after the hire, but it is two people covering a role that was written as one.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="23" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="23" t="inlineStr">
         <is>
           <t>Nothing on this matrix is unowned any more</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr"/>
-    </row>
-    <row r="65" ht="117" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t>The first pass reported three unowned functions. All three are now owned, and none of them were ever actually ownerless - they were missing from the sources. Finance and HR needed the partner organisations added. Marketing, wholesale and Shopify revenue needed the AC Brands landing hub, which defines eleven functions with an explicit lead per function and had three reading "Owned by TBD": Marketing, Finance, and the wholesale half of Sales &amp; Commerce. Resolving those took three decisions rather than three hires. Soraya is accountable for Marketing. Nicole is accountable for all channels - DTC, Amazon and wholesale together, which is broader than the hub had it. Danielle is accountable for web with Nicole as the systems and tech owner. That is 99 activities across eleven functions with an owner on every row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="23" t="inlineStr">
-        <is>
-          <t>Five functions run entirely outside the company</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr"/>
-    </row>
-    <row r="69" ht="91" customHeight="1">
-      <c r="A69" s="17" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+    </row>
+    <row r="70" ht="117" customHeight="1">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>The first pass reported three unowned functions. All three are now owned, and none of them were ever actually ownerless - they were missing from the sources. Finance and HR needed the partner organisations added. Marketing, wholesale and Shopify revenue needed the AC Brands landing hub, which defines eleven functions with an explicit lead per function and had three reading "Owned by TBD": Marketing, Finance, and the wholesale half of Sales &amp; Commerce. Resolving those took three decisions rather than three hires. Soraya is accountable for Marketing. Nicole is accountable for all channels - DTC, Amazon and wholesale together, which is broader than the hub had it. Danielle is accountable for web with Nicole as the systems and tech owner. That is 102 activities across eleven functions with an owner on every row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="23" t="inlineStr">
+        <is>
+          <t>Six functions run entirely outside the company</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+    </row>
+    <row r="74" ht="91" customHeight="1">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>Regulatory goes through Pedrero, Finance through Ironclad (Dan Bender), HR through Calm HR as PEO and co-employer, digital marketing and email through WITHIN, web development through Teknologics. Add the three contractors on packaging, creative and formulation and that is eight external parties holding the execution of eight functions. For a team of nine it is a reasonable shape - it is how this surface gets covered at all. What it means is that continuity rests on eight engagements rather than on employment, and each is a renewal decision rather than a retention one. Engagement terms are recorded for Pedrero only.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="23" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="23" t="inlineStr">
         <is>
           <t>Regulatory is the odd one, and it cuts both ways</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr"/>
-    </row>
-    <row r="73" ht="78" customHeight="1">
-      <c r="A73" s="17" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+    </row>
+    <row r="78" ht="78" customHeight="1">
+      <c r="A78" s="17" t="inlineStr">
         <is>
           <t>Pedrero is consulted on 11 rows and responsible for none. That is not an undervaluation - our own procedures make them consult-only with no Asana access and no internal authority, and Amy Pedrero holds the binding regulatory calls. The consequence is a split bottleneck: Pedrero forms every regulatory opinion, and Alvin performs every regulatory action, because the Operator and Reg Lead gates are both his and Pedrero cannot act inside our systems. Either the Reg Lead gate gets an alternate or Pedrero's remit widens; the current shape means regulatory work stops if either side is unavailable.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="23" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="23" t="inlineStr">
         <is>
           <t>One row is still unowned</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr"/>
-    </row>
-    <row r="77" ht="52" customHeight="1">
-      <c r="A77" s="17" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+    </row>
+    <row r="82" ht="52" customHeight="1">
+      <c r="A82" s="17" t="inlineStr">
         <is>
           <t>Shopify revenue and channel position. It is registered as the revenue connection and named as the primary direct-to-consumer revenue track, but no process assigns ownership or an approval step, so it shows Alvin by inference rather than by source. The function closest to the top line is the least specified.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr"/>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="23" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="23" t="inlineStr">
         <is>
           <t>Single points of failure that remain after both hires</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr"/>
-    </row>
-    <row r="81" ht="91" customHeight="1">
-      <c r="A81" s="17" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+    </row>
+    <row r="86" ht="91" customHeight="1">
+      <c r="A86" s="17" t="inlineStr">
         <is>
           <t>Perrine is an external contractor holding A on 8 rows with no internal counterpart, and one of those - compatibility and stability and RIPT and PET - has her as both A and R. Nobody inside AC Brands can check that work or continue it. Alvin is the other: the Operator gate has no alternate anywhere in the suite, and all 23 scheduled Routines stop at a human approval only he can clear. Succession is documented exactly once in the entire system, for competitive intelligence. Nothing comparable exists for the quality gate, the technical advisor, or the framework owner. That gap costs hours to close, not headcount, and it is the one I would fix first.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr"/>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8729,17 +9156,17 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Five whole functions run through external partner organisations: Regulatory (Pedrero), Finance (Ironclad), HR (Calm HR), digital marketing (WITHIN), web development (Teknologics). Plus three contractors on packaging, creative and formulation.</t>
+          <t>Six whole functions run through external partner organisations: Regulatory (Pedrero), Finance (Ironclad), HR (Calm HR), digital marketing (WITHIN), web development (Teknologics), managed IT (Coastal Interactive). Plus three contractors on packaging, creative and formulation.</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Eight external parties hold the execution of Regulatory, Finance, HR, digital marketing, web development, packaging, creative and formulation. Not a fault - it is how a team of nine covers this surface - but continuity rests on eight engagements rather than on employment, and each one is a renewal decision. Engagement terms are recorded for Pedrero only.</t>
+          <t>Nine external parties hold the execution of Regulatory, Finance, HR, digital marketing, web development, managed IT, packaging, creative and formulation. Not a fault - it is how a team of nine covers this surface - but continuity rests on nine engagements rather than on employment, and each one is a renewal decision. Engagement terms are recorded for Pedrero only.</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Record engagement terms and renewal dates for all eight</t>
+          <t>Record engagement terms and renewal dates for all nine</t>
         </is>
       </c>
       <c r="F9" s="7" t="n">

--- a/deliverables/AC-Brands-RACI.xlsx
+++ b/deliverables/AC-Brands-RACI.xlsx
@@ -2665,7 +2665,7 @@
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>The strictest gate in the suite: explicit approval at every step, §4.A through §4.F each a separate gate. Operator decides severity, team and whether external reporting is needed. A and R both AB. Stays with Alvin as Reg Lead — legal and agency exposure. Nicole consults. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
+          <t>The strictest gate in the suite: explicit approval at every step, §4.A through §4.F each a separate gate. Operator decides severity, team and whether external reporting is needed. A and R both AB. Stays with Alvin as Reg Lead, given the legal and agency exposure. Nicole consults. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>AC — Owner / Founder (Ayesha Curry)</t>
+          <t>AC: Owner / Founder (Ayesha Curry)</t>
         </is>
       </c>
       <c r="B6" s="15">
@@ -7956,7 +7956,7 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>DI — President (Danielle Iturbe)</t>
+          <t>DI: President (Danielle Iturbe)</t>
         </is>
       </c>
       <c r="B7" s="15">
@@ -7989,7 +7989,7 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>AB — VP of Operations (Alvin Belt)</t>
+          <t>AB: VP of Operations (Alvin Belt)</t>
         </is>
       </c>
       <c r="B8" s="15">
@@ -8022,7 +8022,7 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>NI — Sr. Director, Consumer Strategy &amp; Operations (Nicole Iturbe)</t>
+          <t>NI: Sr. Director, Consumer Strategy &amp; Operations (Nicole Iturbe)</t>
         </is>
       </c>
       <c r="B9" s="15">
@@ -8055,7 +8055,7 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>OPS — Operations Specialist (Open seat)</t>
+          <t>OPS: Operations Specialist (Open seat)</t>
         </is>
       </c>
       <c r="B10" s="15">
@@ -8088,7 +8088,7 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>PDS — Product Development Specialist (Open seat)</t>
+          <t>PDS: Product Development Specialist (Open seat)</t>
         </is>
       </c>
       <c r="B11" s="15">
@@ -8121,7 +8121,7 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>SS — Marketing Manager (Soraya Salgadoe)</t>
+          <t>SS: Marketing Manager (Soraya Salgadoe)</t>
         </is>
       </c>
       <c r="B12" s="15">
@@ -8154,7 +8154,7 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>KL — Social Media Coordinator (Kate Le)</t>
+          <t>KL: Social Media Coordinator (Kate Le)</t>
         </is>
       </c>
       <c r="B13" s="15">
@@ -8187,7 +8187,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>EH — Creative Director (Erin Hover)</t>
+          <t>EH: Creative Director (Erin Hover)</t>
         </is>
       </c>
       <c r="B14" s="15">
@@ -8220,7 +8220,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>IT — Creative / Design Coordinator (Ivy Tan)</t>
+          <t>IT: Creative / Design Coordinator (Ivy Tan)</t>
         </is>
       </c>
       <c r="B15" s="15">
@@ -8253,7 +8253,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>JH — Packaging Engineer (Jan Haeck)</t>
+          <t>JH: Packaging Engineer (Jan Haeck)</t>
         </is>
       </c>
       <c r="B16" s="15">
@@ -8286,7 +8286,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>PC — PD / R&amp;D contractor, Milinyc (Perrine Calvet)</t>
+          <t>PC: PD / R&amp;D contractor, Milinyc (Perrine Calvet)</t>
         </is>
       </c>
       <c r="B17" s="15">
@@ -8319,7 +8319,7 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PR — External regulatory partner (Pedrero Regulatory)</t>
+          <t>PR: External regulatory partner (Pedrero Regulatory)</t>
         </is>
       </c>
       <c r="B18" s="15">
@@ -8352,7 +8352,7 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>IF — Outsourced finance (Dan Bender) (Ironclad Finance)</t>
+          <t>IF: Outsourced finance (Dan Bender) (Ironclad Finance)</t>
         </is>
       </c>
       <c r="B19" s="15">
@@ -8385,7 +8385,7 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>CH — PEO and co-employer (Calm HR)</t>
+          <t>CH: PEO and co-employer (Calm HR)</t>
         </is>
       </c>
       <c r="B20" s="15">
@@ -8418,7 +8418,7 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>WI — Digital marketing agency (WITHIN)</t>
+          <t>WI: Digital marketing agency (WITHIN)</t>
         </is>
       </c>
       <c r="B21" s="15">
@@ -8451,7 +8451,7 @@
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>TK — Web development (Teknologics)</t>
+          <t>TK: Web development (Teknologics)</t>
         </is>
       </c>
       <c r="B22" s="15">
@@ -8484,7 +8484,7 @@
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>CI — Managed IT service provider (Coastal Interactive)</t>
+          <t>CI: Managed IT service provider (Coastal Interactive)</t>
         </is>
       </c>
       <c r="B23" s="15">

--- a/deliverables/AC-Brands-RACI.xlsx
+++ b/deliverables/AC-Brands-RACI.xlsx
@@ -7060,7 +7060,7 @@
       <c r="A107" s="11" t="n"/>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>A = answers for the outcome (exactly one per row)</t>
+          <t>A = answers for the outcome (at least one per row, and it can be shared)</t>
         </is>
       </c>
     </row>

--- a/deliverables/AC-Brands-RACI.xlsx
+++ b/deliverables/AC-Brands-RACI.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Gaps" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$W$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RACI'!$A$2:$W$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gaps'!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -561,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W135"/>
+  <dimension ref="A1:W127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -814,7 +814,11 @@
           <t>Formula stage-gate progression through the PD Formula Tracker</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
           <t>I</t>
@@ -830,7 +834,11 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr"/>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -863,7 +871,7 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/asana-pd-manager/SKILL.md:60; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/asana-pd-manager/SKILL.md:60; Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W3" s="6" t="inlineStr">
@@ -883,8 +891,16 @@
           <t>Compatibility, stability, RIPT and PET decisions (pre-launch)</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr"/>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -892,11 +908,19 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr"/>
-      <c r="H4" s="7" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
           <t>I</t>
@@ -906,9 +930,9 @@
       <c r="K4" s="7" t="inlineStr"/>
       <c r="L4" s="7" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="O4" s="7" t="inlineStr"/>
@@ -920,12 +944,12 @@
       <c r="U4" s="6" t="inlineStr"/>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>PD Lead owns the technical call outright. A and R the same person, and PC is an external contractor. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
+          <t>Perrine runs the testing and makes the technical call. Danielle answers for the outcome, which keeps a launch-gating test result in front of the President rather than inside the contractor relationship. Alvin and Nicole consulted. Worth a second look: the technical call and the accountability now sit with different people, and Perrine is external.</t>
         </is>
       </c>
     </row>
@@ -940,43 +964,51 @@
           <t>Packaging development with fillers and component vendors</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr"/>
+      <c r="M5" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
@@ -990,15 +1022,19 @@
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="7" t="inlineStr"/>
       <c r="T5" s="7" t="inlineStr"/>
-      <c r="U5" s="6" t="inlineStr"/>
+      <c r="U5" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:16,23; Alvin, 2026-07-31 (role correction); Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:16,23; Alvin, 2026-07-31 (role correction); Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
-          <t>PD Lead owns packaging dev calls; Jan executes packaging and artwork under Erin. Both are contractors. Erin is the lead technical authority on packaging and artwork and answers for the outcome; Jan executes under her. Perrine consults where formula contact or compatibility is in play. Both Erin and Jan are contractors. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
+          <t>Alvin runs packaging development with the fillers and component vendors. Ayesha answers for it as the founder whose name is on the pack. Perrine consulted where formula contact or compatibility is in play, Danielle and Nicole on the commercial and documentation side. Transitions to the PD Specialist on hire. Worth a second look: Erin and Jan are the two people who actually execute packaging and artwork, and both are now informed rather than accountable.</t>
         </is>
       </c>
     </row>
@@ -1083,14 +1119,14 @@
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>R</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1123,12 +1159,12 @@
       <c r="U7" s="6" t="inlineStr"/>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:19; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:19; Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W7" s="6" t="inlineStr">
         <is>
-          <t>Founder gate. Ayesha receives weekly PD signal through the Friday briefing. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
+          <t>Founder gate. Danielle carries the ask to Ayesha and answers for getting it there; Ayesha holds the decision. Perrine and Soraya stay informed, as on every product decision.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1195,11 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -1192,7 +1232,7 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/fireflies-asana-bridge/SKILL.md:287; .claude/skills/outlook-plm-bridge/SKILL.md:191; .claude/skills/sjs-status-reporter/SKILL.md:331,385; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+          <t>.claude/skills/fireflies-asana-bridge/SKILL.md:287; .claude/skills/outlook-plm-bridge/SKILL.md:191; .claude/skills/sjs-status-reporter/SKILL.md:331,385; Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W8" s="6" t="inlineStr">
@@ -1212,10 +1252,14 @@
           <t>Reformulation triggered by a Quality or Regulatory reverse-handoff</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -1229,7 +1273,11 @@
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
           <t>I</t>
@@ -1239,9 +1287,9 @@
       <c r="K9" s="7" t="inlineStr"/>
       <c r="L9" s="7" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="O9" s="7" t="inlineStr"/>
@@ -1253,12 +1301,12 @@
       <c r="U9" s="6" t="inlineStr"/>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/capa-coordinator/SKILL.md:85; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:16; .claude/skills/capa-coordinator/SKILL.md:85; Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
-          <t>PD Lead is cross-flagged for any PD-side reformulation. Reformulation handoff rides the root-cause approval - no separate gate. Perrine and Soraya are never blank on a PD row - PD technical guidance and the marketing read both need visibility on every product decision.</t>
+          <t>Alvin drives the reformulation once Quality or Regulatory hands it back. Danielle answers for it, since a reformulation moves cost, timeline and claims at once. Perrine and Nicole consulted on the technical root cause. The handoff rides the root-cause approval, so there is no separate gate.</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1322,11 @@
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr"/>
-      <c r="D10" s="7" t="inlineStr"/>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -1326,7 +1378,7 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>SharePoint: Sweet July Skin - Product Development Specialist - Job Description.docx; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+          <t>SharePoint: Sweet July Skin - Product Development Specialist - Job Description.docx; Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W10" s="6" t="inlineStr">
@@ -1346,8 +1398,16 @@
           <t>Vendor master data, onboarding (NDA + W9 gate), sourcing and performance scorecards</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr"/>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
@@ -1391,7 +1451,7 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:42,46,75,154,158</t>
+          <t>.claude/skills/purchasing-manager/SKILL.md:42,46,75,154,158; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W11" s="6" t="inlineStr">
@@ -1418,21 +1478,33 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr"/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J12" s="7" t="inlineStr"/>
       <c r="K12" s="7" t="inlineStr"/>
       <c r="L12" s="7" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="O12" s="7" t="inlineStr"/>
@@ -1448,7 +1520,7 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:108,116,140,248</t>
+          <t>.claude/skills/purchasing-manager/SKILL.md:108,116,140,248; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W12" s="6" t="inlineStr">
@@ -1480,9 +1552,21 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J13" s="7" t="inlineStr"/>
       <c r="K13" s="7" t="inlineStr"/>
       <c r="L13" s="7" t="inlineStr"/>
@@ -1498,10 +1582,14 @@
       <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="7" t="inlineStr"/>
       <c r="T13" s="7" t="inlineStr"/>
-      <c r="U13" s="6" t="inlineStr"/>
+      <c r="U13" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:130</t>
+          <t>.claude/skills/purchasing-manager/SKILL.md:130; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W13" s="6" t="inlineStr">
@@ -1599,7 +1687,11 @@
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -1627,7 +1719,7 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:234,235,238; Alvin, 2026-07-31 (external partners)</t>
+          <t>.claude/skills/purchasing-manager/SKILL.md:234,235,238; Alvin, 2026-07-31 (external partners); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W15" s="6" t="inlineStr">
@@ -1656,7 +1748,7 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
@@ -1664,7 +1756,11 @@
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I16" s="7" t="inlineStr"/>
       <c r="J16" s="7" t="inlineStr"/>
       <c r="K16" s="7" t="inlineStr"/>
@@ -1688,7 +1784,7 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/inventory-manager/SKILL.md:18,52,60</t>
+          <t>.claude/skills/inventory-manager/SKILL.md:18,52,60; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W16" s="6" t="inlineStr">
@@ -1715,7 +1811,11 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -1745,7 +1845,7 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/inventory-manager/SKILL.md:94</t>
+          <t>.claude/skills/inventory-manager/SKILL.md:94; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W17" s="6" t="inlineStr">
@@ -1786,7 +1886,11 @@
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="I18" s="7" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr"/>
       <c r="K18" s="7" t="inlineStr"/>
@@ -1806,7 +1910,7 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/supply-demand-planner/SKILL.md:30-52; .claude/skills/supply-demand-planner/references/plm-schema-additions.md:139</t>
+          <t>.claude/skills/supply-demand-planner/SKILL.md:30-52; .claude/skills/supply-demand-planner/references/plm-schema-additions.md:139; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W18" s="6" t="inlineStr">
@@ -1833,7 +1937,11 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -1863,7 +1971,7 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/logistics-manager/SKILL.md:59,186; .claude/skills/logistics-manager/forms/international-dtc-shipment.md:11</t>
+          <t>.claude/skills/logistics-manager/SKILL.md:59,186; .claude/skills/logistics-manager/forms/international-dtc-shipment.md:11; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W19" s="6" t="inlineStr">
@@ -1940,8 +2048,16 @@
           <t>Pre-ship out-of-stock holds from the shortage sheet</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr"/>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -1958,7 +2074,11 @@
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J21" s="7" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr"/>
       <c r="L21" s="7" t="inlineStr"/>
@@ -1977,7 +2097,7 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/oc3pl-order-manager/SKILL.md:201; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
+          <t>.claude/skills/oc3pl-order-manager/SKILL.md:201; .claude/skills/ayesha-weekly-briefing/SKILL.md:123; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W21" s="6" t="inlineStr">
@@ -2059,7 +2179,11 @@
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
@@ -2076,7 +2200,11 @@
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J23" s="7" t="inlineStr"/>
       <c r="K23" s="7" t="inlineStr"/>
       <c r="L23" s="7" t="inlineStr"/>
@@ -2099,7 +2227,7 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Leadership Business Review 2026-07-30 35:18</t>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Leadership Business Review 2026-07-30 35:18; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W23" s="6" t="inlineStr">
@@ -2119,8 +2247,16 @@
           <t>Customer complaint intake, classification and first response</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr"/>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -2131,13 +2267,21 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I24" s="7" t="inlineStr"/>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J24" s="7" t="inlineStr"/>
       <c r="K24" s="7" t="inlineStr"/>
       <c r="L24" s="7" t="inlineStr"/>
@@ -2160,12 +2304,12 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/complaint-and-event-handler/SKILL.md:20,53</t>
+          <t>.claude/skills/complaint-and-event-handler/SKILL.md:20,53; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W24" s="6" t="inlineStr">
         <is>
-          <t>HITL on every write. Operator approves classification plus first response. A and R both AB. Gate moved to Nicole as the final quality check per Leadership Business Review 2026-07-30 25:18-26:01.</t>
+          <t>HITL on every write. Operator approves classification plus first response. Gate moved to Nicole as the final quality check per Leadership Business Review 2026-07-30 25:18-26:01.</t>
         </is>
       </c>
     </row>
@@ -2180,25 +2324,41 @@
           <t>Complaint trend analysis by SKU and batch</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr"/>
-      <c r="D25" s="7" t="inlineStr"/>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr"/>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J25" s="7" t="inlineStr"/>
       <c r="K25" s="7" t="inlineStr"/>
       <c r="L25" s="7" t="inlineStr"/>
@@ -2221,12 +2381,12 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/quality-manager/references/role-map.md:15</t>
+          <t>.claude/skills/quality-manager/references/role-map.md:15; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
-          <t>Voice of Customer holds gates on complaint classification and complaint-driven escalations. Nicole already held this gate; monthly trend review formalizes it per Leadership Business Review 2026-07-30 26:02-26:17.</t>
+          <t>Alvin answers for the trend read and runs it. Perrine and Nicole consulted on the technical pattern. Monthly trend review per the 30 July leadership review. Transitions to the PD Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -2247,17 +2407,21 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -2286,12 +2450,12 @@
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/capa-coordinator/SKILL.md:54,136; .claude/skills/capa-coordinator/references/ncr-procedure.md:135; .claude/skills/capa-coordinator/references/skn-ops-001.md:64,102</t>
+          <t>.claude/skills/capa-coordinator/SKILL.md:54,136; .claude/skills/capa-coordinator/references/ncr-procedure.md:135; .claude/skills/capa-coordinator/references/skn-ops-001.md:64,102; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>Operator approves intake and both action plans; QA Lead approves conversion, root cause, verification, effectiveness and close. Six SOP phases, one external contractor on every technical gate. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults on technical root cause.</t>
+          <t>Alvin approves intake, both action plans, conversion, root cause, verification, effectiveness and close. Six SOP phases on one seat. Perrine consulted on technical root cause, Nicole on documentation quality. Transitions to the PD Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2471,11 @@
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr"/>
-      <c r="D27" s="7" t="inlineStr"/>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -2318,13 +2486,21 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J27" s="7" t="inlineStr"/>
       <c r="K27" s="7" t="inlineStr"/>
       <c r="L27" s="7" t="inlineStr"/>
@@ -2347,12 +2523,12 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/quality-lab-coordinator/SKILL.md:48,56</t>
+          <t>.claude/skills/quality-lab-coordinator/SKILL.md:48,56; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
-          <t>Operator approves intake and the single-versus-systemic classification. A and R both AB. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:35-25:50. Perrine consults on the technical call.</t>
+          <t>Operator approves intake and the single-versus-systemic classification. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:35-25:50. Perrine consults on the technical call.</t>
         </is>
       </c>
     </row>
@@ -2368,18 +2544,26 @@
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr"/>
-      <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr"/>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -2408,12 +2592,12 @@
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/quality-lab-coordinator/SKILL.md:76; .claude/skills/quality-lab-coordinator/references/vendor-scorecard-signal.md:103</t>
+          <t>.claude/skills/quality-lab-coordinator/SKILL.md:76; .claude/skills/quality-lab-coordinator/references/vendor-scorecard-signal.md:103; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
-          <t>QA Lead approves any vendor flag and the scorecard band. Operator can stage but not commit. A moved from Perrine to Nicole per Leadership Business Review 2026-07-30 25:18-25:50. Perrine consults.</t>
+          <t>Alvin approves any vendor flag and the scorecard band. Perrine and Nicole consulted, and the incoming Operations Specialist can stage a flag but not commit it. Transitions to the PD Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2628,11 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -2473,7 +2661,7 @@
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/batch-lifecycle-tracker/references/batch-lifecycle-procedure.md:208; .claude/skills/batch-lifecycle-tracker/SKILL.md:86</t>
+          <t>.claude/skills/batch-lifecycle-tracker/references/batch-lifecycle-procedure.md:208; .claude/skills/batch-lifecycle-tracker/SKILL.md:86; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W29" s="6" t="inlineStr">
@@ -2494,7 +2682,11 @@
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr"/>
-      <c r="D30" s="7" t="inlineStr"/>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -2505,13 +2697,21 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr"/>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J30" s="7" t="inlineStr"/>
       <c r="K30" s="7" t="inlineStr"/>
       <c r="L30" s="7" t="inlineStr"/>
@@ -2534,7 +2734,7 @@
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
+          <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr">
@@ -2555,7 +2755,11 @@
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr"/>
-      <c r="D31" s="7" t="inlineStr"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
           <t>R</t>
@@ -2566,13 +2770,21 @@
           <t>A</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J31" s="7" t="inlineStr"/>
       <c r="K31" s="7" t="inlineStr"/>
       <c r="L31" s="7" t="inlineStr"/>
@@ -2595,7 +2807,7 @@
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94</t>
+          <t>.claude/skills/batch-lifecycle-tracker/SKILL.md:71,94; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W31" s="6" t="inlineStr">
@@ -2635,9 +2847,21 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr"/>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J32" s="7" t="inlineStr"/>
       <c r="K32" s="7" t="inlineStr"/>
       <c r="L32" s="7" t="inlineStr"/>
@@ -2660,7 +2884,7 @@
       <c r="U32" s="6" t="inlineStr"/>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/complaint-and-event-handler/SKILL.md:85,89,95; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/complaint-and-event-handler/SKILL.md:85,89,95; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W32" s="6" t="inlineStr">
@@ -2681,20 +2905,28 @@
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
       <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J33" s="7" t="inlineStr"/>
       <c r="K33" s="7" t="inlineStr"/>
       <c r="L33" s="7" t="inlineStr"/>
@@ -2713,12 +2945,12 @@
       <c r="U33" s="6" t="inlineStr"/>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/quality-manager/SKILL.md:66,135; .claude/skills/quality-manager/references/sop-catalog.md:120; .claude/skills/quality-manager/references/qos-thresholds.md:52</t>
+          <t>.claude/skills/quality-manager/SKILL.md:66,135; .claude/skills/quality-manager/references/sop-catalog.md:120; .claude/skills/quality-manager/references/qos-thresholds.md:52; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>QA Lead approves every ratification, review outcome, cross-cutting task and QoS threshold task. SOP §7 names a QA Manager for this; that seat is vacant and Perrine is filling it. Gate moved to Nicole per Leadership Business Review 2026-07-30 25:18-25:50.</t>
+          <t>Alvin approves every ratification, review outcome, cross-cutting task and quality-of-service threshold. SOP section 7 names a QA Manager for this and that seat does not exist, so the framework owner holds it. Perrine, Nicole, Danielle and Soraya consulted.</t>
         </is>
       </c>
     </row>
@@ -2734,24 +2966,36 @@
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr"/>
-      <c r="D34" s="7" t="inlineStr"/>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr"/>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J34" s="7" t="inlineStr"/>
       <c r="K34" s="7" t="inlineStr"/>
       <c r="L34" s="7" t="inlineStr"/>
@@ -2774,12 +3018,12 @@
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/quality-status-reporter/SKILL.md:78</t>
+          <t>.claude/skills/quality-status-reporter/SKILL.md:78; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>Operator approves the commit before push. Never commit without confirmation. A and R both AB. Nicole gates the content; Alvin retains the publish mechanics. Per Leadership Business Review 2026-07-30 26:02-26:17.</t>
+          <t>Alvin approves the commit before push and answers for what the dashboard says. Nicole and Perrine consulted on the content. Never commit without confirmation. Transitions to the PD Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -2804,29 +3048,33 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="F35" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr"/>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K35" s="7" t="inlineStr"/>
       <c r="L35" s="7" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
       <c r="N35" s="7" t="inlineStr">
@@ -2840,15 +3088,19 @@
       <c r="R35" s="7" t="inlineStr"/>
       <c r="S35" s="7" t="inlineStr"/>
       <c r="T35" s="7" t="inlineStr"/>
-      <c r="U35" s="6" t="inlineStr"/>
+      <c r="U35" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 25:35-26:01</t>
+          <t>Leadership Business Review 2026-07-30 25:35-26:01; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>The new cross-function gate. Verbatim: "anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check... Even with each function having or being the primary owner, we'll still have that quality gate." A and R both NI.</t>
+          <t>The cross-function gate. Nicole holds it, verbatim from the 30 July review: "anything related to quality of service or quality of product will go through Nicole's eyes as sort of that final quality check." Alvin runs the checks into that gate until the PD Specialist absorbs the work.</t>
         </is>
       </c>
     </row>
@@ -2871,17 +3123,29 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr"/>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J36" s="7" t="inlineStr"/>
       <c r="K36" s="7" t="inlineStr"/>
       <c r="L36" s="7" t="inlineStr"/>
@@ -2900,12 +3164,12 @@
       <c r="U36" s="6" t="inlineStr"/>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 25:18-26:17</t>
+          <t>Leadership Business Review 2026-07-30 25:18-26:17; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W36" s="6" t="inlineStr">
         <is>
-          <t>Alvin owns the overall framework; Nicole runs it. Monthly trend review so recurring issues (the pump issue was the worked example) can drive packaging or formula decisions. Target: implemented by end of Q3.</t>
+          <t>Alvin owns the framework and runs it. Nicole and Perrine consulted. Monthly trend review so recurring issues, the pump issue being the worked example, can drive packaging or formula decisions. Target: implemented by end of Q3.</t>
         </is>
       </c>
     </row>
@@ -2921,18 +3185,26 @@
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr"/>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr"/>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
@@ -2965,12 +3237,12 @@
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:50; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:62; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:50; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:62; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>Operator approves intake. Reg Lead is the same person at v6.6, so the gate fires twice against one person. Pedrero holds the binding external call. A and R both AB. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
+          <t>Alvin runs the review and approves intake; Nicole holds the gate as the final quality and documentation check, so the review and the approval are separate people for the first time. Pedrero holds the binding external call, consult-only internally with no Asana access. Transitions to the PD Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -2986,15 +3258,31 @@
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr"/>
-      <c r="D38" s="7" t="inlineStr"/>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr"/>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="7" t="inlineStr"/>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I38" s="7" t="inlineStr"/>
       <c r="J38" s="7" t="inlineStr"/>
       <c r="K38" s="7" t="inlineStr"/>
@@ -3018,7 +3306,7 @@
       <c r="U38" s="6" t="inlineStr"/>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:60; .claude/skills/regulatory-manager/SKILL.md:140; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:60; .claude/skills/regulatory-manager/SKILL.md:140; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W38" s="6" t="inlineStr">
@@ -3043,17 +3331,21 @@
           <t>C</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E39" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G39" s="7" t="inlineStr"/>
       <c r="H39" s="7" t="inlineStr">
         <is>
@@ -3095,12 +3387,12 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:97; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:29; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:97; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:29; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>Operator approves the path; Reg Lead approves the Pedrero stage. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off. A and R both AB. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off, so both are consulted rather than bypassed. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
+          <t>Alvin runs the substantiation path and the Pedrero stage. Danielle answers for the claim, which is the right level given a claim is a commercial and legal commitment. The procedure exists because new claims from marketing or the founder used to skip Pedrero sign-off, so Soraya, Ayesha, Erin, Perrine and Nicole are consulted rather than bypassed. Transitions to the PD Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -3130,18 +3422,30 @@
           <t>R</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr"/>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr"/>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr"/>
@@ -3165,15 +3469,19 @@
       <c r="R40" s="7" t="inlineStr"/>
       <c r="S40" s="7" t="inlineStr"/>
       <c r="T40" s="7" t="inlineStr"/>
-      <c r="U40" s="6" t="inlineStr"/>
+      <c r="U40" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:85; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:93; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:85; .claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:93; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W40" s="6" t="inlineStr">
         <is>
-          <t>Operator approves each pass outcome; Reg Lead approves any archive entry. Creative produces the artwork under review. Erin answers for the artwork being right as lead technical authority. Alvin runs the IL cross-check and the label-law passes and holds the Reg Lead gate on archive entries, so the regulatory approval and the artwork authority are separate people. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
+          <t>Alvin runs the IL cross-check and the label-law passes. Nicole approves the archive entry, so the documentation gate and the work are separate people. Erin and Jan consulted as the people producing the artwork under review, Pedrero on the external read. Transitions to the PD Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -3188,28 +3496,48 @@
           <t>Reformulation claim bridge when a SKU reformulates without QIL parity</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr"/>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="9" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J41" s="7" t="inlineStr"/>
       <c r="K41" s="7" t="inlineStr"/>
       <c r="L41" s="7" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="O41" s="7" t="inlineStr">
@@ -3222,15 +3550,19 @@
       <c r="R41" s="7" t="inlineStr"/>
       <c r="S41" s="7" t="inlineStr"/>
       <c r="T41" s="7" t="inlineStr"/>
-      <c r="U41" s="6" t="inlineStr"/>
+      <c r="U41" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:281; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/claims-il-and-label-keeper/references/il-claims-label-procedure.md:281; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W41" s="6" t="inlineStr">
         <is>
-          <t>Reg Lead approves the QIL recovery ask to the prior manufacturer; PD Lead does the formulation work. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
+          <t>Alvin makes the QIL recovery ask to the prior manufacturer and rebuilds the claim set. Danielle answers for what is claimed on the reformulated SKU. Perrine and Soraya consulted on the formulation and the marketing read, Pedrero and Nicole on the review. Transitions to the PD Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -3255,23 +3587,31 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E42" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr"/>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="I42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J42" s="7" t="inlineStr"/>
       <c r="K42" s="7" t="inlineStr"/>
       <c r="L42" s="7" t="inlineStr"/>
@@ -3298,12 +3638,12 @@
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:105; .claude/skills/regulatory-manager/SKILL.md:122; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/claims-il-and-label-keeper/SKILL.md:105; .claude/skills/regulatory-manager/SKILL.md:122; Alvin, 2026-07-31 (role correction); .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W42" s="6" t="inlineStr">
         <is>
-          <t>Reg Lead approves the retailer submission after Pedrero approval. Voice of Customer consults where customer-perceived attributes matter. A and R both AB. Ayesha consulted - retailer clean-standard positioning is a brand claim. Pedrero Regulatory holds the binding external review; consult-only internally, with no Asana access and no internal authority, so the Reg Lead gate stays in-house.</t>
+          <t>Alvin prepares and sends the retailer submission after Pedrero approval. Nicole approves it as the documentation gate. Ayesha consulted, since retailer clean-standard positioning is a brand claim. Transitions to the PD Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -3319,13 +3659,21 @@
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr"/>
-      <c r="D43" s="7" t="inlineStr"/>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E43" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr"/>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G43" s="7" t="inlineStr"/>
       <c r="H43" s="7" t="inlineStr">
         <is>
@@ -3343,7 +3691,7 @@
       <c r="M43" s="7" t="inlineStr"/>
       <c r="N43" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="O43" s="7" t="inlineStr">
@@ -3363,7 +3711,7 @@
       </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/regulatory-manager/SKILL.md:114,367; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/regulatory-manager/SKILL.md:114,367; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W43" s="6" t="inlineStr">
@@ -3403,9 +3751,21 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr"/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J44" s="7" t="inlineStr"/>
       <c r="K44" s="7" t="inlineStr"/>
       <c r="L44" s="7" t="inlineStr"/>
@@ -3425,10 +3785,14 @@
       <c r="R44" s="7" t="inlineStr"/>
       <c r="S44" s="7" t="inlineStr"/>
       <c r="T44" s="7" t="inlineStr"/>
-      <c r="U44" s="6" t="inlineStr"/>
+      <c r="U44" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/adverse-event-and-recall-reporter/SKILL.md:65,108; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/adverse-event-and-recall-reporter/SKILL.md:65,108; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W44" s="6" t="inlineStr">
@@ -3449,7 +3813,11 @@
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr"/>
-      <c r="D45" s="7" t="inlineStr"/>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
@@ -3457,12 +3825,24 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J45" s="7" t="inlineStr"/>
       <c r="K45" s="7" t="inlineStr"/>
       <c r="L45" s="7" t="inlineStr"/>
@@ -3482,10 +3862,14 @@
       <c r="R45" s="7" t="inlineStr"/>
       <c r="S45" s="7" t="inlineStr"/>
       <c r="T45" s="7" t="inlineStr"/>
-      <c r="U45" s="6" t="inlineStr"/>
+      <c r="U45" s="6" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/regulatory-manager/SKILL.md:60; .claude/skills/regulatory-status-reporter/SKILL.md:90; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21</t>
+          <t>.claude/skills/regulatory-manager/SKILL.md:60; .claude/skills/regulatory-status-reporter/SKILL.md:90; .claude/skills/regulatory-manager/references/pedrero-contacts.md:9,13,21; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W45" s="6" t="inlineStr">
@@ -3518,11 +3902,15 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
-      <c r="H46" s="7" t="inlineStr"/>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I46" s="7" t="inlineStr"/>
       <c r="J46" s="7" t="inlineStr"/>
       <c r="K46" s="7" t="inlineStr"/>
@@ -3542,7 +3930,7 @@
       <c r="U46" s="6" t="inlineStr"/>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/regulatory-manager/references/pedrero-contacts.md:50; Alvin, 2026-07-31 (external partners)</t>
+          <t>.claude/skills/regulatory-manager/references/pedrero-contacts.md:50; Alvin, 2026-07-31 (external partners); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W46" s="6" t="inlineStr">
@@ -3578,9 +3966,17 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J47" s="7" t="inlineStr"/>
       <c r="K47" s="7" t="inlineStr"/>
       <c r="L47" s="7" t="inlineStr"/>
@@ -3595,7 +3991,7 @@
       <c r="U47" s="6" t="inlineStr"/>
       <c r="V47" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:55; acb-thelanding: data/links.json</t>
+          <t>.claude/skills/purchasing-manager/SKILL.md:55; acb-thelanding: data/links.json; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W47" s="6" t="inlineStr">
@@ -3612,27 +4008,39 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>Retail channel launch programs: UBM cohort positioning, price ladder, Amazon Vendor</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr"/>
+          <t>Wholesale pipeline and new retail partner development</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="F48" s="9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="7" t="inlineStr"/>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -3652,12 +4060,12 @@
       <c r="U48" s="6" t="inlineStr"/>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/purchasing-manager/SKILL.md:55; .claude/skills/sjs-retail-intel/SKILL.md:52; .claude/skills/logistics-manager/SKILL.md:80; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>acb-thelanding: data/links.json (Sales &amp; Commerce lead: "TBD (wholesale)"); Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W48" s="6" t="inlineStr">
         <is>
-          <t>UBM launch June 2026. Nicole holds the channel relationship; Alvin runs the positioning and outbound work. Hub lists wholesale as "Owned by TBD" (links.json, Sales &amp; Commerce lead). Resolved to Nicole as part of all-channel accountability.</t>
+          <t>Hub left wholesale unowned. Resolved to Nicole with all-channel accountability. A and R both Nicole - no second pair of eyes on new-partner decisions.</t>
         </is>
       </c>
     </row>
@@ -3669,7 +4077,7 @@
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>Wholesale pipeline and new retail partner development</t>
+          <t>Retail price architecture and the pricing matrix</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
@@ -3679,7 +4087,7 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
@@ -3692,8 +4100,16 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -3703,7 +4119,11 @@
       <c r="K49" s="7" t="inlineStr"/>
       <c r="L49" s="7" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
-      <c r="N49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O49" s="7" t="inlineStr"/>
       <c r="P49" s="7" t="inlineStr"/>
       <c r="Q49" s="7" t="inlineStr"/>
@@ -3713,12 +4133,12 @@
       <c r="U49" s="6" t="inlineStr"/>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json (Sales &amp; Commerce lead: "TBD (wholesale)"); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>acb-thelanding: data/links.json (Sales &amp; Commerce / Retail Price Architecture, SJS Pricing Matrix); Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W49" s="6" t="inlineStr">
         <is>
-          <t>Hub left wholesale unowned. Resolved to Nicole with all-channel accountability. A and R both Nicole - no second pair of eyes on new-partner decisions.</t>
+          <t>Nicole owns the pricing matrix and does the work. Live on the hub with retail, wholesale and subscription prices and margin colouring. Alvin and Danielle consulted, since it ties to the margin framework and the walk-away call.</t>
         </is>
       </c>
     </row>
@@ -3730,7 +4150,7 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Retail price architecture and the pricing matrix</t>
+          <t>Retailer promo calendar (Sephora, Ulta) and promo planning</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
@@ -3743,32 +4163,40 @@
           <t>C</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="F50" s="9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="7" t="inlineStr"/>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J50" s="7" t="inlineStr"/>
+      <c r="J50" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="K50" s="7" t="inlineStr"/>
       <c r="L50" s="7" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
-      <c r="N50" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N50" s="7" t="inlineStr"/>
       <c r="O50" s="7" t="inlineStr"/>
       <c r="P50" s="7" t="inlineStr"/>
       <c r="Q50" s="7" t="inlineStr"/>
@@ -3778,24 +4206,24 @@
       <c r="U50" s="6" t="inlineStr"/>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json (Sales &amp; Commerce / Retail Price Architecture, SJS Pricing Matrix); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>acb-thelanding: data/links.json (Market Intelligence / Promo Landscape); Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W50" s="6" t="inlineStr">
         <is>
-          <t>Live pricing matrix on the hub carries retail, wholesale and subscription prices with margin colouring. Ties to the margin framework, so Danielle consulted as the walk-away approver.</t>
+          <t>Nicole runs promo planning and answers for the channel commitment. Promo Landscape tracks the Sephora and Ulta calendar. Soraya, Kate, Alvin and Danielle consulted.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Retail &amp; Wholesale</t>
+          <t>Marketing &amp; Brand</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>Retailer promo calendar (Sephora, Ulta) and promo planning</t>
+          <t>Social listening and comp brand monitoring (TikTok, IG, Pinterest, retailer new arrivals)</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -3805,29 +4233,29 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J51" s="8" t="inlineStr">
         <is>
           <t>R</t>
-        </is>
-      </c>
-      <c r="J51" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr"/>
@@ -3843,12 +4271,12 @@
       <c r="U51" s="6" t="inlineStr"/>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json (Market Intelligence / Promo Landscape); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:34,40-44; Alvin, 2026-07-31 (role correction); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W51" s="6" t="inlineStr">
         <is>
-          <t>Promo Landscape tracks the Sephora and Ulta promo calendar. Marketing runs the planning; Nicole answers for the channel commitment.</t>
+          <t>Kate owns social listening tool maintenance, query hygiene and the weekly retailer new-arrivals scan. Soraya answers for what the signal means for the brand. Danielle consulted.</t>
         </is>
       </c>
     </row>
@@ -3860,24 +4288,20 @@
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>Quarterly competitive teardowns across the five comp brands</t>
+          <t>Brand guideline custody (fonts, colors, logos, voice)</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr"/>
       <c r="F52" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -3885,18 +4309,26 @@
       </c>
       <c r="G52" s="7" t="inlineStr"/>
       <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="I52" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K52" s="7" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr"/>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M52" s="7" t="inlineStr"/>
       <c r="N52" s="7" t="inlineStr"/>
       <c r="O52" s="7" t="inlineStr"/>
@@ -3908,12 +4340,12 @@
       <c r="U52" s="6" t="inlineStr"/>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:19,23-30; Alvin, 2026-07-31 (role correction)</t>
+          <t>.claude/skills/sweet-july-skin-brand/SKILL.md:1; references/architecture/system_map.md:157; Alvin, 2026-07-31 (role correction); acb-thelanding: data/links.json; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W52" s="6" t="inlineStr">
         <is>
-          <t>Soraya owns teardown production and comp brand profile maintenance. A and R both SS. Danielle consulted rather than only receiving the finished teardown.</t>
+          <t>Every output-producing skill defers here for canonical brand spec; no skill carries its own copy. Danielle answers for the brand standard, Soraya maintains it as the function lead, Erin consulted as Creative Director. Ayesha consulted, the brand carries her name.</t>
         </is>
       </c>
     </row>
@@ -3925,35 +4357,55 @@
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>Quarterly teardown sign-off before circulation</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="inlineStr"/>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
+          <t>Annual team holiday communications (11 sends across 3 templates)</t>
+        </is>
+      </c>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="J53" s="7" t="inlineStr"/>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J53" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="K53" s="7" t="inlineStr"/>
-      <c r="L53" s="7" t="inlineStr"/>
+      <c r="L53" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="M53" s="7" t="inlineStr"/>
       <c r="N53" s="7" t="inlineStr"/>
       <c r="O53" s="7" t="inlineStr"/>
@@ -3965,12 +4417,12 @@
       <c r="U53" s="6" t="inlineStr"/>
       <c r="V53" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:65; .claude/skills/sjs-comp-intel/SKILL.md:50</t>
+          <t>.claude/skills/ac-brands-holiday-comms/SKILL.md:26,165; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W53" s="6" t="inlineStr">
         <is>
-          <t>Alvin signs off before it circulates to Danielle and the SJS brand team.</t>
+          <t>Sends from alvin@ac-brands.com with the team on BCC, including the Outlook calendar sync and the annual maintenance. Alvin runs it; Danielle answers for what goes out to the team.</t>
         </is>
       </c>
     </row>
@@ -3982,7 +4434,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>Monthly competitive trend digest and cross-stream signal routing</t>
+          <t>Operational special projects: labels, PR seeding, sampling</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
@@ -3997,7 +4449,7 @@
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F54" s="9" t="inlineStr">
@@ -4006,7 +4458,11 @@
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr"/>
-      <c r="H54" s="7" t="inlineStr"/>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -4017,7 +4473,11 @@
           <t>C</t>
         </is>
       </c>
-      <c r="K54" s="7" t="inlineStr"/>
+      <c r="K54" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L54" s="7" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
       <c r="N54" s="7" t="inlineStr"/>
@@ -4030,12 +4490,12 @@
       <c r="U54" s="6" t="inlineStr"/>
       <c r="V54" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:3,9-15; Alvin, 2026-07-31 (role correction)</t>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-07-31 (role correction); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W54" s="6" t="inlineStr">
         <is>
-          <t>Stream DRI owns digest production and the 'what it means for SJS' analytical layer. Named as the stream's heartbeat - first thing protected under capacity pressure. A and R both NI. Danielle consulted on the digest's read.</t>
+          <t>Named in the Ops Specialist JD, and in the 27 July email as making sure product is where it needs to be for launches, promos, PR seeding and sampling. Nicole owns it and runs it. Alvin, Soraya, Kate, Erin and Danielle consulted. The transition marker was cleared, so this stays with Nicole rather than moving to the Operations Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -4047,34 +4507,54 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>Social listening and comp brand monitoring (TikTok, IG, Pinterest, retailer new arrivals)</t>
+          <t>Campaign direction and seasonal brand moments</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr"/>
-      <c r="F55" s="7" t="inlineStr"/>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="K55" s="7" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I55" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="L55" s="7" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
       <c r="N55" s="7" t="inlineStr"/>
@@ -4087,12 +4567,12 @@
       <c r="U55" s="6" t="inlineStr"/>
       <c r="V55" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:34,40-44; Alvin, 2026-07-31 (role correction)</t>
+          <t>Alvin, 2026-07-31 (role correction); .claude/skills/sjs-margin-walk-away/SKILL.md:93; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W55" s="6" t="inlineStr">
         <is>
-          <t>Kate owns social listening tool maintenance, query hygiene and the weekly retailer new-arrivals scan. A and R both KL. Danielle consulted on what the social signal implies for brand.</t>
+          <t>Added 2026-07-31. Campaign direction was absent from the matrix, which is why the President and the Founder had almost no Marketing presence. Danielle answers for it - Soraya reports to her and the margin sources already have her approving every repricing and channel call. Ayesha consulted on brand moments.</t>
         </is>
       </c>
     </row>
@@ -4104,12 +4584,12 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>Brand guideline custody (fonts, colors, logos, voice)</t>
+          <t>Editorial and content calendar</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -4117,30 +4597,34 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr"/>
-      <c r="F56" s="7" t="inlineStr"/>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="I56" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="K56" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="L56" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K56" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L56" s="7" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
       <c r="N56" s="7" t="inlineStr"/>
       <c r="O56" s="7" t="inlineStr"/>
@@ -4152,12 +4636,12 @@
       <c r="U56" s="6" t="inlineStr"/>
       <c r="V56" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sweet-july-skin-brand/SKILL.md:1; references/architecture/system_map.md:157; Alvin, 2026-07-31 (role correction); acb-thelanding: data/links.json</t>
+          <t>acb-thelanding: data/links.json (Marketing / Owned Channels); Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W56" s="6" t="inlineStr">
         <is>
-          <t>Every output-producing skill defers here for canonical brand spec; no skill carries its own copy. President answers for brand custody; Creative Director maintains it. Ayesha consulted - the brand carries her name. Every output-producing skill defers here for canonical spec. Hub lists Brand &amp; Creative as "Owned by Soraya" as function lead; custody accountability sits with the President per the 31 July correction. Both hold: Soraya runs the function, Danielle answers for the brand standard.</t>
+          <t>Soraya runs the editorial and content calendar; Danielle answers for it. Editorial Calendar is a named tool under Owned Channels. Kate, Erin and Nicole consulted.</t>
         </is>
       </c>
     </row>
@@ -4169,60 +4653,64 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>Annual team holiday communications (11 sends across 3 templates)</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr"/>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+          <t>Email marketing: Klaviyo flows and campaign sends</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr"/>
       <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr"/>
-      <c r="L57" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="L57" s="7" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
       <c r="N57" s="7" t="inlineStr"/>
       <c r="O57" s="7" t="inlineStr"/>
       <c r="P57" s="7" t="inlineStr"/>
       <c r="Q57" s="7" t="inlineStr"/>
-      <c r="R57" s="7" t="inlineStr"/>
+      <c r="R57" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="S57" s="7" t="inlineStr"/>
       <c r="T57" s="7" t="inlineStr"/>
       <c r="U57" s="6" t="inlineStr"/>
       <c r="V57" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/ac-brands-holiday-comms/SKILL.md:26,165</t>
+          <t>acb-thelanding: data/links.json (Marketing / Klaviyo Performance); Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W57" s="6" t="inlineStr">
         <is>
-          <t>Sends from alvin@ac-brands.com with the team on BCC. Includes the Outlook calendar sync and annual maintenance. A and R both AB.</t>
+          <t>Soraya owns Klaviyo flows and campaign sends, with WITHIN consulted as the agency doing execution. Danielle answers for the channel. Klaviyo Performance is a named tool on the hub.</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4722,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>Weekly founder briefing, Slides 5 and 6</t>
+          <t>Paid media: Meta, Google and channel spend</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -4242,14 +4730,14 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E58" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -4259,31 +4747,35 @@
       </c>
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
+      <c r="I58" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="J58" s="7" t="inlineStr"/>
       <c r="K58" s="7" t="inlineStr"/>
       <c r="L58" s="7" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
-      <c r="N58" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N58" s="7" t="inlineStr"/>
       <c r="O58" s="7" t="inlineStr"/>
       <c r="P58" s="7" t="inlineStr"/>
       <c r="Q58" s="7" t="inlineStr"/>
-      <c r="R58" s="7" t="inlineStr"/>
+      <c r="R58" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="S58" s="7" t="inlineStr"/>
       <c r="T58" s="7" t="inlineStr"/>
       <c r="U58" s="6" t="inlineStr"/>
       <c r="V58" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/ayesha-weekly-briefing/SKILL.md:49,72</t>
+          <t>acb-thelanding: data/links.json (Marketing / Paid Media Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W58" s="6" t="inlineStr">
         <is>
-          <t>Alvin owns both Slide 5 (Business Operations) and Slide 6 PD-Ops content; Nicole co-authors Slide 6 with her core PD content. A and R both AB.</t>
+          <t>Soraya runs paid spend across Meta and Google, with WITHIN consulted on execution. Danielle answers for it. Alvin consulted on spend against margin floors. Quarterly business reviews with WITHIN, the most recent on 20 July.</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4787,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>Operational special projects: labels, PR seeding, sampling</t>
+          <t>Social media content and publishing</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -4303,43 +4795,35 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J59" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="F59" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J59" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="L59" s="7" t="inlineStr"/>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M59" s="7" t="inlineStr"/>
       <c r="N59" s="7" t="inlineStr"/>
       <c r="O59" s="7" t="inlineStr"/>
@@ -4348,19 +4832,15 @@
       <c r="R59" s="7" t="inlineStr"/>
       <c r="S59" s="7" t="inlineStr"/>
       <c r="T59" s="7" t="inlineStr"/>
-      <c r="U59" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
+      <c r="U59" s="6" t="inlineStr"/>
       <c r="V59" s="6" t="inlineStr">
         <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-07-31 (role correction)</t>
+          <t>acb-thelanding: data/links.json (Marketing / Social Media Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W59" s="6" t="inlineStr">
         <is>
-          <t>Named in the Ops Specialist JD, and in the email as making sure product is where it needs to be for launches, promos, PR seeding and sampling. Danielle consulted - PR seeding and sampling are brand-facing.</t>
+          <t>Distinct from social listening, which Soraya answers for. Kate does the publishing. Soraya and Danielle share the accountability.</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4852,12 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>Campaign direction and seasonal brand moments</t>
+          <t>Influencer and earned media programs</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
@@ -4397,21 +4877,17 @@
       </c>
       <c r="G60" s="7" t="inlineStr"/>
       <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J60" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="J60" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K60" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K60" s="7" t="inlineStr"/>
       <c r="L60" s="7" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
       <c r="N60" s="7" t="inlineStr"/>
@@ -4424,12 +4900,12 @@
       <c r="U60" s="6" t="inlineStr"/>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (role correction); .claude/skills/sjs-margin-walk-away/SKILL.md:93</t>
+          <t>acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W60" s="6" t="inlineStr">
         <is>
-          <t>Added 2026-07-31. Campaign direction was absent from the matrix, which is why the President and the Founder had almost no Marketing presence. Danielle answers for it - Soraya reports to her and the margin sources already have her approving every repricing and channel call. Ayesha consulted on brand moments.</t>
+          <t>Kate runs the programs. Soraya and Danielle share the accountability, since this is brand-facing and founder-adjacent. Nicole consulted. The physical seeding logistics sit on the Operations special-projects row.</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4917,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>Editorial and content calendar</t>
+          <t>WITHIN agency relationship and quarterly business reviews</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -4456,31 +4932,27 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J61" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="K61" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="J61" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="K61" s="7" t="inlineStr"/>
       <c r="L61" s="7" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
       <c r="N61" s="7" t="inlineStr"/>
@@ -4493,29 +4965,29 @@
       <c r="U61" s="6" t="inlineStr"/>
       <c r="V61" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json (Marketing / Owned Channels); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W61" s="6" t="inlineStr">
         <is>
-          <t>Hub lists Marketing as "Owned by TBD"; resolved to Soraya as Marketing Manager. Editorial Calendar is a named tool under Owned Channels.</t>
+          <t>Soraya runs the relationship and the quarterly reviews, with Nicole sharing the accountability. WITHIN holds most of our digital marketing execution, so the engagement is a single point of dependency, the same shape as the other external parties.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>Email marketing: Klaviyo flows and campaign sends</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
+          <t>Creative direction on packaging, artwork and brand visuals</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -4533,53 +5005,69 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G62" s="7" t="inlineStr"/>
-      <c r="H62" s="7" t="inlineStr"/>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J62" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K62" s="7" t="inlineStr"/>
-      <c r="L62" s="7" t="inlineStr"/>
-      <c r="M62" s="7" t="inlineStr"/>
-      <c r="N62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J62" s="7" t="inlineStr"/>
+      <c r="K62" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M62" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="O62" s="7" t="inlineStr"/>
       <c r="P62" s="7" t="inlineStr"/>
       <c r="Q62" s="7" t="inlineStr"/>
-      <c r="R62" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="R62" s="7" t="inlineStr"/>
       <c r="S62" s="7" t="inlineStr"/>
       <c r="T62" s="7" t="inlineStr"/>
       <c r="U62" s="6" t="inlineStr"/>
       <c r="V62" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json (Marketing / Klaviyo Performance); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:22; Alvin, 2026-07-31 (role correction); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W62" s="6" t="inlineStr">
         <is>
-          <t>WITHIN runs most of our digital marketing including email execution. Soraya answers for the channel. Klaviyo Performance is a named tool on the hub.</t>
+          <t>Erin owns packaging, artwork and brand visuals and does the work. Ayesha shares the accountability, the brand carries her name. Erin is a contractor with no internal backup. Jan, Ivy, Nicole, Soraya and Danielle consulted.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Paid media: Meta, Google and channel spend</t>
+          <t>Packaging and artwork execution</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -4594,7 +5082,7 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -4602,86 +5090,106 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="G63" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J63" s="7" t="inlineStr"/>
+      <c r="K63" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J63" s="7" t="inlineStr"/>
-      <c r="K63" s="7" t="inlineStr"/>
       <c r="L63" s="7" t="inlineStr"/>
-      <c r="M63" s="7" t="inlineStr"/>
-      <c r="N63" s="7" t="inlineStr"/>
+      <c r="M63" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O63" s="7" t="inlineStr"/>
       <c r="P63" s="7" t="inlineStr"/>
       <c r="Q63" s="7" t="inlineStr"/>
-      <c r="R63" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="R63" s="7" t="inlineStr"/>
       <c r="S63" s="7" t="inlineStr"/>
       <c r="T63" s="7" t="inlineStr"/>
       <c r="U63" s="6" t="inlineStr"/>
       <c r="V63" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json (Marketing / Paid Media Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:23; .claude/skills/sjs-comp-intel/references/team-ownership.md:79; Alvin, 2026-07-31 (role correction); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W63" s="6" t="inlineStr">
         <is>
-          <t>WITHIN is the digital marketing agency and runs paid execution. Alvin consulted on spend against margin floors. Quarterly business reviews with WITHIN - the most recent was 20 July.</t>
+          <t>Jan is the creative contractor under Erin. Title differs between sources - Packaging Engineer in one, creative contractor in the other. Erin holds technical authority; Jan executes. Both contractors.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Creative</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Social media content and publishing</t>
-        </is>
-      </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr"/>
-      <c r="F64" s="7" t="inlineStr"/>
+          <t>Creative Requests intake and design coordination</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr"/>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G64" s="7" t="inlineStr"/>
       <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J64" s="8" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr"/>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M64" s="7" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="N64" s="7" t="inlineStr"/>
       <c r="O64" s="7" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr"/>
@@ -4692,24 +5200,24 @@
       <c r="U64" s="6" t="inlineStr"/>
       <c r="V64" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json (Marketing / Social Media Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>.claude/skills/sjs-status-reporter/SKILL.md:352; .claude/skills/asana-pd-manager/references/role-map.md:24; Alvin, 2026-07-31 (role correction); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W64" s="6" t="inlineStr">
         <is>
-          <t>Distinct from social listening, which Kate is accountable for. Here she does the publishing work and Soraya answers for the channel.</t>
+          <t>Ivy owns the Creative Requests project and coordinates the queue; Danielle answers for intake priority. Ivy supports Erin and Jan. Nicole, Jan, Erin and Soraya consulted.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Influencer and earned media programs</t>
+          <t>Shopify revenue and channel position read</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
@@ -4719,31 +5227,35 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr"/>
       <c r="K65" s="7" t="inlineStr"/>
       <c r="L65" s="7" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -4754,37 +5266,37 @@
       <c r="R65" s="7" t="inlineStr"/>
       <c r="S65" s="7" t="inlineStr"/>
       <c r="T65" s="7" t="inlineStr"/>
-      <c r="U65" s="6" t="inlineStr"/>
+      <c r="U65" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
       <c r="V65" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>connections.md:7; context/about-business.md:5; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W65" s="6" t="inlineStr">
         <is>
-          <t>Brand-facing and founder-adjacent, so Danielle consulted and Ayesha informed. The physical seeding logistics sit on the Operations special-projects row.</t>
+          <t>Nicole is accountable for all channels, DTC, Amazon and wholesale, and holds the revenue read. Alvin and Soraya consulted, Danielle informed. This was the last row on the matrix with no owner. Transitions to the Operations Specialist on hire.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>WITHIN agency relationship and quarterly business reviews</t>
-        </is>
-      </c>
-      <c r="C66" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>Daily DTC fulfillment KPIs and the SJ Shipping Dashboard</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr"/>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
@@ -4792,16 +5304,20 @@
           <t>C</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G66" s="7" t="inlineStr"/>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="J66" s="7" t="inlineStr"/>
@@ -4815,63 +5331,71 @@
       <c r="R66" s="7" t="inlineStr"/>
       <c r="S66" s="7" t="inlineStr"/>
       <c r="T66" s="7" t="inlineStr"/>
-      <c r="U66" s="6" t="inlineStr"/>
+      <c r="U66" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
       <c r="V66" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>.claude/skills/oc3pl-order-manager/SKILL.md:61,191; .claude/skills/ayesha-weekly-briefing/SKILL.md:123; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W66" s="6" t="inlineStr">
         <is>
-          <t>A and R both Soraya. WITHIN holds most of our digital marketing execution, so the engagement is a single point of dependency - same shape as the other five external parties.</t>
+          <t>Ex-Ops-Coordinator scope, now Nicole per the interim split. A and R both NI.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Creative direction on packaging, artwork and brand visuals</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>Channel operations and promo setup across DTC, UBM and Amazon</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr"/>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr"/>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="J67" s="7" t="inlineStr"/>
-      <c r="K67" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="L67" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr"/>
+      <c r="L67" s="7" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
       <c r="N67" s="7" t="inlineStr"/>
       <c r="O67" s="7" t="inlineStr"/>
@@ -4880,111 +5404,115 @@
       <c r="R67" s="7" t="inlineStr"/>
       <c r="S67" s="7" t="inlineStr"/>
       <c r="T67" s="7" t="inlineStr"/>
-      <c r="U67" s="6" t="inlineStr"/>
+      <c r="U67" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
       <c r="V67" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:22; Alvin, 2026-07-31 (role correction)</t>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W67" s="6" t="inlineStr">
         <is>
-          <t>Creative Director owns packaging, artwork and brand visuals. A and R both EH. Creative Director owns the direction as lead technical authority, and is a contractor. Danielle and Ayesha both consulted. A and R the same person - no second pair of eyes, and no internal backup either.</t>
+          <t>Named in the Ops Specialist JD under Order Management and Channel Operations. Nicole holds the channel relationship and runs the setup until the Operations Specialist absorbs it. Alvin and Kate consulted.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Packaging and artwork execution</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>Proactive reships and fulfillment-issue resolution</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr"/>
+      <c r="D68" s="7" t="inlineStr"/>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F68" s="7" t="inlineStr"/>
-      <c r="G68" s="7" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H68" s="7" t="inlineStr"/>
       <c r="I68" s="7" t="inlineStr"/>
       <c r="J68" s="7" t="inlineStr"/>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L68" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M68" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="N68" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K68" s="7" t="inlineStr"/>
+      <c r="L68" s="7" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+      <c r="N68" s="7" t="inlineStr"/>
       <c r="O68" s="7" t="inlineStr"/>
       <c r="P68" s="7" t="inlineStr"/>
       <c r="Q68" s="7" t="inlineStr"/>
       <c r="R68" s="7" t="inlineStr"/>
       <c r="S68" s="7" t="inlineStr"/>
       <c r="T68" s="7" t="inlineStr"/>
-      <c r="U68" s="6" t="inlineStr"/>
+      <c r="U68" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
       <c r="V68" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:23; .claude/skills/sjs-comp-intel/references/team-ownership.md:79; Alvin, 2026-07-31 (role correction)</t>
+          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
         </is>
       </c>
       <c r="W68" s="6" t="inlineStr">
         <is>
-          <t>Jan is the creative contractor under Erin. Title differs between sources - Packaging Engineer in one, creative contractor in the other. Erin holds technical authority; Jan executes. Both contractors.</t>
+          <t>JD wording: resolve fulfillment issues "before a customer has to follow up." Sits inside Nicole's interim OC3PL coverage. A and R both NI.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>Creative</t>
+          <t>Ecommerce &amp; DTC</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Creative Requests intake and design coordination</t>
-        </is>
-      </c>
-      <c r="C69" s="7" t="inlineStr"/>
+          <t>Amazon channel management (FBA, AWD, Seller Central)</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F69" s="7" t="inlineStr"/>
-      <c r="G69" s="7" t="inlineStr"/>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E69" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr">
         <is>
@@ -4992,16 +5520,8 @@
         </is>
       </c>
       <c r="J69" s="7" t="inlineStr"/>
-      <c r="K69" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L69" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
+      <c r="K69" s="7" t="inlineStr"/>
+      <c r="L69" s="7" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
       <c r="N69" s="7" t="inlineStr"/>
       <c r="O69" s="7" t="inlineStr"/>
@@ -5010,15 +5530,19 @@
       <c r="R69" s="7" t="inlineStr"/>
       <c r="S69" s="7" t="inlineStr"/>
       <c r="T69" s="7" t="inlineStr"/>
-      <c r="U69" s="6" t="inlineStr"/>
+      <c r="U69" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
       <c r="V69" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-status-reporter/SKILL.md:352; .claude/skills/asana-pd-manager/references/role-map.md:24; Alvin, 2026-07-31 (role correction)</t>
+          <t>acb-thelanding: data/links.json (Sales &amp; Commerce / Amazon Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
         </is>
       </c>
       <c r="W69" s="6" t="inlineStr">
         <is>
-          <t>Creative Requests Asana project owner is Ivy, Editorial/Design team. Ivy supports Erin and Jan. A and R both IT. Danielle consulted on intake priority.</t>
+          <t>Hub gave Amazon to Alvin; resolved to Nicole under all-channel accountability with Alvin doing the work. Inventory and inbound pipeline transition to the Ops Specialist.</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5554,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Shopify revenue and channel position read</t>
+          <t>Product detail page content and product copy</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr"/>
@@ -5039,112 +5563,156 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr"/>
-      <c r="H70" s="7" t="inlineStr"/>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I70" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
       <c r="J70" s="7" t="inlineStr"/>
-      <c r="K70" s="7" t="inlineStr"/>
-      <c r="L70" s="7" t="inlineStr"/>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M70" s="7" t="inlineStr"/>
-      <c r="N70" s="7" t="inlineStr"/>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O70" s="7" t="inlineStr"/>
       <c r="P70" s="7" t="inlineStr"/>
       <c r="Q70" s="7" t="inlineStr"/>
       <c r="R70" s="7" t="inlineStr"/>
       <c r="S70" s="7" t="inlineStr"/>
       <c r="T70" s="7" t="inlineStr"/>
-      <c r="U70" s="6" t="inlineStr"/>
+      <c r="U70" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
       <c r="V70" s="6" t="inlineStr">
         <is>
-          <t>connections.md:7; context/about-business.md:5; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>acb-thelanding: data/links.json (Sales &amp; Commerce / SJS Product Copy Database); Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W70" s="6" t="inlineStr">
         <is>
-          <t>Nicole is accountable for all channels - DTC, Amazon and wholesale - with Alvin consulted and Danielle informed. This was the last row on the matrix with no owner; it now has one.</t>
+          <t>Nicole owns product detail page content and copy. Product Copy Database is live from PLM and carries every claim, ingredient line, FAQ and Amazon title across DTC, Amazon and wholesale. Soraya, Perrine, Erin and Ivy consulted, because claims on a PDP are claims. Transitions to the Operations Specialist on hire.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Daily DTC fulfillment KPIs and the SJ Shipping Dashboard</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr"/>
-      <c r="D71" s="7" t="inlineStr"/>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="inlineStr">
+          <t>Margin architecture framework and quarterly portfolio review</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
         </is>
       </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr"/>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="J71" s="7" t="inlineStr"/>
       <c r="K71" s="7" t="inlineStr"/>
       <c r="L71" s="7" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
-      <c r="N71" s="7" t="inlineStr"/>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="O71" s="7" t="inlineStr"/>
-      <c r="P71" s="7" t="inlineStr"/>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="Q71" s="7" t="inlineStr"/>
       <c r="R71" s="7" t="inlineStr"/>
       <c r="S71" s="7" t="inlineStr"/>
       <c r="T71" s="7" t="inlineStr"/>
-      <c r="U71" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
+      <c r="U71" s="6" t="inlineStr"/>
       <c r="V71" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/oc3pl-order-manager/SKILL.md:61,191; .claude/skills/ayesha-weekly-briefing/SKILL.md:123</t>
+          <t>.claude/skills/sjs-margin-architect/references/framework.md:209; .claude/skills/sjs-margin-portfolio-review/SKILL.md:1; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W71" s="6" t="inlineStr">
         <is>
-          <t>Ex-Ops-Coordinator scope, now Nicole per the interim split. A and R both NI.</t>
+          <t>Framework reference plus the quarterly portfolio sweep and traffic-light report. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Channel operations and promo setup across DTC, UBM and Amazon</t>
+          <t>Monthly and quarterly vendor cost rollups</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr"/>
@@ -5153,14 +5721,14 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F72" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
@@ -5168,23 +5736,27 @@
           <t>-&gt;</t>
         </is>
       </c>
-      <c r="H72" s="7" t="inlineStr"/>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J72" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr"/>
       <c r="K72" s="7" t="inlineStr"/>
       <c r="L72" s="7" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
       <c r="N72" s="7" t="inlineStr"/>
       <c r="O72" s="7" t="inlineStr"/>
-      <c r="P72" s="7" t="inlineStr"/>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="Q72" s="7" t="inlineStr"/>
       <c r="R72" s="7" t="inlineStr"/>
       <c r="S72" s="7" t="inlineStr"/>
@@ -5196,43 +5768,39 @@
       </c>
       <c r="V72" s="6" t="inlineStr">
         <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx; acb-thelanding: data/links.json; Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>.claude/skills/regulatory-manager/SKILL.md:196; .claude/skills/purchasing-manager/SKILL.md:365; Alvin, 2026-07-31 (external partners); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W72" s="6" t="inlineStr">
         <is>
-          <t>Named in the Ops Specialist JD under Order Management &amp; Channel Operations. Nicole holds the channel relationship. Part of Nicole's all-channel accountability.</t>
+          <t>regulatory-manager Jobs 8 and 9 read vendor_invoices directly; purchasing-manager has no rollup of its own. A and R both AB. Ironclad consulted - the rollup feeds their books.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Proactive reships and fulfillment-issue resolution</t>
+          <t>Accounts payable, bookkeeping and payroll</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr"/>
-      <c r="D73" s="7" t="inlineStr"/>
+      <c r="D73" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="F73" s="7" t="inlineStr"/>
+      <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="7" t="inlineStr"/>
       <c r="I73" s="7" t="inlineStr"/>
       <c r="J73" s="7" t="inlineStr"/>
@@ -5241,36 +5809,36 @@
       <c r="M73" s="7" t="inlineStr"/>
       <c r="N73" s="7" t="inlineStr"/>
       <c r="O73" s="7" t="inlineStr"/>
-      <c r="P73" s="7" t="inlineStr"/>
+      <c r="P73" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="Q73" s="7" t="inlineStr"/>
       <c r="R73" s="7" t="inlineStr"/>
       <c r="S73" s="7" t="inlineStr"/>
       <c r="T73" s="7" t="inlineStr"/>
-      <c r="U73" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
+      <c r="U73" s="6" t="inlineStr"/>
       <c r="V73" s="6" t="inlineStr">
         <is>
-          <t>SharePoint: Sweet July Skin - Operations Specialist - Job Description.docx</t>
+          <t>Alvin, 2026-07-31 (external partners); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W73" s="6" t="inlineStr">
         <is>
-          <t>JD wording: resolve fulfillment issues "before a customer has to follow up." Sits inside Nicole's interim OC3PL coverage. A and R both NI.</t>
+          <t>Ironclad Finance runs AP, bookkeeping and payroll; Dan Bender is the contact. Danielle answers for it, with Alvin consulted where the vendor-invoice pipeline and its five approval gates feed the books. No longer an unowned function.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Amazon channel management (FBA, AWD, Seller Central)</t>
+          <t>Month-end close and management reporting</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
@@ -5278,79 +5846,75 @@
           <t>I</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F74" s="9" t="inlineStr">
+      <c r="D74" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr"/>
       <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr"/>
       <c r="K74" s="7" t="inlineStr"/>
       <c r="L74" s="7" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
       <c r="N74" s="7" t="inlineStr"/>
       <c r="O74" s="7" t="inlineStr"/>
-      <c r="P74" s="7" t="inlineStr"/>
+      <c r="P74" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="Q74" s="7" t="inlineStr"/>
       <c r="R74" s="7" t="inlineStr"/>
       <c r="S74" s="7" t="inlineStr"/>
       <c r="T74" s="7" t="inlineStr"/>
-      <c r="U74" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
+      <c r="U74" s="6" t="inlineStr"/>
       <c r="V74" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json (Sales &amp; Commerce / Amazon Dashboard); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
       <c r="W74" s="6" t="inlineStr">
         <is>
-          <t>Hub gave Amazon to Alvin; resolved to Nicole under all-channel accountability with Alvin doing the work. Inventory and inbound pipeline transition to the Ops Specialist.</t>
+          <t>Ironclad Finance closes the books and produces the reporting; Dan Bender is the contact. Reporting accountability sits with the President.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>Ecommerce &amp; DTC</t>
+          <t>Finance</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Product detail page content and product copy</t>
-        </is>
-      </c>
-      <c r="C75" s="7" t="inlineStr"/>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
+          <t>Annual budget and forecast consolidation</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -5360,30 +5924,22 @@
       </c>
       <c r="G75" s="7" t="inlineStr"/>
       <c r="H75" s="7" t="inlineStr"/>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="J75" s="7" t="inlineStr"/>
-      <c r="K75" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L75" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="K75" s="7" t="inlineStr"/>
+      <c r="L75" s="7" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
-      <c r="N75" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N75" s="7" t="inlineStr"/>
       <c r="O75" s="7" t="inlineStr"/>
-      <c r="P75" s="7" t="inlineStr"/>
+      <c r="P75" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="Q75" s="7" t="inlineStr"/>
       <c r="R75" s="7" t="inlineStr"/>
       <c r="S75" s="7" t="inlineStr"/>
@@ -5391,12 +5947,12 @@
       <c r="U75" s="6" t="inlineStr"/>
       <c r="V75" s="6" t="inlineStr">
         <is>
-          <t>acb-thelanding: data/links.json (Sales &amp; Commerce / SJS Product Copy Database); Alvin, 2026-07-31 (marketing, wholesale and web)</t>
+          <t>Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
       <c r="W75" s="6" t="inlineStr">
         <is>
-          <t>Product Copy Database is live from PLM and carries every claim, ingredient line, FAQ and Amazon title across DTC, Amazon and wholesale. Perrine and Regulatory consulted because claims on a PDP are claims. A and R both Soraya.</t>
+          <t>President answers for the budget. Operations and Consumer Strategy feed the operating and channel assumptions.</t>
         </is>
       </c>
     </row>
@@ -5408,18 +5964,18 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Margin architecture framework and quarterly portfolio review</t>
+          <t>Inventory valuation and cost of goods</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr"/>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -5427,16 +5983,32 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I76" s="7" t="inlineStr"/>
       <c r="J76" s="7" t="inlineStr"/>
       <c r="K76" s="7" t="inlineStr"/>
       <c r="L76" s="7" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
-      <c r="N76" s="7" t="inlineStr"/>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="O76" s="7" t="inlineStr"/>
-      <c r="P76" s="7" t="inlineStr"/>
+      <c r="P76" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="Q76" s="7" t="inlineStr"/>
       <c r="R76" s="7" t="inlineStr"/>
       <c r="S76" s="7" t="inlineStr"/>
@@ -5444,85 +6016,85 @@
       <c r="U76" s="6" t="inlineStr"/>
       <c r="V76" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-margin-architect/references/framework.md:209; .claude/skills/sjs-margin-portfolio-review/SKILL.md:1</t>
+          <t>Alvin, 2026-07-31 (external partners); .claude/skills/inventory-manager/SKILL.md:18; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W76" s="6" t="inlineStr">
         <is>
-          <t>Framework reference plus the quarterly portfolio sweep and traffic-light report. A and R both AB.</t>
+          <t>Cost side, so accountability sits with Operations - it flows out of purchasing, receiving and the inventory ledger. Ironclad carries it into the books.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Per-SKU margin pressure-test against channel floors</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr"/>
+          <t>Hiring the Operations Specialist and the PD Project Manager Specialist</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E77" s="8" t="inlineStr">
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
         <is>
           <t>R</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr"/>
       <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I77" s="7" t="inlineStr"/>
       <c r="J77" s="7" t="inlineStr"/>
       <c r="K77" s="7" t="inlineStr"/>
       <c r="L77" s="7" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
-      <c r="N77" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="N77" s="7" t="inlineStr"/>
       <c r="O77" s="7" t="inlineStr"/>
       <c r="P77" s="7" t="inlineStr"/>
-      <c r="Q77" s="7" t="inlineStr"/>
+      <c r="Q77" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="R77" s="7" t="inlineStr"/>
       <c r="S77" s="7" t="inlineStr"/>
       <c r="T77" s="7" t="inlineStr"/>
       <c r="U77" s="6" t="inlineStr"/>
       <c r="V77" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-margin-pressure-test/SKILL.md:93</t>
+          <t>decisions/log.md:52,58; context/priorities.md:3; Alvin, 2026-07-31 (external partners)</t>
         </is>
       </c>
       <c r="W77" s="6" t="inlineStr">
         <is>
-          <t>Flagged as Perrine and Soraya's call to ratify, with Alvin on admin, Nicole consulting and Danielle approving.</t>
+          <t>Both new roles report to Nicole. Decision owner recorded as Alvin, with Nicole on the two new roles once filled. Priority 1 of 2 this quarter. Calm HR runs the recruiting process once the RACI clears Danielle.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Walk-away decision when a SKU breaks its channel floor</t>
+          <t>Tool procurement, vendor renewals and shared-folder admin</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr"/>
@@ -5531,9 +6103,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -5541,22 +6113,26 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G78" s="7" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="I78" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="J78" s="7" t="inlineStr"/>
       <c r="K78" s="7" t="inlineStr"/>
       <c r="L78" s="7" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
-      <c r="N78" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N78" s="7" t="inlineStr"/>
       <c r="O78" s="7" t="inlineStr"/>
       <c r="P78" s="7" t="inlineStr"/>
       <c r="Q78" s="7" t="inlineStr"/>
@@ -5566,40 +6142,40 @@
       <c r="U78" s="6" t="inlineStr"/>
       <c r="V78" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:93,105,118</t>
+          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:50; .claude/skills/sjs-comp-intel/references/sequencing-plan.md:12; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W78" s="6" t="inlineStr">
         <is>
-          <t>Danielle approves on three of the four paths. Alvin carries the work on all four.</t>
+          <t>Ex-Ops-Coordinator scope. Alvin carries it directly until the Operations Specialist starts, and answers for it alongside Danielle. Nicole consulted.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>SKU archetype and Standard / Acquisition designation</t>
+          <t>Employee onboarding, offboarding and access deprovisioning</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr"/>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E79" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr"/>
@@ -5609,52 +6185,64 @@
       <c r="K79" s="7" t="inlineStr"/>
       <c r="L79" s="7" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
-      <c r="N79" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
+      <c r="N79" s="7" t="inlineStr"/>
       <c r="O79" s="7" t="inlineStr"/>
       <c r="P79" s="7" t="inlineStr"/>
-      <c r="Q79" s="7" t="inlineStr"/>
+      <c r="Q79" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="R79" s="7" t="inlineStr"/>
       <c r="S79" s="7" t="inlineStr"/>
-      <c r="T79" s="7" t="inlineStr"/>
+      <c r="T79" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="U79" s="6" t="inlineStr"/>
       <c r="V79" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-margin-walk-away/SKILL.md:78</t>
+          <t>.claude/skills/asana-pd-manager/references/role-map.md:48-56; Alvin, 2026-07-31 (external partners); Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W79" s="6" t="inlineStr">
         <is>
-          <t>Perrine as PD owner with Alvin on PD admin and sourcing; Nicole consults.</t>
+          <t>Alvin runs onboarding, offboarding and access deprovisioning and answers for it. Two partners split the execution and both are consulted: Calm HR on the employment side, Coastal Interactive on equipment and account provisioning. Danielle consulted. The departed-role-holder checklist in the PD role-map is the internal system-side counterpart.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Monthly and quarterly vendor cost rollups</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr"/>
+          <t>Operations Specialist recruiting</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G80" s="7" t="inlineStr"/>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr"/>
@@ -5664,39 +6252,43 @@
       <c r="M80" s="7" t="inlineStr"/>
       <c r="N80" s="7" t="inlineStr"/>
       <c r="O80" s="7" t="inlineStr"/>
-      <c r="P80" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q80" s="7" t="inlineStr"/>
+      <c r="P80" s="7" t="inlineStr"/>
+      <c r="Q80" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="R80" s="7" t="inlineStr"/>
       <c r="S80" s="7" t="inlineStr"/>
       <c r="T80" s="7" t="inlineStr"/>
       <c r="U80" s="6" t="inlineStr"/>
       <c r="V80" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/regulatory-manager/SKILL.md:196; .claude/skills/purchasing-manager/SKILL.md:365; Alvin, 2026-07-31 (external partners)</t>
+          <t>Leadership Business Review 2026-07-30 52:48-53:17; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W80" s="6" t="inlineStr">
         <is>
-          <t>regulatory-manager Jobs 8 and 9 read vendor_invoices directly; purchasing-manager has no rollup of its own. A and R both AB. Ironclad consulted - the rollup feeds their books.</t>
+          <t>Prioritized first. Calm HR runs the search as the PEO; Alvin answers for the hire. Danielle: "we're going to prioritize the operations... Specialist." Reports to Nicole. Target in place before Q4. Salary band $72-90K.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Accounts payable, bookkeeping and payroll</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr"/>
+          <t>PD Specialist role definition and phased recruiting</t>
+        </is>
+      </c>
+      <c r="C81" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -5707,7 +6299,11 @@
           <t>A</t>
         </is>
       </c>
-      <c r="F81" s="7" t="inlineStr"/>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="7" t="inlineStr"/>
       <c r="I81" s="7" t="inlineStr"/>
@@ -5717,51 +6313,47 @@
       <c r="M81" s="7" t="inlineStr"/>
       <c r="N81" s="7" t="inlineStr"/>
       <c r="O81" s="7" t="inlineStr"/>
-      <c r="P81" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="Q81" s="7" t="inlineStr"/>
+      <c r="P81" s="7" t="inlineStr"/>
+      <c r="Q81" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="R81" s="7" t="inlineStr"/>
       <c r="S81" s="7" t="inlineStr"/>
       <c r="T81" s="7" t="inlineStr"/>
       <c r="U81" s="6" t="inlineStr"/>
       <c r="V81" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
+          <t>Leadership Business Review 2026-07-30 53:17-57:10; Email to Danielle 2026-07-27 'Proposed Ops Positions'; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W81" s="6" t="inlineStr">
         <is>
-          <t>Ironclad Finance runs AP, bookkeeping and payroll; Dan Bender is the contact. Cost-side accountability sits with Operations because the vendor-invoice pipeline and its five approval gates feed it. No longer an unowned function.</t>
+          <t>Phased in after the Ops Specialist. Danielle scopes it as "air traffic control, holding people accountable" rather than strategy or ideation, and is adding trend-forecasting language to the JD. Reports to Nicole. Salary band $75-95K.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Month-end close and management reporting</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+          <t>SOP cleanup and operational prep before new-hire onboarding</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr"/>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -5778,11 +6370,7 @@
       <c r="M82" s="7" t="inlineStr"/>
       <c r="N82" s="7" t="inlineStr"/>
       <c r="O82" s="7" t="inlineStr"/>
-      <c r="P82" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="P82" s="7" t="inlineStr"/>
       <c r="Q82" s="7" t="inlineStr"/>
       <c r="R82" s="7" t="inlineStr"/>
       <c r="S82" s="7" t="inlineStr"/>
@@ -5790,24 +6378,24 @@
       <c r="U82" s="6" t="inlineStr"/>
       <c r="V82" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
+          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W82" s="6" t="inlineStr">
         <is>
-          <t>Ironclad Finance closes the books and produces the reporting; Dan Bender is the contact. Reporting accountability sits with the President.</t>
+          <t>Danielle's condition on the hire: clean up the system first so the role can function. Alvin does the cleanup and answers for it, with Nicole consulted.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Annual budget and forecast consolidation</t>
+          <t>Employee handbook and HR policy</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
@@ -5827,70 +6415,62 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>I</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr"/>
       <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="I83" s="7" t="inlineStr"/>
       <c r="J83" s="7" t="inlineStr"/>
       <c r="K83" s="7" t="inlineStr"/>
       <c r="L83" s="7" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
       <c r="N83" s="7" t="inlineStr"/>
       <c r="O83" s="7" t="inlineStr"/>
-      <c r="P83" s="8" t="inlineStr">
+      <c r="P83" s="7" t="inlineStr"/>
+      <c r="Q83" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Q83" s="7" t="inlineStr"/>
       <c r="R83" s="7" t="inlineStr"/>
       <c r="S83" s="7" t="inlineStr"/>
       <c r="T83" s="7" t="inlineStr"/>
       <c r="U83" s="6" t="inlineStr"/>
       <c r="V83" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
+          <t>Alvin, 2026-07-31 (external partners); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W83" s="6" t="inlineStr">
         <is>
-          <t>President answers for the budget. Operations and Consumer Strategy feed the operating and channel assumptions.</t>
+          <t>Calm HR drafts and maintains the handbook; Alvin is the liaison; Danielle answers for the policy. In flight as of 30 July and goes to legal review before implementation.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>People &amp; Admin</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Inventory valuation and cost of goods</t>
+          <t>Benefits administration and payroll processing</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr"/>
-      <c r="D84" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="D84" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F84" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr"/>
       <c r="G84" s="7" t="inlineStr"/>
       <c r="H84" s="7" t="inlineStr"/>
       <c r="I84" s="7" t="inlineStr"/>
@@ -5898,30 +6478,30 @@
       <c r="K84" s="7" t="inlineStr"/>
       <c r="L84" s="7" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
-      <c r="N84" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N84" s="7" t="inlineStr"/>
       <c r="O84" s="7" t="inlineStr"/>
-      <c r="P84" s="8" t="inlineStr">
+      <c r="P84" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q84" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="Q84" s="7" t="inlineStr"/>
       <c r="R84" s="7" t="inlineStr"/>
       <c r="S84" s="7" t="inlineStr"/>
       <c r="T84" s="7" t="inlineStr"/>
       <c r="U84" s="6" t="inlineStr"/>
       <c r="V84" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (external partners); .claude/skills/inventory-manager/SKILL.md:18</t>
+          <t>Alvin, 2026-07-31 (external partners); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W84" s="6" t="inlineStr">
         <is>
-          <t>Cost side, so accountability sits with Operations - it flows out of purchasing, receiving and the inventory ledger. Ironclad carries it into the books.</t>
+          <t>Calm HR administers as co-employer. Danielle answers for it. Ironclad consulted where payroll hits the books, Alvin as the liaison.</t>
         </is>
       </c>
     </row>
@@ -5933,29 +6513,21 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Hiring the Operations Specialist and the PD Project Manager Specialist</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
+          <t>Employment compliance and separations</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr"/>
+      <c r="D85" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F85" s="7" t="inlineStr"/>
       <c r="G85" s="7" t="inlineStr"/>
       <c r="H85" s="7" t="inlineStr"/>
       <c r="I85" s="7" t="inlineStr"/>
@@ -5966,9 +6538,9 @@
       <c r="N85" s="7" t="inlineStr"/>
       <c r="O85" s="7" t="inlineStr"/>
       <c r="P85" s="7" t="inlineStr"/>
-      <c r="Q85" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="Q85" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
         </is>
       </c>
       <c r="R85" s="7" t="inlineStr"/>
@@ -5977,24 +6549,24 @@
       <c r="U85" s="6" t="inlineStr"/>
       <c r="V85" s="6" t="inlineStr">
         <is>
-          <t>decisions/log.md:52,58; context/priorities.md:3; Alvin, 2026-07-31 (external partners)</t>
+          <t>Alvin, 2026-07-31 (external partners); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W85" s="6" t="inlineStr">
         <is>
-          <t>Both new roles report to Nicole. Decision owner recorded as Alvin, with Nicole on the two new roles once filled. Priority 1 of 2 this quarter. Calm HR runs the recruiting process once the RACI clears Danielle.</t>
+          <t>Calm HR runs the process with outside counsel where needed. Danielle answers for every separation, Alvin consulted as the liaison.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Tool procurement, vendor renewals and shared-folder admin</t>
+          <t>PLM schema, write path, audit log and Supabase wiki custody</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr"/>
@@ -6004,9 +6576,9 @@
           <t>A/R</t>
         </is>
       </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr"/>
@@ -6014,11 +6586,7 @@
       <c r="I86" s="7" t="inlineStr"/>
       <c r="J86" s="7" t="inlineStr"/>
       <c r="K86" s="7" t="inlineStr"/>
-      <c r="L86" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="L86" s="7" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
       <c r="N86" s="7" t="inlineStr"/>
       <c r="O86" s="7" t="inlineStr"/>
@@ -6030,35 +6598,31 @@
       <c r="U86" s="6" t="inlineStr"/>
       <c r="V86" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/sjs-comp-intel/references/team-ownership.md:50; .claude/skills/sjs-comp-intel/references/sequencing-plan.md:12</t>
+          <t>.claude/skills/plm-assistant/SKILL.md:292; decisions/wiki-layer-audit-2026-07-29.md:52; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W86" s="6" t="inlineStr">
         <is>
-          <t>Ex-Ops-Coordinator scope. Alvin carries it directly until the Operations Specialist starts. A and R both AB.</t>
+          <t>plm-assistant is the sole PLM writer and every write needs Operations sign-off. Alvin runs it, with Nicole sharing the accountability as the systems and tech owner. Job 0 wiki write-back has not fired since 2026-05-26.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Employee onboarding, offboarding and access deprovisioning</t>
+          <t>Landing hub publish and Netlify Function maintenance</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr"/>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="D87" s="7" t="inlineStr"/>
       <c r="E87" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A/R</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -6076,59 +6640,43 @@
       <c r="N87" s="7" t="inlineStr"/>
       <c r="O87" s="7" t="inlineStr"/>
       <c r="P87" s="7" t="inlineStr"/>
-      <c r="Q87" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="Q87" s="7" t="inlineStr"/>
       <c r="R87" s="7" t="inlineStr"/>
       <c r="S87" s="7" t="inlineStr"/>
-      <c r="T87" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="T87" s="7" t="inlineStr"/>
       <c r="U87" s="6" t="inlineStr"/>
       <c r="V87" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/asana-pd-manager/references/role-map.md:48-56; Alvin, 2026-07-31 (external partners); Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+          <t>.claude/skills/quality-status-reporter/SKILL.md:34-50; .claude/skills/quality-status-reporter/references/hub-integration.md:85; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W87" s="6" t="inlineStr">
         <is>
-          <t>Calm HR is the PEO and co-employer and runs the process; Alvin is the liaison and answers for it. Danielle consulted. No longer an unowned function - the departed-role-holder checklist in the PD role-map remains the internal system-side counterpart. Two partners split this: Calm HR runs the employment side, Coastal Interactive runs equipment and account provisioning. Alvin is the liaison to both and answers for the whole.</t>
+          <t>All hub writes go through the landing-hub-publish Function behind an Operator gate. Deploy is commit-and-push only, never Netlify CLI. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Operations Specialist recruiting</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>Asana project, section, custom-field and connector configuration</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr"/>
+      <c r="D88" s="7" t="inlineStr"/>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F88" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr"/>
@@ -6148,44 +6696,36 @@
       <c r="U88" s="6" t="inlineStr"/>
       <c r="V88" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 52:48-53:17; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
+          <t>references/architecture/asana_task_contract.md:227; connections.md:5-13; Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W88" s="6" t="inlineStr">
         <is>
-          <t>Prioritized first. Danielle: "we're going to prioritize the operations... Specialist." Reports to Nicole. Target in place before Q4. Salary band $72-90K.</t>
+          <t>An unresolvable role-holder is surfaced for Alvin to decide, not dropped. Seven tool domains registered; iMessage still not connected. A and R both AB. Coastal Interactive consulted on identity, access and integration plumbing behind the connectors.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>PD Specialist role definition and phased recruiting</t>
-        </is>
-      </c>
-      <c r="C89" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>Skill suite authorship, audit and versioning</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr"/>
+      <c r="D89" s="7" t="inlineStr"/>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr"/>
@@ -6200,45 +6740,45 @@
       <c r="P89" s="7" t="inlineStr"/>
       <c r="Q89" s="7" t="inlineStr"/>
       <c r="R89" s="7" t="inlineStr"/>
-      <c r="S89" s="7" t="inlineStr"/>
+      <c r="S89" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="T89" s="7" t="inlineStr"/>
       <c r="U89" s="6" t="inlineStr"/>
       <c r="V89" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 53:17-57:10; Email to Danielle 2026-07-27 'Proposed Ops Positions'</t>
+          <t>decisions/skills-architecture-tracker.md:4; decisions/log.md:31,45; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W89" s="6" t="inlineStr">
         <is>
-          <t>Phased in after the Ops Specialist. Danielle scopes it as "air traffic control, holding people accountable" rather than strategy or ideation, and is adding trend-forecasting language to the JD. Reports to Nicole. Salary band $75-95K.</t>
+          <t>Owner recorded as Alvin Belt across the architecture decisions. Priority 2 of 2 this quarter. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>SOP cleanup and operational prep before new-hire onboarding</t>
+          <t>The 23 scheduled Routines and their HITL gates</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr"/>
-      <c r="D90" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+      <c r="D90" s="7" t="inlineStr"/>
       <c r="E90" s="9" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
+          <t>A/R</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr"/>
@@ -6253,36 +6793,36 @@
       <c r="P90" s="7" t="inlineStr"/>
       <c r="Q90" s="7" t="inlineStr"/>
       <c r="R90" s="7" t="inlineStr"/>
-      <c r="S90" s="7" t="inlineStr"/>
+      <c r="S90" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="T90" s="7" t="inlineStr"/>
       <c r="U90" s="6" t="inlineStr"/>
       <c r="V90" s="6" t="inlineStr">
         <is>
-          <t>Leadership Business Review 2026-07-30 54:24-55:43, 1:00:32</t>
+          <t>scheduled-prompts/weekly-pd-update.md:91; scheduled-prompts/sjs-purchasing-monthly-rollup-and-snapshot.md:79; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W90" s="6" t="inlineStr">
         <is>
-          <t>Danielle's condition on the hire: clean up the system first so the role can function. Nicole's action item from the review.</t>
+          <t>Nothing commits until Alvin says go. Same pattern across all 23 Routines, including the ones that fire unattended on a schedule. A and R both AB.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Employee handbook and HR policy</t>
-        </is>
-      </c>
-      <c r="C91" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
+          <t>RACI and role framework across Operations and PD</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr"/>
       <c r="D91" s="7" t="inlineStr">
         <is>
           <t>C</t>
@@ -6290,12 +6830,12 @@
       </c>
       <c r="E91" s="9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A/R</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr"/>
@@ -6308,109 +6848,129 @@
       <c r="N91" s="7" t="inlineStr"/>
       <c r="O91" s="7" t="inlineStr"/>
       <c r="P91" s="7" t="inlineStr"/>
-      <c r="Q91" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="Q91" s="7" t="inlineStr"/>
       <c r="R91" s="7" t="inlineStr"/>
       <c r="S91" s="7" t="inlineStr"/>
       <c r="T91" s="7" t="inlineStr"/>
       <c r="U91" s="6" t="inlineStr"/>
       <c r="V91" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
+          <t>Leadership Business Review 2026-07-30 52:12-52:39; Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W91" s="6" t="inlineStr">
         <is>
-          <t>Calm HR drafts and maintains; Alvin is the liaison and answers for it; Danielle co-approves. Handbook is in flight as of 2026-07-30 and goes to legal review before implementation.</t>
+          <t>Alvin owns the framework and builds it, with Nicole and Danielle consulted. Danielle gives final review before it goes to Calm HR to start recruiting.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Benefits administration and payroll processing</t>
+          <t>Website platform, Shopify storefront and web releases</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr"/>
-      <c r="D92" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E92" s="9" t="inlineStr">
+      <c r="D92" s="9" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr"/>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
       <c r="G92" s="7" t="inlineStr"/>
       <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
+      <c r="I92" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J92" s="7" t="inlineStr"/>
-      <c r="K92" s="7" t="inlineStr"/>
-      <c r="L92" s="7" t="inlineStr"/>
+      <c r="K92" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="M92" s="7" t="inlineStr"/>
       <c r="N92" s="7" t="inlineStr"/>
       <c r="O92" s="7" t="inlineStr"/>
-      <c r="P92" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q92" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="P92" s="7" t="inlineStr"/>
+      <c r="Q92" s="7" t="inlineStr"/>
       <c r="R92" s="7" t="inlineStr"/>
-      <c r="S92" s="7" t="inlineStr"/>
+      <c r="S92" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="T92" s="7" t="inlineStr"/>
       <c r="U92" s="6" t="inlineStr"/>
       <c r="V92" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
+          <t>Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W92" s="6" t="inlineStr">
         <is>
-          <t>Calm HR administers as co-employer. Ironclad consulted where payroll hits the books.</t>
+          <t>Danielle and Nicole share the accountability; Nicole runs it as the systems and tech owner. Teknologics consulted as the web development partner, Erin and Ivy on visual design, Soraya on merchandising and content. Alvin informed.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>People &amp; Admin</t>
+          <t>IT / Systems &amp; Data</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Employment compliance and separations</t>
-        </is>
-      </c>
-      <c r="C93" s="7" t="inlineStr"/>
+          <t>Web and digital systems ownership, including the Teknologics engagement</t>
+        </is>
+      </c>
+      <c r="C93" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E93" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr"/>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>A/R</t>
+        </is>
+      </c>
       <c r="G93" s="7" t="inlineStr"/>
       <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="inlineStr"/>
+      <c r="I93" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="J93" s="7" t="inlineStr"/>
       <c r="K93" s="7" t="inlineStr"/>
       <c r="L93" s="7" t="inlineStr"/>
@@ -6418,23 +6978,23 @@
       <c r="N93" s="7" t="inlineStr"/>
       <c r="O93" s="7" t="inlineStr"/>
       <c r="P93" s="7" t="inlineStr"/>
-      <c r="Q93" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="Q93" s="7" t="inlineStr"/>
       <c r="R93" s="7" t="inlineStr"/>
-      <c r="S93" s="7" t="inlineStr"/>
+      <c r="S93" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="T93" s="7" t="inlineStr"/>
       <c r="U93" s="6" t="inlineStr"/>
       <c r="V93" s="6" t="inlineStr">
         <is>
-          <t>Alvin, 2026-07-31 (external partners)</t>
+          <t>Alvin, 2026-07-31 (marketing, wholesale and web); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W93" s="6" t="inlineStr">
         <is>
-          <t>Calm HR runs the process with outside counsel where needed. Danielle co-approves every separation.</t>
+          <t>Nicole owns the web and digital stack outright, including the Teknologics engagement. Scoped to web and digital rather than the whole IT function: the PLM, Asana, hub-publish and Routine rows still sit with Alvin. Confirm whether that should widen.</t>
         </is>
       </c>
     </row>
@@ -6446,17 +7006,25 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>PLM schema, write path, audit log and Supabase wiki custody</t>
+          <t>Back-end IT infrastructure, identity and endpoint management</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr"/>
-      <c r="D94" s="7" t="inlineStr"/>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
       <c r="E94" s="9" t="inlineStr">
         <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr"/>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="G94" s="7" t="inlineStr"/>
       <c r="H94" s="7" t="inlineStr"/>
       <c r="I94" s="7" t="inlineStr"/>
@@ -6464,26 +7032,26 @@
       <c r="K94" s="7" t="inlineStr"/>
       <c r="L94" s="7" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
-      <c r="N94" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N94" s="7" t="inlineStr"/>
       <c r="O94" s="7" t="inlineStr"/>
       <c r="P94" s="7" t="inlineStr"/>
       <c r="Q94" s="7" t="inlineStr"/>
       <c r="R94" s="7" t="inlineStr"/>
       <c r="S94" s="7" t="inlineStr"/>
-      <c r="T94" s="7" t="inlineStr"/>
+      <c r="T94" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="U94" s="6" t="inlineStr"/>
       <c r="V94" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/plm-assistant/SKILL.md:292; decisions/wiki-layer-audit-2026-07-29.md:52</t>
+          <t>Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
         </is>
       </c>
       <c r="W94" s="6" t="inlineStr">
         <is>
-          <t>plm-assistant is the sole PLM writer and every write needs Operations sign-off. Job 0 wiki write-back has not fired since 2026-05-26. A and R both AB.</t>
+          <t>Coastal Interactive is the managed service provider and handles the higher-level IT and systems work. Alvin is the liaison and answers for it. Distinct from the web and digital stack, which sits with Danielle and Nicole.</t>
         </is>
       </c>
     </row>
@@ -6495,18 +7063,30 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Landing hub publish and Netlify Function maintenance</t>
+          <t>Equipment procurement, onboarding and asset lifecycle</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr"/>
-      <c r="D95" s="7" t="inlineStr"/>
-      <c r="E95" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="7" t="inlineStr"/>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
       <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="7" t="inlineStr"/>
       <c r="J95" s="7" t="inlineStr"/>
@@ -6516,19 +7096,31 @@
       <c r="N95" s="7" t="inlineStr"/>
       <c r="O95" s="7" t="inlineStr"/>
       <c r="P95" s="7" t="inlineStr"/>
-      <c r="Q95" s="7" t="inlineStr"/>
+      <c r="Q95" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="R95" s="7" t="inlineStr"/>
       <c r="S95" s="7" t="inlineStr"/>
-      <c r="T95" s="7" t="inlineStr"/>
-      <c r="U95" s="6" t="inlineStr"/>
+      <c r="T95" s="8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="U95" s="6" t="inlineStr">
+        <is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
       <c r="V95" s="6" t="inlineStr">
         <is>
-          <t>.claude/skills/quality-status-reporter/SKILL.md:34-50; .claude/skills/quality-status-reporter/references/hub-integration.md:85</t>
+          <t>Alvin, 2026-07-31 (Coastal Interactive; PD visibility); Alvin, 2026-08-06 (page edits)</t>
         </is>
       </c>
       <c r="W95" s="6" t="inlineStr">
         <is>
-          <t>All hub writes go through the landing-hub-publish Function behind an Operator gate. Deploy is commit-and-push only, never Netlify CLI. A and R both AB.</t>
+          <t>Coastal Interactive provisions and recovers equipment. Danielle answers for it. Pairs with the Calm HR employment side on every start and every exit. Transitions to the Operations Specialist on hire.</t>
         </is>
       </c>
     </row>
@@ -6540,11 +7132,15 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Asana project, section, custom-field and connector configuration</t>
+          <t>Coastal Interactive managed-service engagement and escalation</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr"/>
-      <c r="D96" s="7" t="inlineStr"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E96" s="9" t="inlineStr">
         <is>
           <t>A/R</t>
@@ -6576,614 +7172,446 @@
       <c r="U96" s="6" t="inlineStr"/>
       <c r="V96" s="6" t="inlineStr">
         <is>
-          <t>references/architecture/asana_task_contract.md:227; connections.md:5-13; Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
+          <t>Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
         </is>
       </c>
       <c r="W96" s="6" t="inlineStr">
         <is>
-          <t>An unresolvable role-holder is surfaced for Alvin to decide, not dropped. Seven tool domains registered; iMessage still not connected. A and R both AB. Coastal Interactive consulted on identity, access and integration plumbing behind the connectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="5" t="inlineStr">
-        <is>
-          <t>IT / Systems &amp; Data</t>
-        </is>
-      </c>
-      <c r="B97" s="6" t="inlineStr">
-        <is>
-          <t>Skill suite authorship, audit and versioning</t>
-        </is>
-      </c>
-      <c r="C97" s="7" t="inlineStr"/>
-      <c r="D97" s="7" t="inlineStr"/>
-      <c r="E97" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F97" s="7" t="inlineStr"/>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="7" t="inlineStr"/>
-      <c r="J97" s="7" t="inlineStr"/>
-      <c r="K97" s="7" t="inlineStr"/>
-      <c r="L97" s="7" t="inlineStr"/>
-      <c r="M97" s="7" t="inlineStr"/>
-      <c r="N97" s="7" t="inlineStr"/>
-      <c r="O97" s="7" t="inlineStr"/>
-      <c r="P97" s="7" t="inlineStr"/>
-      <c r="Q97" s="7" t="inlineStr"/>
-      <c r="R97" s="7" t="inlineStr"/>
-      <c r="S97" s="7" t="inlineStr"/>
-      <c r="T97" s="7" t="inlineStr"/>
-      <c r="U97" s="6" t="inlineStr"/>
-      <c r="V97" s="6" t="inlineStr">
-        <is>
-          <t>decisions/skills-architecture-tracker.md:4; decisions/log.md:31,45</t>
-        </is>
-      </c>
-      <c r="W97" s="6" t="inlineStr">
-        <is>
-          <t>Owner recorded as Alvin Belt across the architecture decisions. Priority 2 of 2 this quarter. A and R both AB.</t>
+          <t>A and R both Alvin - he is the sole liaison to the IT managed-service partner. Same single-point shape as the other partner relationships.</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="inlineStr">
-        <is>
-          <t>IT / Systems &amp; Data</t>
-        </is>
-      </c>
-      <c r="B98" s="6" t="inlineStr">
-        <is>
-          <t>The 23 scheduled Routines and their HITL gates</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr"/>
-      <c r="D98" s="7" t="inlineStr"/>
-      <c r="E98" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr"/>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
-      <c r="J98" s="7" t="inlineStr"/>
-      <c r="K98" s="7" t="inlineStr"/>
-      <c r="L98" s="7" t="inlineStr"/>
-      <c r="M98" s="7" t="inlineStr"/>
-      <c r="N98" s="7" t="inlineStr"/>
-      <c r="O98" s="7" t="inlineStr"/>
-      <c r="P98" s="7" t="inlineStr"/>
-      <c r="Q98" s="7" t="inlineStr"/>
-      <c r="R98" s="7" t="inlineStr"/>
-      <c r="S98" s="7" t="inlineStr"/>
-      <c r="T98" s="7" t="inlineStr"/>
-      <c r="U98" s="6" t="inlineStr"/>
-      <c r="V98" s="6" t="inlineStr">
-        <is>
-          <t>scheduled-prompts/weekly-pd-update.md:91; scheduled-prompts/sjs-purchasing-monthly-rollup-and-snapshot.md:79</t>
-        </is>
-      </c>
-      <c r="W98" s="6" t="inlineStr">
-        <is>
-          <t>Nothing commits until Alvin says go. Same pattern across all 23 Routines, including the ones that fire unattended on a schedule. A and R both AB.</t>
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>Legend</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>IT / Systems &amp; Data</t>
-        </is>
-      </c>
-      <c r="B99" s="6" t="inlineStr">
-        <is>
-          <t>RACI and role framework across Operations and PD</t>
-        </is>
-      </c>
-      <c r="C99" s="7" t="inlineStr"/>
-      <c r="D99" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E99" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr"/>
-      <c r="I99" s="7" t="inlineStr"/>
-      <c r="J99" s="7" t="inlineStr"/>
-      <c r="K99" s="7" t="inlineStr"/>
-      <c r="L99" s="7" t="inlineStr"/>
-      <c r="M99" s="7" t="inlineStr"/>
-      <c r="N99" s="7" t="inlineStr"/>
-      <c r="O99" s="7" t="inlineStr"/>
-      <c r="P99" s="7" t="inlineStr"/>
-      <c r="Q99" s="7" t="inlineStr"/>
-      <c r="R99" s="7" t="inlineStr"/>
-      <c r="S99" s="7" t="inlineStr"/>
-      <c r="T99" s="7" t="inlineStr"/>
-      <c r="U99" s="6" t="inlineStr"/>
-      <c r="V99" s="6" t="inlineStr">
-        <is>
-          <t>Leadership Business Review 2026-07-30 52:12-52:39</t>
-        </is>
-      </c>
-      <c r="W99" s="6" t="inlineStr">
-        <is>
-          <t>Alvin owns the framework, built with Nicole in the builder session, then to Danielle for final review before it goes to Calm HR to start recruiting.</t>
+      <c r="A99" s="11" t="n"/>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>A = answers for the outcome (at least one per row, and it can be shared)</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="inlineStr">
-        <is>
-          <t>IT / Systems &amp; Data</t>
-        </is>
-      </c>
-      <c r="B100" s="6" t="inlineStr">
-        <is>
-          <t>Website platform, Shopify storefront and web releases</t>
-        </is>
-      </c>
-      <c r="C100" s="7" t="inlineStr"/>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr"/>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J100" s="7" t="inlineStr"/>
-      <c r="K100" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="L100" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="M100" s="7" t="inlineStr"/>
-      <c r="N100" s="7" t="inlineStr"/>
-      <c r="O100" s="7" t="inlineStr"/>
-      <c r="P100" s="7" t="inlineStr"/>
-      <c r="Q100" s="7" t="inlineStr"/>
-      <c r="R100" s="7" t="inlineStr"/>
-      <c r="S100" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="T100" s="7" t="inlineStr"/>
-      <c r="U100" s="6" t="inlineStr"/>
-      <c r="V100" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (marketing, wholesale and web)</t>
-        </is>
-      </c>
-      <c r="W100" s="6" t="inlineStr">
-        <is>
-          <t>Teknologics is the web development partner. Danielle accountable; Nicole is the systems and tech owner; Erin and Ivy on visual design; Soraya consulted on merchandising and content; Alvin informed.</t>
+      <c r="A100" s="13" t="n"/>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>R = does the work (exactly one per row)</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="inlineStr">
-        <is>
-          <t>IT / Systems &amp; Data</t>
-        </is>
-      </c>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>Web and digital systems ownership, including the Teknologics engagement</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F101" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr"/>
-      <c r="H101" s="7" t="inlineStr"/>
-      <c r="I101" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="inlineStr"/>
-      <c r="K101" s="7" t="inlineStr"/>
-      <c r="L101" s="7" t="inlineStr"/>
-      <c r="M101" s="7" t="inlineStr"/>
-      <c r="N101" s="7" t="inlineStr"/>
-      <c r="O101" s="7" t="inlineStr"/>
-      <c r="P101" s="7" t="inlineStr"/>
-      <c r="Q101" s="7" t="inlineStr"/>
-      <c r="R101" s="7" t="inlineStr"/>
-      <c r="S101" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="T101" s="7" t="inlineStr"/>
-      <c r="U101" s="6" t="inlineStr"/>
-      <c r="V101" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (marketing, wholesale and web)</t>
-        </is>
-      </c>
-      <c r="W101" s="6" t="inlineStr">
-        <is>
-          <t>Nicole is the systems and tech owner for the web and digital stack. Scoped here to web and digital rather than the whole IT function - the PLM, Asana, hub-publish and Routine rows still sit with Alvin. Confirm whether that should widen.</t>
+      <c r="A101" s="11" t="n"/>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>A/R = the same person holds both, so the row has no second pair of eyes</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
-        <is>
-          <t>IT / Systems &amp; Data</t>
-        </is>
-      </c>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>Back-end IT infrastructure, identity and endpoint management</t>
-        </is>
-      </c>
-      <c r="C102" s="7" t="inlineStr"/>
-      <c r="D102" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E102" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr"/>
-      <c r="H102" s="7" t="inlineStr"/>
-      <c r="I102" s="7" t="inlineStr"/>
-      <c r="J102" s="7" t="inlineStr"/>
-      <c r="K102" s="7" t="inlineStr"/>
-      <c r="L102" s="7" t="inlineStr"/>
-      <c r="M102" s="7" t="inlineStr"/>
-      <c r="N102" s="7" t="inlineStr"/>
-      <c r="O102" s="7" t="inlineStr"/>
-      <c r="P102" s="7" t="inlineStr"/>
-      <c r="Q102" s="7" t="inlineStr"/>
-      <c r="R102" s="7" t="inlineStr"/>
-      <c r="S102" s="7" t="inlineStr"/>
-      <c r="T102" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="U102" s="6" t="inlineStr"/>
-      <c r="V102" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
-        </is>
-      </c>
-      <c r="W102" s="6" t="inlineStr">
-        <is>
-          <t>Coastal Interactive is the managed service provider and handles the higher-level IT and systems work. Alvin is the liaison and answers for it. Distinct from the web and digital stack, which sits with Danielle and Nicole.</t>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>C = consulted before the decision</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>IT / Systems &amp; Data</t>
-        </is>
-      </c>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>Equipment procurement, onboarding and asset lifecycle</t>
-        </is>
-      </c>
-      <c r="C103" s="7" t="inlineStr"/>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E103" s="9" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="7" t="inlineStr"/>
-      <c r="J103" s="7" t="inlineStr"/>
-      <c r="K103" s="7" t="inlineStr"/>
-      <c r="L103" s="7" t="inlineStr"/>
-      <c r="M103" s="7" t="inlineStr"/>
-      <c r="N103" s="7" t="inlineStr"/>
-      <c r="O103" s="7" t="inlineStr"/>
-      <c r="P103" s="7" t="inlineStr"/>
-      <c r="Q103" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="R103" s="7" t="inlineStr"/>
-      <c r="S103" s="7" t="inlineStr"/>
-      <c r="T103" s="8" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="U103" s="6" t="inlineStr">
-        <is>
-          <t>Operations Specialist</t>
-        </is>
-      </c>
-      <c r="V103" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
-        </is>
-      </c>
-      <c r="W103" s="6" t="inlineStr">
-        <is>
-          <t>Coastal Interactive provisions and recovers equipment. Pairs with the Calm HR employment side on every start and every exit - the departed-role-holder checklist covers the systems half. Transitions to the Operations Specialist on hire.</t>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>I = informed after it</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>IT / Systems &amp; Data</t>
-        </is>
-      </c>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>Coastal Interactive managed-service engagement and escalation</t>
-        </is>
-      </c>
-      <c r="C104" s="7" t="inlineStr"/>
-      <c r="D104" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E104" s="9" t="inlineStr">
-        <is>
-          <t>A/R</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr"/>
-      <c r="I104" s="7" t="inlineStr"/>
-      <c r="J104" s="7" t="inlineStr"/>
-      <c r="K104" s="7" t="inlineStr"/>
-      <c r="L104" s="7" t="inlineStr"/>
-      <c r="M104" s="7" t="inlineStr"/>
-      <c r="N104" s="7" t="inlineStr"/>
-      <c r="O104" s="7" t="inlineStr"/>
-      <c r="P104" s="7" t="inlineStr"/>
-      <c r="Q104" s="7" t="inlineStr"/>
-      <c r="R104" s="7" t="inlineStr"/>
-      <c r="S104" s="7" t="inlineStr"/>
-      <c r="T104" s="7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="U104" s="6" t="inlineStr"/>
-      <c r="V104" s="6" t="inlineStr">
-        <is>
-          <t>Alvin, 2026-07-31 (Coastal Interactive; PD visibility)</t>
-        </is>
-      </c>
-      <c r="W104" s="6" t="inlineStr">
-        <is>
-          <t>A and R both Alvin - he is the sole liaison to the IT managed-service partner. Same single-point shape as the other partner relationships.</t>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>-&gt; = the open seat that absorbs R on hire. Open seats never hold A or R.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>Legend</t>
+          <t>Positions</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="n"/>
-      <c r="B107" s="12" t="inlineStr">
-        <is>
-          <t>A = answers for the outcome (at least one per row, and it can be shared)</t>
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B107" s="14" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="C107" s="14" t="inlineStr">
+        <is>
+          <t>Holder</t>
+        </is>
+      </c>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E107" s="14" t="inlineStr">
+        <is>
+          <t>A count</t>
+        </is>
+      </c>
+      <c r="F107" s="14" t="inlineStr">
+        <is>
+          <t>R count</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H107" s="14" t="inlineStr">
+        <is>
+          <t>Hands off</t>
+        </is>
+      </c>
+      <c r="I107" s="14" t="inlineStr">
+        <is>
+          <t>Absorbs</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="13" t="n"/>
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
       <c r="B108" s="12" t="inlineStr">
         <is>
-          <t>R = does the work (exactly one per row)</t>
-        </is>
+          <t>Owner / Founder</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>Ayesha Curry</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="n"/>
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>DI</t>
+        </is>
+      </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>A/R = the same person holds both, so the row has no second pair of eyes</t>
-        </is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>Danielle Iturbe</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>23</v>
+      </c>
+      <c r="F109" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
       <c r="B110" s="12" t="inlineStr">
         <is>
-          <t>C = consulted before the decision</t>
-        </is>
+          <t>VP of Operations</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>Alvin Belt</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>39</v>
+      </c>
+      <c r="F110" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="G110" s="15" t="n">
+        <v>34</v>
+      </c>
+      <c r="H110" s="15" t="n">
+        <v>36</v>
+      </c>
+      <c r="I110" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>NI</t>
+        </is>
+      </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>I = informed after it</t>
-        </is>
+          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>Nicole Iturbe</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>27</v>
+      </c>
+      <c r="F111" s="15" t="n">
+        <v>15</v>
+      </c>
+      <c r="G111" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="I111" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>OPS</t>
+        </is>
+      </c>
       <c r="B112" s="12" t="inlineStr">
         <is>
-          <t>-&gt; = the open seat that absorbs R on hire. Open seats never hold A or R.</t>
-        </is>
+          <t>Operations Specialist</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>Open seat</t>
+        </is>
+      </c>
+      <c r="D112" s="16" t="inlineStr">
+        <is>
+          <t>recruiting</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="15" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>PDS</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Product Development Specialist</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>Open seat</t>
+        </is>
+      </c>
+      <c r="D113" s="16" t="inlineStr">
+        <is>
+          <t>phased</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="15" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>Positions</t>
-        </is>
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>Soraya Salgadoe</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F114" s="15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G114" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="14" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B115" s="14" t="inlineStr">
-        <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="C115" s="14" t="inlineStr">
-        <is>
-          <t>Holder</t>
-        </is>
-      </c>
-      <c r="D115" s="14" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E115" s="14" t="inlineStr">
-        <is>
-          <t>A count</t>
-        </is>
-      </c>
-      <c r="F115" s="14" t="inlineStr">
-        <is>
-          <t>R count</t>
-        </is>
-      </c>
-      <c r="G115" s="14" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H115" s="14" t="inlineStr">
-        <is>
-          <t>Hands off</t>
-        </is>
-      </c>
-      <c r="I115" s="14" t="inlineStr">
-        <is>
-          <t>Absorbs</t>
-        </is>
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>KL</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Social Media Coordinator</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>Kate Le</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>filled</t>
+        </is>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G115" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>EH</t>
         </is>
       </c>
       <c r="B116" s="12" t="inlineStr">
         <is>
-          <t>Owner / Founder</t>
+          <t>Creative Director</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>Ayesha Curry</t>
+          <t>Erin Hover</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="E116" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F116" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F116" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="G116" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" s="15" t="n">
         <v>0</v>
@@ -7195,17 +7623,17 @@
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
-          <t>DI</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>President</t>
+          <t>Creative / Design Coordinator</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Danielle Iturbe</t>
+          <t>Ivy Tan</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
@@ -7214,10 +7642,10 @@
         </is>
       </c>
       <c r="E117" s="15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F117" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G117" s="15" t="n">
         <v>0</v>
@@ -7232,35 +7660,35 @@
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>JH</t>
         </is>
       </c>
       <c r="B118" s="12" t="inlineStr">
         <is>
-          <t>VP of Operations</t>
+          <t>Packaging Engineer</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>Alvin Belt</t>
+          <t>Jan Haeck</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F118" s="15" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="G118" s="15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I118" s="15" t="n">
         <v>0</v>
@@ -7269,35 +7697,35 @@
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="B119" s="12" t="inlineStr">
         <is>
-          <t>Sr. Director, Consumer Strategy &amp; Operations</t>
+          <t>PD / R&amp;D contractor, Milinyc</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Nicole Iturbe</t>
+          <t>Perrine Calvet</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>contractor</t>
         </is>
       </c>
       <c r="E119" s="15" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="F119" s="15" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G119" s="15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H119" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I119" s="15" t="n">
         <v>0</v>
@@ -7306,22 +7734,22 @@
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t>OPS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B120" s="12" t="inlineStr">
         <is>
-          <t>Operations Specialist</t>
+          <t>External regulatory partner</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>Open seat</t>
-        </is>
-      </c>
-      <c r="D120" s="16" t="inlineStr">
-        <is>
-          <t>recruiting</t>
+          <t>Pedrero Regulatory</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
         </is>
       </c>
       <c r="E120" s="15" t="n">
@@ -7337,35 +7765,35 @@
         <v>0</v>
       </c>
       <c r="I120" s="15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
         <is>
-          <t>PDS</t>
+          <t>IF</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>Product Development Specialist</t>
+          <t>Outsourced finance (Dan Bender)</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Open seat</t>
-        </is>
-      </c>
-      <c r="D121" s="16" t="inlineStr">
-        <is>
-          <t>phased</t>
+          <t>Ironclad Finance</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>partner</t>
         </is>
       </c>
       <c r="E121" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F121" s="15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G121" s="15" t="n">
         <v>0</v>
@@ -7374,38 +7802,38 @@
         <v>0</v>
       </c>
       <c r="I121" s="15" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="12" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B122" s="12" t="inlineStr">
         <is>
-          <t>Marketing Manager</t>
+          <t>PEO and co-employer</t>
         </is>
       </c>
       <c r="C122" s="12" t="inlineStr">
         <is>
-          <t>Soraya Salgadoe</t>
+          <t>Calm HR</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F122" s="15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G122" s="15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H122" s="15" t="n">
         <v>0</v>
@@ -7417,32 +7845,32 @@
     <row r="123">
       <c r="A123" s="12" t="inlineStr">
         <is>
-          <t>KL</t>
+          <t>WI</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>Social Media Coordinator</t>
+          <t>Digital marketing agency</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Kate Le</t>
+          <t>WITHIN</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="E123" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F123" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G123" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H123" s="15" t="n">
         <v>0</v>
@@ -7454,32 +7882,32 @@
     <row r="124">
       <c r="A124" s="12" t="inlineStr">
         <is>
-          <t>EH</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="B124" s="12" t="inlineStr">
         <is>
-          <t>Creative Director</t>
+          <t>Web development</t>
         </is>
       </c>
       <c r="C124" s="12" t="inlineStr">
         <is>
-          <t>Erin Hover</t>
+          <t>Teknologics</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
-          <t>contractor</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F124" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G124" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" s="15" t="n">
         <v>0</v>
@@ -7491,350 +7919,54 @@
     <row r="125">
       <c r="A125" s="12" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CI</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>Creative / Design Coordinator</t>
+          <t>Managed IT service provider</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Ivy Tan</t>
+          <t>Coastal Interactive</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>filled</t>
+          <t>partner</t>
         </is>
       </c>
       <c r="E125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F125" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H125" s="15" t="n">
-        <v>0</v>
-      </c>
       <c r="I125" s="15" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="12" t="inlineStr">
-        <is>
-          <t>JH</t>
-        </is>
-      </c>
-      <c r="B126" s="12" t="inlineStr">
-        <is>
-          <t>Packaging Engineer</t>
-        </is>
-      </c>
-      <c r="C126" s="12" t="inlineStr">
-        <is>
-          <t>Jan Haeck</t>
-        </is>
-      </c>
-      <c r="D126" s="12" t="inlineStr">
-        <is>
-          <t>contractor</t>
-        </is>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G126" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="127">
-      <c r="A127" s="12" t="inlineStr">
-        <is>
-          <t>PC</t>
-        </is>
-      </c>
-      <c r="B127" s="12" t="inlineStr">
-        <is>
-          <t>PD / R&amp;D contractor, Milinyc</t>
-        </is>
-      </c>
-      <c r="C127" s="12" t="inlineStr">
-        <is>
-          <t>Perrine Calvet</t>
-        </is>
-      </c>
-      <c r="D127" s="12" t="inlineStr">
-        <is>
-          <t>contractor</t>
-        </is>
-      </c>
-      <c r="E127" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="F127" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G127" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H127" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="12" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="B128" s="12" t="inlineStr">
-        <is>
-          <t>External regulatory partner</t>
-        </is>
-      </c>
-      <c r="C128" s="12" t="inlineStr">
-        <is>
-          <t>Pedrero Regulatory</t>
-        </is>
-      </c>
-      <c r="D128" s="12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="12" t="inlineStr">
-        <is>
-          <t>IF</t>
-        </is>
-      </c>
-      <c r="B129" s="12" t="inlineStr">
-        <is>
-          <t>Outsourced finance (Dan Bender)</t>
-        </is>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>Ironclad Finance</t>
-        </is>
-      </c>
-      <c r="D129" s="12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="E129" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G129" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="12" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B130" s="12" t="inlineStr">
-        <is>
-          <t>PEO and co-employer</t>
-        </is>
-      </c>
-      <c r="C130" s="12" t="inlineStr">
-        <is>
-          <t>Calm HR</t>
-        </is>
-      </c>
-      <c r="D130" s="12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F130" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="G130" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="12" t="inlineStr">
-        <is>
-          <t>WI</t>
-        </is>
-      </c>
-      <c r="B131" s="12" t="inlineStr">
-        <is>
-          <t>Digital marketing agency</t>
-        </is>
-      </c>
-      <c r="C131" s="12" t="inlineStr">
-        <is>
-          <t>WITHIN</t>
-        </is>
-      </c>
-      <c r="D131" s="12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F131" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G131" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="12" t="inlineStr">
-        <is>
-          <t>TK</t>
-        </is>
-      </c>
-      <c r="B132" s="12" t="inlineStr">
-        <is>
-          <t>Web development</t>
-        </is>
-      </c>
-      <c r="C132" s="12" t="inlineStr">
-        <is>
-          <t>Teknologics</t>
-        </is>
-      </c>
-      <c r="D132" s="12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G132" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="12" t="inlineStr">
-        <is>
-          <t>CI</t>
-        </is>
-      </c>
-      <c r="B133" s="12" t="inlineStr">
-        <is>
-          <t>Managed IT service provider</t>
-        </is>
-      </c>
-      <c r="C133" s="12" t="inlineStr">
-        <is>
-          <t>Coastal Interactive</t>
-        </is>
-      </c>
-      <c r="D133" s="12" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="E133" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="G133" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I133" s="15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="14" t="inlineStr">
+      <c r="A127" s="14" t="inlineStr">
         <is>
           <t>Source of truth</t>
         </is>
       </c>
-      <c r="B135" s="17" t="inlineStr">
+      <c r="B127" s="17" t="inlineStr">
         <is>
           <t>Rows citing a path are relative to the SJ-OS repo. Rows prefixed acb-thelanding cite the AC Brands landing hub, whose links.json defines eleven functions with a named lead each. Rows citing the 30 July leadership review, the 27 July email to Danielle, a job description, or Alvin directly come from those sources. Every row on this matrix has an owner - there are no inferred owners left.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:W104"/>
+  <autoFilter ref="A2:W96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7927,15 +8059,15 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>COUNTIF(RACI!C3:C104,"A")+COUNTIF(RACI!C3:C104,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C96,"A")+COUNTIF(RACI!C3:C96,"A/R")</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>COUNTIF(RACI!C3:C104,"R")+COUNTIF(RACI!C3:C104,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C96,"R")+COUNTIF(RACI!C3:C96,"A/R")</f>
         <v/>
       </c>
       <c r="D6" s="15">
-        <f>COUNTIF(RACI!C3:C104,"A/R")</f>
+        <f>COUNTIF(RACI!C3:C96,"A/R")</f>
         <v/>
       </c>
       <c r="E6" s="15" t="n">
@@ -7960,15 +8092,15 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>COUNTIF(RACI!D3:D104,"A")+COUNTIF(RACI!D3:D104,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D96,"A")+COUNTIF(RACI!D3:D96,"A/R")</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>COUNTIF(RACI!D3:D104,"R")+COUNTIF(RACI!D3:D104,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D96,"R")+COUNTIF(RACI!D3:D96,"A/R")</f>
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>COUNTIF(RACI!D3:D104,"A/R")</f>
+        <f>COUNTIF(RACI!D3:D96,"A/R")</f>
         <v/>
       </c>
       <c r="E7" s="15" t="n">
@@ -7993,19 +8125,19 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>COUNTIF(RACI!E3:E104,"A")+COUNTIF(RACI!E3:E104,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E96,"A")+COUNTIF(RACI!E3:E96,"A/R")</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>COUNTIF(RACI!E3:E104,"R")+COUNTIF(RACI!E3:E104,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E96,"R")+COUNTIF(RACI!E3:E96,"A/R")</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>COUNTIF(RACI!E3:E104,"A/R")</f>
+        <f>COUNTIF(RACI!E3:E96,"A/R")</f>
         <v/>
       </c>
       <c r="E8" s="15" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0</v>
@@ -8026,19 +8158,19 @@
         </is>
       </c>
       <c r="B9" s="15">
-        <f>COUNTIF(RACI!F3:F104,"A")+COUNTIF(RACI!F3:F104,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F96,"A")+COUNTIF(RACI!F3:F96,"A/R")</f>
         <v/>
       </c>
       <c r="C9" s="15">
-        <f>COUNTIF(RACI!F3:F104,"R")+COUNTIF(RACI!F3:F104,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F96,"R")+COUNTIF(RACI!F3:F96,"A/R")</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>COUNTIF(RACI!F3:F104,"A/R")</f>
+        <f>COUNTIF(RACI!F3:F96,"A/R")</f>
         <v/>
       </c>
       <c r="E9" s="15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>0</v>
@@ -8059,22 +8191,22 @@
         </is>
       </c>
       <c r="B10" s="15">
-        <f>COUNTIF(RACI!G3:G104,"A")+COUNTIF(RACI!G3:G104,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G96,"A")+COUNTIF(RACI!G3:G96,"A/R")</f>
         <v/>
       </c>
       <c r="C10" s="15">
-        <f>COUNTIF(RACI!G3:G104,"R")+COUNTIF(RACI!G3:G104,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G96,"R")+COUNTIF(RACI!G3:G96,"A/R")</f>
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>COUNTIF(RACI!G3:G104,"A/R")</f>
+        <f>COUNTIF(RACI!G3:G96,"A/R")</f>
         <v/>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G10" s="15">
         <f>B10</f>
@@ -8092,22 +8224,22 @@
         </is>
       </c>
       <c r="B11" s="15">
-        <f>COUNTIF(RACI!H3:H104,"A")+COUNTIF(RACI!H3:H104,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H96,"A")+COUNTIF(RACI!H3:H96,"A/R")</f>
         <v/>
       </c>
       <c r="C11" s="15">
-        <f>COUNTIF(RACI!H3:H104,"R")+COUNTIF(RACI!H3:H104,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H96,"R")+COUNTIF(RACI!H3:H96,"A/R")</f>
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>COUNTIF(RACI!H3:H104,"A/R")</f>
+        <f>COUNTIF(RACI!H3:H96,"A/R")</f>
         <v/>
       </c>
       <c r="E11" s="15" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G11" s="15">
         <f>B11</f>
@@ -8125,15 +8257,15 @@
         </is>
       </c>
       <c r="B12" s="15">
-        <f>COUNTIF(RACI!I3:I104,"A")+COUNTIF(RACI!I3:I104,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I96,"A")+COUNTIF(RACI!I3:I96,"A/R")</f>
         <v/>
       </c>
       <c r="C12" s="15">
-        <f>COUNTIF(RACI!I3:I104,"R")+COUNTIF(RACI!I3:I104,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I96,"R")+COUNTIF(RACI!I3:I96,"A/R")</f>
         <v/>
       </c>
       <c r="D12" s="15">
-        <f>COUNTIF(RACI!I3:I104,"A/R")</f>
+        <f>COUNTIF(RACI!I3:I96,"A/R")</f>
         <v/>
       </c>
       <c r="E12" s="15" t="n">
@@ -8158,15 +8290,15 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>COUNTIF(RACI!J3:J104,"A")+COUNTIF(RACI!J3:J104,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J96,"A")+COUNTIF(RACI!J3:J96,"A/R")</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>COUNTIF(RACI!J3:J104,"R")+COUNTIF(RACI!J3:J104,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J96,"R")+COUNTIF(RACI!J3:J96,"A/R")</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>COUNTIF(RACI!J3:J104,"A/R")</f>
+        <f>COUNTIF(RACI!J3:J96,"A/R")</f>
         <v/>
       </c>
       <c r="E13" s="15" t="n">
@@ -8191,15 +8323,15 @@
         </is>
       </c>
       <c r="B14" s="15">
-        <f>COUNTIF(RACI!K3:K104,"A")+COUNTIF(RACI!K3:K104,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K96,"A")+COUNTIF(RACI!K3:K96,"A/R")</f>
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>COUNTIF(RACI!K3:K104,"R")+COUNTIF(RACI!K3:K104,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K96,"R")+COUNTIF(RACI!K3:K96,"A/R")</f>
         <v/>
       </c>
       <c r="D14" s="15">
-        <f>COUNTIF(RACI!K3:K104,"A/R")</f>
+        <f>COUNTIF(RACI!K3:K96,"A/R")</f>
         <v/>
       </c>
       <c r="E14" s="15" t="n">
@@ -8224,15 +8356,15 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF(RACI!L3:L104,"A")+COUNTIF(RACI!L3:L104,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L96,"A")+COUNTIF(RACI!L3:L96,"A/R")</f>
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>COUNTIF(RACI!L3:L104,"R")+COUNTIF(RACI!L3:L104,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L96,"R")+COUNTIF(RACI!L3:L96,"A/R")</f>
         <v/>
       </c>
       <c r="D15" s="15">
-        <f>COUNTIF(RACI!L3:L104,"A/R")</f>
+        <f>COUNTIF(RACI!L3:L96,"A/R")</f>
         <v/>
       </c>
       <c r="E15" s="15" t="n">
@@ -8257,15 +8389,15 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF(RACI!M3:M104,"A")+COUNTIF(RACI!M3:M104,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M96,"A")+COUNTIF(RACI!M3:M96,"A/R")</f>
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>COUNTIF(RACI!M3:M104,"R")+COUNTIF(RACI!M3:M104,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M96,"R")+COUNTIF(RACI!M3:M96,"A/R")</f>
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>COUNTIF(RACI!M3:M104,"A/R")</f>
+        <f>COUNTIF(RACI!M3:M96,"A/R")</f>
         <v/>
       </c>
       <c r="E16" s="15" t="n">
@@ -8290,15 +8422,15 @@
         </is>
       </c>
       <c r="B17" s="15">
-        <f>COUNTIF(RACI!N3:N104,"A")+COUNTIF(RACI!N3:N104,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N96,"A")+COUNTIF(RACI!N3:N96,"A/R")</f>
         <v/>
       </c>
       <c r="C17" s="15">
-        <f>COUNTIF(RACI!N3:N104,"R")+COUNTIF(RACI!N3:N104,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N96,"R")+COUNTIF(RACI!N3:N96,"A/R")</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>COUNTIF(RACI!N3:N104,"A/R")</f>
+        <f>COUNTIF(RACI!N3:N96,"A/R")</f>
         <v/>
       </c>
       <c r="E17" s="15" t="n">
@@ -8323,15 +8455,15 @@
         </is>
       </c>
       <c r="B18" s="15">
-        <f>COUNTIF(RACI!O3:O104,"A")+COUNTIF(RACI!O3:O104,"A/R")</f>
+        <f>COUNTIF(RACI!O3:O96,"A")+COUNTIF(RACI!O3:O96,"A/R")</f>
         <v/>
       </c>
       <c r="C18" s="15">
-        <f>COUNTIF(RACI!O3:O104,"R")+COUNTIF(RACI!O3:O104,"A/R")</f>
+        <f>COUNTIF(RACI!O3:O96,"R")+COUNTIF(RACI!O3:O96,"A/R")</f>
         <v/>
       </c>
       <c r="D18" s="15">
-        <f>COUNTIF(RACI!O3:O104,"A/R")</f>
+        <f>COUNTIF(RACI!O3:O96,"A/R")</f>
         <v/>
       </c>
       <c r="E18" s="15" t="n">
@@ -8356,15 +8488,15 @@
         </is>
       </c>
       <c r="B19" s="15">
-        <f>COUNTIF(RACI!P3:P104,"A")+COUNTIF(RACI!P3:P104,"A/R")</f>
+        <f>COUNTIF(RACI!P3:P96,"A")+COUNTIF(RACI!P3:P96,"A/R")</f>
         <v/>
       </c>
       <c r="C19" s="15">
-        <f>COUNTIF(RACI!P3:P104,"R")+COUNTIF(RACI!P3:P104,"A/R")</f>
+        <f>COUNTIF(RACI!P3:P96,"R")+COUNTIF(RACI!P3:P96,"A/R")</f>
         <v/>
       </c>
       <c r="D19" s="15">
-        <f>COUNTIF(RACI!P3:P104,"A/R")</f>
+        <f>COUNTIF(RACI!P3:P96,"A/R")</f>
         <v/>
       </c>
       <c r="E19" s="15" t="n">
@@ -8389,15 +8521,15 @@
         </is>
       </c>
       <c r="B20" s="15">
-        <f>COUNTIF(RACI!Q3:Q104,"A")+COUNTIF(RACI!Q3:Q104,"A/R")</f>
+        <f>COUNTIF(RACI!Q3:Q96,"A")+COUNTIF(RACI!Q3:Q96,"A/R")</f>
         <v/>
       </c>
       <c r="C20" s="15">
-        <f>COUNTIF(RACI!Q3:Q104,"R")+COUNTIF(RACI!Q3:Q104,"A/R")</f>
+        <f>COUNTIF(RACI!Q3:Q96,"R")+COUNTIF(RACI!Q3:Q96,"A/R")</f>
         <v/>
       </c>
       <c r="D20" s="15">
-        <f>COUNTIF(RACI!Q3:Q104,"A/R")</f>
+        <f>COUNTIF(RACI!Q3:Q96,"A/R")</f>
         <v/>
       </c>
       <c r="E20" s="15" t="n">
@@ -8422,15 +8554,15 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>COUNTIF(RACI!R3:R104,"A")+COUNTIF(RACI!R3:R104,"A/R")</f>
+        <f>COUNTIF(RACI!R3:R96,"A")+COUNTIF(RACI!R3:R96,"A/R")</f>
         <v/>
       </c>
       <c r="C21" s="15">
-        <f>COUNTIF(RACI!R3:R104,"R")+COUNTIF(RACI!R3:R104,"A/R")</f>
+        <f>COUNTIF(RACI!R3:R96,"R")+COUNTIF(RACI!R3:R96,"A/R")</f>
         <v/>
       </c>
       <c r="D21" s="15">
-        <f>COUNTIF(RACI!R3:R104,"A/R")</f>
+        <f>COUNTIF(RACI!R3:R96,"A/R")</f>
         <v/>
       </c>
       <c r="E21" s="15" t="n">
@@ -8455,15 +8587,15 @@
         </is>
       </c>
       <c r="B22" s="15">
-        <f>COUNTIF(RACI!S3:S104,"A")+COUNTIF(RACI!S3:S104,"A/R")</f>
+        <f>COUNTIF(RACI!S3:S96,"A")+COUNTIF(RACI!S3:S96,"A/R")</f>
         <v/>
       </c>
       <c r="C22" s="15">
-        <f>COUNTIF(RACI!S3:S104,"R")+COUNTIF(RACI!S3:S104,"A/R")</f>
+        <f>COUNTIF(RACI!S3:S96,"R")+COUNTIF(RACI!S3:S96,"A/R")</f>
         <v/>
       </c>
       <c r="D22" s="15">
-        <f>COUNTIF(RACI!S3:S104,"A/R")</f>
+        <f>COUNTIF(RACI!S3:S96,"A/R")</f>
         <v/>
       </c>
       <c r="E22" s="15" t="n">
@@ -8488,15 +8620,15 @@
         </is>
       </c>
       <c r="B23" s="15">
-        <f>COUNTIF(RACI!T3:T104,"A")+COUNTIF(RACI!T3:T104,"A/R")</f>
+        <f>COUNTIF(RACI!T3:T96,"A")+COUNTIF(RACI!T3:T96,"A/R")</f>
         <v/>
       </c>
       <c r="C23" s="15">
-        <f>COUNTIF(RACI!T3:T104,"R")+COUNTIF(RACI!T3:T104,"A/R")</f>
+        <f>COUNTIF(RACI!T3:T96,"R")+COUNTIF(RACI!T3:T96,"A/R")</f>
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>COUNTIF(RACI!T3:T104,"A/R")</f>
+        <f>COUNTIF(RACI!T3:T96,"A/R")</f>
         <v/>
       </c>
       <c r="E23" s="15" t="n">
@@ -8521,7 +8653,7 @@
         </is>
       </c>
       <c r="B24" s="21">
-        <f>COUNTA(RACI!B3:B104)</f>
+        <f>COUNTA(RACI!B3:B96)</f>
         <v/>
       </c>
     </row>
